--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>14/09/2026 a las 09:01:23</t>
+    <t>14/09/2026 a las 09:03:02</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>21/09/2026 a las 07:49:13</t>
+    <t>21/09/2026 a las 07:50:28</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1509">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/09/2026 a las 08:55:22</t>
+    <t>29/09/2026 a las 09:00:54</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -2219,15 +2219,6 @@
     <t>12210069-MCA54</t>
   </si>
   <si>
-    <t>CR 65 CL 26E - 83 CS AH6239</t>
-  </si>
-  <si>
-    <t>LA GONGORA  SIXTO</t>
-  </si>
-  <si>
-    <t>12208748-MCA54</t>
-  </si>
-  <si>
     <t>CR 65 CL 27B - 25 CS AH6245</t>
   </si>
   <si>
@@ -2469,6 +2460,21 @@
   </si>
   <si>
     <t>773750-MC084</t>
+  </si>
+  <si>
+    <t>LIBERTADOR</t>
+  </si>
+  <si>
+    <t>CL 18 # 24 - 10 ENTR 2 P AR9695</t>
+  </si>
+  <si>
+    <t>NOGUERA  MARIO</t>
+  </si>
+  <si>
+    <t>249349-MC989</t>
+  </si>
+  <si>
+    <t>Revision Suministromedidor MD PQR ANA ELENA MIRANDA tel 3007751588 - Validar estado del medidor,  realizar pruebas, tomar lectura, giro en vacio, irregularidades, anomalias, ver todo</t>
   </si>
   <si>
     <t>LOS FUNDADORES</t>
@@ -15297,7 +15303,7 @@
         <v>4</v>
       </c>
       <c r="X137" s="4" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y137" s="4"/>
       <c r="Z137" s="4" t="s">
@@ -15634,13 +15640,13 @@
         <v>330</v>
       </c>
       <c r="C142" s="4">
-        <v>167628595</v>
+        <v>167628587</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E142" s="4">
-        <v>2378916</v>
+        <v>2378922</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>35</v>
@@ -15662,10 +15668,10 @@
         <v>730</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="N142" s="4">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="O142" s="4" t="s">
         <v>734</v>
@@ -15678,10 +15684,10 @@
         <v>132</v>
       </c>
       <c r="S142" s="4">
-        <v>21707.92</v>
+        <v>106797.62</v>
       </c>
       <c r="T142" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U142" s="4" t="s">
         <v>736</v>
@@ -15693,14 +15699,14 @@
         <v>4</v>
       </c>
       <c r="X142" s="4" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="Y142" s="4"/>
       <c r="Z142" s="4" t="s">
-        <v>714</v>
+        <v>83</v>
       </c>
       <c r="AA142" s="4" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="AB142" s="4" t="s">
         <v>49</v>
@@ -15714,13 +15720,13 @@
         <v>330</v>
       </c>
       <c r="C143" s="4">
-        <v>167628587</v>
+        <v>167628583</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E143" s="4">
-        <v>2378922</v>
+        <v>2378921</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>35</v>
@@ -15745,7 +15751,7 @@
         <v>722</v>
       </c>
       <c r="N143" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O143" s="4" t="s">
         <v>737</v>
@@ -15758,16 +15764,16 @@
         <v>132</v>
       </c>
       <c r="S143" s="4">
-        <v>106797.62</v>
+        <v>39168.74</v>
       </c>
       <c r="T143" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U143" s="4" t="s">
         <v>739</v>
       </c>
       <c r="V143" s="4" t="s">
-        <v>57</v>
+        <v>325</v>
       </c>
       <c r="W143" s="4">
         <v>4</v>
@@ -15777,10 +15783,10 @@
       </c>
       <c r="Y143" s="4"/>
       <c r="Z143" s="4" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="AA143" s="4" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="AB143" s="4" t="s">
         <v>49</v>
@@ -15794,13 +15800,13 @@
         <v>330</v>
       </c>
       <c r="C144" s="4">
-        <v>167628583</v>
+        <v>167628592</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E144" s="4">
-        <v>2378921</v>
+        <v>2378926</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>35</v>
@@ -15822,32 +15828,32 @@
         <v>730</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
       <c r="N144" s="4">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="P144" s="5"/>
       <c r="Q144" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="R144" s="4" t="s">
         <v>132</v>
       </c>
       <c r="S144" s="4">
-        <v>39168.74</v>
+        <v>7106350.13</v>
       </c>
       <c r="T144" s="4">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="U144" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="V144" s="4" t="s">
-        <v>325</v>
+        <v>57</v>
       </c>
       <c r="W144" s="4">
         <v>4</v>
@@ -15857,13 +15863,13 @@
       </c>
       <c r="Y144" s="4"/>
       <c r="Z144" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="AA144" s="4" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="AB144" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:28">
@@ -15871,16 +15877,16 @@
         <v>1000</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>330</v>
+        <v>138</v>
       </c>
       <c r="C145" s="4">
-        <v>167628592</v>
+        <v>167728205</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E145" s="4">
-        <v>2378926</v>
+        <v>1058833</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>35</v>
@@ -15895,55 +15901,55 @@
         <v>37</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>716</v>
+        <v>744</v>
       </c>
       <c r="K145" s="4"/>
       <c r="L145" s="4" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>743</v>
+        <v>178</v>
       </c>
       <c r="N145" s="4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="P145" s="5"/>
       <c r="Q145" s="4" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="R145" s="4" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="S145" s="4">
-        <v>7106350.13</v>
+        <v>1060979.94</v>
       </c>
       <c r="T145" s="4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="U145" s="4" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="V145" s="4" t="s">
-        <v>57</v>
+        <v>749</v>
       </c>
       <c r="W145" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X145" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y145" s="4"/>
       <c r="Z145" s="4" t="s">
-        <v>88</v>
+        <v>750</v>
       </c>
       <c r="AA145" s="4" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="AB145" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:28">
@@ -15951,16 +15957,16 @@
         <v>1000</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="C146" s="4">
-        <v>167728205</v>
+        <v>167667329</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="E146" s="4">
-        <v>1058833</v>
+        <v>1058794</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>35</v>
@@ -15975,53 +15981,47 @@
         <v>37</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K146" s="4"/>
       <c r="L146" s="4" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="N146" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="P146" s="5"/>
       <c r="Q146" s="4" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="R146" s="4" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="S146" s="4">
-        <v>1060979.94</v>
+        <v>12123800.88</v>
       </c>
       <c r="T146" s="4">
-        <v>6</v>
-      </c>
-      <c r="U146" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="V146" s="4" t="s">
-        <v>752</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="U146" s="4"/>
+      <c r="V146" s="4"/>
       <c r="W146" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X146" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="Y146" s="4"/>
       <c r="Z146" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="AA146" s="4" t="s">
-        <v>109</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="AA146" s="4"/>
       <c r="AB146" s="4" t="s">
         <v>49</v>
       </c>
@@ -16031,16 +16031,16 @@
         <v>1000</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C147" s="4">
-        <v>167667329</v>
+        <v>167733335</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="E147" s="4">
-        <v>1058794</v>
+        <v>8078594</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>35</v>
@@ -16055,45 +16055,45 @@
         <v>37</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K147" s="4"/>
       <c r="L147" s="4" t="s">
         <v>754</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>117</v>
+        <v>755</v>
       </c>
       <c r="N147" s="4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P147" s="5"/>
       <c r="Q147" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="R147" s="4" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="S147" s="4">
-        <v>12123800.88</v>
+        <v>695686.46</v>
       </c>
       <c r="T147" s="4">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
       <c r="W147" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X147" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="Y147" s="4"/>
       <c r="Z147" s="4" t="s">
-        <v>488</v>
+        <v>758</v>
       </c>
       <c r="AA147" s="4"/>
       <c r="AB147" s="4" t="s">
@@ -16105,16 +16105,16 @@
         <v>1000</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>138</v>
+        <v>274</v>
       </c>
       <c r="C148" s="4">
-        <v>167733335</v>
+        <v>167725603</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E148" s="4">
-        <v>8078594</v>
+        <v>1120348</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>35</v>
@@ -16129,18 +16129,16 @@
         <v>37</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K148" s="4"/>
       <c r="L148" s="4" t="s">
-        <v>757</v>
+        <v>389</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="N148" s="4">
-        <v>11</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="N148" s="4"/>
       <c r="O148" s="4" t="s">
         <v>759</v>
       </c>
@@ -16149,16 +16147,20 @@
         <v>760</v>
       </c>
       <c r="R148" s="4" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="S148" s="4">
-        <v>695686.46</v>
+        <v>0</v>
       </c>
       <c r="T148" s="4">
-        <v>1</v>
-      </c>
-      <c r="U148" s="4"/>
-      <c r="V148" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U148" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="V148" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="W148" s="4">
         <v>1</v>
       </c>
@@ -16167,9 +16169,11 @@
       </c>
       <c r="Y148" s="4"/>
       <c r="Z148" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="AA148" s="4"/>
+        <v>762</v>
+      </c>
+      <c r="AA148" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="AB148" s="4" t="s">
         <v>49</v>
       </c>
@@ -16179,16 +16183,16 @@
         <v>1000</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="C149" s="4">
-        <v>167725603</v>
+        <v>167714640</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E149" s="4">
-        <v>1120348</v>
+        <v>7320359</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>35</v>
@@ -16203,25 +16207,27 @@
         <v>37</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K149" s="4"/>
       <c r="L149" s="4" t="s">
-        <v>389</v>
+        <v>763</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="N149" s="4"/>
+        <v>764</v>
+      </c>
+      <c r="N149" s="4">
+        <v>26</v>
+      </c>
       <c r="O149" s="4" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="P149" s="5"/>
       <c r="Q149" s="4" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="R149" s="4" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="S149" s="4">
         <v>0</v>
@@ -16229,12 +16235,8 @@
       <c r="T149" s="4">
         <v>0</v>
       </c>
-      <c r="U149" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="V149" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="U149" s="4"/>
+      <c r="V149" s="4"/>
       <c r="W149" s="4">
         <v>1</v>
       </c>
@@ -16243,10 +16245,10 @@
       </c>
       <c r="Y149" s="4"/>
       <c r="Z149" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AA149" s="4" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AB149" s="4" t="s">
         <v>49</v>
@@ -16257,16 +16259,16 @@
         <v>1000</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="C150" s="4">
-        <v>167714640</v>
+        <v>167664347</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="E150" s="4">
-        <v>7320359</v>
+        <v>8095269</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>35</v>
@@ -16281,17 +16283,17 @@
         <v>37</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K150" s="4"/>
       <c r="L150" s="4" t="s">
-        <v>766</v>
+        <v>513</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="N150" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O150" s="4" t="s">
         <v>768</v>
@@ -16301,31 +16303,31 @@
         <v>769</v>
       </c>
       <c r="R150" s="4" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="S150" s="4">
-        <v>0</v>
+        <v>15308954.96</v>
       </c>
       <c r="T150" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
       <c r="W150" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X150" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="Y150" s="4"/>
       <c r="Z150" s="4" t="s">
         <v>770</v>
       </c>
       <c r="AA150" s="4" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="AB150" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="151" spans="1:28">
@@ -16333,16 +16335,16 @@
         <v>1000</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>100</v>
+        <v>715</v>
       </c>
       <c r="C151" s="4">
-        <v>167664347</v>
+        <v>167628604</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="E151" s="4">
-        <v>8095269</v>
+        <v>6920308</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>35</v>
@@ -16357,48 +16359,52 @@
         <v>37</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="K151" s="4"/>
       <c r="L151" s="4" t="s">
-        <v>513</v>
+        <v>772</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="N151" s="4">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="P151" s="5"/>
       <c r="Q151" s="4" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="R151" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="S151" s="4">
-        <v>15308954.96</v>
+        <v>10154908.43</v>
       </c>
       <c r="T151" s="4">
-        <v>31</v>
-      </c>
-      <c r="U151" s="4"/>
-      <c r="V151" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="U151" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="V151" s="4" t="s">
+        <v>777</v>
+      </c>
       <c r="W151" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X151" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="Y151" s="4"/>
       <c r="Z151" s="4" t="s">
-        <v>773</v>
+        <v>88</v>
       </c>
       <c r="AA151" s="4" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="AB151" s="4" t="s">
         <v>90</v>
@@ -16412,13 +16418,13 @@
         <v>715</v>
       </c>
       <c r="C152" s="4">
-        <v>167628604</v>
+        <v>167628597</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E152" s="4">
-        <v>6920308</v>
+        <v>6920314</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>35</v>
@@ -16433,39 +16439,39 @@
         <v>37</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K152" s="4"/>
       <c r="L152" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="N152" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P152" s="5"/>
       <c r="Q152" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R152" s="4" t="s">
         <v>132</v>
       </c>
       <c r="S152" s="4">
-        <v>10154908.43</v>
+        <v>8168413.93</v>
       </c>
       <c r="T152" s="4">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="U152" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="V152" s="4" t="s">
-        <v>780</v>
+        <v>45</v>
       </c>
       <c r="W152" s="4">
         <v>4</v>
@@ -16475,10 +16481,10 @@
       </c>
       <c r="Y152" s="4"/>
       <c r="Z152" s="4" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="AA152" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="AB152" s="4" t="s">
         <v>90</v>
@@ -16492,13 +16498,13 @@
         <v>715</v>
       </c>
       <c r="C153" s="4">
-        <v>167628597</v>
+        <v>167628600</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E153" s="4">
-        <v>6920314</v>
+        <v>6923863</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>35</v>
@@ -16513,17 +16519,17 @@
         <v>37</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K153" s="4"/>
       <c r="L153" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="N153" s="4">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O153" s="4" t="s">
         <v>781</v>
@@ -16536,10 +16542,10 @@
         <v>132</v>
       </c>
       <c r="S153" s="4">
-        <v>8168413.93</v>
+        <v>9764130.380000001</v>
       </c>
       <c r="T153" s="4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="U153" s="4" t="s">
         <v>783</v>
@@ -16572,13 +16578,13 @@
         <v>715</v>
       </c>
       <c r="C154" s="4">
-        <v>167628600</v>
+        <v>167628602</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E154" s="4">
-        <v>6923863</v>
+        <v>1053010</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>35</v>
@@ -16593,18 +16599,16 @@
         <v>37</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K154" s="4"/>
       <c r="L154" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="N154" s="4">
-        <v>77</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="N154" s="4"/>
       <c r="O154" s="4" t="s">
         <v>784</v>
       </c>
@@ -16616,10 +16620,10 @@
         <v>132</v>
       </c>
       <c r="S154" s="4">
-        <v>9764130.380000001</v>
+        <v>8442079.449999999</v>
       </c>
       <c r="T154" s="4">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="U154" s="4" t="s">
         <v>786</v>
@@ -16635,10 +16639,10 @@
       </c>
       <c r="Y154" s="4"/>
       <c r="Z154" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AA154" s="4" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AB154" s="4" t="s">
         <v>90</v>
@@ -16652,13 +16656,13 @@
         <v>715</v>
       </c>
       <c r="C155" s="4">
-        <v>167628602</v>
+        <v>167628608</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E155" s="4">
-        <v>1053010</v>
+        <v>1023564</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>35</v>
@@ -16673,16 +16677,18 @@
         <v>37</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K155" s="4"/>
       <c r="L155" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M155" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="N155" s="4"/>
+      <c r="N155" s="4">
+        <v>121</v>
+      </c>
       <c r="O155" s="4" t="s">
         <v>787</v>
       </c>
@@ -16691,19 +16697,19 @@
         <v>788</v>
       </c>
       <c r="R155" s="4" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="S155" s="4">
-        <v>8442079.449999999</v>
+        <v>24145258.75</v>
       </c>
       <c r="T155" s="4">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U155" s="4" t="s">
         <v>789</v>
       </c>
       <c r="V155" s="4" t="s">
-        <v>45</v>
+        <v>317</v>
       </c>
       <c r="W155" s="4">
         <v>4</v>
@@ -16713,10 +16719,10 @@
       </c>
       <c r="Y155" s="4"/>
       <c r="Z155" s="4" t="s">
-        <v>108</v>
+        <v>435</v>
       </c>
       <c r="AA155" s="4" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="AB155" s="4" t="s">
         <v>90</v>
@@ -16730,13 +16736,13 @@
         <v>715</v>
       </c>
       <c r="C156" s="4">
-        <v>167628608</v>
+        <v>167628598</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E156" s="4">
-        <v>1023564</v>
+        <v>1026197</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>35</v>
@@ -16751,17 +16757,17 @@
         <v>37</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K156" s="4"/>
       <c r="L156" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M156" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N156" s="4">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="O156" s="4" t="s">
         <v>790</v>
@@ -16771,19 +16777,19 @@
         <v>791</v>
       </c>
       <c r="R156" s="4" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="S156" s="4">
-        <v>24145258.75</v>
+        <v>43651.74</v>
       </c>
       <c r="T156" s="4">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="U156" s="4" t="s">
         <v>792</v>
       </c>
       <c r="V156" s="4" t="s">
-        <v>317</v>
+        <v>749</v>
       </c>
       <c r="W156" s="4">
         <v>4</v>
@@ -16793,13 +16799,11 @@
       </c>
       <c r="Y156" s="4"/>
       <c r="Z156" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="AA156" s="4" t="s">
-        <v>89</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AA156" s="4"/>
       <c r="AB156" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="157" spans="1:28">
@@ -16810,13 +16814,13 @@
         <v>715</v>
       </c>
       <c r="C157" s="4">
-        <v>167628598</v>
+        <v>167628606</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E157" s="4">
-        <v>1026197</v>
+        <v>1052993</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>35</v>
@@ -16831,17 +16835,17 @@
         <v>37</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K157" s="4"/>
       <c r="L157" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N157" s="4">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="O157" s="4" t="s">
         <v>793</v>
@@ -16854,16 +16858,16 @@
         <v>132</v>
       </c>
       <c r="S157" s="4">
-        <v>43651.74</v>
+        <v>4652824.24</v>
       </c>
       <c r="T157" s="4">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="U157" s="4" t="s">
         <v>795</v>
       </c>
       <c r="V157" s="4" t="s">
-        <v>752</v>
+        <v>317</v>
       </c>
       <c r="W157" s="4">
         <v>4</v>
@@ -16873,11 +16877,11 @@
       </c>
       <c r="Y157" s="4"/>
       <c r="Z157" s="4" t="s">
-        <v>387</v>
+        <v>217</v>
       </c>
       <c r="AA157" s="4"/>
       <c r="AB157" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="158" spans="1:28">
@@ -16888,13 +16892,13 @@
         <v>715</v>
       </c>
       <c r="C158" s="4">
-        <v>167628606</v>
+        <v>167628596</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E158" s="4">
-        <v>1052993</v>
+        <v>1052992</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>35</v>
@@ -16909,17 +16913,17 @@
         <v>37</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K158" s="4"/>
       <c r="L158" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M158" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N158" s="4">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O158" s="4" t="s">
         <v>796</v>
@@ -16932,10 +16936,10 @@
         <v>132</v>
       </c>
       <c r="S158" s="4">
-        <v>4652824.24</v>
+        <v>169190</v>
       </c>
       <c r="T158" s="4">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="U158" s="4" t="s">
         <v>798</v>
@@ -16951,9 +16955,11 @@
       </c>
       <c r="Y158" s="4"/>
       <c r="Z158" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA158" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="AA158" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="AB158" s="4" t="s">
         <v>90</v>
       </c>
@@ -16963,16 +16969,16 @@
         <v>1000</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>715</v>
+        <v>370</v>
       </c>
       <c r="C159" s="4">
-        <v>167628596</v>
+        <v>167628607</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E159" s="4">
-        <v>1052992</v>
+        <v>1052979</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>35</v>
@@ -16987,17 +16993,17 @@
         <v>37</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K159" s="4"/>
       <c r="L159" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M159" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N159" s="4">
-        <v>206</v>
+        <v>55</v>
       </c>
       <c r="O159" s="4" t="s">
         <v>799</v>
@@ -17010,16 +17016,16 @@
         <v>132</v>
       </c>
       <c r="S159" s="4">
-        <v>169190</v>
+        <v>27126185.04</v>
       </c>
       <c r="T159" s="4">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="U159" s="4" t="s">
         <v>801</v>
       </c>
       <c r="V159" s="4" t="s">
-        <v>317</v>
+        <v>802</v>
       </c>
       <c r="W159" s="4">
         <v>4</v>
@@ -17029,10 +17035,10 @@
       </c>
       <c r="Y159" s="4"/>
       <c r="Z159" s="4" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="AA159" s="4" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="AB159" s="4" t="s">
         <v>90</v>
@@ -17046,13 +17052,13 @@
         <v>370</v>
       </c>
       <c r="C160" s="4">
-        <v>167628607</v>
+        <v>167628603</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E160" s="4">
-        <v>1052979</v>
+        <v>1053005</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>35</v>
@@ -17067,39 +17073,39 @@
         <v>37</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K160" s="4"/>
       <c r="L160" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M160" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N160" s="4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P160" s="5"/>
       <c r="Q160" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="R160" s="4" t="s">
         <v>132</v>
       </c>
       <c r="S160" s="4">
-        <v>27126185.04</v>
+        <v>11141070.19</v>
       </c>
       <c r="T160" s="4">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="U160" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="V160" s="4" t="s">
-        <v>805</v>
+        <v>57</v>
       </c>
       <c r="W160" s="4">
         <v>4</v>
@@ -17126,13 +17132,13 @@
         <v>370</v>
       </c>
       <c r="C161" s="4">
-        <v>167628603</v>
+        <v>167628605</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E161" s="4">
-        <v>1053005</v>
+        <v>6920320</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>35</v>
@@ -17147,17 +17153,17 @@
         <v>37</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K161" s="4"/>
       <c r="L161" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M161" s="4" t="s">
         <v>695</v>
       </c>
       <c r="N161" s="4">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="O161" s="4" t="s">
         <v>806</v>
@@ -17170,16 +17176,16 @@
         <v>132</v>
       </c>
       <c r="S161" s="4">
-        <v>11141070.19</v>
+        <v>14025232.71</v>
       </c>
       <c r="T161" s="4">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U161" s="4" t="s">
         <v>808</v>
       </c>
       <c r="V161" s="4" t="s">
-        <v>57</v>
+        <v>777</v>
       </c>
       <c r="W161" s="4">
         <v>4</v>
@@ -17206,13 +17212,13 @@
         <v>370</v>
       </c>
       <c r="C162" s="4">
-        <v>167628605</v>
+        <v>167628601</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E162" s="4">
-        <v>6920320</v>
+        <v>6776468</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>35</v>
@@ -17227,18 +17233,16 @@
         <v>37</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K162" s="4"/>
       <c r="L162" s="4" t="s">
-        <v>775</v>
+        <v>52</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="N162" s="4">
-        <v>95</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N162" s="4"/>
       <c r="O162" s="4" t="s">
         <v>809</v>
       </c>
@@ -17250,16 +17254,16 @@
         <v>132</v>
       </c>
       <c r="S162" s="4">
-        <v>14025232.71</v>
+        <v>9710573.67</v>
       </c>
       <c r="T162" s="4">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U162" s="4" t="s">
         <v>811</v>
       </c>
       <c r="V162" s="4" t="s">
-        <v>780</v>
+        <v>45</v>
       </c>
       <c r="W162" s="4">
         <v>4</v>
@@ -17269,10 +17273,10 @@
       </c>
       <c r="Y162" s="4"/>
       <c r="Z162" s="4" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="AA162" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="AB162" s="4" t="s">
         <v>90</v>
@@ -17286,13 +17290,13 @@
         <v>370</v>
       </c>
       <c r="C163" s="4">
-        <v>167628601</v>
+        <v>167628609</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E163" s="4">
-        <v>6776468</v>
+        <v>1052974</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>35</v>
@@ -17307,7 +17311,7 @@
         <v>37</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K163" s="4"/>
       <c r="L163" s="4" t="s">
@@ -17316,7 +17320,9 @@
       <c r="M163" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="N163" s="4"/>
+      <c r="N163" s="4">
+        <v>3</v>
+      </c>
       <c r="O163" s="4" t="s">
         <v>812</v>
       </c>
@@ -17328,16 +17334,16 @@
         <v>132</v>
       </c>
       <c r="S163" s="4">
-        <v>9710573.67</v>
+        <v>1261992.29</v>
       </c>
       <c r="T163" s="4">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="U163" s="4" t="s">
         <v>814</v>
       </c>
       <c r="V163" s="4" t="s">
-        <v>45</v>
+        <v>749</v>
       </c>
       <c r="W163" s="4">
         <v>4</v>
@@ -17347,13 +17353,13 @@
       </c>
       <c r="Y163" s="4"/>
       <c r="Z163" s="4" t="s">
-        <v>114</v>
+        <v>714</v>
       </c>
       <c r="AA163" s="4" t="s">
         <v>68</v>
       </c>
       <c r="AB163" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="164" spans="1:28">
@@ -17361,16 +17367,16 @@
         <v>1000</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="C164" s="4">
-        <v>167628609</v>
+        <v>167775006</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E164" s="4">
-        <v>1052974</v>
+        <v>1265051</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>35</v>
@@ -17385,53 +17391,49 @@
         <v>37</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>774</v>
+        <v>815</v>
       </c>
       <c r="K164" s="4"/>
       <c r="L164" s="4" t="s">
-        <v>52</v>
+        <v>492</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="N164" s="4">
-        <v>3</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="N164" s="4"/>
       <c r="O164" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P164" s="5"/>
       <c r="Q164" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="R164" s="4" t="s">
-        <v>132</v>
+        <v>527</v>
       </c>
       <c r="S164" s="4">
-        <v>1261992.29</v>
+        <v>0</v>
       </c>
       <c r="T164" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U164" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="V164" s="4" t="s">
-        <v>752</v>
+        <v>359</v>
       </c>
       <c r="W164" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X164" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="Y164" s="4"/>
       <c r="Z164" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="AA164" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="AA164" s="4"/>
       <c r="AB164" s="4" t="s">
         <v>49</v>
       </c>
@@ -17465,11 +17467,11 @@
         <v>37</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K165" s="4"/>
       <c r="L165" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>230</v>
@@ -17478,11 +17480,11 @@
         <v>17</v>
       </c>
       <c r="O165" s="4" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P165" s="5"/>
       <c r="Q165" s="4" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="R165" s="4" t="s">
         <v>132</v>
@@ -17494,7 +17496,7 @@
         <v>0</v>
       </c>
       <c r="U165" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="V165" s="4" t="s">
         <v>57</v>
@@ -17507,7 +17509,7 @@
       </c>
       <c r="Y165" s="4"/>
       <c r="Z165" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AA165" s="4"/>
       <c r="AB165" s="4" t="s">
@@ -17519,7 +17521,7 @@
         <v>1000</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C166" s="4">
         <v>167719730</v>
@@ -17543,22 +17545,22 @@
         <v>37</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="K166" s="4"/>
       <c r="L166" s="4" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M166" s="4"/>
       <c r="N166" s="4">
         <v>52</v>
       </c>
       <c r="O166" s="4" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="P166" s="5"/>
       <c r="Q166" s="4" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="R166" s="4" t="s">
         <v>55</v>
@@ -17579,7 +17581,7 @@
       </c>
       <c r="Y166" s="4"/>
       <c r="Z166" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="AA166" s="4" t="s">
         <v>109</v>
@@ -17593,7 +17595,7 @@
         <v>1000</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C167" s="4">
         <v>167719731</v>
@@ -17617,22 +17619,22 @@
         <v>37</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="K167" s="4"/>
       <c r="L167" s="4" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M167" s="4"/>
       <c r="N167" s="4">
         <v>52</v>
       </c>
       <c r="O167" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P167" s="5"/>
       <c r="Q167" s="4" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="R167" s="4" t="s">
         <v>55</v>
@@ -17653,7 +17655,7 @@
       </c>
       <c r="Y167" s="4"/>
       <c r="Z167" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AA167" s="4" t="s">
         <v>68</v>
@@ -17691,24 +17693,24 @@
         <v>37</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="K168" s="4"/>
       <c r="L168" s="4" t="s">
         <v>666</v>
       </c>
       <c r="M168" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="N168" s="4">
         <v>129</v>
       </c>
       <c r="O168" s="4" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="P168" s="5"/>
       <c r="Q168" s="4" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="R168" s="4" t="s">
         <v>132</v>
@@ -17729,7 +17731,7 @@
       </c>
       <c r="Y168" s="4"/>
       <c r="Z168" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AA168" s="4"/>
       <c r="AB168" s="4" t="s">
@@ -17765,24 +17767,24 @@
         <v>37</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K169" s="4"/>
       <c r="L169" s="4" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="M169" s="4" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="N169" s="4">
         <v>22</v>
       </c>
       <c r="O169" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="P169" s="5"/>
       <c r="Q169" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="R169" s="4" t="s">
         <v>75</v>
@@ -17794,7 +17796,7 @@
         <v>0</v>
       </c>
       <c r="U169" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="V169" s="4" t="s">
         <v>65</v>
@@ -17807,7 +17809,7 @@
       </c>
       <c r="Y169" s="4"/>
       <c r="Z169" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AA169" s="4"/>
       <c r="AB169" s="4" t="s">
@@ -17843,24 +17845,24 @@
         <v>37</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K170" s="4"/>
       <c r="L170" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N170" s="4">
         <v>58</v>
       </c>
       <c r="O170" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="P170" s="5"/>
       <c r="Q170" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="R170" s="4" t="s">
         <v>43</v>
@@ -17872,7 +17874,7 @@
         <v>74</v>
       </c>
       <c r="U170" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="V170" s="4" t="s">
         <v>45</v>
@@ -17923,11 +17925,11 @@
         <v>37</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K171" s="4"/>
       <c r="L171" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>178</v>
@@ -17936,11 +17938,11 @@
         <v>55</v>
       </c>
       <c r="O171" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="P171" s="5"/>
       <c r="Q171" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="R171" s="4" t="s">
         <v>43</v>
@@ -17999,11 +18001,11 @@
         <v>37</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K172" s="4"/>
       <c r="L172" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="M172" s="4" t="s">
         <v>178</v>
@@ -18012,11 +18014,11 @@
         <v>68</v>
       </c>
       <c r="O172" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="P172" s="5"/>
       <c r="Q172" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="R172" s="4" t="s">
         <v>43</v>
@@ -18028,7 +18030,7 @@
         <v>74</v>
       </c>
       <c r="U172" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="V172" s="4" t="s">
         <v>243</v>
@@ -18079,24 +18081,24 @@
         <v>37</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K173" s="4"/>
       <c r="L173" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M173" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N173" s="4">
         <v>51</v>
       </c>
       <c r="O173" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="R173" s="4" t="s">
         <v>43</v>
@@ -18108,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="U173" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="V173" s="4" t="s">
         <v>194</v>
@@ -18159,22 +18161,22 @@
         <v>37</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K174" s="4"/>
       <c r="L174" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M174" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N174" s="4"/>
       <c r="O174" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="P174" s="5"/>
       <c r="Q174" s="4" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="R174" s="4" t="s">
         <v>144</v>
@@ -18186,7 +18188,7 @@
         <v>0</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="V174" s="4" t="s">
         <v>65</v>
@@ -18199,7 +18201,7 @@
       </c>
       <c r="Y174" s="4"/>
       <c r="Z174" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="AA174" s="4" t="s">
         <v>68</v>
@@ -18237,11 +18239,11 @@
         <v>37</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K175" s="4"/>
       <c r="L175" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>141</v>
@@ -18250,11 +18252,11 @@
         <v>52</v>
       </c>
       <c r="O175" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="P175" s="5"/>
       <c r="Q175" s="4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="R175" s="4" t="s">
         <v>43</v>
@@ -18266,7 +18268,7 @@
         <v>64</v>
       </c>
       <c r="U175" s="4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="V175" s="4" t="s">
         <v>243</v>
@@ -18317,22 +18319,22 @@
         <v>37</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K176" s="4"/>
       <c r="L176" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M176" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N176" s="4"/>
       <c r="O176" s="4" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="P176" s="5"/>
       <c r="Q176" s="4" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="R176" s="4" t="s">
         <v>43</v>
@@ -18344,7 +18346,7 @@
         <v>0</v>
       </c>
       <c r="U176" s="4" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="V176" s="4" t="s">
         <v>65</v>
@@ -18395,22 +18397,22 @@
         <v>37</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K177" s="4"/>
       <c r="L177" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M177" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N177" s="4"/>
       <c r="O177" s="4" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="P177" s="5"/>
       <c r="Q177" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="R177" s="4" t="s">
         <v>43</v>
@@ -18469,22 +18471,22 @@
         <v>37</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K178" s="4"/>
       <c r="L178" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M178" s="4" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N178" s="4"/>
       <c r="O178" s="4" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="P178" s="5"/>
       <c r="Q178" s="4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="R178" s="4" t="s">
         <v>43</v>
@@ -18541,7 +18543,7 @@
         <v>37</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K179" s="4"/>
       <c r="L179" s="4" t="s">
@@ -18554,11 +18556,11 @@
         <v>30</v>
       </c>
       <c r="O179" s="4" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="P179" s="5"/>
       <c r="Q179" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="R179" s="4" t="s">
         <v>43</v>
@@ -18570,7 +18572,7 @@
         <v>0</v>
       </c>
       <c r="U179" s="4" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="V179" s="4" t="s">
         <v>98</v>
@@ -18621,18 +18623,18 @@
         <v>37</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="K180" s="4"/>
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
       <c r="O180" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="P180" s="5"/>
       <c r="Q180" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="R180" s="4" t="s">
         <v>43</v>
@@ -18653,7 +18655,7 @@
       </c>
       <c r="Y180" s="4"/>
       <c r="Z180" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AA180" s="4"/>
       <c r="AB180" s="4" t="s">
@@ -18689,24 +18691,24 @@
         <v>37</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="K181" s="4"/>
       <c r="L181" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="N181" s="4">
         <v>28</v>
       </c>
       <c r="O181" s="4" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="P181" s="5"/>
       <c r="Q181" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="R181" s="4" t="s">
         <v>43</v>
@@ -18727,7 +18729,7 @@
       </c>
       <c r="Y181" s="4"/>
       <c r="Z181" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AA181" s="4" t="s">
         <v>48</v>
@@ -18765,22 +18767,22 @@
         <v>37</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="K182" s="4"/>
       <c r="L182" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="M182" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="N182" s="4"/>
       <c r="O182" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="P182" s="5"/>
       <c r="Q182" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="R182" s="4" t="s">
         <v>43</v>
@@ -18792,7 +18794,7 @@
         <v>0</v>
       </c>
       <c r="U182" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="V182" s="4" t="s">
         <v>65</v>
@@ -18805,7 +18807,7 @@
       </c>
       <c r="Y182" s="4"/>
       <c r="Z182" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AA182" s="4" t="s">
         <v>48</v>
@@ -18843,22 +18845,22 @@
         <v>37</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="K183" s="4"/>
       <c r="L183" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="N183" s="4"/>
       <c r="O183" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="P183" s="5"/>
       <c r="Q183" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="R183" s="4" t="s">
         <v>43</v>
@@ -18870,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="U183" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="V183" s="4" t="s">
         <v>636</v>
@@ -18883,7 +18885,7 @@
       </c>
       <c r="Y183" s="4"/>
       <c r="Z183" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="AA183" s="4" t="s">
         <v>68</v>
@@ -18921,24 +18923,24 @@
         <v>37</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="K184" s="4"/>
       <c r="L184" s="4" t="s">
         <v>504</v>
       </c>
       <c r="M184" s="4" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="N184" s="4">
         <v>360</v>
       </c>
       <c r="O184" s="4" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="P184" s="5"/>
       <c r="Q184" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="R184" s="4" t="s">
         <v>75</v>
@@ -18950,10 +18952,10 @@
         <v>75</v>
       </c>
       <c r="U184" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="V184" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="W184" s="4">
         <v>1</v>
@@ -18983,7 +18985,7 @@
         <v>166555136</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E185" s="4">
         <v>8379062</v>
@@ -19001,18 +19003,18 @@
         <v>37</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
       <c r="N185" s="4"/>
       <c r="O185" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="P185" s="5"/>
       <c r="Q185" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="R185" s="4" t="s">
         <v>132</v>
@@ -19033,7 +19035,7 @@
       </c>
       <c r="Y185" s="4"/>
       <c r="Z185" s="4" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="AA185" s="4"/>
       <c r="AB185" s="4" t="s">
@@ -19069,18 +19071,18 @@
         <v>37</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="K186" s="4"/>
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
       <c r="N186" s="4"/>
       <c r="O186" s="4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="P186" s="5"/>
       <c r="Q186" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="R186" s="4" t="s">
         <v>75</v>
@@ -19101,7 +19103,7 @@
       </c>
       <c r="Y186" s="4"/>
       <c r="Z186" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AA186" s="4"/>
       <c r="AB186" s="4" t="s">
@@ -19137,22 +19139,22 @@
         <v>37</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="K187" s="4"/>
       <c r="L187" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="N187" s="4"/>
       <c r="O187" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="P187" s="5"/>
       <c r="Q187" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="R187" s="4" t="s">
         <v>43</v>
@@ -19164,7 +19166,7 @@
         <v>72</v>
       </c>
       <c r="U187" s="4" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="V187" s="4" t="s">
         <v>317</v>
@@ -19215,11 +19217,11 @@
         <v>37</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="K188" s="4"/>
       <c r="L188" s="4" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>101</v>
@@ -19228,11 +19230,11 @@
         <v>29</v>
       </c>
       <c r="O188" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="P188" s="5"/>
       <c r="Q188" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="R188" s="4" t="s">
         <v>43</v>
@@ -19244,7 +19246,7 @@
         <v>0</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="V188" s="4" t="s">
         <v>359</v>
@@ -19257,7 +19259,7 @@
       </c>
       <c r="Y188" s="4"/>
       <c r="Z188" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AA188" s="4" t="s">
         <v>68</v>
@@ -19295,24 +19297,24 @@
         <v>37</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
         <v>284</v>
       </c>
       <c r="M189" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N189" s="4">
         <v>19</v>
       </c>
       <c r="O189" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="P189" s="5"/>
       <c r="Q189" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="R189" s="4" t="s">
         <v>43</v>
@@ -19324,10 +19326,10 @@
         <v>0</v>
       </c>
       <c r="U189" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="V189" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="W189" s="4">
         <v>1</v>
@@ -19337,7 +19339,7 @@
       </c>
       <c r="Y189" s="4"/>
       <c r="Z189" s="4" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="AA189" s="4" t="s">
         <v>68</v>
@@ -19372,27 +19374,27 @@
         <v>37</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="M190" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="N190" s="4">
         <v>295</v>
       </c>
       <c r="O190" s="4" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="P190" s="5"/>
       <c r="Q190" s="4" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="R190" s="4" t="s">
         <v>43</v>
@@ -19449,11 +19451,11 @@
         <v>37</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="K191" s="4"/>
       <c r="L191" s="4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>39</v>
@@ -19462,11 +19464,11 @@
         <v>58</v>
       </c>
       <c r="O191" s="4" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="P191" s="5"/>
       <c r="Q191" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="R191" s="4" t="s">
         <v>75</v>
@@ -19478,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="U191" s="4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="V191" s="4" t="s">
         <v>57</v>
@@ -19491,7 +19493,7 @@
       </c>
       <c r="Y191" s="4"/>
       <c r="Z191" s="4" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="AA191" s="4"/>
       <c r="AB191" s="4" t="s">
@@ -19527,24 +19529,24 @@
         <v>37</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="K192" s="4"/>
       <c r="L192" s="4" t="s">
         <v>559</v>
       </c>
       <c r="M192" s="4" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="N192" s="4">
         <v>67</v>
       </c>
       <c r="O192" s="4" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="P192" s="5"/>
       <c r="Q192" s="4" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="R192" s="4" t="s">
         <v>75</v>
@@ -19556,7 +19558,7 @@
         <v>74</v>
       </c>
       <c r="U192" s="4" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="V192" s="4" t="s">
         <v>243</v>
@@ -19607,7 +19609,7 @@
         <v>37</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="K193" s="4"/>
       <c r="L193" s="4" t="s">
@@ -19620,11 +19622,11 @@
         <v>35</v>
       </c>
       <c r="O193" s="4" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="P193" s="5"/>
       <c r="Q193" s="4" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="R193" s="4" t="s">
         <v>43</v>
@@ -19636,7 +19638,7 @@
         <v>1</v>
       </c>
       <c r="U193" s="4" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="V193" s="4" t="s">
         <v>106</v>
@@ -19645,7 +19647,7 @@
         <v>7</v>
       </c>
       <c r="X193" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="Y193" s="4"/>
       <c r="Z193" s="4" t="s">
@@ -19687,7 +19689,7 @@
         <v>37</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="K194" s="4"/>
       <c r="L194" s="4" t="s">
@@ -19700,11 +19702,11 @@
         <v>53</v>
       </c>
       <c r="O194" s="4" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="P194" s="5"/>
       <c r="Q194" s="4" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="R194" s="4" t="s">
         <v>43</v>
@@ -19716,7 +19718,7 @@
         <v>0</v>
       </c>
       <c r="U194" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="V194" s="4" t="s">
         <v>65</v>
@@ -19767,18 +19769,18 @@
         <v>37</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="K195" s="4"/>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
       <c r="N195" s="4"/>
       <c r="O195" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="P195" s="5"/>
       <c r="Q195" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="R195" s="4" t="s">
         <v>55</v>
@@ -19799,7 +19801,7 @@
       </c>
       <c r="Y195" s="4"/>
       <c r="Z195" s="4" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4" t="s">
@@ -19835,24 +19837,24 @@
         <v>37</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="K196" s="4"/>
       <c r="L196" s="4" t="s">
         <v>451</v>
       </c>
       <c r="M196" s="4" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="N196" s="4">
         <v>100</v>
       </c>
       <c r="O196" s="4" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="P196" s="5"/>
       <c r="Q196" s="4" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="R196" s="4" t="s">
         <v>144</v>
@@ -19864,7 +19866,7 @@
         <v>51</v>
       </c>
       <c r="U196" s="4" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="V196" s="4" t="s">
         <v>98</v>
@@ -19877,7 +19879,7 @@
       </c>
       <c r="Y196" s="4"/>
       <c r="Z196" s="4" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="AA196" s="4" t="s">
         <v>165</v>
@@ -19915,7 +19917,7 @@
         <v>37</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
@@ -19926,11 +19928,11 @@
       </c>
       <c r="N197" s="4"/>
       <c r="O197" s="4" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="P197" s="5"/>
       <c r="Q197" s="4" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="R197" s="4" t="s">
         <v>43</v>
@@ -19942,7 +19944,7 @@
         <v>0</v>
       </c>
       <c r="U197" s="4" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="V197" s="4" t="s">
         <v>243</v>
@@ -19955,7 +19957,7 @@
       </c>
       <c r="Y197" s="4"/>
       <c r="Z197" s="4" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="AA197" s="4"/>
       <c r="AB197" s="4" t="s">
@@ -19991,7 +19993,7 @@
         <v>37</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
@@ -20002,11 +20004,11 @@
       </c>
       <c r="N198" s="4"/>
       <c r="O198" s="4" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="P198" s="5"/>
       <c r="Q198" s="4" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="R198" s="4" t="s">
         <v>43</v>
@@ -20018,10 +20020,10 @@
         <v>0</v>
       </c>
       <c r="U198" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="V198" s="4" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="W198" s="4">
         <v>3</v>
@@ -20031,7 +20033,7 @@
       </c>
       <c r="Y198" s="4"/>
       <c r="Z198" s="4" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="AA198" s="4"/>
       <c r="AB198" s="4" t="s">
@@ -20067,7 +20069,7 @@
         <v>37</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="4" t="s">
@@ -20078,11 +20080,11 @@
       </c>
       <c r="N199" s="4"/>
       <c r="O199" s="4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="P199" s="5"/>
       <c r="Q199" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="R199" s="4" t="s">
         <v>43</v>
@@ -20094,7 +20096,7 @@
         <v>3</v>
       </c>
       <c r="U199" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="V199" s="4" t="s">
         <v>57</v>
@@ -20107,7 +20109,7 @@
       </c>
       <c r="Y199" s="4"/>
       <c r="Z199" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="AA199" s="4" t="s">
         <v>68</v>
@@ -20127,7 +20129,7 @@
         <v>167743790</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E200" s="4">
         <v>7508124</v>
@@ -20145,7 +20147,7 @@
         <v>37</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="4" t="s">
@@ -20156,11 +20158,11 @@
       </c>
       <c r="N200" s="4"/>
       <c r="O200" s="4" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="P200" s="5"/>
       <c r="Q200" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="R200" s="4" t="s">
         <v>144</v>
@@ -20181,7 +20183,7 @@
       </c>
       <c r="Y200" s="4"/>
       <c r="Z200" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="AA200" s="4" t="s">
         <v>68</v>
@@ -20219,22 +20221,22 @@
         <v>37</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K201" s="4"/>
       <c r="L201" s="4" t="s">
         <v>246</v>
       </c>
       <c r="M201" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N201" s="4"/>
       <c r="O201" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="P201" s="5"/>
       <c r="Q201" s="4" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="R201" s="4" t="s">
         <v>43</v>
@@ -20255,7 +20257,7 @@
       </c>
       <c r="Y201" s="4"/>
       <c r="Z201" s="4" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="AA201" s="4"/>
       <c r="AB201" s="4" t="s">
@@ -20291,7 +20293,7 @@
         <v>37</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K202" s="4"/>
       <c r="L202" s="4" t="s">
@@ -20302,11 +20304,11 @@
       </c>
       <c r="N202" s="4"/>
       <c r="O202" s="4" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="P202" s="5"/>
       <c r="Q202" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="R202" s="4" t="s">
         <v>43</v>
@@ -20327,7 +20329,7 @@
       </c>
       <c r="Y202" s="4"/>
       <c r="Z202" s="4" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="AA202" s="4" t="s">
         <v>165</v>
@@ -20365,7 +20367,7 @@
         <v>37</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K203" s="4"/>
       <c r="L203" s="4" t="s">
@@ -20376,11 +20378,11 @@
       </c>
       <c r="N203" s="4"/>
       <c r="O203" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="P203" s="5"/>
       <c r="Q203" s="4" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="R203" s="4" t="s">
         <v>43</v>
@@ -20401,7 +20403,7 @@
       </c>
       <c r="Y203" s="4"/>
       <c r="Z203" s="4" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="AA203" s="4" t="s">
         <v>68</v>
@@ -20439,22 +20441,22 @@
         <v>37</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="K204" s="4"/>
       <c r="L204" s="4" t="s">
         <v>464</v>
       </c>
       <c r="M204" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="N204" s="4"/>
       <c r="O204" s="4" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="P204" s="5"/>
       <c r="Q204" s="4" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="R204" s="4" t="s">
         <v>144</v>
@@ -20466,7 +20468,7 @@
         <v>3</v>
       </c>
       <c r="U204" s="4" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="V204" s="4" t="s">
         <v>171</v>
@@ -20479,7 +20481,7 @@
       </c>
       <c r="Y204" s="4"/>
       <c r="Z204" s="4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="AA204" s="4" t="s">
         <v>165</v>
@@ -20517,22 +20519,22 @@
         <v>37</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="K205" s="4"/>
       <c r="L205" s="4" t="s">
         <v>464</v>
       </c>
       <c r="M205" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="N205" s="4"/>
       <c r="O205" s="4" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="P205" s="5"/>
       <c r="Q205" s="4" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="R205" s="4" t="s">
         <v>144</v>
@@ -20544,7 +20546,7 @@
         <v>0</v>
       </c>
       <c r="U205" s="4" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="V205" s="4" t="s">
         <v>171</v>
@@ -20557,7 +20559,7 @@
       </c>
       <c r="Y205" s="4"/>
       <c r="Z205" s="4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="AA205" s="4" t="s">
         <v>68</v>
@@ -20595,18 +20597,18 @@
         <v>37</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K206" s="4"/>
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
       <c r="N206" s="4"/>
       <c r="O206" s="4" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="P206" s="5"/>
       <c r="Q206" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="R206" s="4" t="s">
         <v>75</v>
@@ -20627,7 +20629,7 @@
       </c>
       <c r="Y206" s="4"/>
       <c r="Z206" s="4" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="AA206" s="4" t="s">
         <v>109</v>
@@ -20665,24 +20667,24 @@
         <v>37</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="4" t="s">
         <v>504</v>
       </c>
       <c r="M207" s="4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="N207" s="4">
         <v>86</v>
       </c>
       <c r="O207" s="4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="P207" s="5"/>
       <c r="Q207" s="4" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="R207" s="4" t="s">
         <v>55</v>
@@ -20694,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="U207" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="V207" s="4" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="W207" s="4">
         <v>1</v>
@@ -20707,7 +20709,7 @@
       </c>
       <c r="Y207" s="4"/>
       <c r="Z207" s="4" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="AA207" s="4" t="s">
         <v>68</v>
@@ -20745,7 +20747,7 @@
         <v>37</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="4" t="s">
@@ -20758,11 +20760,11 @@
         <v>37</v>
       </c>
       <c r="O208" s="4" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="P208" s="5"/>
       <c r="Q208" s="4" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="R208" s="4" t="s">
         <v>43</v>
@@ -20774,7 +20776,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="4" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="V208" s="4" t="s">
         <v>317</v>
@@ -20787,7 +20789,7 @@
       </c>
       <c r="Y208" s="4"/>
       <c r="Z208" s="4" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="AA208" s="4" t="s">
         <v>109</v>
@@ -20825,7 +20827,7 @@
         <v>37</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="4" t="s">
@@ -20838,11 +20840,11 @@
         <v>9</v>
       </c>
       <c r="O209" s="4" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="P209" s="5"/>
       <c r="Q209" s="4" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>43</v>
@@ -20854,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="U209" s="4" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="V209" s="4" t="s">
         <v>57</v>
@@ -20867,7 +20869,7 @@
       </c>
       <c r="Y209" s="4"/>
       <c r="Z209" s="4" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="AA209" s="4" t="s">
         <v>68</v>
@@ -20887,7 +20889,7 @@
         <v>167624909</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E210" s="4">
         <v>1002352</v>
@@ -20902,27 +20904,27 @@
         <v>37</v>
       </c>
       <c r="I210" s="4" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="M210" s="4" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="N210" s="4">
         <v>374</v>
       </c>
       <c r="O210" s="4" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="P210" s="5"/>
       <c r="Q210" s="4" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="R210" s="4" t="s">
         <v>75</v>
@@ -20934,10 +20936,10 @@
         <v>1</v>
       </c>
       <c r="U210" s="4" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="V210" s="4" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="W210" s="4">
         <v>4</v>
@@ -20947,7 +20949,7 @@
       </c>
       <c r="Y210" s="4"/>
       <c r="Z210" s="4" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="AA210" s="4" t="s">
         <v>68</v>
@@ -20985,18 +20987,18 @@
         <v>37</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="K211" s="4"/>
       <c r="L211" s="4"/>
       <c r="M211" s="4"/>
       <c r="N211" s="4"/>
       <c r="O211" s="4" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="P211" s="5"/>
       <c r="Q211" s="4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="R211" s="4" t="s">
         <v>144</v>
@@ -21017,7 +21019,7 @@
       </c>
       <c r="Y211" s="4"/>
       <c r="Z211" s="4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="AA211" s="4"/>
       <c r="AB211" s="4" t="s">
@@ -21053,24 +21055,24 @@
         <v>37</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="K212" s="4"/>
       <c r="L212" s="4" t="s">
         <v>503</v>
       </c>
       <c r="M212" s="4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="N212" s="4">
         <v>139</v>
       </c>
       <c r="O212" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="P212" s="5"/>
       <c r="Q212" s="4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="R212" s="4" t="s">
         <v>43</v>
@@ -21082,7 +21084,7 @@
         <v>0</v>
       </c>
       <c r="U212" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="V212" s="4" t="s">
         <v>317</v>
@@ -21133,7 +21135,7 @@
         <v>37</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="K213" s="4"/>
       <c r="L213" s="4" t="s">
@@ -21146,11 +21148,11 @@
         <v>33</v>
       </c>
       <c r="O213" s="4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="P213" s="5"/>
       <c r="Q213" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="R213" s="4" t="s">
         <v>132</v>
@@ -21207,22 +21209,22 @@
         <v>37</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="K214" s="4"/>
       <c r="L214" s="4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="M214" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="N214" s="4"/>
       <c r="O214" s="4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="P214" s="5"/>
       <c r="Q214" s="4" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="R214" s="4" t="s">
         <v>55</v>
@@ -21243,7 +21245,7 @@
       </c>
       <c r="Y214" s="4"/>
       <c r="Z214" s="4" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="AA214" s="4" t="s">
         <v>109</v>
@@ -21281,22 +21283,22 @@
         <v>37</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="K215" s="4"/>
       <c r="L215" s="4" t="s">
         <v>284</v>
       </c>
       <c r="M215" s="4" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="N215" s="4"/>
       <c r="O215" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="P215" s="5"/>
       <c r="Q215" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="R215" s="4" t="s">
         <v>75</v>
@@ -21317,7 +21319,7 @@
       </c>
       <c r="Y215" s="4"/>
       <c r="Z215" s="4" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="AA215" s="4"/>
       <c r="AB215" s="4" t="s">
@@ -21353,22 +21355,22 @@
         <v>37</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="K216" s="4"/>
       <c r="L216" s="4" t="s">
         <v>284</v>
       </c>
       <c r="M216" s="4" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="N216" s="4"/>
       <c r="O216" s="4" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="P216" s="5"/>
       <c r="Q216" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>75</v>
@@ -21389,7 +21391,7 @@
       </c>
       <c r="Y216" s="4"/>
       <c r="Z216" s="4" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="AA216" s="4"/>
       <c r="AB216" s="4" t="s">
@@ -21425,22 +21427,22 @@
         <v>37</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="4" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>102</v>
       </c>
       <c r="N217" s="4"/>
       <c r="O217" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="P217" s="5"/>
       <c r="Q217" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="R217" s="4" t="s">
         <v>75</v>
@@ -21461,7 +21463,7 @@
       </c>
       <c r="Y217" s="4"/>
       <c r="Z217" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="AA217" s="4" t="s">
         <v>68</v>
@@ -21499,11 +21501,11 @@
         <v>37</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>549</v>
@@ -21512,11 +21514,11 @@
         <v>40</v>
       </c>
       <c r="O218" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="P218" s="5"/>
       <c r="Q218" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="R218" s="4" t="s">
         <v>75</v>
@@ -21528,7 +21530,7 @@
         <v>0</v>
       </c>
       <c r="U218" s="4" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="V218" s="4" t="s">
         <v>216</v>
@@ -21541,7 +21543,7 @@
       </c>
       <c r="Y218" s="4"/>
       <c r="Z218" s="4" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="AA218" s="4" t="s">
         <v>68</v>
@@ -21579,24 +21581,24 @@
         <v>37</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="M219" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="N219" s="4">
         <v>28</v>
       </c>
       <c r="O219" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="P219" s="5"/>
       <c r="Q219" s="4" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>132</v>
@@ -21608,7 +21610,7 @@
         <v>0</v>
       </c>
       <c r="U219" s="4" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="V219" s="4" t="s">
         <v>87</v>
@@ -21659,22 +21661,22 @@
         <v>37</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="4" t="s">
         <v>129</v>
       </c>
       <c r="M220" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N220" s="4"/>
       <c r="O220" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="P220" s="5"/>
       <c r="Q220" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="R220" s="4" t="s">
         <v>132</v>
@@ -21731,22 +21733,22 @@
         <v>37</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K221" s="4"/>
       <c r="L221" s="4" t="s">
         <v>129</v>
       </c>
       <c r="M221" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N221" s="4"/>
       <c r="O221" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="P221" s="5"/>
       <c r="Q221" s="4" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="R221" s="4" t="s">
         <v>132</v>
@@ -21805,22 +21807,22 @@
         <v>37</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K222" s="4"/>
       <c r="L222" s="4" t="s">
         <v>129</v>
       </c>
       <c r="M222" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N222" s="4"/>
       <c r="O222" s="4" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="P222" s="5"/>
       <c r="Q222" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="R222" s="4" t="s">
         <v>132</v>
@@ -21879,22 +21881,22 @@
         <v>37</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K223" s="4"/>
       <c r="L223" s="4" t="s">
         <v>129</v>
       </c>
       <c r="M223" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N223" s="4"/>
       <c r="O223" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="P223" s="5"/>
       <c r="Q223" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="R223" s="4" t="s">
         <v>132</v>
@@ -21953,24 +21955,24 @@
         <v>37</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K224" s="4"/>
       <c r="L224" s="4" t="s">
         <v>129</v>
       </c>
       <c r="M224" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N224" s="4">
         <v>31</v>
       </c>
       <c r="O224" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="P224" s="5"/>
       <c r="Q224" s="4" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="R224" s="4" t="s">
         <v>132</v>
@@ -22029,22 +22031,22 @@
         <v>37</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K225" s="4"/>
       <c r="L225" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M225" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="N225" s="4"/>
       <c r="O225" s="4" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="P225" s="5"/>
       <c r="Q225" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="R225" s="4" t="s">
         <v>75</v>
@@ -22056,7 +22058,7 @@
         <v>0</v>
       </c>
       <c r="U225" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="V225" s="4" t="s">
         <v>87</v>
@@ -22105,24 +22107,24 @@
         <v>37</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K226" s="4"/>
       <c r="L226" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M226" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="N226" s="4">
         <v>19</v>
       </c>
       <c r="O226" s="4" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="P226" s="5"/>
       <c r="Q226" s="4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="R226" s="4" t="s">
         <v>132</v>
@@ -22134,7 +22136,7 @@
         <v>0</v>
       </c>
       <c r="U226" s="4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="V226" s="4" t="s">
         <v>87</v>
@@ -22147,7 +22149,7 @@
       </c>
       <c r="Y226" s="4"/>
       <c r="Z226" s="4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="AA226" s="4" t="s">
         <v>68</v>
@@ -22185,24 +22187,24 @@
         <v>37</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K227" s="4"/>
       <c r="L227" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M227" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="N227" s="4">
         <v>36</v>
       </c>
       <c r="O227" s="4" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="P227" s="5"/>
       <c r="Q227" s="4" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="R227" s="4" t="s">
         <v>132</v>
@@ -22261,24 +22263,24 @@
         <v>37</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K228" s="4"/>
       <c r="L228" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M228" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="N228" s="4">
         <v>5</v>
       </c>
       <c r="O228" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="P228" s="5"/>
       <c r="Q228" s="4" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="R228" s="4" t="s">
         <v>132</v>
@@ -22290,7 +22292,7 @@
         <v>73</v>
       </c>
       <c r="U228" s="4" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="V228" s="4" t="s">
         <v>57</v>
@@ -22341,24 +22343,24 @@
         <v>37</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K229" s="4"/>
       <c r="L229" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M229" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="N229" s="4">
         <v>98</v>
       </c>
       <c r="O229" s="4" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="P229" s="5"/>
       <c r="Q229" s="4" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="R229" s="4" t="s">
         <v>132</v>
@@ -22370,7 +22372,7 @@
         <v>0</v>
       </c>
       <c r="U229" s="4" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="V229" s="4" t="s">
         <v>57</v>
@@ -22419,11 +22421,11 @@
         <v>37</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K230" s="4"/>
       <c r="L230" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>129</v>
@@ -22432,11 +22434,11 @@
         <v>23</v>
       </c>
       <c r="O230" s="4" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="P230" s="5"/>
       <c r="Q230" s="4" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="R230" s="4" t="s">
         <v>132</v>
@@ -22495,11 +22497,11 @@
         <v>37</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="K231" s="4"/>
       <c r="L231" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M231" s="4" t="s">
         <v>129</v>
@@ -22508,11 +22510,11 @@
         <v>29</v>
       </c>
       <c r="O231" s="4" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="P231" s="5"/>
       <c r="Q231" s="4" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>132</v>
@@ -22524,7 +22526,7 @@
         <v>0</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="V231" s="4" t="s">
         <v>57</v>
@@ -22537,7 +22539,7 @@
       </c>
       <c r="Y231" s="4"/>
       <c r="Z231" s="4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="AA231" s="4" t="s">
         <v>68</v>
@@ -22557,7 +22559,7 @@
         <v>167738789</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E232" s="4">
         <v>8385629</v>
@@ -22572,27 +22574,27 @@
         <v>37</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K232" s="4"/>
       <c r="L232" s="4" t="s">
         <v>484</v>
       </c>
       <c r="M232" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N232" s="4">
         <v>50</v>
       </c>
       <c r="O232" s="4" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="P232" s="5"/>
       <c r="Q232" s="4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="R232" s="4" t="s">
         <v>132</v>
@@ -22613,7 +22615,7 @@
       </c>
       <c r="Y232" s="4"/>
       <c r="Z232" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="AA232" s="4"/>
       <c r="AB232" s="4" t="s">
@@ -22646,10 +22648,10 @@
         <v>37</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K233" s="4"/>
       <c r="L233" s="4" t="s">
@@ -22662,11 +22664,11 @@
         <v>39</v>
       </c>
       <c r="O233" s="4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="P233" s="5"/>
       <c r="Q233" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="R233" s="4" t="s">
         <v>144</v>
@@ -22678,7 +22680,7 @@
         <v>1</v>
       </c>
       <c r="U233" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="V233" s="4" t="s">
         <v>359</v>
@@ -22691,7 +22693,7 @@
       </c>
       <c r="Y233" s="4"/>
       <c r="Z233" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="AA233" s="4" t="s">
         <v>48</v>
@@ -22726,10 +22728,10 @@
         <v>37</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
@@ -22742,11 +22744,11 @@
         <v>123</v>
       </c>
       <c r="O234" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="P234" s="5"/>
       <c r="Q234" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="R234" s="4" t="s">
         <v>132</v>
@@ -22767,7 +22769,7 @@
       </c>
       <c r="Y234" s="4"/>
       <c r="Z234" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="AA234" s="4" t="s">
         <v>48</v>
@@ -22802,25 +22804,25 @@
         <v>37</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K235" s="4"/>
       <c r="L235" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>219</v>
       </c>
       <c r="N235" s="4"/>
       <c r="O235" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="P235" s="5"/>
       <c r="Q235" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="R235" s="4" t="s">
         <v>144</v>
@@ -22832,7 +22834,7 @@
         <v>2</v>
       </c>
       <c r="U235" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="V235" s="4" t="s">
         <v>57</v>
@@ -22845,7 +22847,7 @@
       </c>
       <c r="Y235" s="4"/>
       <c r="Z235" s="4" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AA235" s="4" t="s">
         <v>68</v>
@@ -22883,22 +22885,22 @@
         <v>37</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="K236" s="4"/>
       <c r="L236" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>167</v>
       </c>
       <c r="N236" s="4"/>
       <c r="O236" s="4" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="P236" s="5"/>
       <c r="Q236" s="4" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="R236" s="4" t="s">
         <v>132</v>
@@ -22919,7 +22921,7 @@
       </c>
       <c r="Y236" s="4"/>
       <c r="Z236" s="4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AA236" s="4" t="s">
         <v>68</v>
@@ -22933,13 +22935,13 @@
         <v>1000</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C237" s="4">
         <v>166999267</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E237" s="4">
         <v>8385018</v>
@@ -22957,18 +22959,18 @@
         <v>37</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K237" s="4"/>
       <c r="L237" s="4"/>
       <c r="M237" s="4"/>
       <c r="N237" s="4"/>
       <c r="O237" s="4" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="P237" s="5"/>
       <c r="Q237" s="4" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="R237" s="4" t="s">
         <v>132</v>
@@ -22989,7 +22991,7 @@
       </c>
       <c r="Y237" s="4"/>
       <c r="Z237" s="4" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="AA237" s="4"/>
       <c r="AB237" s="4" t="s">
@@ -23025,18 +23027,18 @@
         <v>37</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K238" s="4"/>
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
       <c r="N238" s="4"/>
       <c r="O238" s="4" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="P238" s="5"/>
       <c r="Q238" s="4" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="R238" s="4" t="s">
         <v>132</v>
@@ -23057,7 +23059,7 @@
       </c>
       <c r="Y238" s="4"/>
       <c r="Z238" s="4" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="AA238" s="4"/>
       <c r="AB238" s="4" t="s">
@@ -23093,18 +23095,18 @@
         <v>37</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K239" s="4"/>
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
       <c r="N239" s="4"/>
       <c r="O239" s="4" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="P239" s="5"/>
       <c r="Q239" s="4" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="R239" s="4" t="s">
         <v>132</v>
@@ -23125,7 +23127,7 @@
       </c>
       <c r="Y239" s="4"/>
       <c r="Z239" s="4" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="AA239" s="4"/>
       <c r="AB239" s="4" t="s">
@@ -23161,18 +23163,18 @@
         <v>37</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K240" s="4"/>
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
       <c r="N240" s="4"/>
       <c r="O240" s="4" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="P240" s="5"/>
       <c r="Q240" s="4" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="R240" s="4" t="s">
         <v>132</v>
@@ -23193,7 +23195,7 @@
       </c>
       <c r="Y240" s="4"/>
       <c r="Z240" s="4" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="AA240" s="4"/>
       <c r="AB240" s="4" t="s">
@@ -23229,7 +23231,7 @@
         <v>37</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K241" s="4"/>
       <c r="L241" s="4" t="s">
@@ -23238,11 +23240,11 @@
       <c r="M241" s="4"/>
       <c r="N241" s="4"/>
       <c r="O241" s="4" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="P241" s="5"/>
       <c r="Q241" s="4" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="R241" s="4" t="s">
         <v>132</v>
@@ -23263,7 +23265,7 @@
       </c>
       <c r="Y241" s="4"/>
       <c r="Z241" s="4" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="AA241" s="4" t="s">
         <v>109</v>
@@ -23301,7 +23303,7 @@
         <v>37</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K242" s="4"/>
       <c r="L242" s="4" t="s">
@@ -23310,11 +23312,11 @@
       <c r="M242" s="4"/>
       <c r="N242" s="4"/>
       <c r="O242" s="4" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="P242" s="5"/>
       <c r="Q242" s="4" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="R242" s="4" t="s">
         <v>132</v>
@@ -23326,7 +23328,7 @@
         <v>1</v>
       </c>
       <c r="U242" s="4" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="V242" s="4" t="s">
         <v>65</v>
@@ -23339,7 +23341,7 @@
       </c>
       <c r="Y242" s="4"/>
       <c r="Z242" s="4" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="AA242" s="4"/>
       <c r="AB242" s="4" t="s">
@@ -23357,7 +23359,7 @@
         <v>166810764</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E243" s="4">
         <v>8389436</v>
@@ -23375,18 +23377,18 @@
         <v>37</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="K243" s="4"/>
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
       <c r="N243" s="4"/>
       <c r="O243" s="4" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="P243" s="5"/>
       <c r="Q243" s="4" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="R243" s="4" t="s">
         <v>132</v>
@@ -23407,7 +23409,7 @@
       </c>
       <c r="Y243" s="4"/>
       <c r="Z243" s="4" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="AA243" s="4"/>
       <c r="AB243" s="4" t="s">
@@ -23443,7 +23445,7 @@
         <v>37</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="K244" s="4"/>
       <c r="L244" s="4" t="s">
@@ -23452,11 +23454,11 @@
       <c r="M244" s="4"/>
       <c r="N244" s="4"/>
       <c r="O244" s="4" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="P244" s="5"/>
       <c r="Q244" s="4" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="R244" s="4" t="s">
         <v>43</v>
@@ -23477,7 +23479,7 @@
       </c>
       <c r="Y244" s="4"/>
       <c r="Z244" s="4" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="AA244" s="4"/>
       <c r="AB244" s="4" t="s">
@@ -23513,7 +23515,7 @@
         <v>37</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K245" s="4"/>
       <c r="L245" s="4" t="s">
@@ -23522,11 +23524,11 @@
       <c r="M245" s="4"/>
       <c r="N245" s="4"/>
       <c r="O245" s="4" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="P245" s="5"/>
       <c r="Q245" s="4" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="R245" s="4" t="s">
         <v>75</v>
@@ -23538,7 +23540,7 @@
         <v>1</v>
       </c>
       <c r="U245" s="4" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="V245" s="4" t="s">
         <v>359</v>
@@ -23551,7 +23553,7 @@
       </c>
       <c r="Y245" s="4"/>
       <c r="Z245" s="4" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="AA245" s="4" t="s">
         <v>68</v>
@@ -23589,7 +23591,7 @@
         <v>37</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K246" s="4"/>
       <c r="L246" s="4" t="s">
@@ -23598,11 +23600,11 @@
       <c r="M246" s="4"/>
       <c r="N246" s="4"/>
       <c r="O246" s="4" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="P246" s="5"/>
       <c r="Q246" s="4" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="R246" s="4" t="s">
         <v>75</v>
@@ -23623,7 +23625,7 @@
       </c>
       <c r="Y246" s="4"/>
       <c r="Z246" s="4" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="AA246" s="4" t="s">
         <v>68</v>
@@ -23661,7 +23663,7 @@
         <v>37</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K247" s="4"/>
       <c r="L247" s="4" t="s">
@@ -23670,11 +23672,11 @@
       <c r="M247" s="4"/>
       <c r="N247" s="4"/>
       <c r="O247" s="4" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="P247" s="5"/>
       <c r="Q247" s="4" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="R247" s="4" t="s">
         <v>75</v>
@@ -23695,7 +23697,7 @@
       </c>
       <c r="Y247" s="4"/>
       <c r="Z247" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AA247" s="4" t="s">
         <v>68</v>
@@ -23733,18 +23735,18 @@
         <v>37</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K248" s="4"/>
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
       <c r="N248" s="4"/>
       <c r="O248" s="4" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P248" s="5"/>
       <c r="Q248" s="4" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="R248" s="4" t="s">
         <v>75</v>
@@ -23803,7 +23805,7 @@
         <v>37</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K249" s="4"/>
       <c r="L249" s="4" t="s">
@@ -23812,11 +23814,11 @@
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
       <c r="O249" s="4" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="P249" s="5"/>
       <c r="Q249" s="4" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="R249" s="4" t="s">
         <v>75</v>
@@ -23828,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="U249" s="4" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="V249" s="4" t="s">
         <v>359</v>
@@ -23841,7 +23843,7 @@
       </c>
       <c r="Y249" s="4"/>
       <c r="Z249" s="4" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="AA249" s="4" t="s">
         <v>48</v>
@@ -23879,7 +23881,7 @@
         <v>37</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K250" s="4"/>
       <c r="L250" s="4" t="s">
@@ -23888,11 +23890,11 @@
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
       <c r="O250" s="4" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="P250" s="5"/>
       <c r="Q250" s="4" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="R250" s="4" t="s">
         <v>75</v>
@@ -23904,7 +23906,7 @@
         <v>1</v>
       </c>
       <c r="U250" s="4" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="V250" s="4" t="s">
         <v>359</v>
@@ -23917,7 +23919,7 @@
       </c>
       <c r="Y250" s="4"/>
       <c r="Z250" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA250" s="4" t="s">
         <v>68</v>
@@ -23955,7 +23957,7 @@
         <v>37</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K251" s="4"/>
       <c r="L251" s="4" t="s">
@@ -23964,11 +23966,11 @@
       <c r="M251" s="4"/>
       <c r="N251" s="4"/>
       <c r="O251" s="4" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="P251" s="5"/>
       <c r="Q251" s="4" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="R251" s="4" t="s">
         <v>75</v>
@@ -23989,7 +23991,7 @@
       </c>
       <c r="Y251" s="4"/>
       <c r="Z251" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA251" s="4" t="s">
         <v>68</v>
@@ -24027,7 +24029,7 @@
         <v>37</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K252" s="4"/>
       <c r="L252" s="4" t="s">
@@ -24036,11 +24038,11 @@
       <c r="M252" s="4"/>
       <c r="N252" s="4"/>
       <c r="O252" s="4" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="P252" s="5"/>
       <c r="Q252" s="4" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="R252" s="4" t="s">
         <v>75</v>
@@ -24061,7 +24063,7 @@
       </c>
       <c r="Y252" s="4"/>
       <c r="Z252" s="4" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="AA252" s="4"/>
       <c r="AB252" s="4" t="s">
@@ -24097,7 +24099,7 @@
         <v>37</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="K253" s="4"/>
       <c r="L253" s="4" t="s">
@@ -24106,11 +24108,11 @@
       <c r="M253" s="4"/>
       <c r="N253" s="4"/>
       <c r="O253" s="4" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="P253" s="5"/>
       <c r="Q253" s="4" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="R253" s="4" t="s">
         <v>43</v>
@@ -24131,7 +24133,7 @@
       </c>
       <c r="Y253" s="4"/>
       <c r="Z253" s="4" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="AA253" s="4" t="s">
         <v>109</v>
@@ -24169,7 +24171,7 @@
         <v>37</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="K254" s="4"/>
       <c r="L254" s="4" t="s">
@@ -24178,11 +24180,11 @@
       <c r="M254" s="4"/>
       <c r="N254" s="4"/>
       <c r="O254" s="4" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="P254" s="5"/>
       <c r="Q254" s="4" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="R254" s="4" t="s">
         <v>75</v>
@@ -24194,7 +24196,7 @@
         <v>1</v>
       </c>
       <c r="U254" s="4" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="V254" s="4" t="s">
         <v>87</v>
@@ -24207,7 +24209,7 @@
       </c>
       <c r="Y254" s="4"/>
       <c r="Z254" s="4" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="AA254" s="4" t="s">
         <v>68</v>
@@ -24245,24 +24247,24 @@
         <v>37</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="K255" s="4"/>
       <c r="L255" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M255" s="4" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="N255" s="4">
         <v>5</v>
       </c>
       <c r="O255" s="4" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="P255" s="5"/>
       <c r="Q255" s="4" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="R255" s="4" t="s">
         <v>75</v>
@@ -24274,7 +24276,7 @@
         <v>0</v>
       </c>
       <c r="U255" s="4" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="V255" s="4" t="s">
         <v>87</v>
@@ -24287,7 +24289,7 @@
       </c>
       <c r="Y255" s="4"/>
       <c r="Z255" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA255" s="4" t="s">
         <v>68</v>
@@ -24325,24 +24327,24 @@
         <v>37</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="K256" s="4"/>
       <c r="L256" s="4" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="M256" s="4" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="N256" s="4">
         <v>30</v>
       </c>
       <c r="O256" s="4" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="P256" s="5"/>
       <c r="Q256" s="4" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="R256" s="4" t="s">
         <v>43</v>
@@ -24354,7 +24356,7 @@
         <v>1</v>
       </c>
       <c r="U256" s="4" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="V256" s="4" t="s">
         <v>65</v>
@@ -24367,7 +24369,7 @@
       </c>
       <c r="Y256" s="4"/>
       <c r="Z256" s="4" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="AA256" s="4" t="s">
         <v>109</v>
@@ -24405,24 +24407,24 @@
         <v>37</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="K257" s="4"/>
       <c r="L257" s="4" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="M257" s="4" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="N257" s="4">
         <v>15</v>
       </c>
       <c r="O257" s="4" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="P257" s="5"/>
       <c r="Q257" s="4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="R257" s="4" t="s">
         <v>43</v>
@@ -24434,7 +24436,7 @@
         <v>0</v>
       </c>
       <c r="U257" s="4" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="V257" s="4" t="s">
         <v>153</v>
@@ -24447,7 +24449,7 @@
       </c>
       <c r="Y257" s="4"/>
       <c r="Z257" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA257" s="4" t="s">
         <v>68</v>
@@ -24485,18 +24487,18 @@
         <v>37</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K258" s="4"/>
       <c r="L258" s="4"/>
       <c r="M258" s="4"/>
       <c r="N258" s="4"/>
       <c r="O258" s="4" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="P258" s="5"/>
       <c r="Q258" s="4" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="R258" s="4" t="s">
         <v>132</v>
@@ -24517,7 +24519,7 @@
       </c>
       <c r="Y258" s="4"/>
       <c r="Z258" s="4" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="AA258" s="4" t="s">
         <v>109</v>
@@ -24555,18 +24557,18 @@
         <v>37</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K259" s="4"/>
       <c r="L259" s="4"/>
       <c r="M259" s="4"/>
       <c r="N259" s="4"/>
       <c r="O259" s="4" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="P259" s="5"/>
       <c r="Q259" s="4" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="R259" s="4" t="s">
         <v>132</v>
@@ -24578,7 +24580,7 @@
         <v>0</v>
       </c>
       <c r="U259" s="4" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="V259" s="4" t="s">
         <v>45</v>
@@ -24591,7 +24593,7 @@
       </c>
       <c r="Y259" s="4"/>
       <c r="Z259" s="4" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="AA259" s="4"/>
       <c r="AB259" s="4" t="s">
@@ -24627,18 +24629,18 @@
         <v>37</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K260" s="4"/>
       <c r="L260" s="4"/>
       <c r="M260" s="4"/>
       <c r="N260" s="4"/>
       <c r="O260" s="4" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="P260" s="5"/>
       <c r="Q260" s="4" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="R260" s="4" t="s">
         <v>132</v>
@@ -24650,10 +24652,10 @@
         <v>0</v>
       </c>
       <c r="U260" s="4" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="V260" s="4" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="W260" s="4">
         <v>1</v>
@@ -24663,7 +24665,7 @@
       </c>
       <c r="Y260" s="4"/>
       <c r="Z260" s="4" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="AA260" s="4" t="s">
         <v>68</v>
@@ -24701,7 +24703,7 @@
         <v>37</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K261" s="4"/>
       <c r="L261" s="4" t="s">
@@ -24710,11 +24712,11 @@
       <c r="M261" s="4"/>
       <c r="N261" s="4"/>
       <c r="O261" s="4" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="P261" s="5"/>
       <c r="Q261" s="4" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="R261" s="4" t="s">
         <v>132</v>
@@ -24735,7 +24737,7 @@
       </c>
       <c r="Y261" s="4"/>
       <c r="Z261" s="4" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="AA261" s="4" t="s">
         <v>68</v>
@@ -24773,7 +24775,7 @@
         <v>37</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K262" s="4"/>
       <c r="L262" s="4" t="s">
@@ -24782,11 +24784,11 @@
       <c r="M262" s="4"/>
       <c r="N262" s="4"/>
       <c r="O262" s="4" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="P262" s="5"/>
       <c r="Q262" s="4" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="R262" s="4" t="s">
         <v>132</v>
@@ -24798,7 +24800,7 @@
         <v>0</v>
       </c>
       <c r="U262" s="4" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="V262" s="4" t="s">
         <v>65</v>
@@ -24811,7 +24813,7 @@
       </c>
       <c r="Y262" s="4"/>
       <c r="Z262" s="4" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="AA262" s="4" t="s">
         <v>89</v>
@@ -24849,7 +24851,7 @@
         <v>37</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K263" s="4"/>
       <c r="L263" s="4" t="s">
@@ -24858,11 +24860,11 @@
       <c r="M263" s="4"/>
       <c r="N263" s="4"/>
       <c r="O263" s="4" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="P263" s="5"/>
       <c r="Q263" s="4" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="R263" s="4" t="s">
         <v>132</v>
@@ -24883,7 +24885,7 @@
       </c>
       <c r="Y263" s="4"/>
       <c r="Z263" s="4" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="AA263" s="4" t="s">
         <v>109</v>
@@ -24921,7 +24923,7 @@
         <v>37</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="K264" s="4"/>
       <c r="L264" s="4" t="s">
@@ -24930,11 +24932,11 @@
       <c r="M264" s="4"/>
       <c r="N264" s="4"/>
       <c r="O264" s="4" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="P264" s="5"/>
       <c r="Q264" s="4" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="R264" s="4" t="s">
         <v>75</v>
@@ -24955,7 +24957,7 @@
       </c>
       <c r="Y264" s="4"/>
       <c r="Z264" s="4" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="AA264" s="4" t="s">
         <v>68</v>
@@ -24993,24 +24995,24 @@
         <v>37</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K265" s="4"/>
       <c r="L265" s="4" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="M265" s="4" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="N265" s="4">
         <v>28</v>
       </c>
       <c r="O265" s="4" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="P265" s="5"/>
       <c r="Q265" s="4" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="R265" s="4" t="s">
         <v>75</v>
@@ -25022,7 +25024,7 @@
         <v>1</v>
       </c>
       <c r="U265" s="4" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="V265" s="4" t="s">
         <v>359</v>
@@ -25035,7 +25037,7 @@
       </c>
       <c r="Y265" s="4"/>
       <c r="Z265" s="4" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="AA265" s="4" t="s">
         <v>109</v>
@@ -25073,24 +25075,24 @@
         <v>37</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K266" s="4"/>
       <c r="L266" s="4" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="M266" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N266" s="4">
         <v>20</v>
       </c>
       <c r="O266" s="4" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="P266" s="5"/>
       <c r="Q266" s="4" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="R266" s="4" t="s">
         <v>43</v>
@@ -25102,7 +25104,7 @@
         <v>0</v>
       </c>
       <c r="U266" s="4" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="V266" s="4" t="s">
         <v>65</v>
@@ -25115,7 +25117,7 @@
       </c>
       <c r="Y266" s="4"/>
       <c r="Z266" s="4" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="AA266" s="4"/>
       <c r="AB266" s="4" t="s">
@@ -25151,24 +25153,24 @@
         <v>37</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="M267" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N267" s="4">
         <v>8</v>
       </c>
       <c r="O267" s="4" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="P267" s="5"/>
       <c r="Q267" s="4" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="R267" s="4" t="s">
         <v>43</v>
@@ -25189,7 +25191,7 @@
       </c>
       <c r="Y267" s="4"/>
       <c r="Z267" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA267" s="4" t="s">
         <v>68</v>
@@ -25227,24 +25229,24 @@
         <v>37</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="M268" s="4" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="N268" s="4">
         <v>19</v>
       </c>
       <c r="O268" s="4" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="P268" s="5"/>
       <c r="Q268" s="4" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="R268" s="4" t="s">
         <v>43</v>
@@ -25256,7 +25258,7 @@
         <v>0</v>
       </c>
       <c r="U268" s="4" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="V268" s="4" t="s">
         <v>65</v>
@@ -25269,7 +25271,7 @@
       </c>
       <c r="Y268" s="4"/>
       <c r="Z268" s="4" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="AA268" s="4" t="s">
         <v>109</v>
@@ -25307,11 +25309,11 @@
         <v>37</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M269" s="4" t="s">
         <v>528</v>
@@ -25320,11 +25322,11 @@
         <v>52</v>
       </c>
       <c r="O269" s="4" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="P269" s="5"/>
       <c r="Q269" s="4" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="R269" s="4" t="s">
         <v>75</v>
@@ -25336,7 +25338,7 @@
         <v>0</v>
       </c>
       <c r="U269" s="4" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="V269" s="4" t="s">
         <v>87</v>
@@ -25349,7 +25351,7 @@
       </c>
       <c r="Y269" s="4"/>
       <c r="Z269" s="4" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="AA269" s="4" t="s">
         <v>109</v>
@@ -25387,22 +25389,22 @@
         <v>37</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K270" s="4"/>
       <c r="L270" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M270" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N270" s="4"/>
       <c r="O270" s="4" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="P270" s="5"/>
       <c r="Q270" s="4" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="R270" s="4" t="s">
         <v>43</v>
@@ -25423,7 +25425,7 @@
       </c>
       <c r="Y270" s="4"/>
       <c r="Z270" s="4" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="AA270" s="4" t="s">
         <v>48</v>
@@ -25461,22 +25463,22 @@
         <v>37</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K271" s="4"/>
       <c r="L271" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M271" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N271" s="4"/>
       <c r="O271" s="4" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="P271" s="5"/>
       <c r="Q271" s="4" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="R271" s="4" t="s">
         <v>43</v>
@@ -25488,10 +25490,10 @@
         <v>0</v>
       </c>
       <c r="U271" s="4" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="V271" s="4" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="W271" s="4">
         <v>4</v>
@@ -25501,7 +25503,7 @@
       </c>
       <c r="Y271" s="4"/>
       <c r="Z271" s="4" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="AA271" s="4" t="s">
         <v>165</v>
@@ -25515,7 +25517,7 @@
         <v>1000</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C272" s="4">
         <v>167628481</v>
@@ -25539,24 +25541,24 @@
         <v>37</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K272" s="4"/>
       <c r="L272" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M272" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N272" s="4">
         <v>21</v>
       </c>
       <c r="O272" s="4" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="4" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="R272" s="4" t="s">
         <v>75</v>
@@ -25577,7 +25579,7 @@
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="AA272" s="4" t="s">
         <v>109</v>
@@ -25591,7 +25593,7 @@
         <v>1000</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C273" s="4">
         <v>167628489</v>
@@ -25615,24 +25617,24 @@
         <v>37</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K273" s="4"/>
       <c r="L273" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M273" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N273" s="4">
         <v>21</v>
       </c>
       <c r="O273" s="4" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="P273" s="5"/>
       <c r="Q273" s="4" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="R273" s="4" t="s">
         <v>75</v>
@@ -25644,10 +25646,10 @@
         <v>0</v>
       </c>
       <c r="U273" s="4" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="V273" s="4" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="W273" s="4">
         <v>4</v>
@@ -25657,7 +25659,7 @@
       </c>
       <c r="Y273" s="4"/>
       <c r="Z273" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA273" s="4" t="s">
         <v>68</v>
@@ -25671,7 +25673,7 @@
         <v>1000</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C274" s="4">
         <v>167628490</v>
@@ -25695,24 +25697,24 @@
         <v>37</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M274" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N274" s="4">
         <v>27</v>
       </c>
       <c r="O274" s="4" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="P274" s="5"/>
       <c r="Q274" s="4" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="R274" s="4" t="s">
         <v>75</v>
@@ -25733,7 +25735,7 @@
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="AA274" s="4"/>
       <c r="AB274" s="4" t="s">
@@ -25769,24 +25771,24 @@
         <v>37</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K275" s="4"/>
       <c r="L275" s="4" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="M275" s="4" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="N275" s="4">
         <v>5</v>
       </c>
       <c r="O275" s="4" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="P275" s="5"/>
       <c r="Q275" s="4" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="R275" s="4" t="s">
         <v>43</v>
@@ -25798,7 +25800,7 @@
         <v>3</v>
       </c>
       <c r="U275" s="4" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="V275" s="4" t="s">
         <v>317</v>
@@ -25811,7 +25813,7 @@
       </c>
       <c r="Y275" s="4"/>
       <c r="Z275" s="4" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="AA275" s="4" t="s">
         <v>48</v>
@@ -25849,24 +25851,24 @@
         <v>37</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K276" s="4"/>
       <c r="L276" s="4" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="M276" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N276" s="4">
         <v>11</v>
       </c>
       <c r="O276" s="4" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="P276" s="5"/>
       <c r="Q276" s="4" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="R276" s="4" t="s">
         <v>43</v>
@@ -25887,7 +25889,7 @@
       </c>
       <c r="Y276" s="4"/>
       <c r="Z276" s="4" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="AA276" s="4" t="s">
         <v>68</v>
@@ -25925,24 +25927,24 @@
         <v>37</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K277" s="4"/>
       <c r="L277" s="4" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="M277" s="4" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="N277" s="4">
         <v>49</v>
       </c>
       <c r="O277" s="4" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="P277" s="5"/>
       <c r="Q277" s="4" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="R277" s="4" t="s">
         <v>43</v>
@@ -25963,7 +25965,7 @@
       </c>
       <c r="Y277" s="4"/>
       <c r="Z277" s="4" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="AA277" s="4" t="s">
         <v>68</v>
@@ -26001,7 +26003,7 @@
         <v>37</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K278" s="4"/>
       <c r="L278" s="4" t="s">
@@ -26014,11 +26016,11 @@
         <v>4</v>
       </c>
       <c r="O278" s="4" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="P278" s="5"/>
       <c r="Q278" s="4" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="R278" s="4" t="s">
         <v>43</v>
@@ -26030,7 +26032,7 @@
         <v>0</v>
       </c>
       <c r="U278" s="4" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="V278" s="4" t="s">
         <v>57</v>
@@ -26081,24 +26083,24 @@
         <v>37</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K279" s="4"/>
       <c r="L279" s="4" t="s">
         <v>559</v>
       </c>
       <c r="M279" s="4" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="N279" s="4">
         <v>99</v>
       </c>
       <c r="O279" s="4" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="P279" s="5"/>
       <c r="Q279" s="4" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="R279" s="4" t="s">
         <v>43</v>
@@ -26119,7 +26121,7 @@
       </c>
       <c r="Y279" s="4"/>
       <c r="Z279" s="4" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="AA279" s="4" t="s">
         <v>89</v>
@@ -26133,7 +26135,7 @@
         <v>1000</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C280" s="4">
         <v>166944053</v>
@@ -26157,22 +26159,22 @@
         <v>37</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K280" s="4"/>
       <c r="L280" s="4" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M280" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="N280" s="4"/>
       <c r="O280" s="4" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="P280" s="5"/>
       <c r="Q280" s="4" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="R280" s="4" t="s">
         <v>43</v>
@@ -26184,7 +26186,7 @@
         <v>0</v>
       </c>
       <c r="U280" s="4" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="V280" s="4" t="s">
         <v>87</v>
@@ -26197,7 +26199,7 @@
       </c>
       <c r="Y280" s="4"/>
       <c r="Z280" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA280" s="4" t="s">
         <v>68</v>
@@ -26211,7 +26213,7 @@
         <v>1000</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C281" s="4">
         <v>166944054</v>
@@ -26235,22 +26237,22 @@
         <v>37</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K281" s="4"/>
       <c r="L281" s="4" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M281" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="N281" s="4"/>
       <c r="O281" s="4" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="P281" s="5"/>
       <c r="Q281" s="4" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="R281" s="4" t="s">
         <v>43</v>
@@ -26262,7 +26264,7 @@
         <v>2</v>
       </c>
       <c r="U281" s="4" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="V281" s="4" t="s">
         <v>636</v>
@@ -26275,7 +26277,7 @@
       </c>
       <c r="Y281" s="4"/>
       <c r="Z281" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA281" s="4" t="s">
         <v>68</v>
@@ -26313,24 +26315,24 @@
         <v>37</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K282" s="4"/>
       <c r="L282" s="4" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M282" s="4" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="N282" s="4">
         <v>28</v>
       </c>
       <c r="O282" s="4" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="P282" s="5"/>
       <c r="Q282" s="4" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="R282" s="4" t="s">
         <v>43</v>
@@ -26342,7 +26344,7 @@
         <v>0</v>
       </c>
       <c r="U282" s="4" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="V282" s="4" t="s">
         <v>57</v>
@@ -26355,7 +26357,7 @@
       </c>
       <c r="Y282" s="4"/>
       <c r="Z282" s="4" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="AA282" s="4" t="s">
         <v>68</v>
@@ -26369,7 +26371,7 @@
         <v>1000</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C283" s="4">
         <v>167005592</v>
@@ -26393,24 +26395,24 @@
         <v>37</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K283" s="4"/>
       <c r="L283" s="4" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M283" s="4" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="N283" s="4">
         <v>29</v>
       </c>
       <c r="O283" s="4" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="P283" s="5"/>
       <c r="Q283" s="4" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="R283" s="4" t="s">
         <v>43</v>
@@ -26431,7 +26433,7 @@
       </c>
       <c r="Y283" s="4"/>
       <c r="Z283" s="4" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="AA283" s="4" t="s">
         <v>109</v>
@@ -26469,24 +26471,24 @@
         <v>37</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K284" s="4"/>
       <c r="L284" s="4" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M284" s="4" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="N284" s="4">
         <v>50</v>
       </c>
       <c r="O284" s="4" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="P284" s="5"/>
       <c r="Q284" s="4" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="R284" s="4" t="s">
         <v>75</v>
@@ -26498,7 +26500,7 @@
         <v>0</v>
       </c>
       <c r="U284" s="4" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="V284" s="4" t="s">
         <v>359</v>
@@ -26547,24 +26549,24 @@
         <v>37</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K285" s="4"/>
       <c r="L285" s="4" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M285" s="4" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="N285" s="4">
         <v>68</v>
       </c>
       <c r="O285" s="4" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="P285" s="5"/>
       <c r="Q285" s="4" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="R285" s="4" t="s">
         <v>43</v>
@@ -26576,7 +26578,7 @@
         <v>0</v>
       </c>
       <c r="U285" s="4" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="V285" s="4" t="s">
         <v>57</v>
@@ -26627,24 +26629,24 @@
         <v>37</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K286" s="4"/>
       <c r="L286" s="4" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="M286" s="4" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="N286" s="4">
         <v>68</v>
       </c>
       <c r="O286" s="4" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="P286" s="5"/>
       <c r="Q286" s="4" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="R286" s="4" t="s">
         <v>43</v>
@@ -26665,7 +26667,7 @@
       </c>
       <c r="Y286" s="4"/>
       <c r="Z286" s="4" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="AA286" s="4" t="s">
         <v>109</v>
@@ -26703,22 +26705,22 @@
         <v>37</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K287" s="4"/>
       <c r="L287" s="4" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="M287" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="N287" s="4"/>
       <c r="O287" s="4" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="4" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="R287" s="4" t="s">
         <v>43</v>
@@ -26739,7 +26741,7 @@
       </c>
       <c r="Y287" s="4"/>
       <c r="Z287" s="4" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="AA287" s="4" t="s">
         <v>68</v>
@@ -26777,22 +26779,22 @@
         <v>37</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K288" s="4"/>
       <c r="L288" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M288" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="N288" s="4"/>
       <c r="O288" s="4" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="P288" s="5"/>
       <c r="Q288" s="4" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="R288" s="4" t="s">
         <v>43</v>
@@ -26804,7 +26806,7 @@
         <v>2</v>
       </c>
       <c r="U288" s="4" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="V288" s="4" t="s">
         <v>98</v>
@@ -26817,7 +26819,7 @@
       </c>
       <c r="Y288" s="4"/>
       <c r="Z288" s="4" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="AA288" s="4" t="s">
         <v>109</v>
@@ -26855,22 +26857,22 @@
         <v>37</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K289" s="4"/>
       <c r="L289" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M289" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="N289" s="4"/>
       <c r="O289" s="4" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="P289" s="5"/>
       <c r="Q289" s="4" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="R289" s="4" t="s">
         <v>43</v>
@@ -26882,7 +26884,7 @@
         <v>1</v>
       </c>
       <c r="U289" s="4" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="V289" s="4" t="s">
         <v>359</v>
@@ -26895,7 +26897,7 @@
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="AA289" s="4" t="s">
         <v>109</v>
@@ -26933,24 +26935,24 @@
         <v>37</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M290" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="N290" s="4">
         <v>18</v>
       </c>
       <c r="O290" s="4" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="R290" s="4" t="s">
         <v>43</v>
@@ -26962,7 +26964,7 @@
         <v>0</v>
       </c>
       <c r="U290" s="4" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="V290" s="4" t="s">
         <v>243</v>
@@ -26975,7 +26977,7 @@
       </c>
       <c r="Y290" s="4"/>
       <c r="Z290" s="4" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="AA290" s="4"/>
       <c r="AB290" s="4" t="s">
@@ -27011,24 +27013,24 @@
         <v>37</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K291" s="4"/>
       <c r="L291" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M291" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="N291" s="4">
         <v>35</v>
       </c>
       <c r="O291" s="4" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="P291" s="5"/>
       <c r="Q291" s="4" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="R291" s="4" t="s">
         <v>75</v>
@@ -27040,7 +27042,7 @@
         <v>0</v>
       </c>
       <c r="U291" s="4" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="V291" s="4" t="s">
         <v>317</v>
@@ -27091,24 +27093,24 @@
         <v>37</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="K292" s="4"/>
       <c r="L292" s="4" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="M292" s="4" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="N292" s="4">
         <v>28</v>
       </c>
       <c r="O292" s="4" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="R292" s="4" t="s">
         <v>43</v>
@@ -27120,7 +27122,7 @@
         <v>0</v>
       </c>
       <c r="U292" s="4" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="V292" s="4" t="s">
         <v>359</v>
@@ -27171,24 +27173,24 @@
         <v>37</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="K293" s="4"/>
       <c r="L293" s="4" t="s">
         <v>72</v>
       </c>
       <c r="M293" s="4" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="N293" s="4">
         <v>48</v>
       </c>
       <c r="O293" s="4" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="P293" s="5"/>
       <c r="Q293" s="4" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="R293" s="4" t="s">
         <v>43</v>
@@ -27200,7 +27202,7 @@
         <v>3</v>
       </c>
       <c r="U293" s="4" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="V293" s="4" t="s">
         <v>359</v>
@@ -27213,7 +27215,7 @@
       </c>
       <c r="Y293" s="4"/>
       <c r="Z293" s="4" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="AA293" s="4" t="s">
         <v>305</v>
@@ -27227,13 +27229,13 @@
         <v>1000</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C294" s="4">
         <v>166923331</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E294" s="4">
         <v>8296427</v>
@@ -27251,24 +27253,24 @@
         <v>37</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="K294" s="4"/>
       <c r="L294" s="4" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="M294" s="4" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="N294" s="4">
         <v>46</v>
       </c>
       <c r="O294" s="4" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="P294" s="5"/>
       <c r="Q294" s="4" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="R294" s="4" t="s">
         <v>132</v>
@@ -27289,7 +27291,7 @@
       </c>
       <c r="Y294" s="4"/>
       <c r="Z294" s="4" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="AA294" s="4"/>
       <c r="AB294" s="4" t="s">
@@ -27301,7 +27303,7 @@
         <v>1000</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C295" s="4">
         <v>167632441</v>
@@ -27325,7 +27327,7 @@
         <v>37</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K295" s="4"/>
       <c r="L295" s="4" t="s">
@@ -27336,11 +27338,11 @@
       </c>
       <c r="N295" s="4"/>
       <c r="O295" s="4" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>43</v>
@@ -27352,7 +27354,7 @@
         <v>2</v>
       </c>
       <c r="U295" s="4" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="V295" s="4" t="s">
         <v>106</v>
@@ -27379,7 +27381,7 @@
         <v>1000</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C296" s="4">
         <v>167632438</v>
@@ -27403,22 +27405,22 @@
         <v>37</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
         <v>187</v>
       </c>
       <c r="M296" s="4" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="N296" s="4"/>
       <c r="O296" s="4" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>144</v>
@@ -27430,7 +27432,7 @@
         <v>0</v>
       </c>
       <c r="U296" s="4" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="V296" s="4" t="s">
         <v>243</v>
@@ -27481,7 +27483,7 @@
         <v>37</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
@@ -27492,11 +27494,11 @@
       </c>
       <c r="N297" s="4"/>
       <c r="O297" s="4" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>75</v>
@@ -27517,7 +27519,7 @@
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="AA297" s="4" t="s">
         <v>89</v>
@@ -27531,7 +27533,7 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C298" s="4">
         <v>167632440</v>
@@ -27555,22 +27557,22 @@
         <v>37</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="M298" s="4" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="R298" s="4" t="s">
         <v>43</v>
@@ -27582,7 +27584,7 @@
         <v>3</v>
       </c>
       <c r="U298" s="4" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="V298" s="4" t="s">
         <v>153</v>
@@ -27633,11 +27635,11 @@
         <v>37</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="M299" s="4" t="s">
         <v>187</v>
@@ -27646,11 +27648,11 @@
         <v>71</v>
       </c>
       <c r="O299" s="4" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>43</v>
@@ -27662,7 +27664,7 @@
         <v>7</v>
       </c>
       <c r="U299" s="4" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="V299" s="4" t="s">
         <v>106</v>
@@ -27713,22 +27715,22 @@
         <v>37</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K300" s="4"/>
       <c r="L300" s="4" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="M300" s="4" t="s">
         <v>101</v>
       </c>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="R300" s="4" t="s">
         <v>43</v>
@@ -27740,7 +27742,7 @@
         <v>0</v>
       </c>
       <c r="U300" s="4" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="V300" s="4" t="s">
         <v>359</v>
@@ -27791,11 +27793,11 @@
         <v>37</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K301" s="4"/>
       <c r="L301" s="4" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="M301" s="4" t="s">
         <v>52</v>
@@ -27804,11 +27806,11 @@
         <v>52</v>
       </c>
       <c r="O301" s="4" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="R301" s="4" t="s">
         <v>43</v>
@@ -27820,7 +27822,7 @@
         <v>73</v>
       </c>
       <c r="U301" s="4" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="V301" s="4" t="s">
         <v>317</v>
@@ -27871,18 +27873,18 @@
         <v>37</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4"/>
       <c r="M302" s="4"/>
       <c r="N302" s="4"/>
       <c r="O302" s="4" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="P302" s="5"/>
       <c r="Q302" s="4" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="R302" s="4" t="s">
         <v>132</v>
@@ -27903,7 +27905,7 @@
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="AA302" s="4"/>
       <c r="AB302" s="4" t="s">
@@ -27939,18 +27941,18 @@
         <v>37</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4"/>
       <c r="M303" s="4"/>
       <c r="N303" s="4"/>
       <c r="O303" s="4" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="R303" s="4" t="s">
         <v>132</v>
@@ -27971,7 +27973,7 @@
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="AA303" s="4" t="s">
         <v>109</v>
@@ -27985,7 +27987,7 @@
         <v>1000</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C304" s="4">
         <v>167612550</v>
@@ -28009,7 +28011,7 @@
         <v>37</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
@@ -28018,11 +28020,11 @@
       <c r="M304" s="4"/>
       <c r="N304" s="4"/>
       <c r="O304" s="4" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>75</v>
@@ -28055,7 +28057,7 @@
         <v>1000</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C305" s="4">
         <v>167612549</v>
@@ -28079,22 +28081,22 @@
         <v>37</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M305" s="4" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="N305" s="4"/>
       <c r="O305" s="4" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="R305" s="4" t="s">
         <v>75</v>
@@ -28153,24 +28155,24 @@
         <v>37</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="M306" s="4" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="N306" s="4">
         <v>30</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="R306" s="4" t="s">
         <v>75</v>
@@ -28182,7 +28184,7 @@
         <v>0</v>
       </c>
       <c r="U306" s="4" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="V306" s="4" t="s">
         <v>317</v>
@@ -28195,7 +28197,7 @@
       </c>
       <c r="Y306" s="4"/>
       <c r="Z306" s="4" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="AA306" s="4" t="s">
         <v>68</v>
@@ -28233,24 +28235,24 @@
         <v>37</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="M307" s="4" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="N307" s="4">
         <v>3</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>75</v>
@@ -28271,7 +28273,7 @@
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="AA307" s="4"/>
       <c r="AB307" s="4" t="s">
@@ -28307,7 +28309,7 @@
         <v>37</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
@@ -28316,11 +28318,11 @@
       <c r="M308" s="4"/>
       <c r="N308" s="4"/>
       <c r="O308" s="4" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="4" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="R308" s="4" t="s">
         <v>43</v>
@@ -28341,7 +28343,7 @@
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="AA308" s="4" t="s">
         <v>68</v>
@@ -28379,22 +28381,22 @@
         <v>37</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="M309" s="4" t="s">
         <v>72</v>
       </c>
       <c r="N309" s="4"/>
       <c r="O309" s="4" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="R309" s="4" t="s">
         <v>43</v>
@@ -28415,7 +28417,7 @@
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="AA309" s="4" t="s">
         <v>68</v>
@@ -28453,7 +28455,7 @@
         <v>344</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -28462,11 +28464,11 @@
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
       <c r="O310" s="4" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="R310" s="4" t="s">
         <v>132</v>
@@ -28478,7 +28480,7 @@
         <v>0</v>
       </c>
       <c r="U310" s="4" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="V310" s="4" t="s">
         <v>98</v>
@@ -28491,7 +28493,7 @@
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="AA310" s="4"/>
       <c r="AB310" s="4" t="s">
@@ -28527,7 +28529,7 @@
         <v>37</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
@@ -28536,11 +28538,11 @@
       <c r="M311" s="4"/>
       <c r="N311" s="4"/>
       <c r="O311" s="4" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="P311" s="5"/>
       <c r="Q311" s="4" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="R311" s="4" t="s">
         <v>43</v>
@@ -28561,7 +28563,7 @@
       </c>
       <c r="Y311" s="4"/>
       <c r="Z311" s="4" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="AA311" s="4" t="s">
         <v>68</v>
@@ -28581,7 +28583,7 @@
         <v>167200579</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E312" s="4">
         <v>7280561</v>
@@ -28599,22 +28601,22 @@
         <v>37</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="M312" s="4" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="N312" s="4"/>
       <c r="O312" s="4" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>75</v>
@@ -28635,7 +28637,7 @@
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="AA312" s="4"/>
       <c r="AB312" s="4" t="s">
@@ -28671,22 +28673,22 @@
         <v>37</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M313" s="4" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="N313" s="4"/>
       <c r="O313" s="4" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="R313" s="4" t="s">
         <v>43</v>
@@ -28698,7 +28700,7 @@
         <v>2</v>
       </c>
       <c r="U313" s="4" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="V313" s="4" t="s">
         <v>65</v>
@@ -28711,7 +28713,7 @@
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="AA313" s="4" t="s">
         <v>48</v>
@@ -28749,22 +28751,22 @@
         <v>37</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M314" s="4" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="N314" s="4"/>
       <c r="O314" s="4" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>75</v>
@@ -28785,7 +28787,7 @@
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="AA314" s="4" t="s">
         <v>68</v>
@@ -28823,22 +28825,22 @@
         <v>37</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="N315" s="4"/>
       <c r="O315" s="4" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="R315" s="4" t="s">
         <v>75</v>
@@ -28850,7 +28852,7 @@
         <v>0</v>
       </c>
       <c r="U315" s="4" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="V315" s="4" t="s">
         <v>243</v>
@@ -28863,7 +28865,7 @@
       </c>
       <c r="Y315" s="4"/>
       <c r="Z315" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA315" s="4" t="s">
         <v>68</v>
@@ -28901,22 +28903,22 @@
         <v>37</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="M316" s="4" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="N316" s="4"/>
       <c r="O316" s="4" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="R316" s="4" t="s">
         <v>75</v>
@@ -28928,10 +28930,10 @@
         <v>74</v>
       </c>
       <c r="U316" s="4" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="V316" s="4" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="W316" s="4">
         <v>1</v>
@@ -28955,7 +28957,7 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C317" s="4">
         <v>167632444</v>
@@ -28979,24 +28981,24 @@
         <v>37</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="K317" s="4"/>
       <c r="L317" s="4" t="s">
         <v>575</v>
       </c>
       <c r="M317" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="N317" s="4">
         <v>30</v>
       </c>
       <c r="O317" s="4" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="R317" s="4" t="s">
         <v>75</v>
@@ -29055,22 +29057,22 @@
         <v>37</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="K318" s="4"/>
       <c r="L318" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M318" s="4" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="N318" s="4"/>
       <c r="O318" s="4" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="R318" s="4" t="s">
         <v>55</v>
@@ -29082,10 +29084,10 @@
         <v>0</v>
       </c>
       <c r="U318" s="4" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="V318" s="4" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="W318" s="4">
         <v>1</v>
@@ -29095,7 +29097,7 @@
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="AA318" s="4"/>
       <c r="AB318" s="4" t="s">
@@ -29131,7 +29133,7 @@
         <v>37</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
@@ -29140,11 +29142,11 @@
       <c r="M319" s="4"/>
       <c r="N319" s="4"/>
       <c r="O319" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="R319" s="4" t="s">
         <v>43</v>
@@ -29156,7 +29158,7 @@
         <v>1</v>
       </c>
       <c r="U319" s="4" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="V319" s="4" t="s">
         <v>153</v>
@@ -29169,7 +29171,7 @@
       </c>
       <c r="Y319" s="4"/>
       <c r="Z319" s="4" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="AA319" s="4" t="s">
         <v>68</v>
@@ -29207,7 +29209,7 @@
         <v>37</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
@@ -29216,11 +29218,11 @@
       <c r="M320" s="4"/>
       <c r="N320" s="4"/>
       <c r="O320" s="4" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="R320" s="4" t="s">
         <v>43</v>
@@ -29279,7 +29281,7 @@
         <v>37</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
@@ -29288,11 +29290,11 @@
       <c r="M321" s="4"/>
       <c r="N321" s="4"/>
       <c r="O321" s="4" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="R321" s="4" t="s">
         <v>43</v>
@@ -29313,7 +29315,7 @@
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="AA321" s="4" t="s">
         <v>48</v>
@@ -29327,7 +29329,7 @@
         <v>1000</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C322" s="4">
         <v>167628474</v>
@@ -29351,7 +29353,7 @@
         <v>37</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
@@ -29360,11 +29362,11 @@
       <c r="M322" s="4"/>
       <c r="N322" s="4"/>
       <c r="O322" s="4" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="P322" s="5"/>
       <c r="Q322" s="4" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="R322" s="4" t="s">
         <v>43</v>
@@ -29376,10 +29378,10 @@
         <v>0</v>
       </c>
       <c r="U322" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="V322" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="W322" s="4">
         <v>4</v>
@@ -29403,7 +29405,7 @@
         <v>1000</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C323" s="4">
         <v>167628477</v>
@@ -29427,7 +29429,7 @@
         <v>37</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
@@ -29436,11 +29438,11 @@
       <c r="M323" s="4"/>
       <c r="N323" s="4"/>
       <c r="O323" s="4" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="R323" s="4" t="s">
         <v>43</v>
@@ -29452,7 +29454,7 @@
         <v>0</v>
       </c>
       <c r="U323" s="4" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="V323" s="4" t="s">
         <v>87</v>
@@ -29465,7 +29467,7 @@
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA323" s="4" t="s">
         <v>68</v>
@@ -29479,7 +29481,7 @@
         <v>1000</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C324" s="4">
         <v>167628478</v>
@@ -29503,7 +29505,7 @@
         <v>37</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
@@ -29512,11 +29514,11 @@
       <c r="M324" s="4"/>
       <c r="N324" s="4"/>
       <c r="O324" s="4" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="R324" s="4" t="s">
         <v>43</v>
@@ -29528,7 +29530,7 @@
         <v>0</v>
       </c>
       <c r="U324" s="4" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="V324" s="4" t="s">
         <v>359</v>
@@ -29541,7 +29543,7 @@
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
@@ -29553,7 +29555,7 @@
         <v>1000</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C325" s="4">
         <v>167628479</v>
@@ -29577,7 +29579,7 @@
         <v>37</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
@@ -29586,11 +29588,11 @@
       <c r="M325" s="4"/>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="R325" s="4" t="s">
         <v>75</v>
@@ -29602,7 +29604,7 @@
         <v>0</v>
       </c>
       <c r="U325" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="V325" s="4" t="s">
         <v>98</v>
@@ -29615,7 +29617,7 @@
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="AA325" s="4"/>
       <c r="AB325" s="4" t="s">
@@ -29627,7 +29629,7 @@
         <v>1000</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C326" s="4">
         <v>167628480</v>
@@ -29651,7 +29653,7 @@
         <v>37</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
@@ -29660,11 +29662,11 @@
       <c r="M326" s="4"/>
       <c r="N326" s="4"/>
       <c r="O326" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="R326" s="4" t="s">
         <v>43</v>
@@ -29676,7 +29678,7 @@
         <v>1</v>
       </c>
       <c r="U326" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="V326" s="4" t="s">
         <v>359</v>
@@ -29689,7 +29691,7 @@
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="AA326" s="4" t="s">
         <v>165</v>
@@ -29703,7 +29705,7 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C327" s="4">
         <v>167628483</v>
@@ -29727,7 +29729,7 @@
         <v>37</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
@@ -29736,11 +29738,11 @@
       <c r="M327" s="4"/>
       <c r="N327" s="4"/>
       <c r="O327" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="P327" s="5"/>
       <c r="Q327" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="R327" s="4" t="s">
         <v>43</v>
@@ -29752,7 +29754,7 @@
         <v>0</v>
       </c>
       <c r="U327" s="4" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="V327" s="4" t="s">
         <v>359</v>
@@ -29765,7 +29767,7 @@
       </c>
       <c r="Y327" s="4"/>
       <c r="Z327" s="4" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="AA327" s="4" t="s">
         <v>68</v>
@@ -29803,7 +29805,7 @@
         <v>37</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
@@ -29812,11 +29814,11 @@
       <c r="M328" s="4"/>
       <c r="N328" s="4"/>
       <c r="O328" s="4" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="R328" s="4" t="s">
         <v>43</v>
@@ -29828,10 +29830,10 @@
         <v>95</v>
       </c>
       <c r="U328" s="4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="V328" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="W328" s="4">
         <v>4</v>
@@ -29841,7 +29843,7 @@
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="AA328" s="4" t="s">
         <v>263</v>
@@ -29879,7 +29881,7 @@
         <v>37</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
@@ -29888,11 +29890,11 @@
       <c r="M329" s="4"/>
       <c r="N329" s="4"/>
       <c r="O329" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="R329" s="4" t="s">
         <v>43</v>
@@ -29913,7 +29915,7 @@
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="AA329" s="4" t="s">
         <v>48</v>
@@ -29951,7 +29953,7 @@
         <v>37</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
@@ -29960,11 +29962,11 @@
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="P330" s="5"/>
       <c r="Q330" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="R330" s="4" t="s">
         <v>43</v>
@@ -29985,7 +29987,7 @@
       </c>
       <c r="Y330" s="4"/>
       <c r="Z330" s="4" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="AA330" s="4"/>
       <c r="AB330" s="4" t="s">
@@ -30021,22 +30023,22 @@
         <v>37</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
         <v>337</v>
       </c>
       <c r="M331" s="4" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="N331" s="4"/>
       <c r="O331" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>75</v>
@@ -30095,22 +30097,22 @@
         <v>37</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="M332" s="4" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="N332" s="4"/>
       <c r="O332" s="4" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>43</v>
@@ -30122,10 +30124,10 @@
         <v>0</v>
       </c>
       <c r="U332" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="V332" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="W332" s="4">
         <v>4</v>
@@ -30135,7 +30137,7 @@
       </c>
       <c r="Y332" s="4"/>
       <c r="Z332" s="4" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="AA332" s="4" t="s">
         <v>48</v>
@@ -30173,22 +30175,22 @@
         <v>37</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="M333" s="4" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="N333" s="4"/>
       <c r="O333" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="R333" s="4" t="s">
         <v>43</v>
@@ -30200,7 +30202,7 @@
         <v>0</v>
       </c>
       <c r="U333" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="V333" s="4" t="s">
         <v>65</v>
@@ -30251,22 +30253,22 @@
         <v>37</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="M334" s="4" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="R334" s="4" t="s">
         <v>43</v>
@@ -30278,7 +30280,7 @@
         <v>0</v>
       </c>
       <c r="U334" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="V334" s="4" t="s">
         <v>98</v>
@@ -30291,7 +30293,7 @@
       </c>
       <c r="Y334" s="4"/>
       <c r="Z334" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA334" s="4" t="s">
         <v>68</v>
@@ -30329,24 +30331,24 @@
         <v>37</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="M335" s="4" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="N335" s="4">
         <v>38</v>
       </c>
       <c r="O335" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="P335" s="5"/>
       <c r="Q335" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="R335" s="4" t="s">
         <v>43</v>
@@ -30367,7 +30369,7 @@
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="AA335" s="4" t="s">
         <v>109</v>
@@ -30405,24 +30407,24 @@
         <v>37</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K336" s="4"/>
       <c r="L336" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="M336" s="4" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="N336" s="4">
         <v>38</v>
       </c>
       <c r="O336" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="R336" s="4" t="s">
         <v>43</v>
@@ -30434,7 +30436,7 @@
         <v>0</v>
       </c>
       <c r="U336" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="V336" s="4" t="s">
         <v>359</v>
@@ -30447,7 +30449,7 @@
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="AA336" s="4" t="s">
         <v>109</v>
@@ -30485,7 +30487,7 @@
         <v>37</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K337" s="4"/>
       <c r="L337" s="4" t="s">
@@ -30496,11 +30498,11 @@
       </c>
       <c r="N337" s="4"/>
       <c r="O337" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="R337" s="4" t="s">
         <v>43</v>
@@ -30521,7 +30523,7 @@
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="AA337" s="4" t="s">
         <v>68</v>
@@ -30541,7 +30543,7 @@
         <v>166811590</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E338" s="4">
         <v>8389358</v>
@@ -30559,18 +30561,18 @@
         <v>344</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="K338" s="4"/>
       <c r="L338" s="4"/>
       <c r="M338" s="4"/>
       <c r="N338" s="4"/>
       <c r="O338" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="R338" s="4" t="s">
         <v>132</v>
@@ -30591,7 +30593,7 @@
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="AA338" s="4"/>
       <c r="AB338" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>08/10/2026 a las 08:01:12</t>
+    <t>08/10/2026 a las 08:01:56</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>08/10/2026 a las 15:01:07</t>
+    <t>08/10/2026 a las 15:01:52</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>11/10/2026 a las 13:01:07</t>
+    <t>11/10/2026 a las 14:01:02</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>11/10/2026 a las 18:02:28</t>
+    <t>11/10/2026 a las 19:01:14</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>11/10/2026 a las 21:01:43</t>
+    <t>11/10/2026 a las 22:01:36</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>12/10/2026 a las 16:01:07</t>
+    <t>12/10/2026 a las 16:01:47</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1738">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 18:00:55</t>
+    <t>17/10/2026 a las 20:22:54</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -4136,18 +4136,6 @@
     <t>Revision Suministromedidor MD Analisis Macro 110-01-RevisionNormalizacion PCI-MAG Medidor manipuladoPuente</t>
   </si>
   <si>
-    <t>CL 29J1 CR 21D - 24</t>
-  </si>
-  <si>
-    <t>GOMEZ PALOMINO  SANDRA PATRICIA</t>
-  </si>
-  <si>
-    <t>119294-MC987</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD Analisis Macro 110-01-RevisionNormalizacion PCI-MAG Posible manipulaciÃ³n del medidor</t>
-  </si>
-  <si>
     <t>CR 21D1</t>
   </si>
   <si>
@@ -4671,18 +4659,6 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD Analisis Macro SUSPENSION AUTOSOPORTADA 110-01-RevisionNormalizacion PCI-MAG Acometida intervenida 3 Habitado con Energia Casa Acometida Intervenida Medidor Tipo 2 en fachada y Enrejado Red Trenzada en buen estado Brigada Pesada  3 Habitado con Energia Casa Acometida Intervenida Medidor T</t>
-  </si>
-  <si>
-    <t>CR 31A CL 26 - 42 APTO 4 F199</t>
-  </si>
-  <si>
-    <t>UBANDO  NIDIA</t>
-  </si>
-  <si>
-    <t>0000426546-MC957</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD Analisis Macro 110-01-RevisionNormalizacion PCI-MAG Medidor manipuladoPuente predio habitado con energia casa medidor tipo 1 red trenzada medidor con tapa principal maltratada sellos repisado brigada pesada  medidor con tapa principal maltratada sellos repisado</t>
   </si>
   <si>
     <t>CR 31B</t>
@@ -5646,7 +5622,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB375"/>
+  <dimension ref="A1:AB373"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -27142,16 +27118,16 @@
         <v>1000</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>420</v>
+        <v>917</v>
       </c>
       <c r="C289" s="4">
-        <v>169240190</v>
+        <v>169240208</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E289" s="4">
-        <v>4322109</v>
+        <v>6508453</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>49</v>
@@ -27173,17 +27149,17 @@
         <v>875</v>
       </c>
       <c r="M289" s="4" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="N289" s="4">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="O289" s="4" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="P289" s="5"/>
       <c r="Q289" s="4" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="R289" s="4" t="s">
         <v>61</v>
@@ -27194,23 +27170,21 @@
       <c r="T289" s="4">
         <v>0</v>
       </c>
-      <c r="U289" s="4" t="s">
-        <v>1375</v>
-      </c>
-      <c r="V289" s="4" t="s">
-        <v>1361</v>
-      </c>
+      <c r="U289" s="4"/>
+      <c r="V289" s="4"/>
       <c r="W289" s="4">
         <v>3</v>
       </c>
       <c r="X289" s="4" t="s">
-        <v>820</v>
+        <v>202</v>
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1376</v>
-      </c>
-      <c r="AA289" s="4"/>
+        <v>1334</v>
+      </c>
+      <c r="AA289" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB289" s="4" t="s">
         <v>47</v>
       </c>
@@ -27220,16 +27194,16 @@
         <v>1000</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>917</v>
+        <v>33</v>
       </c>
       <c r="C290" s="4">
-        <v>169240208</v>
+        <v>169240192</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E290" s="4">
-        <v>6508453</v>
+        <v>6568702</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>49</v>
@@ -27248,44 +27222,48 @@
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M290" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="M290" s="4" t="s">
+      <c r="N290" s="4">
+        <v>12</v>
+      </c>
+      <c r="O290" s="4" t="s">
         <v>1377</v>
-      </c>
-      <c r="N290" s="4">
-        <v>31</v>
-      </c>
-      <c r="O290" s="4" t="s">
-        <v>1378</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="R290" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S290" s="4">
+        <v>0</v>
+      </c>
+      <c r="T290" s="4">
+        <v>0</v>
+      </c>
+      <c r="U290" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="R290" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S290" s="4">
-        <v>0</v>
-      </c>
-      <c r="T290" s="4">
-        <v>0</v>
-      </c>
-      <c r="U290" s="4"/>
-      <c r="V290" s="4"/>
+      <c r="V290" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W290" s="4">
         <v>3</v>
       </c>
       <c r="X290" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y290" s="4"/>
       <c r="Z290" s="4" t="s">
-        <v>1334</v>
+        <v>1380</v>
       </c>
       <c r="AA290" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB290" s="4" t="s">
         <v>47</v>
@@ -27299,13 +27277,13 @@
         <v>33</v>
       </c>
       <c r="C291" s="4">
-        <v>169240192</v>
+        <v>169240194</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E291" s="4">
-        <v>6568702</v>
+        <v>6837112</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>49</v>
@@ -27324,13 +27302,13 @@
       </c>
       <c r="K291" s="4"/>
       <c r="L291" s="4" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>875</v>
       </c>
       <c r="N291" s="4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O291" s="4" t="s">
         <v>1381</v>
@@ -27340,7 +27318,7 @@
         <v>1382</v>
       </c>
       <c r="R291" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S291" s="4">
         <v>0</v>
@@ -27348,12 +27326,8 @@
       <c r="T291" s="4">
         <v>0</v>
       </c>
-      <c r="U291" s="4" t="s">
-        <v>1383</v>
-      </c>
-      <c r="V291" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U291" s="4"/>
+      <c r="V291" s="4"/>
       <c r="W291" s="4">
         <v>3</v>
       </c>
@@ -27362,7 +27336,7 @@
       </c>
       <c r="Y291" s="4"/>
       <c r="Z291" s="4" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="AA291" s="4" t="s">
         <v>65</v>
@@ -27376,16 +27350,16 @@
         <v>1000</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C292" s="4">
-        <v>169240194</v>
+        <v>169338674</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E292" s="4">
-        <v>6837112</v>
+        <v>8330993</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>49</v>
@@ -27400,49 +27374,41 @@
         <v>183</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1354</v>
+        <v>1383</v>
       </c>
       <c r="K292" s="4"/>
-      <c r="L292" s="4" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M292" s="4" t="s">
-        <v>875</v>
-      </c>
-      <c r="N292" s="4">
-        <v>4</v>
-      </c>
+      <c r="L292" s="4"/>
+      <c r="M292" s="4"/>
+      <c r="N292" s="4"/>
       <c r="O292" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="R292" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S292" s="4">
-        <v>0</v>
+        <v>93737.62</v>
       </c>
       <c r="T292" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U292" s="4"/>
       <c r="V292" s="4"/>
       <c r="W292" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X292" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y292" s="4"/>
       <c r="Z292" s="4" t="s">
-        <v>1384</v>
-      </c>
-      <c r="AA292" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1386</v>
+      </c>
+      <c r="AA292" s="4"/>
       <c r="AB292" s="4" t="s">
         <v>47</v>
       </c>
@@ -27452,16 +27418,16 @@
         <v>1000</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C293" s="4">
-        <v>169338674</v>
+        <v>169528013</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E293" s="4">
-        <v>8330993</v>
+        <v>7815930</v>
       </c>
       <c r="F293" s="4" t="s">
         <v>49</v>
@@ -27479,9 +27445,13 @@
         <v>1387</v>
       </c>
       <c r="K293" s="4"/>
-      <c r="L293" s="4"/>
+      <c r="L293" s="4" t="s">
+        <v>516</v>
+      </c>
       <c r="M293" s="4"/>
-      <c r="N293" s="4"/>
+      <c r="N293" s="4">
+        <v>25</v>
+      </c>
       <c r="O293" s="4" t="s">
         <v>1388</v>
       </c>
@@ -27493,24 +27463,26 @@
         <v>61</v>
       </c>
       <c r="S293" s="4">
-        <v>93737.62</v>
+        <v>0</v>
       </c>
       <c r="T293" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U293" s="4"/>
       <c r="V293" s="4"/>
       <c r="W293" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X293" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y293" s="4"/>
       <c r="Z293" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="AA293" s="4"/>
+      <c r="AA293" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB293" s="4" t="s">
         <v>47</v>
       </c>
@@ -27520,16 +27492,16 @@
         <v>1000</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>33</v>
+        <v>1059</v>
       </c>
       <c r="C294" s="4">
-        <v>169528013</v>
+        <v>169355860</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E294" s="4">
-        <v>7815930</v>
+        <v>7063828</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>49</v>
@@ -27547,13 +27519,9 @@
         <v>1391</v>
       </c>
       <c r="K294" s="4"/>
-      <c r="L294" s="4" t="s">
-        <v>516</v>
-      </c>
+      <c r="L294" s="4"/>
       <c r="M294" s="4"/>
-      <c r="N294" s="4">
-        <v>25</v>
-      </c>
+      <c r="N294" s="4"/>
       <c r="O294" s="4" t="s">
         <v>1392</v>
       </c>
@@ -27562,28 +27530,28 @@
         <v>1393</v>
       </c>
       <c r="R294" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S294" s="4">
-        <v>0</v>
+        <v>99693.64999999999</v>
       </c>
       <c r="T294" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U294" s="4"/>
       <c r="V294" s="4"/>
       <c r="W294" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X294" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y294" s="4"/>
       <c r="Z294" s="4" t="s">
-        <v>1394</v>
+        <v>287</v>
       </c>
       <c r="AA294" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB294" s="4" t="s">
         <v>47</v>
@@ -27597,13 +27565,13 @@
         <v>1059</v>
       </c>
       <c r="C295" s="4">
-        <v>169355860</v>
+        <v>169355855</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E295" s="4">
-        <v>7063828</v>
+        <v>5883241</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>49</v>
@@ -27618,27 +27586,29 @@
         <v>183</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="K295" s="4"/>
-      <c r="L295" s="4"/>
+      <c r="L295" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
       <c r="O295" s="4" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S295" s="4">
-        <v>99693.64999999999</v>
+        <v>179936.31</v>
       </c>
       <c r="T295" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U295" s="4"/>
       <c r="V295" s="4"/>
@@ -27650,10 +27620,10 @@
       </c>
       <c r="Y295" s="4"/>
       <c r="Z295" s="4" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="AA295" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB295" s="4" t="s">
         <v>47</v>
@@ -27664,16 +27634,16 @@
         <v>1000</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>1059</v>
+        <v>222</v>
       </c>
       <c r="C296" s="4">
-        <v>169355855</v>
+        <v>169359076</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E296" s="4">
-        <v>5883241</v>
+        <v>6989239</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>49</v>
@@ -27688,29 +27658,29 @@
         <v>183</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
-        <v>289</v>
+        <v>1343</v>
       </c>
       <c r="M296" s="4"/>
       <c r="N296" s="4"/>
       <c r="O296" s="4" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S296" s="4">
-        <v>179936.31</v>
+        <v>0</v>
       </c>
       <c r="T296" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
@@ -27722,10 +27692,10 @@
       </c>
       <c r="Y296" s="4"/>
       <c r="Z296" s="4" t="s">
-        <v>403</v>
+        <v>1398</v>
       </c>
       <c r="AA296" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB296" s="4" t="s">
         <v>47</v>
@@ -27736,16 +27706,16 @@
         <v>1000</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C297" s="4">
-        <v>169359076</v>
+        <v>169475694</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E297" s="4">
-        <v>6989239</v>
+        <v>7353382</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>49</v>
@@ -27760,7 +27730,7 @@
         <v>183</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
@@ -27769,11 +27739,11 @@
       <c r="M297" s="4"/>
       <c r="N297" s="4"/>
       <c r="O297" s="4" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>79</v>
@@ -27787,17 +27757,17 @@
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
       <c r="W297" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X297" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="AA297" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB297" s="4" t="s">
         <v>47</v>
@@ -27808,16 +27778,16 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>246</v>
+        <v>1402</v>
       </c>
       <c r="C298" s="4">
-        <v>169475694</v>
+        <v>168725316</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E298" s="4">
-        <v>7353382</v>
+        <v>1099225</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>49</v>
@@ -27832,44 +27802,50 @@
         <v>183</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>1343</v>
-      </c>
-      <c r="M298" s="4"/>
+        <v>1404</v>
+      </c>
+      <c r="M298" s="4" t="s">
+        <v>1405</v>
+      </c>
       <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="R298" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S298" s="4">
-        <v>0</v>
+        <v>724798.47</v>
       </c>
       <c r="T298" s="4">
-        <v>0</v>
-      </c>
-      <c r="U298" s="4"/>
-      <c r="V298" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U298" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V298" s="4" t="s">
+        <v>1409</v>
+      </c>
       <c r="W298" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X298" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>1405</v>
+        <v>1269</v>
       </c>
       <c r="AA298" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB298" s="4" t="s">
         <v>47</v>
@@ -27880,13 +27856,13 @@
         <v>1000</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>1406</v>
+        <v>33</v>
       </c>
       <c r="C299" s="4">
-        <v>168725316</v>
+        <v>169523105</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E299" s="4">
         <v>1099225</v>
@@ -27904,47 +27880,47 @@
         <v>183</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="M299" s="4" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="N299" s="4"/>
       <c r="O299" s="4" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S299" s="4">
-        <v>724798.47</v>
+        <v>364931.37</v>
       </c>
       <c r="T299" s="4">
         <v>3</v>
       </c>
       <c r="U299" s="4" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="V299" s="4" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="W299" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X299" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y299" s="4"/>
       <c r="Z299" s="4" t="s">
-        <v>1269</v>
+        <v>1410</v>
       </c>
       <c r="AA299" s="4" t="s">
         <v>65</v>
@@ -27958,16 +27934,16 @@
         <v>1000</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C300" s="4">
-        <v>169523105</v>
+        <v>169228645</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E300" s="4">
-        <v>1099225</v>
+        <v>8388337</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>49</v>
@@ -27982,53 +27958,43 @@
         <v>183</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K300" s="4"/>
-      <c r="L300" s="4" t="s">
-        <v>1408</v>
-      </c>
-      <c r="M300" s="4" t="s">
-        <v>1409</v>
-      </c>
+      <c r="L300" s="4"/>
+      <c r="M300" s="4"/>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="R300" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S300" s="4">
-        <v>364931.37</v>
+        <v>0</v>
       </c>
       <c r="T300" s="4">
+        <v>0</v>
+      </c>
+      <c r="U300" s="4"/>
+      <c r="V300" s="4"/>
+      <c r="W300" s="4">
         <v>3</v>
       </c>
-      <c r="U300" s="4" t="s">
-        <v>1412</v>
-      </c>
-      <c r="V300" s="4" t="s">
-        <v>1413</v>
-      </c>
-      <c r="W300" s="4">
-        <v>0</v>
-      </c>
       <c r="X300" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="AA300" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA300" s="4"/>
       <c r="AB300" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="301" spans="1:28">
@@ -28036,16 +28002,16 @@
         <v>1000</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
       <c r="C301" s="4">
-        <v>169228645</v>
+        <v>169348751</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E301" s="4">
-        <v>8388337</v>
+        <v>7936320</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>49</v>
@@ -28060,32 +28026,38 @@
         <v>183</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="K301" s="4"/>
-      <c r="L301" s="4"/>
+      <c r="L301" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
       <c r="O301" s="4" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="R301" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S301" s="4">
+        <v>0</v>
+      </c>
+      <c r="T301" s="4">
+        <v>0</v>
+      </c>
+      <c r="U301" s="4" t="s">
         <v>1417</v>
       </c>
-      <c r="R301" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S301" s="4">
-        <v>0</v>
-      </c>
-      <c r="T301" s="4">
-        <v>0</v>
-      </c>
-      <c r="U301" s="4"/>
-      <c r="V301" s="4"/>
+      <c r="V301" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W301" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X301" s="4" t="s">
         <v>202</v>
@@ -28096,7 +28068,7 @@
       </c>
       <c r="AA301" s="4"/>
       <c r="AB301" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="302" spans="1:28">
@@ -28104,16 +28076,16 @@
         <v>1000</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C302" s="4">
-        <v>169348751</v>
+        <v>169528466</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E302" s="4">
-        <v>7936320</v>
+        <v>1116215</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>49</v>
@@ -28128,13 +28100,15 @@
         <v>183</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M302" s="4"/>
+        <v>284</v>
+      </c>
+      <c r="M302" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="N302" s="4"/>
       <c r="O302" s="4" t="s">
         <v>1419</v>
@@ -28144,7 +28118,7 @@
         <v>1420</v>
       </c>
       <c r="R302" s="4" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S302" s="4">
         <v>0</v>
@@ -28156,17 +28130,17 @@
         <v>1421</v>
       </c>
       <c r="V302" s="4" t="s">
-        <v>69</v>
+        <v>1422</v>
       </c>
       <c r="W302" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X302" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="AA302" s="4"/>
       <c r="AB302" s="4" t="s">
@@ -28178,16 +28152,16 @@
         <v>1000</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C303" s="4">
-        <v>169528466</v>
+        <v>168897696</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E303" s="4">
-        <v>1116215</v>
+        <v>8305739</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>49</v>
@@ -28202,49 +28176,49 @@
         <v>183</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4" t="s">
-        <v>284</v>
+        <v>880</v>
       </c>
       <c r="M303" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="N303" s="4"/>
+        <v>982</v>
+      </c>
+      <c r="N303" s="4">
+        <v>101</v>
+      </c>
       <c r="O303" s="4" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="R303" s="4" t="s">
-        <v>257</v>
+        <v>61</v>
       </c>
       <c r="S303" s="4">
-        <v>0</v>
+        <v>184614.72</v>
       </c>
       <c r="T303" s="4">
-        <v>0</v>
-      </c>
-      <c r="U303" s="4" t="s">
-        <v>1425</v>
-      </c>
-      <c r="V303" s="4" t="s">
-        <v>1426</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U303" s="4"/>
+      <c r="V303" s="4"/>
       <c r="W303" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X303" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="AA303" s="4"/>
+        <v>1426</v>
+      </c>
+      <c r="AA303" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="AB303" s="4" t="s">
         <v>47</v>
       </c>
@@ -28254,16 +28228,16 @@
         <v>1000</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="C304" s="4">
-        <v>168897696</v>
+        <v>169525511</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E304" s="4">
-        <v>8305739</v>
+        <v>8305779</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>49</v>
@@ -28278,7 +28252,7 @@
         <v>183</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
@@ -28291,32 +28265,32 @@
         <v>101</v>
       </c>
       <c r="O304" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S304" s="4">
-        <v>184614.72</v>
+        <v>54320.17</v>
       </c>
       <c r="T304" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U304" s="4"/>
       <c r="V304" s="4"/>
       <c r="W304" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X304" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y304" s="4"/>
       <c r="Z304" s="4" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="AA304" s="4" t="s">
         <v>305</v>
@@ -28333,13 +28307,13 @@
         <v>33</v>
       </c>
       <c r="C305" s="4">
-        <v>169525511</v>
+        <v>169525177</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>188</v>
+        <v>471</v>
       </c>
       <c r="E305" s="4">
-        <v>8305779</v>
+        <v>8289365</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>49</v>
@@ -28354,33 +28328,33 @@
         <v>183</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1415</v>
+        <v>1430</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
-        <v>880</v>
+        <v>1431</v>
       </c>
       <c r="M305" s="4" t="s">
-        <v>982</v>
+        <v>1432</v>
       </c>
       <c r="N305" s="4">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="O305" s="4" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="R305" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S305" s="4">
-        <v>54320.17</v>
+        <v>469783.86</v>
       </c>
       <c r="T305" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U305" s="4"/>
       <c r="V305" s="4"/>
@@ -28392,13 +28366,13 @@
       </c>
       <c r="Y305" s="4"/>
       <c r="Z305" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="AA305" s="4" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="AB305" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="306" spans="1:28">
@@ -28406,16 +28380,16 @@
         <v>1000</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="C306" s="4">
-        <v>169525177</v>
+        <v>168896160</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>471</v>
+        <v>57</v>
       </c>
       <c r="E306" s="4">
-        <v>8289365</v>
+        <v>5920990</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>49</v>
@@ -28430,51 +28404,55 @@
         <v>183</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="M306" s="4" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="N306" s="4">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="R306" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S306" s="4">
-        <v>469783.86</v>
+        <v>181369.34</v>
       </c>
       <c r="T306" s="4">
-        <v>4</v>
-      </c>
-      <c r="U306" s="4"/>
-      <c r="V306" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U306" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="V306" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W306" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X306" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y306" s="4"/>
       <c r="Z306" s="4" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="AA306" s="4" t="s">
-        <v>46</v>
+        <v>1443</v>
       </c>
       <c r="AB306" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="307" spans="1:28">
@@ -28482,16 +28460,16 @@
         <v>1000</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>420</v>
+        <v>337</v>
       </c>
       <c r="C307" s="4">
-        <v>168896160</v>
+        <v>169365038</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E307" s="4">
-        <v>5920990</v>
+        <v>6591932</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>49</v>
@@ -28506,52 +28484,52 @@
         <v>183</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="M307" s="4" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="N307" s="4">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S307" s="4">
-        <v>181369.34</v>
+        <v>0</v>
       </c>
       <c r="T307" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U307" s="4" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="V307" s="4" t="s">
-        <v>476</v>
+        <v>43</v>
       </c>
       <c r="W307" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X307" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="AA307" s="4" t="s">
-        <v>1447</v>
+        <v>46</v>
       </c>
       <c r="AB307" s="4" t="s">
         <v>47</v>
@@ -28562,16 +28540,16 @@
         <v>1000</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C308" s="4">
-        <v>169365038</v>
+        <v>169240239</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E308" s="4">
-        <v>6591932</v>
+        <v>7735512</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>49</v>
@@ -28586,17 +28564,17 @@
         <v>183</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
-        <v>1448</v>
+        <v>107</v>
       </c>
       <c r="M308" s="4" t="s">
-        <v>1449</v>
+        <v>875</v>
       </c>
       <c r="N308" s="4">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="O308" s="4" t="s">
         <v>1450</v>
@@ -28614,21 +28592,17 @@
       <c r="T308" s="4">
         <v>0</v>
       </c>
-      <c r="U308" s="4" t="s">
-        <v>1452</v>
-      </c>
-      <c r="V308" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="U308" s="4"/>
+      <c r="V308" s="4"/>
       <c r="W308" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X308" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="AA308" s="4" t="s">
         <v>46</v>
@@ -28645,13 +28619,13 @@
         <v>352</v>
       </c>
       <c r="C309" s="4">
-        <v>169240239</v>
+        <v>169240240</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E309" s="4">
-        <v>7735512</v>
+        <v>6588082</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>49</v>
@@ -28666,7 +28640,7 @@
         <v>183</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
@@ -28679,11 +28653,11 @@
         <v>58</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="R309" s="4" t="s">
         <v>61</v>
@@ -28704,10 +28678,10 @@
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="AA309" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB309" s="4" t="s">
         <v>47</v>
@@ -28721,13 +28695,13 @@
         <v>352</v>
       </c>
       <c r="C310" s="4">
-        <v>169240240</v>
+        <v>169240182</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E310" s="4">
-        <v>6588082</v>
+        <v>5878950</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>49</v>
@@ -28742,7 +28716,7 @@
         <v>183</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -28752,17 +28726,17 @@
         <v>875</v>
       </c>
       <c r="N310" s="4">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="S310" s="4">
         <v>0</v>
@@ -28780,10 +28754,10 @@
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="AA310" s="4" t="s">
-        <v>65</v>
+        <v>351</v>
       </c>
       <c r="AB310" s="4" t="s">
         <v>47</v>
@@ -28794,16 +28768,16 @@
         <v>1000</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>352</v>
+        <v>1331</v>
       </c>
       <c r="C311" s="4">
-        <v>169240182</v>
+        <v>169240231</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E311" s="4">
-        <v>5878950</v>
+        <v>8026082</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>49</v>
@@ -28818,17 +28792,17 @@
         <v>183</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
-        <v>107</v>
+        <v>1175</v>
       </c>
       <c r="M311" s="4" t="s">
-        <v>875</v>
+        <v>1458</v>
       </c>
       <c r="N311" s="4">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="O311" s="4" t="s">
         <v>1459</v>
@@ -28838,7 +28812,7 @@
         <v>1460</v>
       </c>
       <c r="R311" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S311" s="4">
         <v>0</v>
@@ -28859,7 +28833,7 @@
         <v>1461</v>
       </c>
       <c r="AA311" s="4" t="s">
-        <v>351</v>
+        <v>46</v>
       </c>
       <c r="AB311" s="4" t="s">
         <v>47</v>
@@ -28870,16 +28844,16 @@
         <v>1000</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1331</v>
+        <v>33</v>
       </c>
       <c r="C312" s="4">
-        <v>169240231</v>
+        <v>168896205</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E312" s="4">
-        <v>8026082</v>
+        <v>6530459</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>49</v>
@@ -28894,24 +28868,24 @@
         <v>183</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>1175</v>
+        <v>874</v>
       </c>
       <c r="M312" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="N312" s="4">
+        <v>105</v>
+      </c>
+      <c r="O312" s="4" t="s">
         <v>1462</v>
-      </c>
-      <c r="N312" s="4">
-        <v>6</v>
-      </c>
-      <c r="O312" s="4" t="s">
-        <v>1463</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>61</v>
@@ -28922,13 +28896,17 @@
       <c r="T312" s="4">
         <v>0</v>
       </c>
-      <c r="U312" s="4"/>
-      <c r="V312" s="4"/>
+      <c r="U312" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="V312" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W312" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X312" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
@@ -28946,16 +28924,16 @@
         <v>1000</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>33</v>
+        <v>1331</v>
       </c>
       <c r="C313" s="4">
-        <v>168896205</v>
+        <v>169240188</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E313" s="4">
-        <v>6530459</v>
+        <v>6567408</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>49</v>
@@ -28970,24 +28948,24 @@
         <v>183</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>874</v>
+        <v>1438</v>
       </c>
       <c r="M313" s="4" t="s">
-        <v>875</v>
+        <v>1466</v>
       </c>
       <c r="N313" s="4">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="O313" s="4" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="R313" s="4" t="s">
         <v>61</v>
@@ -28999,24 +28977,22 @@
         <v>0</v>
       </c>
       <c r="U313" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="V313" s="4" t="s">
-        <v>476</v>
+        <v>1470</v>
       </c>
       <c r="W313" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X313" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
-        <v>1469</v>
-      </c>
-      <c r="AA313" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1471</v>
+      </c>
+      <c r="AA313" s="4"/>
       <c r="AB313" s="4" t="s">
         <v>47</v>
       </c>
@@ -29026,16 +29002,16 @@
         <v>1000</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1331</v>
+        <v>33</v>
       </c>
       <c r="C314" s="4">
-        <v>169240188</v>
+        <v>169528015</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E314" s="4">
-        <v>6567408</v>
+        <v>7609168</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>49</v>
@@ -29050,24 +29026,24 @@
         <v>183</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1440</v>
+        <v>1472</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>1442</v>
+        <v>949</v>
       </c>
       <c r="M314" s="4" t="s">
-        <v>1470</v>
+        <v>749</v>
       </c>
       <c r="N314" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O314" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>61</v>
@@ -29078,23 +29054,21 @@
       <c r="T314" s="4">
         <v>0</v>
       </c>
-      <c r="U314" s="4" t="s">
-        <v>1473</v>
-      </c>
-      <c r="V314" s="4" t="s">
-        <v>1474</v>
-      </c>
+      <c r="U314" s="4"/>
+      <c r="V314" s="4"/>
       <c r="W314" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X314" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
         <v>1475</v>
       </c>
-      <c r="AA314" s="4"/>
+      <c r="AA314" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB314" s="4" t="s">
         <v>47</v>
       </c>
@@ -29104,16 +29078,16 @@
         <v>1000</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>33</v>
+        <v>1402</v>
       </c>
       <c r="C315" s="4">
-        <v>169528015</v>
+        <v>168725318</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E315" s="4">
-        <v>7609168</v>
+        <v>7378230</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>49</v>
@@ -29132,44 +29106,48 @@
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
-        <v>949</v>
+        <v>1477</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>749</v>
+        <v>1478</v>
       </c>
       <c r="N315" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O315" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="R315" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S315" s="4">
-        <v>0</v>
+        <v>736214.27</v>
       </c>
       <c r="T315" s="4">
-        <v>0</v>
-      </c>
-      <c r="U315" s="4"/>
-      <c r="V315" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="U315" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="V315" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W315" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X315" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y315" s="4"/>
       <c r="Z315" s="4" t="s">
-        <v>1479</v>
+        <v>592</v>
       </c>
       <c r="AA315" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB315" s="4" t="s">
         <v>47</v>
@@ -29180,16 +29158,16 @@
         <v>1000</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1406</v>
+        <v>246</v>
       </c>
       <c r="C316" s="4">
-        <v>168725318</v>
+        <v>169350529</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E316" s="4">
-        <v>7378230</v>
+        <v>6817697</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>49</v>
@@ -29204,18 +29182,14 @@
         <v>183</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>1481</v>
-      </c>
-      <c r="M316" s="4" t="s">
-        <v>1482</v>
-      </c>
-      <c r="N316" s="4">
-        <v>17</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M316" s="4"/>
+      <c r="N316" s="4"/>
       <c r="O316" s="4" t="s">
         <v>1483</v>
       </c>
@@ -29224,29 +29198,25 @@
         <v>1484</v>
       </c>
       <c r="R316" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S316" s="4">
-        <v>736214.27</v>
+        <v>0</v>
       </c>
       <c r="T316" s="4">
-        <v>6</v>
-      </c>
-      <c r="U316" s="4" t="s">
-        <v>1485</v>
-      </c>
-      <c r="V316" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U316" s="4"/>
+      <c r="V316" s="4"/>
       <c r="W316" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X316" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>592</v>
+        <v>1485</v>
       </c>
       <c r="AA316" s="4" t="s">
         <v>46</v>
@@ -29260,16 +29230,16 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>246</v>
+        <v>447</v>
       </c>
       <c r="C317" s="4">
-        <v>169350529</v>
+        <v>168910101</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E317" s="4">
-        <v>6817697</v>
+        <v>8307826</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>49</v>
@@ -29287,9 +29257,7 @@
         <v>1486</v>
       </c>
       <c r="K317" s="4"/>
-      <c r="L317" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L317" s="4"/>
       <c r="M317" s="4"/>
       <c r="N317" s="4"/>
       <c r="O317" s="4" t="s">
@@ -29300,7 +29268,7 @@
         <v>1488</v>
       </c>
       <c r="R317" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S317" s="4">
         <v>0</v>
@@ -29311,7 +29279,7 @@
       <c r="U317" s="4"/>
       <c r="V317" s="4"/>
       <c r="W317" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X317" s="4" t="s">
         <v>202</v>
@@ -29321,7 +29289,7 @@
         <v>1489</v>
       </c>
       <c r="AA317" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB317" s="4" t="s">
         <v>47</v>
@@ -29335,13 +29303,13 @@
         <v>447</v>
       </c>
       <c r="C318" s="4">
-        <v>168910101</v>
+        <v>168908257</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>188</v>
+        <v>580</v>
       </c>
       <c r="E318" s="4">
-        <v>8307826</v>
+        <v>6945604</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>49</v>
@@ -29356,30 +29324,36 @@
         <v>183</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="K318" s="4"/>
-      <c r="L318" s="4"/>
+      <c r="L318" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
       <c r="O318" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
+        <v>1491</v>
+      </c>
+      <c r="R318" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S318" s="4">
+        <v>0</v>
+      </c>
+      <c r="T318" s="4">
+        <v>0</v>
+      </c>
+      <c r="U318" s="4" t="s">
         <v>1492</v>
       </c>
-      <c r="R318" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S318" s="4">
-        <v>0</v>
-      </c>
-      <c r="T318" s="4">
-        <v>0</v>
-      </c>
-      <c r="U318" s="4"/>
-      <c r="V318" s="4"/>
+      <c r="V318" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W318" s="4">
         <v>7</v>
       </c>
@@ -29391,7 +29365,7 @@
         <v>1493</v>
       </c>
       <c r="AA318" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB318" s="4" t="s">
         <v>47</v>
@@ -29402,16 +29376,16 @@
         <v>1000</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="C319" s="4">
-        <v>168908257</v>
+        <v>169517835</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>580</v>
+        <v>471</v>
       </c>
       <c r="E319" s="4">
-        <v>6945604</v>
+        <v>7666029</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>49</v>
@@ -29426,45 +29400,49 @@
         <v>183</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M319" s="4"/>
-      <c r="N319" s="4"/>
+        <v>1494</v>
+      </c>
+      <c r="M319" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="N319" s="4">
+        <v>19</v>
+      </c>
       <c r="O319" s="4" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="R319" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S319" s="4">
-        <v>0</v>
+        <v>65879.17999999999</v>
       </c>
       <c r="T319" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U319" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="V319" s="4" t="s">
         <v>476</v>
       </c>
       <c r="W319" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X319" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y319" s="4"/>
       <c r="Z319" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="AA319" s="4" t="s">
         <v>46</v>
@@ -29481,13 +29459,13 @@
         <v>33</v>
       </c>
       <c r="C320" s="4">
-        <v>169517835</v>
+        <v>169531384</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="E320" s="4">
-        <v>7666029</v>
+        <v>7770159</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>49</v>
@@ -29502,36 +29480,36 @@
         <v>183</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
-        <v>1498</v>
+        <v>712</v>
       </c>
       <c r="M320" s="4" t="s">
-        <v>712</v>
+        <v>1499</v>
       </c>
       <c r="N320" s="4">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O320" s="4" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="R320" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S320" s="4">
-        <v>65879.17999999999</v>
+        <v>398662.86</v>
       </c>
       <c r="T320" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U320" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="V320" s="4" t="s">
         <v>476</v>
@@ -29544,13 +29522,13 @@
       </c>
       <c r="Y320" s="4"/>
       <c r="Z320" s="4" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="AA320" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB320" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="321" spans="1:28">
@@ -29558,16 +29536,16 @@
         <v>1000</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C321" s="4">
-        <v>169531384</v>
+        <v>169351859</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E321" s="4">
-        <v>7770159</v>
+        <v>6824154</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>49</v>
@@ -29582,17 +29560,17 @@
         <v>183</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>712</v>
+        <v>354</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>1503</v>
+        <v>516</v>
       </c>
       <c r="N321" s="4">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="O321" s="4" t="s">
         <v>1504</v>
@@ -29602,35 +29580,31 @@
         <v>1505</v>
       </c>
       <c r="R321" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S321" s="4">
-        <v>398662.86</v>
+        <v>0</v>
       </c>
       <c r="T321" s="4">
-        <v>5</v>
-      </c>
-      <c r="U321" s="4" t="s">
-        <v>1506</v>
-      </c>
-      <c r="V321" s="4" t="s">
-        <v>476</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U321" s="4"/>
+      <c r="V321" s="4"/>
       <c r="W321" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X321" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="AA321" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB321" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="322" spans="1:28">
@@ -29638,16 +29612,16 @@
         <v>1000</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C322" s="4">
-        <v>169351859</v>
+        <v>169521367</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>188</v>
+        <v>471</v>
       </c>
       <c r="E322" s="4">
-        <v>6824154</v>
+        <v>7984315</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>49</v>
@@ -29662,18 +29636,14 @@
         <v>183</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1490</v>
+        <v>1507</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="M322" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="N322" s="4">
-        <v>12</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M322" s="4"/>
+      <c r="N322" s="4"/>
       <c r="O322" s="4" t="s">
         <v>1508</v>
       </c>
@@ -29685,18 +29655,18 @@
         <v>61</v>
       </c>
       <c r="S322" s="4">
-        <v>0</v>
+        <v>807922.91</v>
       </c>
       <c r="T322" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U322" s="4"/>
       <c r="V322" s="4"/>
       <c r="W322" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X322" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y322" s="4"/>
       <c r="Z322" s="4" t="s">
@@ -29714,16 +29684,16 @@
         <v>1000</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>33</v>
+        <v>1293</v>
       </c>
       <c r="C323" s="4">
-        <v>169521367</v>
+        <v>169355862</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>471</v>
+        <v>57</v>
       </c>
       <c r="E323" s="4">
-        <v>7984315</v>
+        <v>1025722</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>49</v>
@@ -29738,13 +29708,15 @@
         <v>183</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M323" s="4"/>
+      <c r="M323" s="4" t="s">
+        <v>1511</v>
+      </c>
       <c r="N323" s="4"/>
       <c r="O323" s="4" t="s">
         <v>1512</v>
@@ -29757,26 +29729,28 @@
         <v>61</v>
       </c>
       <c r="S323" s="4">
-        <v>807922.91</v>
+        <v>0</v>
       </c>
       <c r="T323" s="4">
-        <v>4</v>
-      </c>
-      <c r="U323" s="4"/>
-      <c r="V323" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U323" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="V323" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W323" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X323" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>1514</v>
-      </c>
-      <c r="AA323" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="AA323" s="4"/>
       <c r="AB323" s="4" t="s">
         <v>47</v>
       </c>
@@ -29786,16 +29760,16 @@
         <v>1000</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1293</v>
+        <v>33</v>
       </c>
       <c r="C324" s="4">
-        <v>169355862</v>
+        <v>168895978</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E324" s="4">
-        <v>1025722</v>
+        <v>1052361</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>49</v>
@@ -29810,25 +29784,25 @@
         <v>183</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
-        <v>289</v>
+        <v>177</v>
       </c>
       <c r="M324" s="4" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="N324" s="4"/>
       <c r="O324" s="4" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="R324" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S324" s="4">
         <v>0</v>
@@ -29837,20 +29811,20 @@
         <v>0</v>
       </c>
       <c r="U324" s="4" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="V324" s="4" t="s">
-        <v>127</v>
+        <v>1520</v>
       </c>
       <c r="W324" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X324" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>671</v>
+        <v>1521</v>
       </c>
       <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
@@ -29862,16 +29836,16 @@
         <v>1000</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>33</v>
+        <v>1522</v>
       </c>
       <c r="C325" s="4">
-        <v>168895978</v>
+        <v>168896121</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E325" s="4">
-        <v>1052361</v>
+        <v>1052274</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>49</v>
@@ -29886,22 +29860,22 @@
         <v>183</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
-        <v>177</v>
+        <v>1523</v>
       </c>
       <c r="M325" s="4" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="R325" s="4" t="s">
         <v>41</v>
@@ -29913,20 +29887,20 @@
         <v>0</v>
       </c>
       <c r="U325" s="4" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="V325" s="4" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="W325" s="4">
         <v>8</v>
       </c>
       <c r="X325" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="AA325" s="4"/>
       <c r="AB325" s="4" t="s">
@@ -29938,16 +29912,16 @@
         <v>1000</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="C326" s="4">
-        <v>168896121</v>
+        <v>169240252</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E326" s="4">
-        <v>1052274</v>
+        <v>1051677</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>49</v>
@@ -29962,25 +29936,25 @@
         <v>183</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>1527</v>
+        <v>320</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>1528</v>
+        <v>299</v>
       </c>
       <c r="N326" s="4"/>
       <c r="O326" s="4" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="R326" s="4" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S326" s="4">
         <v>0</v>
@@ -29989,13 +29963,13 @@
         <v>0</v>
       </c>
       <c r="U326" s="4" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="V326" s="4" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="W326" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X326" s="4" t="s">
         <v>202</v>
@@ -30004,7 +29978,9 @@
       <c r="Z326" s="4" t="s">
         <v>1533</v>
       </c>
-      <c r="AA326" s="4"/>
+      <c r="AA326" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB326" s="4" t="s">
         <v>47</v>
       </c>
@@ -30014,16 +29990,16 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="C327" s="4">
-        <v>169240252</v>
+        <v>168896063</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E327" s="4">
-        <v>1051677</v>
+        <v>1103901</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>49</v>
@@ -30038,14 +30014,14 @@
         <v>183</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
         <v>320</v>
       </c>
       <c r="M327" s="4" t="s">
-        <v>299</v>
+        <v>791</v>
       </c>
       <c r="N327" s="4"/>
       <c r="O327" s="4" t="s">
@@ -30056,7 +30032,7 @@
         <v>1535</v>
       </c>
       <c r="R327" s="4" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="S327" s="4">
         <v>0</v>
@@ -30068,17 +30044,17 @@
         <v>1536</v>
       </c>
       <c r="V327" s="4" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="W327" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y327" s="4"/>
       <c r="Z327" s="4" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="AA327" s="4" t="s">
         <v>46</v>
@@ -30092,16 +30068,16 @@
         <v>1000</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1526</v>
+        <v>455</v>
       </c>
       <c r="C328" s="4">
-        <v>168896063</v>
+        <v>168896653</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E328" s="4">
-        <v>1103901</v>
+        <v>1052622</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>49</v>
@@ -30116,22 +30092,22 @@
         <v>183</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
-        <v>320</v>
+        <v>1539</v>
       </c>
       <c r="M328" s="4" t="s">
-        <v>791</v>
+        <v>1523</v>
       </c>
       <c r="N328" s="4"/>
       <c r="O328" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="R328" s="4" t="s">
         <v>41</v>
@@ -30142,12 +30118,8 @@
       <c r="T328" s="4">
         <v>0</v>
       </c>
-      <c r="U328" s="4" t="s">
-        <v>1540</v>
-      </c>
-      <c r="V328" s="4" t="s">
-        <v>1541</v>
-      </c>
+      <c r="U328" s="4"/>
+      <c r="V328" s="4"/>
       <c r="W328" s="4">
         <v>8</v>
       </c>
@@ -30159,7 +30131,7 @@
         <v>1542</v>
       </c>
       <c r="AA328" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB328" s="4" t="s">
         <v>47</v>
@@ -30170,16 +30142,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>455</v>
+        <v>1522</v>
       </c>
       <c r="C329" s="4">
-        <v>168896653</v>
+        <v>168896015</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E329" s="4">
-        <v>1052622</v>
+        <v>7900282</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>49</v>
@@ -30194,14 +30166,14 @@
         <v>183</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
         <v>1543</v>
       </c>
       <c r="M329" s="4" t="s">
-        <v>1527</v>
+        <v>177</v>
       </c>
       <c r="N329" s="4"/>
       <c r="O329" s="4" t="s">
@@ -30215,13 +30187,17 @@
         <v>41</v>
       </c>
       <c r="S329" s="4">
-        <v>0</v>
+        <v>127746.05</v>
       </c>
       <c r="T329" s="4">
-        <v>0</v>
-      </c>
-      <c r="U329" s="4"/>
-      <c r="V329" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U329" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="V329" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W329" s="4">
         <v>8</v>
       </c>
@@ -30230,10 +30206,10 @@
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="AA329" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB329" s="4" t="s">
         <v>47</v>
@@ -30244,16 +30220,16 @@
         <v>1000</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1526</v>
+        <v>455</v>
       </c>
       <c r="C330" s="4">
-        <v>168896015</v>
+        <v>168896073</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E330" s="4">
-        <v>7900282</v>
+        <v>7769908</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>49</v>
@@ -30268,38 +30244,34 @@
         <v>183</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="M330" s="4" t="s">
-        <v>177</v>
+        <v>1523</v>
       </c>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="P330" s="5"/>
       <c r="Q330" s="4" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="R330" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S330" s="4">
-        <v>127746.05</v>
+        <v>393191.56</v>
       </c>
       <c r="T330" s="4">
         <v>1</v>
       </c>
-      <c r="U330" s="4" t="s">
-        <v>1550</v>
-      </c>
-      <c r="V330" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U330" s="4"/>
+      <c r="V330" s="4"/>
       <c r="W330" s="4">
         <v>8</v>
       </c>
@@ -30322,16 +30294,16 @@
         <v>1000</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1526</v>
+        <v>455</v>
       </c>
       <c r="C331" s="4">
-        <v>168896076</v>
+        <v>168896081</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E331" s="4">
-        <v>7063878</v>
+        <v>6943901</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>49</v>
@@ -30346,17 +30318,17 @@
         <v>183</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
-        <v>684</v>
+        <v>1548</v>
       </c>
       <c r="M331" s="4" t="s">
         <v>568</v>
       </c>
       <c r="N331" s="4">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="O331" s="4" t="s">
         <v>1552</v>
@@ -30378,7 +30350,7 @@
         <v>1554</v>
       </c>
       <c r="V331" s="4" t="s">
-        <v>426</v>
+        <v>966</v>
       </c>
       <c r="W331" s="4">
         <v>8</v>
@@ -30390,7 +30362,9 @@
       <c r="Z331" s="4" t="s">
         <v>1555</v>
       </c>
-      <c r="AA331" s="4"/>
+      <c r="AA331" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB331" s="4" t="s">
         <v>47</v>
       </c>
@@ -30400,16 +30374,16 @@
         <v>1000</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>455</v>
+        <v>1293</v>
       </c>
       <c r="C332" s="4">
-        <v>168896073</v>
+        <v>168896094</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E332" s="4">
-        <v>7769908</v>
+        <v>1052309</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>49</v>
@@ -30424,34 +30398,40 @@
         <v>183</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="M332" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="N332" s="4">
+        <v>59</v>
+      </c>
+      <c r="O332" s="4" t="s">
         <v>1556</v>
-      </c>
-      <c r="M332" s="4" t="s">
-        <v>1527</v>
-      </c>
-      <c r="N332" s="4"/>
-      <c r="O332" s="4" t="s">
-        <v>1557</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S332" s="4">
-        <v>393191.56</v>
+        <v>0</v>
       </c>
       <c r="T332" s="4">
-        <v>1</v>
-      </c>
-      <c r="U332" s="4"/>
-      <c r="V332" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U332" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="V332" s="4" t="s">
+        <v>1033</v>
+      </c>
       <c r="W332" s="4">
         <v>8</v>
       </c>
@@ -30474,16 +30454,16 @@
         <v>1000</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>455</v>
+        <v>196</v>
       </c>
       <c r="C333" s="4">
-        <v>168896081</v>
+        <v>169217388</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>57</v>
+        <v>1560</v>
       </c>
       <c r="E333" s="4">
-        <v>6943901</v>
+        <v>1052314</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>49</v>
@@ -30498,27 +30478,25 @@
         <v>183</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
       <c r="M333" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="N333" s="4">
-        <v>12</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="N333" s="4"/>
       <c r="O333" s="4" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="4" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="R333" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S333" s="4">
         <v>0</v>
@@ -30526,14 +30504,10 @@
       <c r="T333" s="4">
         <v>0</v>
       </c>
-      <c r="U333" s="4" t="s">
-        <v>1562</v>
-      </c>
-      <c r="V333" s="4" t="s">
-        <v>966</v>
-      </c>
+      <c r="U333" s="4"/>
+      <c r="V333" s="4"/>
       <c r="W333" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X333" s="4" t="s">
         <v>202</v>
@@ -30543,7 +30517,7 @@
         <v>1563</v>
       </c>
       <c r="AA333" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB333" s="4" t="s">
         <v>47</v>
@@ -30554,16 +30528,16 @@
         <v>1000</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1293</v>
+        <v>455</v>
       </c>
       <c r="C334" s="4">
-        <v>168896094</v>
+        <v>168896120</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E334" s="4">
-        <v>1052309</v>
+        <v>1052344</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>49</v>
@@ -30578,24 +30552,22 @@
         <v>183</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
       <c r="M334" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="N334" s="4">
-        <v>59</v>
-      </c>
+        <v>1564</v>
+      </c>
+      <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="R334" s="4" t="s">
         <v>41</v>
@@ -30607,10 +30579,10 @@
         <v>0</v>
       </c>
       <c r="U334" s="4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="V334" s="4" t="s">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="W334" s="4">
         <v>8</v>
@@ -30620,10 +30592,10 @@
       </c>
       <c r="Y334" s="4"/>
       <c r="Z334" s="4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="AA334" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB334" s="4" t="s">
         <v>47</v>
@@ -30637,13 +30609,13 @@
         <v>196</v>
       </c>
       <c r="C335" s="4">
-        <v>169217388</v>
+        <v>169097745</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>1568</v>
+        <v>34</v>
       </c>
       <c r="E335" s="4">
-        <v>1052314</v>
+        <v>6930250</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>49</v>
@@ -30658,25 +30630,27 @@
         <v>183</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
-        <v>1556</v>
+        <v>1569</v>
       </c>
       <c r="M335" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="N335" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="N335" s="4">
+        <v>22</v>
+      </c>
       <c r="O335" s="4" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="P335" s="5"/>
       <c r="Q335" s="4" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="R335" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S335" s="4">
         <v>0</v>
@@ -30684,20 +30658,24 @@
       <c r="T335" s="4">
         <v>0</v>
       </c>
-      <c r="U335" s="4"/>
-      <c r="V335" s="4"/>
+      <c r="U335" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="V335" s="4" t="s">
+        <v>303</v>
+      </c>
       <c r="W335" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X335" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="AA335" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB335" s="4" t="s">
         <v>47</v>
@@ -30708,16 +30686,16 @@
         <v>1000</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>455</v>
+        <v>222</v>
       </c>
       <c r="C336" s="4">
-        <v>168896120</v>
+        <v>169361669</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E336" s="4">
-        <v>1052344</v>
+        <v>7730211</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>49</v>
@@ -30732,25 +30710,21 @@
         <v>183</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1519</v>
+        <v>1574</v>
       </c>
       <c r="K336" s="4"/>
-      <c r="L336" s="4" t="s">
-        <v>1556</v>
-      </c>
-      <c r="M336" s="4" t="s">
-        <v>1572</v>
-      </c>
+      <c r="L336" s="4"/>
+      <c r="M336" s="4"/>
       <c r="N336" s="4"/>
       <c r="O336" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="R336" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S336" s="4">
         <v>0</v>
@@ -30759,23 +30733,23 @@
         <v>0</v>
       </c>
       <c r="U336" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="V336" s="4" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="W336" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X336" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="AA336" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB336" s="4" t="s">
         <v>47</v>
@@ -30786,16 +30760,16 @@
         <v>1000</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="C337" s="4">
-        <v>169097745</v>
+        <v>169527541</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E337" s="4">
-        <v>6930250</v>
+        <v>7798459</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>49</v>
@@ -30810,24 +30784,22 @@
         <v>183</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1519</v>
+        <v>1574</v>
       </c>
       <c r="K337" s="4"/>
       <c r="L337" s="4" t="s">
-        <v>1577</v>
-      </c>
-      <c r="M337" s="4" t="s">
-        <v>178</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="M337" s="4"/>
       <c r="N337" s="4">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O337" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="R337" s="4" t="s">
         <v>41</v>
@@ -30839,23 +30811,23 @@
         <v>0</v>
       </c>
       <c r="U337" s="4" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="V337" s="4" t="s">
-        <v>303</v>
+        <v>445</v>
       </c>
       <c r="W337" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X337" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="AA337" s="4" t="s">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="AB337" s="4" t="s">
         <v>47</v>
@@ -30866,16 +30838,16 @@
         <v>1000</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="C338" s="4">
-        <v>169361669</v>
+        <v>169515495</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E338" s="4">
-        <v>7730211</v>
+        <v>5905827</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>49</v>
@@ -30890,21 +30862,23 @@
         <v>183</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="K338" s="4"/>
-      <c r="L338" s="4"/>
+      <c r="L338" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M338" s="4"/>
       <c r="N338" s="4"/>
       <c r="O338" s="4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="4" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="R338" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S338" s="4">
         <v>0</v>
@@ -30912,25 +30886,19 @@
       <c r="T338" s="4">
         <v>0</v>
       </c>
-      <c r="U338" s="4" t="s">
-        <v>1585</v>
-      </c>
-      <c r="V338" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="U338" s="4"/>
+      <c r="V338" s="4"/>
       <c r="W338" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X338" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
         <v>1586</v>
       </c>
-      <c r="AA338" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA338" s="4"/>
       <c r="AB338" s="4" t="s">
         <v>47</v>
       </c>
@@ -30940,16 +30908,16 @@
         <v>1000</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C339" s="4">
-        <v>169527541</v>
+        <v>169339010</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E339" s="4">
-        <v>7798459</v>
+        <v>8029935</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>49</v>
@@ -30964,50 +30932,42 @@
         <v>183</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
       <c r="K339" s="4"/>
-      <c r="L339" s="4" t="s">
-        <v>613</v>
-      </c>
+      <c r="L339" s="4"/>
       <c r="M339" s="4"/>
-      <c r="N339" s="4">
-        <v>4</v>
-      </c>
+      <c r="N339" s="4"/>
       <c r="O339" s="4" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="R339" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S339" s="4">
-        <v>0</v>
+        <v>153870.42</v>
       </c>
       <c r="T339" s="4">
-        <v>0</v>
-      </c>
-      <c r="U339" s="4" t="s">
-        <v>1589</v>
-      </c>
-      <c r="V339" s="4" t="s">
-        <v>445</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U339" s="4"/>
+      <c r="V339" s="4"/>
       <c r="W339" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X339" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y339" s="4"/>
       <c r="Z339" s="4" t="s">
         <v>1590</v>
       </c>
       <c r="AA339" s="4" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="AB339" s="4" t="s">
         <v>47</v>
@@ -31018,16 +30978,16 @@
         <v>1000</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C340" s="4">
-        <v>169515495</v>
+        <v>169334978</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E340" s="4">
-        <v>5905827</v>
+        <v>2380524</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>49</v>
@@ -31042,7 +31002,7 @@
         <v>183</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1591</v>
+        <v>1587</v>
       </c>
       <c r="K340" s="4"/>
       <c r="L340" s="4" t="s">
@@ -31051,11 +31011,11 @@
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="4" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="R340" s="4" t="s">
         <v>41</v>
@@ -31066,19 +31026,25 @@
       <c r="T340" s="4">
         <v>0</v>
       </c>
-      <c r="U340" s="4"/>
-      <c r="V340" s="4"/>
+      <c r="U340" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="V340" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="W340" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X340" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y340" s="4"/>
       <c r="Z340" s="4" t="s">
         <v>1594</v>
       </c>
-      <c r="AA340" s="4"/>
+      <c r="AA340" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB340" s="4" t="s">
         <v>47</v>
       </c>
@@ -31088,16 +31054,16 @@
         <v>1000</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C341" s="4">
-        <v>169339010</v>
+        <v>169512979</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E341" s="4">
-        <v>8029935</v>
+        <v>1107566</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>49</v>
@@ -31126,25 +31092,29 @@
         <v>1597</v>
       </c>
       <c r="R341" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S341" s="4">
-        <v>153870.42</v>
+        <v>41450.93</v>
       </c>
       <c r="T341" s="4">
         <v>1</v>
       </c>
-      <c r="U341" s="4"/>
-      <c r="V341" s="4"/>
+      <c r="U341" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="V341" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="W341" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X341" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y341" s="4"/>
       <c r="Z341" s="4" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="AA341" s="4" t="s">
         <v>46</v>
@@ -31158,16 +31128,16 @@
         <v>1000</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C342" s="4">
-        <v>169334978</v>
+        <v>169520460</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E342" s="4">
-        <v>2380524</v>
+        <v>7654420</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>49</v>
@@ -31186,16 +31156,20 @@
       </c>
       <c r="K342" s="4"/>
       <c r="L342" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M342" s="4"/>
-      <c r="N342" s="4"/>
+        <v>1600</v>
+      </c>
+      <c r="M342" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="N342" s="4">
+        <v>48</v>
+      </c>
       <c r="O342" s="4" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="R342" s="4" t="s">
         <v>41</v>
@@ -31206,24 +31180,20 @@
       <c r="T342" s="4">
         <v>0</v>
       </c>
-      <c r="U342" s="4" t="s">
-        <v>1601</v>
-      </c>
-      <c r="V342" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="U342" s="4"/>
+      <c r="V342" s="4"/>
       <c r="W342" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X342" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y342" s="4"/>
       <c r="Z342" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="AA342" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB342" s="4" t="s">
         <v>47</v>
@@ -31234,16 +31204,16 @@
         <v>1000</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>33</v>
+        <v>246</v>
       </c>
       <c r="C343" s="4">
-        <v>169512979</v>
+        <v>169087616</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E343" s="4">
-        <v>1107566</v>
+        <v>8397569</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>49</v>
@@ -31258,49 +31228,43 @@
         <v>183</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="K343" s="4"/>
       <c r="L343" s="4"/>
       <c r="M343" s="4"/>
       <c r="N343" s="4"/>
       <c r="O343" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="R343" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S343" s="4">
-        <v>41450.93</v>
+        <v>0</v>
       </c>
       <c r="T343" s="4">
-        <v>1</v>
-      </c>
-      <c r="U343" s="4" t="s">
-        <v>1606</v>
-      </c>
-      <c r="V343" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U343" s="4"/>
+      <c r="V343" s="4"/>
       <c r="W343" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X343" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y343" s="4"/>
       <c r="Z343" s="4" t="s">
-        <v>1607</v>
-      </c>
-      <c r="AA343" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1608</v>
+      </c>
+      <c r="AA343" s="4"/>
       <c r="AB343" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="344" spans="1:28">
@@ -31308,16 +31272,16 @@
         <v>1000</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>33</v>
+        <v>246</v>
       </c>
       <c r="C344" s="4">
-        <v>169520460</v>
+        <v>169088129</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E344" s="4">
-        <v>7654420</v>
+        <v>8397590</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>49</v>
@@ -31332,27 +31296,21 @@
         <v>183</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="K344" s="4"/>
-      <c r="L344" s="4" t="s">
-        <v>1608</v>
-      </c>
-      <c r="M344" s="4" t="s">
+      <c r="L344" s="4"/>
+      <c r="M344" s="4"/>
+      <c r="N344" s="4"/>
+      <c r="O344" s="4" t="s">
         <v>1609</v>
-      </c>
-      <c r="N344" s="4">
-        <v>48</v>
-      </c>
-      <c r="O344" s="4" t="s">
-        <v>1610</v>
       </c>
       <c r="P344" s="5"/>
       <c r="Q344" s="4" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="R344" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S344" s="4">
         <v>0</v>
@@ -31363,20 +31321,18 @@
       <c r="U344" s="4"/>
       <c r="V344" s="4"/>
       <c r="W344" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X344" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
-        <v>1612</v>
-      </c>
-      <c r="AA344" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1610</v>
+      </c>
+      <c r="AA344" s="4"/>
       <c r="AB344" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="345" spans="1:28">
@@ -31384,16 +31340,16 @@
         <v>1000</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C345" s="4">
-        <v>169087616</v>
+        <v>168912853</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E345" s="4">
-        <v>8397569</v>
+        <v>6956336</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>49</v>
@@ -31408,43 +31364,55 @@
         <v>183</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="K345" s="4"/>
-      <c r="L345" s="4"/>
-      <c r="M345" s="4"/>
-      <c r="N345" s="4"/>
+      <c r="L345" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="M345" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N345" s="4">
+        <v>2</v>
+      </c>
       <c r="O345" s="4" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="P345" s="5"/>
       <c r="Q345" s="4" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="R345" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S345" s="4">
-        <v>0</v>
+        <v>161390.36</v>
       </c>
       <c r="T345" s="4">
-        <v>0</v>
-      </c>
-      <c r="U345" s="4"/>
-      <c r="V345" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="U345" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="V345" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W345" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X345" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1616</v>
-      </c>
-      <c r="AA345" s="4"/>
+        <v>1614</v>
+      </c>
+      <c r="AA345" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="AB345" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="346" spans="1:28">
@@ -31452,16 +31420,16 @@
         <v>1000</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="C346" s="4">
-        <v>169088129</v>
+        <v>169528116</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="E346" s="4">
-        <v>8397590</v>
+        <v>6528821</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>49</v>
@@ -31476,21 +31444,23 @@
         <v>183</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="K346" s="4"/>
-      <c r="L346" s="4"/>
+      <c r="L346" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M346" s="4"/>
       <c r="N346" s="4"/>
       <c r="O346" s="4" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="P346" s="5"/>
       <c r="Q346" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="R346" s="4" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="S346" s="4">
         <v>0</v>
@@ -31498,21 +31468,27 @@
       <c r="T346" s="4">
         <v>0</v>
       </c>
-      <c r="U346" s="4"/>
-      <c r="V346" s="4"/>
+      <c r="U346" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="V346" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W346" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X346" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y346" s="4"/>
       <c r="Z346" s="4" t="s">
-        <v>1618</v>
-      </c>
-      <c r="AA346" s="4"/>
+        <v>1619</v>
+      </c>
+      <c r="AA346" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB346" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="347" spans="1:28">
@@ -31520,16 +31496,16 @@
         <v>1000</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="C347" s="4">
-        <v>168912853</v>
+        <v>169465695</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>188</v>
+        <v>1105</v>
       </c>
       <c r="E347" s="4">
-        <v>6956336</v>
+        <v>1012616</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>49</v>
@@ -31544,52 +31520,50 @@
         <v>183</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1613</v>
+        <v>1620</v>
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>812</v>
+        <v>178</v>
       </c>
       <c r="M347" s="4" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N347" s="4">
-        <v>2</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N347" s="4"/>
       <c r="O347" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="R347" s="4" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="S347" s="4">
-        <v>161390.36</v>
+        <v>0</v>
       </c>
       <c r="T347" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U347" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="V347" s="4" t="s">
-        <v>127</v>
+        <v>1624</v>
       </c>
       <c r="W347" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X347" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y347" s="4"/>
       <c r="Z347" s="4" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="AA347" s="4" t="s">
-        <v>336</v>
+        <v>215</v>
       </c>
       <c r="AB347" s="4" t="s">
         <v>47</v>
@@ -31600,16 +31574,16 @@
         <v>1000</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>33</v>
+        <v>230</v>
       </c>
       <c r="C348" s="4">
-        <v>169528116</v>
+        <v>168614318</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E348" s="4">
-        <v>6528821</v>
+        <v>8296444</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>49</v>
@@ -31624,23 +31598,27 @@
         <v>183</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M348" s="4"/>
-      <c r="N348" s="4"/>
+        <v>1171</v>
+      </c>
+      <c r="M348" s="4" t="s">
+        <v>1627</v>
+      </c>
+      <c r="N348" s="4">
+        <v>74</v>
+      </c>
       <c r="O348" s="4" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="R348" s="4" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="S348" s="4">
         <v>0</v>
@@ -31648,25 +31626,19 @@
       <c r="T348" s="4">
         <v>0</v>
       </c>
-      <c r="U348" s="4" t="s">
-        <v>1626</v>
-      </c>
-      <c r="V348" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U348" s="4"/>
+      <c r="V348" s="4"/>
       <c r="W348" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X348" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y348" s="4"/>
       <c r="Z348" s="4" t="s">
-        <v>1627</v>
-      </c>
-      <c r="AA348" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA348" s="4"/>
       <c r="AB348" s="4" t="s">
         <v>47</v>
       </c>
@@ -31676,16 +31648,16 @@
         <v>1000</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="C349" s="4">
-        <v>169465695</v>
+        <v>169354713</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>1105</v>
+        <v>57</v>
       </c>
       <c r="E349" s="4">
-        <v>1012616</v>
+        <v>7533945</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>49</v>
@@ -31700,25 +31672,27 @@
         <v>183</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
-        <v>178</v>
+        <v>1171</v>
       </c>
       <c r="M349" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="N349" s="4"/>
+        <v>1630</v>
+      </c>
+      <c r="N349" s="4">
+        <v>76</v>
+      </c>
       <c r="O349" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="R349" s="4" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="S349" s="4">
         <v>0</v>
@@ -31726,24 +31700,20 @@
       <c r="T349" s="4">
         <v>0</v>
       </c>
-      <c r="U349" s="4" t="s">
-        <v>1631</v>
-      </c>
-      <c r="V349" s="4" t="s">
-        <v>1632</v>
-      </c>
+      <c r="U349" s="4"/>
+      <c r="V349" s="4"/>
       <c r="W349" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X349" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y349" s="4"/>
       <c r="Z349" s="4" t="s">
         <v>1633</v>
       </c>
       <c r="AA349" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB349" s="4" t="s">
         <v>47</v>
@@ -31754,16 +31724,16 @@
         <v>1000</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>230</v>
+        <v>1634</v>
       </c>
       <c r="C350" s="4">
-        <v>168614318</v>
+        <v>169240215</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E350" s="4">
-        <v>8296444</v>
+        <v>1037589</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>49</v>
@@ -31778,27 +31748,25 @@
         <v>183</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
-        <v>1171</v>
+        <v>289</v>
       </c>
       <c r="M350" s="4" t="s">
-        <v>1635</v>
-      </c>
-      <c r="N350" s="4">
-        <v>74</v>
-      </c>
+        <v>1636</v>
+      </c>
+      <c r="N350" s="4"/>
       <c r="O350" s="4" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="R350" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S350" s="4">
         <v>0</v>
@@ -31806,19 +31774,25 @@
       <c r="T350" s="4">
         <v>0</v>
       </c>
-      <c r="U350" s="4"/>
-      <c r="V350" s="4"/>
+      <c r="U350" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="V350" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W350" s="4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y350" s="4"/>
       <c r="Z350" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA350" s="4"/>
+        <v>1640</v>
+      </c>
+      <c r="AA350" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB350" s="4" t="s">
         <v>47</v>
       </c>
@@ -31828,16 +31802,16 @@
         <v>1000</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>420</v>
+        <v>872</v>
       </c>
       <c r="C351" s="4">
-        <v>169354713</v>
+        <v>169240216</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E351" s="4">
-        <v>7533945</v>
+        <v>1037569</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>49</v>
@@ -31852,27 +31826,25 @@
         <v>183</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
-        <v>1171</v>
+        <v>289</v>
       </c>
       <c r="M351" s="4" t="s">
-        <v>1638</v>
-      </c>
-      <c r="N351" s="4">
-        <v>76</v>
-      </c>
+        <v>1641</v>
+      </c>
+      <c r="N351" s="4"/>
       <c r="O351" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="P351" s="5"/>
       <c r="Q351" s="4" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="R351" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S351" s="4">
         <v>0</v>
@@ -31880,20 +31852,24 @@
       <c r="T351" s="4">
         <v>0</v>
       </c>
-      <c r="U351" s="4"/>
-      <c r="V351" s="4"/>
+      <c r="U351" s="4" t="s">
+        <v>1644</v>
+      </c>
+      <c r="V351" s="4" t="s">
+        <v>426</v>
+      </c>
       <c r="W351" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X351" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1641</v>
+        <v>1380</v>
       </c>
       <c r="AA351" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB351" s="4" t="s">
         <v>47</v>
@@ -31904,16 +31880,16 @@
         <v>1000</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1642</v>
+        <v>667</v>
       </c>
       <c r="C352" s="4">
-        <v>169240215</v>
+        <v>168725375</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E352" s="4">
-        <v>1037589</v>
+        <v>4321965</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>49</v>
@@ -31928,50 +31904,50 @@
         <v>183</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M352" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="N352" s="4"/>
       <c r="O352" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="P352" s="5"/>
       <c r="Q352" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="R352" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S352" s="4">
-        <v>0</v>
+        <v>165052.22</v>
       </c>
       <c r="T352" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U352" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="W352" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X352" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y352" s="4"/>
       <c r="Z352" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="AA352" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB352" s="4" t="s">
         <v>47</v>
@@ -31982,16 +31958,16 @@
         <v>1000</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>872</v>
+        <v>1522</v>
       </c>
       <c r="C353" s="4">
-        <v>169240216</v>
+        <v>168896049</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E353" s="4">
-        <v>1037569</v>
+        <v>8020879</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>49</v>
@@ -32006,25 +31982,27 @@
         <v>183</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
-        <v>289</v>
+        <v>1651</v>
       </c>
       <c r="M353" s="4" t="s">
-        <v>1649</v>
-      </c>
-      <c r="N353" s="4"/>
+        <v>523</v>
+      </c>
+      <c r="N353" s="4">
+        <v>30</v>
+      </c>
       <c r="O353" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="P353" s="5"/>
       <c r="Q353" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="R353" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S353" s="4">
         <v>0</v>
@@ -32032,25 +32010,19 @@
       <c r="T353" s="4">
         <v>0</v>
       </c>
-      <c r="U353" s="4" t="s">
-        <v>1652</v>
-      </c>
-      <c r="V353" s="4" t="s">
-        <v>426</v>
-      </c>
+      <c r="U353" s="4"/>
+      <c r="V353" s="4"/>
       <c r="W353" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X353" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1384</v>
-      </c>
-      <c r="AA353" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1654</v>
+      </c>
+      <c r="AA353" s="4"/>
       <c r="AB353" s="4" t="s">
         <v>47</v>
       </c>
@@ -32060,16 +32032,16 @@
         <v>1000</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>667</v>
+        <v>230</v>
       </c>
       <c r="C354" s="4">
-        <v>168725375</v>
+        <v>169511125</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E354" s="4">
-        <v>4321965</v>
+        <v>1030462</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>49</v>
@@ -32084,51 +32056,45 @@
         <v>183</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="M354" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="N354" s="4"/>
       <c r="O354" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="P354" s="5"/>
       <c r="Q354" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="R354" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S354" s="4">
-        <v>165052.22</v>
+        <v>0</v>
       </c>
       <c r="T354" s="4">
-        <v>1</v>
-      </c>
-      <c r="U354" s="4" t="s">
-        <v>1657</v>
-      </c>
-      <c r="V354" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U354" s="4"/>
+      <c r="V354" s="4"/>
       <c r="W354" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y354" s="4"/>
       <c r="Z354" s="4" t="s">
-        <v>1658</v>
-      </c>
-      <c r="AA354" s="4" t="s">
-        <v>215</v>
-      </c>
+        <v>1659</v>
+      </c>
+      <c r="AA354" s="4"/>
       <c r="AB354" s="4" t="s">
         <v>47</v>
       </c>
@@ -32138,16 +32104,16 @@
         <v>1000</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1526</v>
+        <v>872</v>
       </c>
       <c r="C355" s="4">
-        <v>168896049</v>
+        <v>169354695</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E355" s="4">
-        <v>8020879</v>
+        <v>1037638</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>49</v>
@@ -32162,27 +32128,23 @@
         <v>183</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="K355" s="4"/>
       <c r="L355" s="4" t="s">
-        <v>1659</v>
-      </c>
-      <c r="M355" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="N355" s="4">
-        <v>30</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M355" s="4"/>
+      <c r="N355" s="4"/>
       <c r="O355" s="4" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="R355" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S355" s="4">
         <v>0</v>
@@ -32193,16 +32155,18 @@
       <c r="U355" s="4"/>
       <c r="V355" s="4"/>
       <c r="W355" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X355" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
-        <v>1662</v>
-      </c>
-      <c r="AA355" s="4"/>
+        <v>1663</v>
+      </c>
+      <c r="AA355" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB355" s="4" t="s">
         <v>47</v>
       </c>
@@ -32212,16 +32176,16 @@
         <v>1000</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>230</v>
+        <v>1634</v>
       </c>
       <c r="C356" s="4">
-        <v>169511125</v>
+        <v>169354696</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E356" s="4">
-        <v>1030462</v>
+        <v>1037665</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>49</v>
@@ -32236,22 +32200,20 @@
         <v>183</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="K356" s="4"/>
       <c r="L356" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M356" s="4" t="s">
-        <v>1664</v>
-      </c>
+      <c r="M356" s="4"/>
       <c r="N356" s="4"/>
       <c r="O356" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="P356" s="5"/>
       <c r="Q356" s="4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="R356" s="4" t="s">
         <v>61</v>
@@ -32265,16 +32227,18 @@
       <c r="U356" s="4"/>
       <c r="V356" s="4"/>
       <c r="W356" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X356" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y356" s="4"/>
       <c r="Z356" s="4" t="s">
-        <v>1667</v>
-      </c>
-      <c r="AA356" s="4"/>
+        <v>1666</v>
+      </c>
+      <c r="AA356" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB356" s="4" t="s">
         <v>47</v>
       </c>
@@ -32284,16 +32248,16 @@
         <v>1000</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>872</v>
+        <v>1634</v>
       </c>
       <c r="C357" s="4">
-        <v>169354695</v>
+        <v>169354700</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E357" s="4">
-        <v>1037638</v>
+        <v>1037643</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>49</v>
@@ -32308,7 +32272,7 @@
         <v>183</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K357" s="4"/>
       <c r="L357" s="4" t="s">
@@ -32317,20 +32281,20 @@
       <c r="M357" s="4"/>
       <c r="N357" s="4"/>
       <c r="O357" s="4" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="P357" s="5"/>
       <c r="Q357" s="4" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="R357" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S357" s="4">
-        <v>0</v>
+        <v>16183109.58</v>
       </c>
       <c r="T357" s="4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="U357" s="4"/>
       <c r="V357" s="4"/>
@@ -32342,13 +32306,13 @@
       </c>
       <c r="Y357" s="4"/>
       <c r="Z357" s="4" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="AA357" s="4" t="s">
-        <v>46</v>
+        <v>388</v>
       </c>
       <c r="AB357" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="358" spans="1:28">
@@ -32356,16 +32320,16 @@
         <v>1000</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="C358" s="4">
-        <v>169354696</v>
+        <v>169354701</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E358" s="4">
-        <v>1037665</v>
+        <v>1037642</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>49</v>
@@ -32380,7 +32344,7 @@
         <v>183</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
@@ -32389,23 +32353,27 @@
       <c r="M358" s="4"/>
       <c r="N358" s="4"/>
       <c r="O358" s="4" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="P358" s="5"/>
       <c r="Q358" s="4" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="R358" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S358" s="4">
-        <v>0</v>
+        <v>532142.46</v>
       </c>
       <c r="T358" s="4">
-        <v>0</v>
-      </c>
-      <c r="U358" s="4"/>
-      <c r="V358" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U358" s="4" t="s">
+        <v>1672</v>
+      </c>
+      <c r="V358" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W358" s="4">
         <v>2</v>
       </c>
@@ -32414,10 +32382,10 @@
       </c>
       <c r="Y358" s="4"/>
       <c r="Z358" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AA358" s="4" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
       <c r="AB358" s="4" t="s">
         <v>47</v>
@@ -32428,16 +32396,16 @@
         <v>1000</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="C359" s="4">
-        <v>169354700</v>
+        <v>169354702</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E359" s="4">
-        <v>1037643</v>
+        <v>1037647</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>49</v>
@@ -32452,7 +32420,7 @@
         <v>183</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
@@ -32461,20 +32429,20 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="R359" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S359" s="4">
-        <v>16183109.58</v>
+        <v>0</v>
       </c>
       <c r="T359" s="4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="U359" s="4"/>
       <c r="V359" s="4"/>
@@ -32486,13 +32454,13 @@
       </c>
       <c r="Y359" s="4"/>
       <c r="Z359" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="AA359" s="4" t="s">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="AB359" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="360" spans="1:28">
@@ -32500,16 +32468,16 @@
         <v>1000</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1642</v>
+        <v>1331</v>
       </c>
       <c r="C360" s="4">
-        <v>169354701</v>
+        <v>169354703</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E360" s="4">
-        <v>1037642</v>
+        <v>1037655</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>49</v>
@@ -32524,7 +32492,7 @@
         <v>183</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
@@ -32533,23 +32501,23 @@
       <c r="M360" s="4"/>
       <c r="N360" s="4"/>
       <c r="O360" s="4" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="P360" s="5"/>
       <c r="Q360" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="R360" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S360" s="4">
-        <v>532142.46</v>
+        <v>0</v>
       </c>
       <c r="T360" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U360" s="4" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="V360" s="4" t="s">
         <v>127</v>
@@ -32562,10 +32530,10 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="AA360" s="4" t="s">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="AB360" s="4" t="s">
         <v>47</v>
@@ -32576,16 +32544,16 @@
         <v>1000</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1642</v>
+        <v>1331</v>
       </c>
       <c r="C361" s="4">
-        <v>169354702</v>
+        <v>169354708</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E361" s="4">
-        <v>1037647</v>
+        <v>1037651</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>49</v>
@@ -32600,7 +32568,7 @@
         <v>183</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
@@ -32609,11 +32577,11 @@
       <c r="M361" s="4"/>
       <c r="N361" s="4"/>
       <c r="O361" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="R361" s="4" t="s">
         <v>61</v>
@@ -32624,8 +32592,12 @@
       <c r="T361" s="4">
         <v>0</v>
       </c>
-      <c r="U361" s="4"/>
-      <c r="V361" s="4"/>
+      <c r="U361" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="V361" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W361" s="4">
         <v>2</v>
       </c>
@@ -32637,7 +32609,7 @@
         <v>1684</v>
       </c>
       <c r="AA361" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB361" s="4" t="s">
         <v>47</v>
@@ -32648,16 +32620,16 @@
         <v>1000</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1331</v>
+        <v>352</v>
       </c>
       <c r="C362" s="4">
-        <v>169354703</v>
+        <v>169354710</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E362" s="4">
-        <v>1037655</v>
+        <v>7616012</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>49</v>
@@ -32672,7 +32644,7 @@
         <v>183</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4" t="s">
@@ -32696,12 +32668,8 @@
       <c r="T362" s="4">
         <v>0</v>
       </c>
-      <c r="U362" s="4" t="s">
-        <v>1687</v>
-      </c>
-      <c r="V362" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U362" s="4"/>
+      <c r="V362" s="4"/>
       <c r="W362" s="4">
         <v>2</v>
       </c>
@@ -32710,10 +32678,10 @@
       </c>
       <c r="Y362" s="4"/>
       <c r="Z362" s="4" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="AA362" s="4" t="s">
-        <v>65</v>
+        <v>351</v>
       </c>
       <c r="AB362" s="4" t="s">
         <v>47</v>
@@ -32724,16 +32692,16 @@
         <v>1000</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1331</v>
+        <v>352</v>
       </c>
       <c r="C363" s="4">
-        <v>169354708</v>
+        <v>169354711</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E363" s="4">
-        <v>1037651</v>
+        <v>5918582</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>49</v>
@@ -32748,7 +32716,7 @@
         <v>183</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4" t="s">
@@ -32757,23 +32725,23 @@
       <c r="M363" s="4"/>
       <c r="N363" s="4"/>
       <c r="O363" s="4" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="P363" s="5"/>
       <c r="Q363" s="4" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="R363" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S363" s="4">
-        <v>0</v>
+        <v>9429108.630000001</v>
       </c>
       <c r="T363" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U363" s="4" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="V363" s="4" t="s">
         <v>127</v>
@@ -32786,13 +32754,11 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>1692</v>
-      </c>
-      <c r="AA363" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1691</v>
+      </c>
+      <c r="AA363" s="4"/>
       <c r="AB363" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="364" spans="1:28">
@@ -32803,13 +32769,13 @@
         <v>352</v>
       </c>
       <c r="C364" s="4">
-        <v>169354710</v>
+        <v>169354712</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E364" s="4">
-        <v>7616012</v>
+        <v>1037657</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>49</v>
@@ -32824,7 +32790,7 @@
         <v>183</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4" t="s">
@@ -32833,11 +32799,11 @@
       <c r="M364" s="4"/>
       <c r="N364" s="4"/>
       <c r="O364" s="4" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="R364" s="4" t="s">
         <v>61</v>
@@ -32848,8 +32814,12 @@
       <c r="T364" s="4">
         <v>0</v>
       </c>
-      <c r="U364" s="4"/>
-      <c r="V364" s="4"/>
+      <c r="U364" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="V364" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W364" s="4">
         <v>2</v>
       </c>
@@ -32861,7 +32831,7 @@
         <v>1695</v>
       </c>
       <c r="AA364" s="4" t="s">
-        <v>351</v>
+        <v>215</v>
       </c>
       <c r="AB364" s="4" t="s">
         <v>47</v>
@@ -32875,13 +32845,13 @@
         <v>352</v>
       </c>
       <c r="C365" s="4">
-        <v>169354711</v>
+        <v>169354709</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E365" s="4">
-        <v>5918582</v>
+        <v>1037653</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>49</v>
@@ -32896,36 +32866,34 @@
         <v>183</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M365" s="4"/>
+      <c r="M365" s="4" t="s">
+        <v>1696</v>
+      </c>
       <c r="N365" s="4"/>
       <c r="O365" s="4" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="P365" s="5"/>
       <c r="Q365" s="4" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="R365" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S365" s="4">
-        <v>9429108.630000001</v>
+        <v>0</v>
       </c>
       <c r="T365" s="4">
-        <v>75</v>
-      </c>
-      <c r="U365" s="4" t="s">
-        <v>1698</v>
-      </c>
-      <c r="V365" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U365" s="4"/>
+      <c r="V365" s="4"/>
       <c r="W365" s="4">
         <v>2</v>
       </c>
@@ -32936,9 +32904,11 @@
       <c r="Z365" s="4" t="s">
         <v>1699</v>
       </c>
-      <c r="AA365" s="4"/>
+      <c r="AA365" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB365" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="366" spans="1:28">
@@ -32946,16 +32916,16 @@
         <v>1000</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C366" s="4">
-        <v>169354712</v>
+        <v>169360455</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E366" s="4">
-        <v>1037657</v>
+        <v>1037656</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>49</v>
@@ -32970,13 +32940,15 @@
         <v>183</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="K366" s="4"/>
       <c r="L366" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M366" s="4"/>
+      <c r="M366" s="4" t="s">
+        <v>1696</v>
+      </c>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
         <v>1700</v>
@@ -32989,17 +32961,13 @@
         <v>61</v>
       </c>
       <c r="S366" s="4">
-        <v>0</v>
+        <v>57340.82</v>
       </c>
       <c r="T366" s="4">
-        <v>0</v>
-      </c>
-      <c r="U366" s="4" t="s">
-        <v>1702</v>
-      </c>
-      <c r="V366" s="4" t="s">
-        <v>476</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U366" s="4"/>
+      <c r="V366" s="4"/>
       <c r="W366" s="4">
         <v>2</v>
       </c>
@@ -33008,7 +32976,7 @@
       </c>
       <c r="Y366" s="4"/>
       <c r="Z366" s="4" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="AA366" s="4" t="s">
         <v>215</v>
@@ -33022,16 +32990,16 @@
         <v>1000</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>352</v>
+        <v>33</v>
       </c>
       <c r="C367" s="4">
-        <v>169354709</v>
+        <v>169527823</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E367" s="4">
-        <v>1037653</v>
+        <v>4268253</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>49</v>
@@ -33046,46 +33014,50 @@
         <v>183</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1668</v>
+        <v>1703</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
-        <v>289</v>
+        <v>224</v>
       </c>
       <c r="M367" s="4" t="s">
-        <v>1704</v>
+        <v>517</v>
       </c>
       <c r="N367" s="4"/>
       <c r="O367" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
+        <v>1705</v>
+      </c>
+      <c r="R367" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S367" s="4">
+        <v>0</v>
+      </c>
+      <c r="T367" s="4">
+        <v>0</v>
+      </c>
+      <c r="U367" s="4" t="s">
         <v>1706</v>
       </c>
-      <c r="R367" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S367" s="4">
-        <v>0</v>
-      </c>
-      <c r="T367" s="4">
-        <v>0</v>
-      </c>
-      <c r="U367" s="4"/>
-      <c r="V367" s="4"/>
+      <c r="V367" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W367" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X367" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y367" s="4"/>
       <c r="Z367" s="4" t="s">
         <v>1707</v>
       </c>
       <c r="AA367" s="4" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="AB367" s="4" t="s">
         <v>47</v>
@@ -33099,13 +33071,13 @@
         <v>337</v>
       </c>
       <c r="C368" s="4">
-        <v>169360455</v>
+        <v>169345689</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>34</v>
+        <v>722</v>
       </c>
       <c r="E368" s="4">
-        <v>1037656</v>
+        <v>1030127</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>49</v>
@@ -33120,34 +33092,36 @@
         <v>183</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1668</v>
+        <v>1708</v>
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M368" s="4" t="s">
-        <v>1704</v>
-      </c>
+      <c r="M368" s="4"/>
       <c r="N368" s="4"/>
       <c r="O368" s="4" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="P368" s="5"/>
       <c r="Q368" s="4" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="R368" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S368" s="4">
-        <v>57340.82</v>
+        <v>0</v>
       </c>
       <c r="T368" s="4">
-        <v>1</v>
-      </c>
-      <c r="U368" s="4"/>
-      <c r="V368" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U368" s="4" t="s">
+        <v>1711</v>
+      </c>
+      <c r="V368" s="4" t="s">
+        <v>1712</v>
+      </c>
       <c r="W368" s="4">
         <v>2</v>
       </c>
@@ -33156,10 +33130,10 @@
       </c>
       <c r="Y368" s="4"/>
       <c r="Z368" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="AA368" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB368" s="4" t="s">
         <v>47</v>
@@ -33170,16 +33144,16 @@
         <v>1000</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>33</v>
+        <v>645</v>
       </c>
       <c r="C369" s="4">
-        <v>169527823</v>
+        <v>169240241</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E369" s="4">
-        <v>4268253</v>
+        <v>6825959</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>49</v>
@@ -33194,50 +33168,44 @@
         <v>183</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="M369" s="4" t="s">
-        <v>517</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="R369" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S369" s="4">
-        <v>0</v>
+        <v>412514.71</v>
       </c>
       <c r="T369" s="4">
-        <v>0</v>
-      </c>
-      <c r="U369" s="4" t="s">
-        <v>1714</v>
-      </c>
-      <c r="V369" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U369" s="4"/>
+      <c r="V369" s="4"/>
       <c r="W369" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X369" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y369" s="4"/>
       <c r="Z369" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="AA369" s="4" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="AB369" s="4" t="s">
         <v>47</v>
@@ -33248,16 +33216,16 @@
         <v>1000</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C370" s="4">
-        <v>169345689</v>
+        <v>169521806</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>722</v>
+        <v>34</v>
       </c>
       <c r="E370" s="4">
-        <v>1030127</v>
+        <v>6699162</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>49</v>
@@ -33272,7 +33240,7 @@
         <v>183</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -33281,14 +33249,14 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="R370" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S370" s="4">
         <v>0</v>
@@ -33296,24 +33264,20 @@
       <c r="T370" s="4">
         <v>0</v>
       </c>
-      <c r="U370" s="4" t="s">
-        <v>1719</v>
-      </c>
-      <c r="V370" s="4" t="s">
-        <v>1720</v>
-      </c>
+      <c r="U370" s="4"/>
+      <c r="V370" s="4"/>
       <c r="W370" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X370" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y370" s="4"/>
       <c r="Z370" s="4" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="AA370" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB370" s="4" t="s">
         <v>47</v>
@@ -33324,16 +33288,16 @@
         <v>1000</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>645</v>
+        <v>33</v>
       </c>
       <c r="C371" s="4">
-        <v>169240241</v>
+        <v>169511424</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E371" s="4">
-        <v>6825959</v>
+        <v>7187541</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>49</v>
@@ -33348,7 +33312,7 @@
         <v>183</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
@@ -33357,36 +33321,38 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="R371" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S371" s="4">
+        <v>0</v>
+      </c>
+      <c r="T371" s="4">
+        <v>0</v>
+      </c>
+      <c r="U371" s="4" t="s">
         <v>1724</v>
       </c>
-      <c r="R371" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S371" s="4">
-        <v>412514.71</v>
-      </c>
-      <c r="T371" s="4">
-        <v>1</v>
-      </c>
-      <c r="U371" s="4"/>
-      <c r="V371" s="4"/>
+      <c r="V371" s="4" t="s">
+        <v>604</v>
+      </c>
       <c r="W371" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X371" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y371" s="4"/>
       <c r="Z371" s="4" t="s">
         <v>1725</v>
       </c>
-      <c r="AA371" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA371" s="4"/>
       <c r="AB371" s="4" t="s">
         <v>47</v>
       </c>
@@ -33396,16 +33362,16 @@
         <v>1000</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="C372" s="4">
-        <v>169521806</v>
+        <v>169347543</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>34</v>
+        <v>580</v>
       </c>
       <c r="E372" s="4">
-        <v>6699162</v>
+        <v>1072186</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>49</v>
@@ -33420,7 +33386,7 @@
         <v>183</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="K372" s="4"/>
       <c r="L372" s="4" t="s">
@@ -33429,35 +33395,39 @@
       <c r="M372" s="4"/>
       <c r="N372" s="4"/>
       <c r="O372" s="4" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="P372" s="5"/>
       <c r="Q372" s="4" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="R372" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S372" s="4">
-        <v>0</v>
+        <v>20024.22</v>
       </c>
       <c r="T372" s="4">
-        <v>0</v>
-      </c>
-      <c r="U372" s="4"/>
-      <c r="V372" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U372" s="4" t="s">
+        <v>1729</v>
+      </c>
+      <c r="V372" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="W372" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X372" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="AA372" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB372" s="4" t="s">
         <v>47</v>
@@ -33471,13 +33441,13 @@
         <v>33</v>
       </c>
       <c r="C373" s="4">
-        <v>169511424</v>
+        <v>169527018</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E373" s="4">
-        <v>7187541</v>
+        <v>6658632</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>49</v>
@@ -33486,26 +33456,24 @@
         <v>36</v>
       </c>
       <c r="H373" s="4" t="s">
-        <v>183</v>
+        <v>1731</v>
       </c>
       <c r="I373" s="4" t="s">
-        <v>183</v>
+        <v>1732</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="K373" s="4"/>
-      <c r="L373" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L373" s="4"/>
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="R373" s="4" t="s">
         <v>79</v>
@@ -33517,10 +33485,10 @@
         <v>0</v>
       </c>
       <c r="U373" s="4" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="V373" s="4" t="s">
-        <v>604</v>
+        <v>43</v>
       </c>
       <c r="W373" s="4">
         <v>0</v>
@@ -33530,160 +33498,12 @@
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
-        <v>1733</v>
-      </c>
-      <c r="AA373" s="4"/>
+        <v>1737</v>
+      </c>
+      <c r="AA373" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB373" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="374" spans="1:28">
-      <c r="A374" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B374" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C374" s="4">
-        <v>169347543</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="E374" s="4">
-        <v>1072186</v>
-      </c>
-      <c r="F374" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G374" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H374" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I374" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="J374" s="4" t="s">
-        <v>1734</v>
-      </c>
-      <c r="K374" s="4"/>
-      <c r="L374" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M374" s="4"/>
-      <c r="N374" s="4"/>
-      <c r="O374" s="4" t="s">
-        <v>1735</v>
-      </c>
-      <c r="P374" s="5"/>
-      <c r="Q374" s="4" t="s">
-        <v>1736</v>
-      </c>
-      <c r="R374" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S374" s="4">
-        <v>20024.22</v>
-      </c>
-      <c r="T374" s="4">
-        <v>1</v>
-      </c>
-      <c r="U374" s="4" t="s">
-        <v>1737</v>
-      </c>
-      <c r="V374" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="W374" s="4">
-        <v>2</v>
-      </c>
-      <c r="X374" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y374" s="4"/>
-      <c r="Z374" s="4" t="s">
-        <v>1738</v>
-      </c>
-      <c r="AA374" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB374" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="375" spans="1:28">
-      <c r="A375" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B375" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C375" s="4">
-        <v>169527018</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E375" s="4">
-        <v>6658632</v>
-      </c>
-      <c r="F375" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G375" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H375" s="4" t="s">
-        <v>1739</v>
-      </c>
-      <c r="I375" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="J375" s="4" t="s">
-        <v>1741</v>
-      </c>
-      <c r="K375" s="4"/>
-      <c r="L375" s="4"/>
-      <c r="M375" s="4"/>
-      <c r="N375" s="4"/>
-      <c r="O375" s="4" t="s">
-        <v>1742</v>
-      </c>
-      <c r="P375" s="5"/>
-      <c r="Q375" s="4" t="s">
-        <v>1743</v>
-      </c>
-      <c r="R375" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S375" s="4">
-        <v>0</v>
-      </c>
-      <c r="T375" s="4">
-        <v>0</v>
-      </c>
-      <c r="U375" s="4" t="s">
-        <v>1744</v>
-      </c>
-      <c r="V375" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="W375" s="4">
-        <v>0</v>
-      </c>
-      <c r="X375" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y375" s="4"/>
-      <c r="Z375" s="4" t="s">
-        <v>1745</v>
-      </c>
-      <c r="AA375" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB375" s="4" t="s">
         <v>47</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 20:22:54</t>
+    <t>17/10/2026 a las 21:00:53</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1743">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 21:00:53</t>
+    <t>17/10/2026 a las 22:00:54</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -3675,6 +3675,21 @@
   </si>
   <si>
     <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>CR 21G</t>
+  </si>
+  <si>
+    <t>CR 21G CL 45 - 60 APTO 201 DT8041</t>
+  </si>
+  <si>
+    <t>OROZCO CALLE  RODOLFO</t>
+  </si>
+  <si>
+    <t>12030000-MCA54</t>
+  </si>
+  <si>
+    <t>Revision Suministromedidor MD PQR sr rodolfo orozco, cel 3113383956,Se requiere orden de servicio para validar el estado del suministro, aportar lecturas, censo verificado, pruebas con equipo patron, pruebas con equipo AVM, pruebas de giro en vacio, revisar todo.</t>
   </si>
   <si>
     <t>CR 23</t>
@@ -5622,7 +5637,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB373"/>
+  <dimension ref="A1:AB374"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -24454,16 +24469,16 @@
         <v>1000</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="C253" s="4">
-        <v>169249255</v>
+        <v>169536262</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E253" s="4">
-        <v>1032625</v>
+        <v>7914368</v>
       </c>
       <c r="F253" s="4" t="s">
         <v>49</v>
@@ -24488,7 +24503,7 @@
         <v>612</v>
       </c>
       <c r="N253" s="4">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="O253" s="4" t="s">
         <v>1221</v>
@@ -24510,13 +24525,13 @@
         <v>1223</v>
       </c>
       <c r="V253" s="4" t="s">
-        <v>364</v>
+        <v>127</v>
       </c>
       <c r="W253" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X253" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y253" s="4"/>
       <c r="Z253" s="4" t="s">
@@ -24535,13 +24550,13 @@
         <v>447</v>
       </c>
       <c r="C254" s="4">
-        <v>169234272</v>
+        <v>169249255</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E254" s="4">
-        <v>5886380</v>
+        <v>1032625</v>
       </c>
       <c r="F254" s="4" t="s">
         <v>49</v>
@@ -24560,13 +24575,13 @@
       </c>
       <c r="K254" s="4"/>
       <c r="L254" s="4" t="s">
-        <v>82</v>
+        <v>1225</v>
       </c>
       <c r="M254" s="4" t="s">
-        <v>1225</v>
+        <v>612</v>
       </c>
       <c r="N254" s="4">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="O254" s="4" t="s">
         <v>1226</v>
@@ -24576,19 +24591,19 @@
         <v>1227</v>
       </c>
       <c r="R254" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S254" s="4">
-        <v>8635328.380000001</v>
+        <v>0</v>
       </c>
       <c r="T254" s="4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="U254" s="4" t="s">
         <v>1228</v>
       </c>
       <c r="V254" s="4" t="s">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="W254" s="4">
         <v>3</v>
@@ -24600,11 +24615,9 @@
       <c r="Z254" s="4" t="s">
         <v>1229</v>
       </c>
-      <c r="AA254" s="4" t="s">
-        <v>388</v>
-      </c>
+      <c r="AA254" s="4"/>
       <c r="AB254" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="255" spans="1:28">
@@ -24612,16 +24625,16 @@
         <v>1000</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C255" s="4">
-        <v>169100048</v>
+        <v>169234272</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E255" s="4">
-        <v>6883467</v>
+        <v>5886380</v>
       </c>
       <c r="F255" s="4" t="s">
         <v>49</v>
@@ -24636,14 +24649,18 @@
         <v>183</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>1230</v>
+        <v>1219</v>
       </c>
       <c r="K255" s="4"/>
       <c r="L255" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M255" s="4"/>
-      <c r="N255" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="M255" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N255" s="4">
+        <v>17</v>
+      </c>
       <c r="O255" s="4" t="s">
         <v>1231</v>
       </c>
@@ -24655,26 +24672,32 @@
         <v>61</v>
       </c>
       <c r="S255" s="4">
-        <v>0</v>
+        <v>8635328.380000001</v>
       </c>
       <c r="T255" s="4">
-        <v>0</v>
-      </c>
-      <c r="U255" s="4"/>
-      <c r="V255" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="U255" s="4" t="s">
+        <v>1233</v>
+      </c>
+      <c r="V255" s="4" t="s">
+        <v>426</v>
+      </c>
       <c r="W255" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X255" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y255" s="4"/>
       <c r="Z255" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="AA255" s="4"/>
+        <v>1234</v>
+      </c>
+      <c r="AA255" s="4" t="s">
+        <v>388</v>
+      </c>
       <c r="AB255" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="256" spans="1:28">
@@ -24682,16 +24705,16 @@
         <v>1000</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="C256" s="4">
-        <v>169101360</v>
+        <v>169100048</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E256" s="4">
-        <v>4321758</v>
+        <v>6883467</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>49</v>
@@ -24706,7 +24729,7 @@
         <v>183</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="K256" s="4"/>
       <c r="L256" s="4" t="s">
@@ -24715,14 +24738,14 @@
       <c r="M256" s="4"/>
       <c r="N256" s="4"/>
       <c r="O256" s="4" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="P256" s="5"/>
       <c r="Q256" s="4" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="R256" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S256" s="4">
         <v>0</v>
@@ -24730,21 +24753,17 @@
       <c r="T256" s="4">
         <v>0</v>
       </c>
-      <c r="U256" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="V256" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U256" s="4"/>
+      <c r="V256" s="4"/>
       <c r="W256" s="4">
         <v>4</v>
       </c>
       <c r="X256" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y256" s="4"/>
       <c r="Z256" s="4" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="AA256" s="4"/>
       <c r="AB256" s="4" t="s">
@@ -24759,13 +24778,13 @@
         <v>196</v>
       </c>
       <c r="C257" s="4">
-        <v>168898228</v>
+        <v>169101360</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E257" s="4">
-        <v>6938291</v>
+        <v>4321758</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>49</v>
@@ -24780,24 +24799,20 @@
         <v>183</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="K257" s="4"/>
       <c r="L257" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="M257" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="N257" s="4">
-        <v>53</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M257" s="4"/>
+      <c r="N257" s="4"/>
       <c r="O257" s="4" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="P257" s="5"/>
       <c r="Q257" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="R257" s="4" t="s">
         <v>41</v>
@@ -24809,24 +24824,22 @@
         <v>0</v>
       </c>
       <c r="U257" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="V257" s="4" t="s">
         <v>127</v>
       </c>
       <c r="W257" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X257" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y257" s="4"/>
       <c r="Z257" s="4" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AA257" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1242</v>
+      </c>
+      <c r="AA257" s="4"/>
       <c r="AB257" s="4" t="s">
         <v>47</v>
       </c>
@@ -24836,16 +24849,16 @@
         <v>1000</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
       <c r="C258" s="4">
-        <v>169483274</v>
+        <v>168898228</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="E258" s="4">
-        <v>8384193</v>
+        <v>6938291</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>49</v>
@@ -24857,20 +24870,20 @@
         <v>183</v>
       </c>
       <c r="I258" s="4" t="s">
-        <v>1242</v>
+        <v>183</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="K258" s="4"/>
       <c r="L258" s="4" t="s">
-        <v>459</v>
+        <v>672</v>
       </c>
       <c r="M258" s="4" t="s">
-        <v>466</v>
+        <v>523</v>
       </c>
       <c r="N258" s="4">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O258" s="4" t="s">
         <v>1243</v>
@@ -24880,7 +24893,7 @@
         <v>1244</v>
       </c>
       <c r="R258" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S258" s="4">
         <v>0</v>
@@ -24888,19 +24901,25 @@
       <c r="T258" s="4">
         <v>0</v>
       </c>
-      <c r="U258" s="4"/>
-      <c r="V258" s="4"/>
+      <c r="U258" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="V258" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W258" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X258" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y258" s="4"/>
       <c r="Z258" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA258" s="4"/>
+        <v>1246</v>
+      </c>
+      <c r="AA258" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB258" s="4" t="s">
         <v>47</v>
       </c>
@@ -24910,16 +24929,16 @@
         <v>1000</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>312</v>
+        <v>33</v>
       </c>
       <c r="C259" s="4">
-        <v>168617735</v>
+        <v>169483274</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="E259" s="4">
-        <v>7007877</v>
+        <v>8384193</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>49</v>
@@ -24931,25 +24950,27 @@
         <v>183</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="K259" s="4"/>
       <c r="L259" s="4" t="s">
-        <v>1245</v>
+        <v>459</v>
       </c>
       <c r="M259" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="N259" s="4"/>
+        <v>466</v>
+      </c>
+      <c r="N259" s="4">
+        <v>30</v>
+      </c>
       <c r="O259" s="4" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="P259" s="5"/>
       <c r="Q259" s="4" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="R259" s="4" t="s">
         <v>79</v>
@@ -24960,25 +24981,19 @@
       <c r="T259" s="4">
         <v>0</v>
       </c>
-      <c r="U259" s="4" t="s">
-        <v>1248</v>
-      </c>
-      <c r="V259" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="U259" s="4"/>
+      <c r="V259" s="4"/>
       <c r="W259" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X259" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y259" s="4"/>
       <c r="Z259" s="4" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AA259" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA259" s="4"/>
       <c r="AB259" s="4" t="s">
         <v>47</v>
       </c>
@@ -24988,16 +25003,16 @@
         <v>1000</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>33</v>
+        <v>312</v>
       </c>
       <c r="C260" s="4">
-        <v>169085226</v>
+        <v>168617735</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E260" s="4">
-        <v>5914143</v>
+        <v>7007877</v>
       </c>
       <c r="F260" s="4" t="s">
         <v>49</v>
@@ -25009,17 +25024,17 @@
         <v>183</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="K260" s="4"/>
       <c r="L260" s="4" t="s">
-        <v>123</v>
+        <v>1250</v>
       </c>
       <c r="M260" s="4" t="s">
-        <v>1250</v>
+        <v>483</v>
       </c>
       <c r="N260" s="4"/>
       <c r="O260" s="4" t="s">
@@ -25030,7 +25045,7 @@
         <v>1252</v>
       </c>
       <c r="R260" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S260" s="4">
         <v>0</v>
@@ -25042,20 +25057,20 @@
         <v>1253</v>
       </c>
       <c r="V260" s="4" t="s">
-        <v>463</v>
+        <v>69</v>
       </c>
       <c r="W260" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X260" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y260" s="4"/>
       <c r="Z260" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="AA260" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB260" s="4" t="s">
         <v>47</v>
@@ -25066,16 +25081,16 @@
         <v>1000</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>312</v>
+        <v>33</v>
       </c>
       <c r="C261" s="4">
-        <v>169236551</v>
+        <v>169085226</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E261" s="4">
-        <v>1056366</v>
+        <v>5914143</v>
       </c>
       <c r="F261" s="4" t="s">
         <v>49</v>
@@ -25087,14 +25102,14 @@
         <v>183</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="K261" s="4"/>
       <c r="L261" s="4" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>1255</v>
@@ -25108,28 +25123,32 @@
         <v>1257</v>
       </c>
       <c r="R261" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S261" s="4">
-        <v>923639.33</v>
+        <v>0</v>
       </c>
       <c r="T261" s="4">
-        <v>2</v>
-      </c>
-      <c r="U261" s="4"/>
-      <c r="V261" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U261" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="V261" s="4" t="s">
+        <v>463</v>
+      </c>
       <c r="W261" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X261" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y261" s="4"/>
       <c r="Z261" s="4" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="AA261" s="4" t="s">
-        <v>351</v>
+        <v>215</v>
       </c>
       <c r="AB261" s="4" t="s">
         <v>47</v>
@@ -25140,16 +25159,16 @@
         <v>1000</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>33</v>
+        <v>312</v>
       </c>
       <c r="C262" s="4">
-        <v>169483359</v>
+        <v>169236551</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="E262" s="4">
-        <v>8394283</v>
+        <v>1056366</v>
       </c>
       <c r="F262" s="4" t="s">
         <v>49</v>
@@ -25161,50 +25180,50 @@
         <v>183</v>
       </c>
       <c r="I262" s="4" t="s">
-        <v>183</v>
+        <v>1247</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="K262" s="4"/>
       <c r="L262" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M262" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="M262" s="4" t="s">
+      <c r="N262" s="4"/>
+      <c r="O262" s="4" t="s">
         <v>1261</v>
-      </c>
-      <c r="N262" s="4">
-        <v>42</v>
-      </c>
-      <c r="O262" s="4" t="s">
-        <v>1262</v>
       </c>
       <c r="P262" s="5"/>
       <c r="Q262" s="4" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="R262" s="4" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="S262" s="4">
-        <v>0</v>
+        <v>923639.33</v>
       </c>
       <c r="T262" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U262" s="4"/>
       <c r="V262" s="4"/>
       <c r="W262" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X262" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y262" s="4"/>
       <c r="Z262" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA262" s="4"/>
+        <v>1263</v>
+      </c>
+      <c r="AA262" s="4" t="s">
+        <v>351</v>
+      </c>
       <c r="AB262" s="4" t="s">
         <v>47</v>
       </c>
@@ -25214,16 +25233,16 @@
         <v>1000</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>420</v>
+        <v>33</v>
       </c>
       <c r="C263" s="4">
-        <v>168725418</v>
+        <v>169483359</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E263" s="4">
-        <v>6957391</v>
+        <v>8394283</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>49</v>
@@ -25242,23 +25261,23 @@
       </c>
       <c r="K263" s="4"/>
       <c r="L263" s="4" t="s">
-        <v>466</v>
+        <v>1265</v>
       </c>
       <c r="M263" s="4" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N263" s="4">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="O263" s="4" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="P263" s="5"/>
       <c r="Q263" s="4" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="R263" s="4" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="S263" s="4">
         <v>0</v>
@@ -25266,25 +25285,19 @@
       <c r="T263" s="4">
         <v>0</v>
       </c>
-      <c r="U263" s="4" t="s">
-        <v>1268</v>
-      </c>
-      <c r="V263" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="U263" s="4"/>
+      <c r="V263" s="4"/>
       <c r="W263" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X263" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y263" s="4"/>
       <c r="Z263" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="AA263" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA263" s="4"/>
       <c r="AB263" s="4" t="s">
         <v>47</v>
       </c>
@@ -25294,16 +25307,16 @@
         <v>1000</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="C264" s="4">
-        <v>169525716</v>
+        <v>168725418</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>471</v>
+        <v>57</v>
       </c>
       <c r="E264" s="4">
-        <v>7709720</v>
+        <v>6957391</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>49</v>
@@ -25318,17 +25331,17 @@
         <v>183</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K264" s="4"/>
       <c r="L264" s="4" t="s">
-        <v>97</v>
+        <v>466</v>
       </c>
       <c r="M264" s="4" t="s">
-        <v>523</v>
+        <v>1270</v>
       </c>
       <c r="N264" s="4">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="O264" s="4" t="s">
         <v>1271</v>
@@ -25338,35 +25351,35 @@
         <v>1272</v>
       </c>
       <c r="R264" s="4" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="S264" s="4">
-        <v>1383640.89</v>
+        <v>0</v>
       </c>
       <c r="T264" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U264" s="4" t="s">
         <v>1273</v>
       </c>
       <c r="V264" s="4" t="s">
-        <v>476</v>
+        <v>69</v>
       </c>
       <c r="W264" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X264" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y264" s="4"/>
       <c r="Z264" s="4" t="s">
         <v>1274</v>
       </c>
       <c r="AA264" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB264" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="265" spans="1:28">
@@ -25377,13 +25390,13 @@
         <v>33</v>
       </c>
       <c r="C265" s="4">
-        <v>169470167</v>
+        <v>169525716</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>188</v>
+        <v>471</v>
       </c>
       <c r="E265" s="4">
-        <v>7725658</v>
+        <v>7709720</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>49</v>
@@ -25395,58 +25408,58 @@
         <v>183</v>
       </c>
       <c r="I265" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J265" s="4" t="s">
         <v>1275</v>
-      </c>
-      <c r="J265" s="4" t="s">
-        <v>1276</v>
       </c>
       <c r="K265" s="4"/>
       <c r="L265" s="4" t="s">
-        <v>1277</v>
+        <v>97</v>
       </c>
       <c r="M265" s="4" t="s">
-        <v>1101</v>
+        <v>523</v>
       </c>
       <c r="N265" s="4">
-        <v>254</v>
+        <v>5</v>
       </c>
       <c r="O265" s="4" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="P265" s="5"/>
       <c r="Q265" s="4" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="R265" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S265" s="4">
-        <v>0</v>
+        <v>1383640.89</v>
       </c>
       <c r="T265" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U265" s="4" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="V265" s="4" t="s">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="W265" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X265" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y265" s="4"/>
       <c r="Z265" s="4" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="AA265" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB265" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="266" spans="1:28">
@@ -25457,13 +25470,13 @@
         <v>33</v>
       </c>
       <c r="C266" s="4">
-        <v>168796051</v>
+        <v>169470167</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="E266" s="4">
-        <v>8384343</v>
+        <v>7725658</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>49</v>
@@ -25475,15 +25488,21 @@
         <v>183</v>
       </c>
       <c r="I266" s="4" t="s">
-        <v>183</v>
+        <v>1280</v>
       </c>
       <c r="J266" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="K266" s="4"/>
+      <c r="L266" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="K266" s="4"/>
-      <c r="L266" s="4"/>
-      <c r="M266" s="4"/>
-      <c r="N266" s="4"/>
+      <c r="M266" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N266" s="4">
+        <v>254</v>
+      </c>
       <c r="O266" s="4" t="s">
         <v>1283</v>
       </c>
@@ -25492,27 +25511,33 @@
         <v>1284</v>
       </c>
       <c r="R266" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S266" s="4">
-        <v>401418.42</v>
+        <v>0</v>
       </c>
       <c r="T266" s="4">
-        <v>2</v>
-      </c>
-      <c r="U266" s="4"/>
-      <c r="V266" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U266" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="V266" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="W266" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X266" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y266" s="4"/>
       <c r="Z266" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA266" s="4"/>
+        <v>1286</v>
+      </c>
+      <c r="AA266" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB266" s="4" t="s">
         <v>47</v>
       </c>
@@ -25525,13 +25550,13 @@
         <v>33</v>
       </c>
       <c r="C267" s="4">
-        <v>168799239</v>
+        <v>168796051</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E267" s="4">
-        <v>8391518</v>
+        <v>8384343</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>49</v>
@@ -25546,27 +25571,27 @@
         <v>183</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4"/>
       <c r="M267" s="4"/>
       <c r="N267" s="4"/>
       <c r="O267" s="4" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="P267" s="5"/>
       <c r="Q267" s="4" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="R267" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S267" s="4">
-        <v>0</v>
+        <v>401418.42</v>
       </c>
       <c r="T267" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
@@ -25590,16 +25615,16 @@
         <v>1000</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="C268" s="4">
-        <v>169339745</v>
+        <v>168799239</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E268" s="4">
-        <v>8001278</v>
+        <v>8391518</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>49</v>
@@ -25614,18 +25639,18 @@
         <v>183</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4"/>
       <c r="M268" s="4"/>
       <c r="N268" s="4"/>
       <c r="O268" s="4" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="P268" s="5"/>
       <c r="Q268" s="4" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="R268" s="4" t="s">
         <v>79</v>
@@ -25639,18 +25664,16 @@
       <c r="U268" s="4"/>
       <c r="V268" s="4"/>
       <c r="W268" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X268" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y268" s="4"/>
       <c r="Z268" s="4" t="s">
-        <v>1289</v>
-      </c>
-      <c r="AA268" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA268" s="4"/>
       <c r="AB268" s="4" t="s">
         <v>47</v>
       </c>
@@ -25660,16 +25683,16 @@
         <v>1000</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>1059</v>
+        <v>246</v>
       </c>
       <c r="C269" s="4">
-        <v>168886822</v>
+        <v>169339745</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E269" s="4">
-        <v>8392361</v>
+        <v>8001278</v>
       </c>
       <c r="F269" s="4" t="s">
         <v>49</v>
@@ -25684,18 +25707,18 @@
         <v>183</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4"/>
       <c r="M269" s="4"/>
       <c r="N269" s="4"/>
       <c r="O269" s="4" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="P269" s="5"/>
       <c r="Q269" s="4" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="R269" s="4" t="s">
         <v>79</v>
@@ -25709,16 +25732,18 @@
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
       <c r="W269" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X269" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y269" s="4"/>
       <c r="Z269" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA269" s="4"/>
+        <v>1294</v>
+      </c>
+      <c r="AA269" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB269" s="4" t="s">
         <v>47</v>
       </c>
@@ -25728,16 +25753,16 @@
         <v>1000</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>1293</v>
+        <v>1059</v>
       </c>
       <c r="C270" s="4">
-        <v>166657163</v>
+        <v>168886822</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E270" s="4">
-        <v>1346167</v>
+        <v>8392361</v>
       </c>
       <c r="F270" s="4" t="s">
         <v>49</v>
@@ -25752,22 +25777,18 @@
         <v>183</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="K270" s="4"/>
-      <c r="L270" s="4" t="s">
-        <v>1294</v>
-      </c>
-      <c r="M270" s="4" t="s">
-        <v>459</v>
-      </c>
+      <c r="L270" s="4"/>
+      <c r="M270" s="4"/>
       <c r="N270" s="4"/>
       <c r="O270" s="4" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="P270" s="5"/>
       <c r="Q270" s="4" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="R270" s="4" t="s">
         <v>79</v>
@@ -25778,25 +25799,19 @@
       <c r="T270" s="4">
         <v>0</v>
       </c>
-      <c r="U270" s="4" t="s">
-        <v>1297</v>
-      </c>
-      <c r="V270" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U270" s="4"/>
+      <c r="V270" s="4"/>
       <c r="W270" s="4">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="X270" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y270" s="4"/>
       <c r="Z270" s="4" t="s">
-        <v>1298</v>
-      </c>
-      <c r="AA270" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA270" s="4"/>
       <c r="AB270" s="4" t="s">
         <v>47</v>
       </c>
@@ -25806,16 +25821,16 @@
         <v>1000</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>33</v>
+        <v>1298</v>
       </c>
       <c r="C271" s="4">
-        <v>168799295</v>
+        <v>166657163</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E271" s="4">
-        <v>8391485</v>
+        <v>1346167</v>
       </c>
       <c r="F271" s="4" t="s">
         <v>49</v>
@@ -25830,11 +25845,15 @@
         <v>183</v>
       </c>
       <c r="J271" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="K271" s="4"/>
+      <c r="L271" s="4" t="s">
         <v>1299</v>
       </c>
-      <c r="K271" s="4"/>
-      <c r="L271" s="4"/>
-      <c r="M271" s="4"/>
+      <c r="M271" s="4" t="s">
+        <v>459</v>
+      </c>
       <c r="N271" s="4"/>
       <c r="O271" s="4" t="s">
         <v>1300</v>
@@ -25852,19 +25871,25 @@
       <c r="T271" s="4">
         <v>0</v>
       </c>
-      <c r="U271" s="4"/>
-      <c r="V271" s="4"/>
+      <c r="U271" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="V271" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W271" s="4">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="X271" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y271" s="4"/>
       <c r="Z271" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA271" s="4"/>
+        <v>1303</v>
+      </c>
+      <c r="AA271" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB271" s="4" t="s">
         <v>47</v>
       </c>
@@ -25874,16 +25899,16 @@
         <v>1000</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="C272" s="4">
-        <v>169343653</v>
+        <v>168799295</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="E272" s="4">
-        <v>7951786</v>
+        <v>8391485</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>49</v>
@@ -25898,23 +25923,21 @@
         <v>183</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="K272" s="4"/>
-      <c r="L272" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L272" s="4"/>
       <c r="M272" s="4"/>
       <c r="N272" s="4"/>
       <c r="O272" s="4" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="4" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="R272" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S272" s="4">
         <v>0</v>
@@ -25922,21 +25945,17 @@
       <c r="T272" s="4">
         <v>0</v>
       </c>
-      <c r="U272" s="4" t="s">
-        <v>1305</v>
-      </c>
-      <c r="V272" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U272" s="4"/>
+      <c r="V272" s="4"/>
       <c r="W272" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X272" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
-        <v>1306</v>
+        <v>56</v>
       </c>
       <c r="AA272" s="4"/>
       <c r="AB272" s="4" t="s">
@@ -25948,16 +25967,16 @@
         <v>1000</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>447</v>
+        <v>222</v>
       </c>
       <c r="C273" s="4">
-        <v>169009528</v>
+        <v>169343653</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E273" s="4">
-        <v>6903524</v>
+        <v>7951786</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>49</v>
@@ -25996,21 +26015,23 @@
       <c r="T273" s="4">
         <v>0</v>
       </c>
-      <c r="U273" s="4"/>
-      <c r="V273" s="4"/>
+      <c r="U273" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="V273" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W273" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X273" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y273" s="4"/>
       <c r="Z273" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="AA273" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1311</v>
+      </c>
+      <c r="AA273" s="4"/>
       <c r="AB273" s="4" t="s">
         <v>47</v>
       </c>
@@ -26020,16 +26041,16 @@
         <v>1000</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C274" s="4">
-        <v>169519267</v>
+        <v>169009528</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E274" s="4">
-        <v>6862401</v>
+        <v>6903524</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>49</v>
@@ -26044,7 +26065,7 @@
         <v>183</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4" t="s">
@@ -26053,14 +26074,14 @@
       <c r="M274" s="4"/>
       <c r="N274" s="4"/>
       <c r="O274" s="4" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="P274" s="5"/>
       <c r="Q274" s="4" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="R274" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S274" s="4">
         <v>0</v>
@@ -26071,14 +26092,14 @@
       <c r="U274" s="4"/>
       <c r="V274" s="4"/>
       <c r="W274" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X274" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="AA274" s="4" t="s">
         <v>46</v>
@@ -26092,16 +26113,16 @@
         <v>1000</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>617</v>
+        <v>33</v>
       </c>
       <c r="C275" s="4">
-        <v>169089966</v>
+        <v>169519267</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E275" s="4">
-        <v>8397606</v>
+        <v>6862401</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>49</v>
@@ -26116,18 +26137,20 @@
         <v>183</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="K275" s="4"/>
-      <c r="L275" s="4"/>
+      <c r="L275" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M275" s="4"/>
       <c r="N275" s="4"/>
       <c r="O275" s="4" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="P275" s="5"/>
       <c r="Q275" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="R275" s="4" t="s">
         <v>41</v>
@@ -26141,18 +26164,20 @@
       <c r="U275" s="4"/>
       <c r="V275" s="4"/>
       <c r="W275" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X275" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y275" s="4"/>
       <c r="Z275" s="4" t="s">
-        <v>1317</v>
-      </c>
-      <c r="AA275" s="4"/>
+        <v>1318</v>
+      </c>
+      <c r="AA275" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB275" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="276" spans="1:28">
@@ -26160,16 +26185,16 @@
         <v>1000</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>892</v>
+        <v>617</v>
       </c>
       <c r="C276" s="4">
-        <v>169227224</v>
+        <v>169089966</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E276" s="4">
-        <v>8391001</v>
+        <v>8397606</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>49</v>
@@ -26184,18 +26209,18 @@
         <v>183</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="K276" s="4"/>
       <c r="L276" s="4"/>
       <c r="M276" s="4"/>
       <c r="N276" s="4"/>
       <c r="O276" s="4" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="P276" s="5"/>
       <c r="Q276" s="4" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="R276" s="4" t="s">
         <v>41</v>
@@ -26209,14 +26234,14 @@
       <c r="U276" s="4"/>
       <c r="V276" s="4"/>
       <c r="W276" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X276" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y276" s="4"/>
       <c r="Z276" s="4" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="AA276" s="4"/>
       <c r="AB276" s="4" t="s">
@@ -26228,16 +26253,16 @@
         <v>1000</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>447</v>
+        <v>892</v>
       </c>
       <c r="C277" s="4">
-        <v>169487174</v>
+        <v>169227224</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E277" s="4">
-        <v>6959985</v>
+        <v>8391001</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>49</v>
@@ -26252,20 +26277,18 @@
         <v>183</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="K277" s="4"/>
-      <c r="L277" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L277" s="4"/>
       <c r="M277" s="4"/>
       <c r="N277" s="4"/>
       <c r="O277" s="4" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="P277" s="5"/>
       <c r="Q277" s="4" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="R277" s="4" t="s">
         <v>41</v>
@@ -26276,14 +26299,10 @@
       <c r="T277" s="4">
         <v>0</v>
       </c>
-      <c r="U277" s="4" t="s">
-        <v>1324</v>
-      </c>
-      <c r="V277" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="U277" s="4"/>
+      <c r="V277" s="4"/>
       <c r="W277" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X277" s="4" t="s">
         <v>202</v>
@@ -26292,11 +26311,9 @@
       <c r="Z277" s="4" t="s">
         <v>1325</v>
       </c>
-      <c r="AA277" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA277" s="4"/>
       <c r="AB277" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -26304,16 +26321,16 @@
         <v>1000</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>267</v>
+        <v>447</v>
       </c>
       <c r="C278" s="4">
-        <v>168896173</v>
+        <v>169487174</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E278" s="4">
-        <v>6619680</v>
+        <v>6959985</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>49</v>
@@ -26347,19 +26364,19 @@
         <v>41</v>
       </c>
       <c r="S278" s="4">
-        <v>338342.08</v>
+        <v>0</v>
       </c>
       <c r="T278" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U278" s="4" t="s">
         <v>1329</v>
       </c>
       <c r="V278" s="4" t="s">
-        <v>349</v>
+        <v>69</v>
       </c>
       <c r="W278" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X278" s="4" t="s">
         <v>202</v>
@@ -26369,7 +26386,7 @@
         <v>1330</v>
       </c>
       <c r="AA278" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB278" s="4" t="s">
         <v>47</v>
@@ -26380,16 +26397,16 @@
         <v>1000</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>1331</v>
+        <v>267</v>
       </c>
       <c r="C279" s="4">
-        <v>169240223</v>
+        <v>168896173</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E279" s="4">
-        <v>5873839</v>
+        <v>6619680</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>49</v>
@@ -26404,7 +26421,7 @@
         <v>183</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="K279" s="4"/>
       <c r="L279" s="4" t="s">
@@ -26423,25 +26440,29 @@
         <v>41</v>
       </c>
       <c r="S279" s="4">
-        <v>0</v>
+        <v>338342.08</v>
       </c>
       <c r="T279" s="4">
-        <v>0</v>
-      </c>
-      <c r="U279" s="4"/>
-      <c r="V279" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U279" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="V279" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="W279" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X279" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y279" s="4"/>
       <c r="Z279" s="4" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="AA279" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB279" s="4" t="s">
         <v>47</v>
@@ -26452,16 +26473,16 @@
         <v>1000</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="C280" s="4">
-        <v>169240234</v>
+        <v>169240223</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E280" s="4">
-        <v>8020360</v>
+        <v>5873839</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>49</v>
@@ -26476,24 +26497,20 @@
         <v>183</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="K280" s="4"/>
       <c r="L280" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M280" s="4" t="s">
-        <v>1335</v>
-      </c>
-      <c r="N280" s="4">
-        <v>8</v>
-      </c>
+      <c r="M280" s="4"/>
+      <c r="N280" s="4"/>
       <c r="O280" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="P280" s="5"/>
       <c r="Q280" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="R280" s="4" t="s">
         <v>41</v>
@@ -26514,10 +26531,10 @@
       </c>
       <c r="Y280" s="4"/>
       <c r="Z280" s="4" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="AA280" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB280" s="4" t="s">
         <v>47</v>
@@ -26528,16 +26545,16 @@
         <v>1000</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>33</v>
+        <v>1336</v>
       </c>
       <c r="C281" s="4">
-        <v>168725355</v>
+        <v>169240234</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E281" s="4">
-        <v>6893139</v>
+        <v>8020360</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>49</v>
@@ -26552,23 +26569,27 @@
         <v>183</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
       <c r="K281" s="4"/>
       <c r="L281" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M281" s="4"/>
-      <c r="N281" s="4"/>
+      <c r="M281" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="N281" s="4">
+        <v>8</v>
+      </c>
       <c r="O281" s="4" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="P281" s="5"/>
       <c r="Q281" s="4" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="R281" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S281" s="4">
         <v>0</v>
@@ -26579,14 +26600,14 @@
       <c r="U281" s="4"/>
       <c r="V281" s="4"/>
       <c r="W281" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X281" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y281" s="4"/>
       <c r="Z281" s="4" t="s">
-        <v>1269</v>
+        <v>1343</v>
       </c>
       <c r="AA281" s="4" t="s">
         <v>65</v>
@@ -26600,16 +26621,16 @@
         <v>1000</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>645</v>
+        <v>33</v>
       </c>
       <c r="C282" s="4">
-        <v>169240243</v>
+        <v>168725355</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E282" s="4">
-        <v>7703360</v>
+        <v>6893139</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>49</v>
@@ -26624,41 +26645,41 @@
         <v>183</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="K282" s="4"/>
       <c r="L282" s="4" t="s">
-        <v>1343</v>
+        <v>289</v>
       </c>
       <c r="M282" s="4"/>
       <c r="N282" s="4"/>
       <c r="O282" s="4" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="P282" s="5"/>
       <c r="Q282" s="4" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="R282" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S282" s="4">
-        <v>173348.56</v>
+        <v>0</v>
       </c>
       <c r="T282" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U282" s="4"/>
       <c r="V282" s="4"/>
       <c r="W282" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X282" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y282" s="4"/>
       <c r="Z282" s="4" t="s">
-        <v>1346</v>
+        <v>1274</v>
       </c>
       <c r="AA282" s="4" t="s">
         <v>65</v>
@@ -26672,16 +26693,16 @@
         <v>1000</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>33</v>
+        <v>645</v>
       </c>
       <c r="C283" s="4">
-        <v>169522397</v>
+        <v>169240243</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E283" s="4">
-        <v>7703225</v>
+        <v>7703360</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>49</v>
@@ -26696,41 +26717,41 @@
         <v>183</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="K283" s="4"/>
       <c r="L283" s="4" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="M283" s="4"/>
       <c r="N283" s="4"/>
       <c r="O283" s="4" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="P283" s="5"/>
       <c r="Q283" s="4" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="R283" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S283" s="4">
-        <v>0</v>
+        <v>173348.56</v>
       </c>
       <c r="T283" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U283" s="4"/>
       <c r="V283" s="4"/>
       <c r="W283" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X283" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y283" s="4"/>
       <c r="Z283" s="4" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="AA283" s="4" t="s">
         <v>65</v>
@@ -26744,16 +26765,16 @@
         <v>1000</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>617</v>
+        <v>33</v>
       </c>
       <c r="C284" s="4">
-        <v>168805201</v>
+        <v>169522397</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="E284" s="4">
-        <v>8397173</v>
+        <v>7703225</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>49</v>
@@ -26768,18 +26789,20 @@
         <v>183</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="K284" s="4"/>
-      <c r="L284" s="4"/>
+      <c r="L284" s="4" t="s">
+        <v>1348</v>
+      </c>
       <c r="M284" s="4"/>
       <c r="N284" s="4"/>
       <c r="O284" s="4" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="P284" s="5"/>
       <c r="Q284" s="4" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="R284" s="4" t="s">
         <v>61</v>
@@ -26793,18 +26816,20 @@
       <c r="U284" s="4"/>
       <c r="V284" s="4"/>
       <c r="W284" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X284" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y284" s="4"/>
       <c r="Z284" s="4" t="s">
-        <v>1353</v>
-      </c>
-      <c r="AA284" s="4"/>
+        <v>1354</v>
+      </c>
+      <c r="AA284" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB284" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="285" spans="1:28">
@@ -26812,16 +26837,16 @@
         <v>1000</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>420</v>
+        <v>617</v>
       </c>
       <c r="C285" s="4">
-        <v>169354697</v>
+        <v>168805201</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="E285" s="4">
-        <v>1125234</v>
+        <v>8397173</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>49</v>
@@ -26836,20 +26861,18 @@
         <v>183</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K285" s="4"/>
-      <c r="L285" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L285" s="4"/>
       <c r="M285" s="4"/>
       <c r="N285" s="4"/>
       <c r="O285" s="4" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="P285" s="5"/>
       <c r="Q285" s="4" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="R285" s="4" t="s">
         <v>61</v>
@@ -26860,14 +26883,10 @@
       <c r="T285" s="4">
         <v>0</v>
       </c>
-      <c r="U285" s="4" t="s">
-        <v>1357</v>
-      </c>
-      <c r="V285" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="U285" s="4"/>
+      <c r="V285" s="4"/>
       <c r="W285" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X285" s="4" t="s">
         <v>202</v>
@@ -26876,11 +26895,9 @@
       <c r="Z285" s="4" t="s">
         <v>1358</v>
       </c>
-      <c r="AA285" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA285" s="4"/>
       <c r="AB285" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="286" spans="1:28">
@@ -26891,13 +26908,13 @@
         <v>420</v>
       </c>
       <c r="C286" s="4">
-        <v>169354698</v>
+        <v>169354697</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E286" s="4">
-        <v>6560463</v>
+        <v>1125234</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>49</v>
@@ -26912,7 +26929,7 @@
         <v>183</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K286" s="4"/>
       <c r="L286" s="4" t="s">
@@ -26921,11 +26938,11 @@
       <c r="M286" s="4"/>
       <c r="N286" s="4"/>
       <c r="O286" s="4" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="P286" s="5"/>
       <c r="Q286" s="4" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="R286" s="4" t="s">
         <v>61</v>
@@ -26937,10 +26954,10 @@
         <v>0</v>
       </c>
       <c r="U286" s="4" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="V286" s="4" t="s">
-        <v>1361</v>
+        <v>69</v>
       </c>
       <c r="W286" s="4">
         <v>2</v>
@@ -26950,10 +26967,10 @@
       </c>
       <c r="Y286" s="4"/>
       <c r="Z286" s="4" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="AA286" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB286" s="4" t="s">
         <v>47</v>
@@ -26964,16 +26981,16 @@
         <v>1000</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>337</v>
+        <v>420</v>
       </c>
       <c r="C287" s="4">
-        <v>169468953</v>
+        <v>169354698</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E287" s="4">
-        <v>1034443</v>
+        <v>6560463</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>49</v>
@@ -26988,24 +27005,20 @@
         <v>183</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K287" s="4"/>
       <c r="L287" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="M287" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="M287" s="4"/>
+      <c r="N287" s="4"/>
+      <c r="O287" s="4" t="s">
         <v>1364</v>
-      </c>
-      <c r="N287" s="4">
-        <v>34</v>
-      </c>
-      <c r="O287" s="4" t="s">
-        <v>1365</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="4" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="R287" s="4" t="s">
         <v>61</v>
@@ -27016,10 +27029,14 @@
       <c r="T287" s="4">
         <v>0</v>
       </c>
-      <c r="U287" s="4"/>
-      <c r="V287" s="4"/>
+      <c r="U287" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="V287" s="4" t="s">
+        <v>1366</v>
+      </c>
       <c r="W287" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X287" s="4" t="s">
         <v>202</v>
@@ -27029,7 +27046,7 @@
         <v>1367</v>
       </c>
       <c r="AA287" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB287" s="4" t="s">
         <v>47</v>
@@ -27040,16 +27057,16 @@
         <v>1000</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>967</v>
+        <v>337</v>
       </c>
       <c r="C288" s="4">
-        <v>169240185</v>
+        <v>169468953</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E288" s="4">
-        <v>6517492</v>
+        <v>1034443</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>49</v>
@@ -27064,24 +27081,24 @@
         <v>183</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K288" s="4"/>
       <c r="L288" s="4" t="s">
-        <v>875</v>
+        <v>1368</v>
       </c>
       <c r="M288" s="4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N288" s="4">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="O288" s="4" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="P288" s="5"/>
       <c r="Q288" s="4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="R288" s="4" t="s">
         <v>61</v>
@@ -27092,14 +27109,10 @@
       <c r="T288" s="4">
         <v>0</v>
       </c>
-      <c r="U288" s="4" t="s">
-        <v>1371</v>
-      </c>
-      <c r="V288" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="U288" s="4"/>
+      <c r="V288" s="4"/>
       <c r="W288" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X288" s="4" t="s">
         <v>202</v>
@@ -27108,7 +27121,9 @@
       <c r="Z288" s="4" t="s">
         <v>1372</v>
       </c>
-      <c r="AA288" s="4"/>
+      <c r="AA288" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB288" s="4" t="s">
         <v>47</v>
       </c>
@@ -27118,16 +27133,16 @@
         <v>1000</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>917</v>
+        <v>967</v>
       </c>
       <c r="C289" s="4">
-        <v>169240208</v>
+        <v>169240185</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E289" s="4">
-        <v>6508453</v>
+        <v>6517492</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>49</v>
@@ -27142,7 +27157,7 @@
         <v>183</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K289" s="4"/>
       <c r="L289" s="4" t="s">
@@ -27152,7 +27167,7 @@
         <v>1373</v>
       </c>
       <c r="N289" s="4">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="O289" s="4" t="s">
         <v>1374</v>
@@ -27170,8 +27185,12 @@
       <c r="T289" s="4">
         <v>0</v>
       </c>
-      <c r="U289" s="4"/>
-      <c r="V289" s="4"/>
+      <c r="U289" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="V289" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="W289" s="4">
         <v>3</v>
       </c>
@@ -27180,11 +27199,9 @@
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1334</v>
-      </c>
-      <c r="AA289" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1377</v>
+      </c>
+      <c r="AA289" s="4"/>
       <c r="AB289" s="4" t="s">
         <v>47</v>
       </c>
@@ -27194,16 +27211,16 @@
         <v>1000</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>33</v>
+        <v>917</v>
       </c>
       <c r="C290" s="4">
-        <v>169240192</v>
+        <v>169240208</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E290" s="4">
-        <v>6568702</v>
+        <v>6508453</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>49</v>
@@ -27218,27 +27235,27 @@
         <v>183</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
-        <v>1376</v>
+        <v>875</v>
       </c>
       <c r="M290" s="4" t="s">
-        <v>875</v>
+        <v>1378</v>
       </c>
       <c r="N290" s="4">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="O290" s="4" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="R290" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S290" s="4">
         <v>0</v>
@@ -27246,24 +27263,20 @@
       <c r="T290" s="4">
         <v>0</v>
       </c>
-      <c r="U290" s="4" t="s">
-        <v>1379</v>
-      </c>
-      <c r="V290" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U290" s="4"/>
+      <c r="V290" s="4"/>
       <c r="W290" s="4">
         <v>3</v>
       </c>
       <c r="X290" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y290" s="4"/>
       <c r="Z290" s="4" t="s">
-        <v>1380</v>
+        <v>1339</v>
       </c>
       <c r="AA290" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB290" s="4" t="s">
         <v>47</v>
@@ -27277,13 +27290,13 @@
         <v>33</v>
       </c>
       <c r="C291" s="4">
-        <v>169240194</v>
+        <v>169240192</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E291" s="4">
-        <v>6837112</v>
+        <v>6568702</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>49</v>
@@ -27298,27 +27311,27 @@
         <v>183</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="K291" s="4"/>
       <c r="L291" s="4" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>875</v>
       </c>
       <c r="N291" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O291" s="4" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="P291" s="5"/>
       <c r="Q291" s="4" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="R291" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S291" s="4">
         <v>0</v>
@@ -27326,8 +27339,12 @@
       <c r="T291" s="4">
         <v>0</v>
       </c>
-      <c r="U291" s="4"/>
-      <c r="V291" s="4"/>
+      <c r="U291" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="V291" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W291" s="4">
         <v>3</v>
       </c>
@@ -27336,7 +27353,7 @@
       </c>
       <c r="Y291" s="4"/>
       <c r="Z291" s="4" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="AA291" s="4" t="s">
         <v>65</v>
@@ -27350,16 +27367,16 @@
         <v>1000</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C292" s="4">
-        <v>169338674</v>
+        <v>169240194</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="E292" s="4">
-        <v>8330993</v>
+        <v>6837112</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>49</v>
@@ -27374,41 +27391,49 @@
         <v>183</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1383</v>
+        <v>1359</v>
       </c>
       <c r="K292" s="4"/>
-      <c r="L292" s="4"/>
-      <c r="M292" s="4"/>
-      <c r="N292" s="4"/>
+      <c r="L292" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="M292" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="N292" s="4">
+        <v>4</v>
+      </c>
       <c r="O292" s="4" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="R292" s="4" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="S292" s="4">
-        <v>93737.62</v>
+        <v>0</v>
       </c>
       <c r="T292" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U292" s="4"/>
       <c r="V292" s="4"/>
       <c r="W292" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X292" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y292" s="4"/>
       <c r="Z292" s="4" t="s">
-        <v>1386</v>
-      </c>
-      <c r="AA292" s="4"/>
+        <v>1385</v>
+      </c>
+      <c r="AA292" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB292" s="4" t="s">
         <v>47</v>
       </c>
@@ -27418,16 +27443,16 @@
         <v>1000</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C293" s="4">
-        <v>169528013</v>
+        <v>169338674</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E293" s="4">
-        <v>7815930</v>
+        <v>8330993</v>
       </c>
       <c r="F293" s="4" t="s">
         <v>49</v>
@@ -27442,47 +27467,41 @@
         <v>183</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="K293" s="4"/>
-      <c r="L293" s="4" t="s">
-        <v>516</v>
-      </c>
+      <c r="L293" s="4"/>
       <c r="M293" s="4"/>
-      <c r="N293" s="4">
-        <v>25</v>
-      </c>
+      <c r="N293" s="4"/>
       <c r="O293" s="4" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="P293" s="5"/>
       <c r="Q293" s="4" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="R293" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S293" s="4">
-        <v>0</v>
+        <v>93737.62</v>
       </c>
       <c r="T293" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U293" s="4"/>
       <c r="V293" s="4"/>
       <c r="W293" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X293" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y293" s="4"/>
       <c r="Z293" s="4" t="s">
-        <v>1390</v>
-      </c>
-      <c r="AA293" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1391</v>
+      </c>
+      <c r="AA293" s="4"/>
       <c r="AB293" s="4" t="s">
         <v>47</v>
       </c>
@@ -27492,16 +27511,16 @@
         <v>1000</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>1059</v>
+        <v>33</v>
       </c>
       <c r="C294" s="4">
-        <v>169355860</v>
+        <v>169528013</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E294" s="4">
-        <v>7063828</v>
+        <v>7815930</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>49</v>
@@ -27516,42 +27535,46 @@
         <v>183</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="K294" s="4"/>
-      <c r="L294" s="4"/>
+      <c r="L294" s="4" t="s">
+        <v>516</v>
+      </c>
       <c r="M294" s="4"/>
-      <c r="N294" s="4"/>
+      <c r="N294" s="4">
+        <v>25</v>
+      </c>
       <c r="O294" s="4" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="P294" s="5"/>
       <c r="Q294" s="4" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="R294" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S294" s="4">
-        <v>99693.64999999999</v>
+        <v>0</v>
       </c>
       <c r="T294" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U294" s="4"/>
       <c r="V294" s="4"/>
       <c r="W294" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X294" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y294" s="4"/>
       <c r="Z294" s="4" t="s">
-        <v>287</v>
+        <v>1395</v>
       </c>
       <c r="AA294" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB294" s="4" t="s">
         <v>47</v>
@@ -27565,13 +27588,13 @@
         <v>1059</v>
       </c>
       <c r="C295" s="4">
-        <v>169355855</v>
+        <v>169355860</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E295" s="4">
-        <v>5883241</v>
+        <v>7063828</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>49</v>
@@ -27586,29 +27609,27 @@
         <v>183</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="K295" s="4"/>
-      <c r="L295" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L295" s="4"/>
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
       <c r="O295" s="4" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S295" s="4">
-        <v>179936.31</v>
+        <v>99693.64999999999</v>
       </c>
       <c r="T295" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U295" s="4"/>
       <c r="V295" s="4"/>
@@ -27620,10 +27641,10 @@
       </c>
       <c r="Y295" s="4"/>
       <c r="Z295" s="4" t="s">
-        <v>403</v>
+        <v>287</v>
       </c>
       <c r="AA295" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB295" s="4" t="s">
         <v>47</v>
@@ -27634,16 +27655,16 @@
         <v>1000</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>222</v>
+        <v>1059</v>
       </c>
       <c r="C296" s="4">
-        <v>169359076</v>
+        <v>169355855</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="E296" s="4">
-        <v>6989239</v>
+        <v>5883241</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>49</v>
@@ -27658,29 +27679,29 @@
         <v>183</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
-        <v>1343</v>
+        <v>289</v>
       </c>
       <c r="M296" s="4"/>
       <c r="N296" s="4"/>
       <c r="O296" s="4" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S296" s="4">
-        <v>0</v>
+        <v>179936.31</v>
       </c>
       <c r="T296" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
@@ -27692,10 +27713,10 @@
       </c>
       <c r="Y296" s="4"/>
       <c r="Z296" s="4" t="s">
-        <v>1398</v>
+        <v>403</v>
       </c>
       <c r="AA296" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB296" s="4" t="s">
         <v>47</v>
@@ -27706,16 +27727,16 @@
         <v>1000</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C297" s="4">
-        <v>169475694</v>
+        <v>169359076</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E297" s="4">
-        <v>7353382</v>
+        <v>6989239</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>49</v>
@@ -27730,20 +27751,20 @@
         <v>183</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="M297" s="4"/>
       <c r="N297" s="4"/>
       <c r="O297" s="4" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>79</v>
@@ -27757,17 +27778,17 @@
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
       <c r="W297" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X297" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="AA297" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB297" s="4" t="s">
         <v>47</v>
@@ -27778,16 +27799,16 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>1402</v>
+        <v>246</v>
       </c>
       <c r="C298" s="4">
-        <v>168725316</v>
+        <v>169475694</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E298" s="4">
-        <v>1099225</v>
+        <v>7353382</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>49</v>
@@ -27802,50 +27823,44 @@
         <v>183</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>1404</v>
-      </c>
-      <c r="M298" s="4" t="s">
-        <v>1405</v>
-      </c>
+        <v>1348</v>
+      </c>
+      <c r="M298" s="4"/>
       <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="R298" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S298" s="4">
-        <v>724798.47</v>
+        <v>0</v>
       </c>
       <c r="T298" s="4">
-        <v>3</v>
-      </c>
-      <c r="U298" s="4" t="s">
-        <v>1408</v>
-      </c>
-      <c r="V298" s="4" t="s">
-        <v>1409</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U298" s="4"/>
+      <c r="V298" s="4"/>
       <c r="W298" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X298" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>1269</v>
+        <v>1406</v>
       </c>
       <c r="AA298" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB298" s="4" t="s">
         <v>47</v>
@@ -27856,13 +27871,13 @@
         <v>1000</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>33</v>
+        <v>1407</v>
       </c>
       <c r="C299" s="4">
-        <v>169523105</v>
+        <v>168725316</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="E299" s="4">
         <v>1099225</v>
@@ -27880,47 +27895,47 @@
         <v>183</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="M299" s="4" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
       <c r="N299" s="4"/>
       <c r="O299" s="4" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S299" s="4">
-        <v>364931.37</v>
+        <v>724798.47</v>
       </c>
       <c r="T299" s="4">
         <v>3</v>
       </c>
       <c r="U299" s="4" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="V299" s="4" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="W299" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X299" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y299" s="4"/>
       <c r="Z299" s="4" t="s">
-        <v>1410</v>
+        <v>1274</v>
       </c>
       <c r="AA299" s="4" t="s">
         <v>65</v>
@@ -27934,16 +27949,16 @@
         <v>1000</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="C300" s="4">
-        <v>169228645</v>
+        <v>169523105</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E300" s="4">
-        <v>8388337</v>
+        <v>1099225</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>49</v>
@@ -27958,43 +27973,53 @@
         <v>183</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="K300" s="4"/>
-      <c r="L300" s="4"/>
-      <c r="M300" s="4"/>
+      <c r="L300" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="M300" s="4" t="s">
+        <v>1410</v>
+      </c>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="R300" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S300" s="4">
+        <v>364931.37</v>
+      </c>
+      <c r="T300" s="4">
+        <v>3</v>
+      </c>
+      <c r="U300" s="4" t="s">
         <v>1413</v>
       </c>
-      <c r="R300" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S300" s="4">
-        <v>0</v>
-      </c>
-      <c r="T300" s="4">
-        <v>0</v>
-      </c>
-      <c r="U300" s="4"/>
-      <c r="V300" s="4"/>
+      <c r="V300" s="4" t="s">
+        <v>1414</v>
+      </c>
       <c r="W300" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X300" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
-        <v>1414</v>
-      </c>
-      <c r="AA300" s="4"/>
+        <v>1415</v>
+      </c>
+      <c r="AA300" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB300" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="301" spans="1:28">
@@ -28002,16 +28027,16 @@
         <v>1000</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>337</v>
+        <v>447</v>
       </c>
       <c r="C301" s="4">
-        <v>169348751</v>
+        <v>169228645</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E301" s="4">
-        <v>7936320</v>
+        <v>8388337</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>49</v>
@@ -28026,23 +28051,21 @@
         <v>183</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="K301" s="4"/>
-      <c r="L301" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L301" s="4"/>
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
       <c r="O301" s="4" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="R301" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S301" s="4">
         <v>0</v>
@@ -28050,25 +28073,21 @@
       <c r="T301" s="4">
         <v>0</v>
       </c>
-      <c r="U301" s="4" t="s">
-        <v>1417</v>
-      </c>
-      <c r="V301" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="U301" s="4"/>
+      <c r="V301" s="4"/>
       <c r="W301" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X301" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y301" s="4"/>
       <c r="Z301" s="4" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="AA301" s="4"/>
       <c r="AB301" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="302" spans="1:28">
@@ -28076,16 +28095,16 @@
         <v>1000</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C302" s="4">
-        <v>169528466</v>
+        <v>169348751</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E302" s="4">
-        <v>1116215</v>
+        <v>7936320</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>49</v>
@@ -28100,25 +28119,23 @@
         <v>183</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="M302" s="4" t="s">
-        <v>185</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M302" s="4"/>
       <c r="N302" s="4"/>
       <c r="O302" s="4" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="P302" s="5"/>
       <c r="Q302" s="4" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="R302" s="4" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="S302" s="4">
         <v>0</v>
@@ -28127,16 +28144,16 @@
         <v>0</v>
       </c>
       <c r="U302" s="4" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="V302" s="4" t="s">
-        <v>1422</v>
+        <v>69</v>
       </c>
       <c r="W302" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X302" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
@@ -28152,16 +28169,16 @@
         <v>1000</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="C303" s="4">
-        <v>168897696</v>
+        <v>169528466</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E303" s="4">
-        <v>8305739</v>
+        <v>1116215</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>49</v>
@@ -28176,18 +28193,16 @@
         <v>183</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4" t="s">
-        <v>880</v>
+        <v>284</v>
       </c>
       <c r="M303" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="N303" s="4">
-        <v>101</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N303" s="4"/>
       <c r="O303" s="4" t="s">
         <v>1424</v>
       </c>
@@ -28196,29 +28211,31 @@
         <v>1425</v>
       </c>
       <c r="R303" s="4" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="S303" s="4">
-        <v>184614.72</v>
+        <v>0</v>
       </c>
       <c r="T303" s="4">
-        <v>2</v>
-      </c>
-      <c r="U303" s="4"/>
-      <c r="V303" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U303" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="V303" s="4" t="s">
+        <v>1427</v>
+      </c>
       <c r="W303" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X303" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="AA303" s="4" t="s">
-        <v>305</v>
-      </c>
+        <v>1428</v>
+      </c>
+      <c r="AA303" s="4"/>
       <c r="AB303" s="4" t="s">
         <v>47</v>
       </c>
@@ -28228,16 +28245,16 @@
         <v>1000</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C304" s="4">
-        <v>169525511</v>
+        <v>168897696</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E304" s="4">
-        <v>8305779</v>
+        <v>8305739</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>49</v>
@@ -28252,7 +28269,7 @@
         <v>183</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
@@ -28265,32 +28282,32 @@
         <v>101</v>
       </c>
       <c r="O304" s="4" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S304" s="4">
-        <v>54320.17</v>
+        <v>184614.72</v>
       </c>
       <c r="T304" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U304" s="4"/>
       <c r="V304" s="4"/>
       <c r="W304" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X304" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y304" s="4"/>
       <c r="Z304" s="4" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="AA304" s="4" t="s">
         <v>305</v>
@@ -28307,13 +28324,13 @@
         <v>33</v>
       </c>
       <c r="C305" s="4">
-        <v>169525177</v>
+        <v>169525511</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="E305" s="4">
-        <v>8289365</v>
+        <v>8305779</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>49</v>
@@ -28328,33 +28345,33 @@
         <v>183</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
-        <v>1431</v>
+        <v>880</v>
       </c>
       <c r="M305" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="N305" s="4">
+        <v>101</v>
+      </c>
+      <c r="O305" s="4" t="s">
         <v>1432</v>
-      </c>
-      <c r="N305" s="4">
-        <v>36</v>
-      </c>
-      <c r="O305" s="4" t="s">
-        <v>1433</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="R305" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S305" s="4">
-        <v>469783.86</v>
+        <v>54320.17</v>
       </c>
       <c r="T305" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U305" s="4"/>
       <c r="V305" s="4"/>
@@ -28366,13 +28383,13 @@
       </c>
       <c r="Y305" s="4"/>
       <c r="Z305" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="AA305" s="4" t="s">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="AB305" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="306" spans="1:28">
@@ -28380,16 +28397,16 @@
         <v>1000</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>420</v>
+        <v>33</v>
       </c>
       <c r="C306" s="4">
-        <v>168896160</v>
+        <v>169525177</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>57</v>
+        <v>471</v>
       </c>
       <c r="E306" s="4">
-        <v>5920990</v>
+        <v>8289365</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>49</v>
@@ -28404,55 +28421,51 @@
         <v>183</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="M306" s="4" t="s">
         <v>1437</v>
       </c>
-      <c r="M306" s="4" t="s">
+      <c r="N306" s="4">
+        <v>36</v>
+      </c>
+      <c r="O306" s="4" t="s">
         <v>1438</v>
-      </c>
-      <c r="N306" s="4">
-        <v>122</v>
-      </c>
-      <c r="O306" s="4" t="s">
-        <v>1439</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="R306" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S306" s="4">
-        <v>181369.34</v>
+        <v>469783.86</v>
       </c>
       <c r="T306" s="4">
-        <v>1</v>
-      </c>
-      <c r="U306" s="4" t="s">
-        <v>1441</v>
-      </c>
-      <c r="V306" s="4" t="s">
-        <v>476</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U306" s="4"/>
+      <c r="V306" s="4"/>
       <c r="W306" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X306" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y306" s="4"/>
       <c r="Z306" s="4" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="AA306" s="4" t="s">
-        <v>1443</v>
+        <v>46</v>
       </c>
       <c r="AB306" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="307" spans="1:28">
@@ -28460,16 +28473,16 @@
         <v>1000</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>337</v>
+        <v>420</v>
       </c>
       <c r="C307" s="4">
-        <v>169365038</v>
+        <v>168896160</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E307" s="4">
-        <v>6591932</v>
+        <v>5920990</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>49</v>
@@ -28484,52 +28497,52 @@
         <v>183</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="M307" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="N307" s="4">
+        <v>122</v>
+      </c>
+      <c r="O307" s="4" t="s">
         <v>1444</v>
-      </c>
-      <c r="M307" s="4" t="s">
-        <v>1445</v>
-      </c>
-      <c r="N307" s="4">
-        <v>23</v>
-      </c>
-      <c r="O307" s="4" t="s">
-        <v>1446</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S307" s="4">
-        <v>0</v>
+        <v>181369.34</v>
       </c>
       <c r="T307" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U307" s="4" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="V307" s="4" t="s">
-        <v>43</v>
+        <v>476</v>
       </c>
       <c r="W307" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X307" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="AA307" s="4" t="s">
-        <v>46</v>
+        <v>1448</v>
       </c>
       <c r="AB307" s="4" t="s">
         <v>47</v>
@@ -28540,16 +28553,16 @@
         <v>1000</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C308" s="4">
-        <v>169240239</v>
+        <v>169365038</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E308" s="4">
-        <v>7735512</v>
+        <v>6591932</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>49</v>
@@ -28564,24 +28577,24 @@
         <v>183</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
-        <v>107</v>
+        <v>1449</v>
       </c>
       <c r="M308" s="4" t="s">
-        <v>875</v>
+        <v>1450</v>
       </c>
       <c r="N308" s="4">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="O308" s="4" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="4" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="R308" s="4" t="s">
         <v>61</v>
@@ -28592,17 +28605,21 @@
       <c r="T308" s="4">
         <v>0</v>
       </c>
-      <c r="U308" s="4"/>
-      <c r="V308" s="4"/>
+      <c r="U308" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="V308" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="W308" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X308" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="AA308" s="4" t="s">
         <v>46</v>
@@ -28619,13 +28636,13 @@
         <v>352</v>
       </c>
       <c r="C309" s="4">
-        <v>169240240</v>
+        <v>169240239</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E309" s="4">
-        <v>6588082</v>
+        <v>7735512</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>49</v>
@@ -28640,7 +28657,7 @@
         <v>183</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
@@ -28653,11 +28670,11 @@
         <v>58</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="R309" s="4" t="s">
         <v>61</v>
@@ -28678,10 +28695,10 @@
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="AA309" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB309" s="4" t="s">
         <v>47</v>
@@ -28695,13 +28712,13 @@
         <v>352</v>
       </c>
       <c r="C310" s="4">
-        <v>169240182</v>
+        <v>169240240</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E310" s="4">
-        <v>5878950</v>
+        <v>6588082</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>49</v>
@@ -28716,7 +28733,7 @@
         <v>183</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -28726,17 +28743,17 @@
         <v>875</v>
       </c>
       <c r="N310" s="4">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
         <v>1456</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S310" s="4">
         <v>0</v>
@@ -28754,10 +28771,10 @@
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="AA310" s="4" t="s">
-        <v>351</v>
+        <v>65</v>
       </c>
       <c r="AB310" s="4" t="s">
         <v>47</v>
@@ -28768,16 +28785,16 @@
         <v>1000</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>1331</v>
+        <v>352</v>
       </c>
       <c r="C311" s="4">
-        <v>169240231</v>
+        <v>169240182</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E311" s="4">
-        <v>8026082</v>
+        <v>5878950</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>49</v>
@@ -28792,27 +28809,27 @@
         <v>183</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
-        <v>1175</v>
+        <v>107</v>
       </c>
       <c r="M311" s="4" t="s">
-        <v>1458</v>
+        <v>875</v>
       </c>
       <c r="N311" s="4">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="O311" s="4" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="P311" s="5"/>
       <c r="Q311" s="4" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="R311" s="4" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="S311" s="4">
         <v>0</v>
@@ -28830,10 +28847,10 @@
       </c>
       <c r="Y311" s="4"/>
       <c r="Z311" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="AA311" s="4" t="s">
-        <v>46</v>
+        <v>351</v>
       </c>
       <c r="AB311" s="4" t="s">
         <v>47</v>
@@ -28844,16 +28861,16 @@
         <v>1000</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>33</v>
+        <v>1336</v>
       </c>
       <c r="C312" s="4">
-        <v>168896205</v>
+        <v>169240231</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E312" s="4">
-        <v>6530459</v>
+        <v>8026082</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>49</v>
@@ -28868,24 +28885,24 @@
         <v>183</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>874</v>
+        <v>1175</v>
       </c>
       <c r="M312" s="4" t="s">
-        <v>875</v>
+        <v>1463</v>
       </c>
       <c r="N312" s="4">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="O312" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>61</v>
@@ -28896,21 +28913,17 @@
       <c r="T312" s="4">
         <v>0</v>
       </c>
-      <c r="U312" s="4" t="s">
-        <v>1464</v>
-      </c>
-      <c r="V312" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U312" s="4"/>
+      <c r="V312" s="4"/>
       <c r="W312" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X312" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="AA312" s="4" t="s">
         <v>46</v>
@@ -28924,16 +28937,16 @@
         <v>1000</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1331</v>
+        <v>33</v>
       </c>
       <c r="C313" s="4">
-        <v>169240188</v>
+        <v>168896205</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E313" s="4">
-        <v>6567408</v>
+        <v>6530459</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>49</v>
@@ -28948,17 +28961,17 @@
         <v>183</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>1438</v>
+        <v>874</v>
       </c>
       <c r="M313" s="4" t="s">
-        <v>1466</v>
+        <v>875</v>
       </c>
       <c r="N313" s="4">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="O313" s="4" t="s">
         <v>1467</v>
@@ -28980,19 +28993,21 @@
         <v>1469</v>
       </c>
       <c r="V313" s="4" t="s">
-        <v>1470</v>
+        <v>476</v>
       </c>
       <c r="W313" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X313" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
-        <v>1471</v>
-      </c>
-      <c r="AA313" s="4"/>
+        <v>1470</v>
+      </c>
+      <c r="AA313" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB313" s="4" t="s">
         <v>47</v>
       </c>
@@ -29002,16 +29017,16 @@
         <v>1000</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>33</v>
+        <v>1336</v>
       </c>
       <c r="C314" s="4">
-        <v>169528015</v>
+        <v>169240188</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E314" s="4">
-        <v>7609168</v>
+        <v>6567408</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>49</v>
@@ -29026,24 +29041,24 @@
         <v>183</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1472</v>
+        <v>1441</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>949</v>
+        <v>1443</v>
       </c>
       <c r="M314" s="4" t="s">
-        <v>749</v>
+        <v>1471</v>
       </c>
       <c r="N314" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O314" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>61</v>
@@ -29054,21 +29069,23 @@
       <c r="T314" s="4">
         <v>0</v>
       </c>
-      <c r="U314" s="4"/>
-      <c r="V314" s="4"/>
+      <c r="U314" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="V314" s="4" t="s">
+        <v>1475</v>
+      </c>
       <c r="W314" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X314" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
-        <v>1475</v>
-      </c>
-      <c r="AA314" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1476</v>
+      </c>
+      <c r="AA314" s="4"/>
       <c r="AB314" s="4" t="s">
         <v>47</v>
       </c>
@@ -29078,16 +29095,16 @@
         <v>1000</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>1402</v>
+        <v>33</v>
       </c>
       <c r="C315" s="4">
-        <v>168725318</v>
+        <v>169528015</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E315" s="4">
-        <v>7378230</v>
+        <v>7609168</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>49</v>
@@ -29102,52 +29119,48 @@
         <v>183</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
-        <v>1477</v>
+        <v>949</v>
       </c>
       <c r="M315" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="N315" s="4">
+        <v>12</v>
+      </c>
+      <c r="O315" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="N315" s="4">
-        <v>17</v>
-      </c>
-      <c r="O315" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="R315" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S315" s="4">
-        <v>736214.27</v>
+        <v>0</v>
       </c>
       <c r="T315" s="4">
-        <v>6</v>
-      </c>
-      <c r="U315" s="4" t="s">
-        <v>1481</v>
-      </c>
-      <c r="V315" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U315" s="4"/>
+      <c r="V315" s="4"/>
       <c r="W315" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X315" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y315" s="4"/>
       <c r="Z315" s="4" t="s">
-        <v>592</v>
+        <v>1480</v>
       </c>
       <c r="AA315" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB315" s="4" t="s">
         <v>47</v>
@@ -29158,16 +29171,16 @@
         <v>1000</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>246</v>
+        <v>1407</v>
       </c>
       <c r="C316" s="4">
-        <v>169350529</v>
+        <v>168725318</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E316" s="4">
-        <v>6817697</v>
+        <v>7378230</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>49</v>
@@ -29182,41 +29195,49 @@
         <v>183</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M316" s="4"/>
-      <c r="N316" s="4"/>
+        <v>1482</v>
+      </c>
+      <c r="M316" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="N316" s="4">
+        <v>17</v>
+      </c>
       <c r="O316" s="4" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="4" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="R316" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S316" s="4">
-        <v>0</v>
+        <v>736214.27</v>
       </c>
       <c r="T316" s="4">
-        <v>0</v>
-      </c>
-      <c r="U316" s="4"/>
-      <c r="V316" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="U316" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="V316" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W316" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X316" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>1485</v>
+        <v>592</v>
       </c>
       <c r="AA316" s="4" t="s">
         <v>46</v>
@@ -29230,16 +29251,16 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>447</v>
+        <v>246</v>
       </c>
       <c r="C317" s="4">
-        <v>168910101</v>
+        <v>169350529</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E317" s="4">
-        <v>8307826</v>
+        <v>6817697</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>49</v>
@@ -29254,21 +29275,23 @@
         <v>183</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="K317" s="4"/>
-      <c r="L317" s="4"/>
+      <c r="L317" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M317" s="4"/>
       <c r="N317" s="4"/>
       <c r="O317" s="4" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="R317" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S317" s="4">
         <v>0</v>
@@ -29279,17 +29302,17 @@
       <c r="U317" s="4"/>
       <c r="V317" s="4"/>
       <c r="W317" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X317" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y317" s="4"/>
       <c r="Z317" s="4" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="AA317" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB317" s="4" t="s">
         <v>47</v>
@@ -29303,13 +29326,13 @@
         <v>447</v>
       </c>
       <c r="C318" s="4">
-        <v>168908257</v>
+        <v>168910101</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>580</v>
+        <v>188</v>
       </c>
       <c r="E318" s="4">
-        <v>6945604</v>
+        <v>8307826</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>49</v>
@@ -29324,23 +29347,21 @@
         <v>183</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="K318" s="4"/>
-      <c r="L318" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L318" s="4"/>
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
       <c r="O318" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="R318" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S318" s="4">
         <v>0</v>
@@ -29348,12 +29369,8 @@
       <c r="T318" s="4">
         <v>0</v>
       </c>
-      <c r="U318" s="4" t="s">
-        <v>1492</v>
-      </c>
-      <c r="V318" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="U318" s="4"/>
+      <c r="V318" s="4"/>
       <c r="W318" s="4">
         <v>7</v>
       </c>
@@ -29362,10 +29379,10 @@
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="AA318" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB318" s="4" t="s">
         <v>47</v>
@@ -29376,16 +29393,16 @@
         <v>1000</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="C319" s="4">
-        <v>169517835</v>
+        <v>168908257</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>471</v>
+        <v>580</v>
       </c>
       <c r="E319" s="4">
-        <v>7666029</v>
+        <v>6945604</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>49</v>
@@ -29400,18 +29417,14 @@
         <v>183</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
-        <v>1494</v>
-      </c>
-      <c r="M319" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="N319" s="4">
-        <v>19</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M319" s="4"/>
+      <c r="N319" s="4"/>
       <c r="O319" s="4" t="s">
         <v>1495</v>
       </c>
@@ -29420,13 +29433,13 @@
         <v>1496</v>
       </c>
       <c r="R319" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S319" s="4">
-        <v>65879.17999999999</v>
+        <v>0</v>
       </c>
       <c r="T319" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U319" s="4" t="s">
         <v>1497</v>
@@ -29435,10 +29448,10 @@
         <v>476</v>
       </c>
       <c r="W319" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X319" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y319" s="4"/>
       <c r="Z319" s="4" t="s">
@@ -29459,13 +29472,13 @@
         <v>33</v>
       </c>
       <c r="C320" s="4">
-        <v>169531384</v>
+        <v>169517835</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>188</v>
+        <v>471</v>
       </c>
       <c r="E320" s="4">
-        <v>7770159</v>
+        <v>7666029</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>49</v>
@@ -29480,17 +29493,17 @@
         <v>183</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="M320" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="M320" s="4" t="s">
-        <v>1499</v>
-      </c>
       <c r="N320" s="4">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O320" s="4" t="s">
         <v>1500</v>
@@ -29500,13 +29513,13 @@
         <v>1501</v>
       </c>
       <c r="R320" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S320" s="4">
-        <v>398662.86</v>
+        <v>65879.17999999999</v>
       </c>
       <c r="T320" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U320" s="4" t="s">
         <v>1502</v>
@@ -29528,7 +29541,7 @@
         <v>46</v>
       </c>
       <c r="AB320" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="321" spans="1:28">
@@ -29536,16 +29549,16 @@
         <v>1000</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C321" s="4">
-        <v>169351859</v>
+        <v>169531384</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E321" s="4">
-        <v>6824154</v>
+        <v>7770159</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>49</v>
@@ -29560,51 +29573,55 @@
         <v>183</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>354</v>
+        <v>712</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>516</v>
+        <v>1504</v>
       </c>
       <c r="N321" s="4">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="O321" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="R321" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S321" s="4">
-        <v>0</v>
+        <v>398662.86</v>
       </c>
       <c r="T321" s="4">
-        <v>0</v>
-      </c>
-      <c r="U321" s="4"/>
-      <c r="V321" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="U321" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="V321" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W321" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X321" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="AA321" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB321" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="322" spans="1:28">
@@ -29612,16 +29629,16 @@
         <v>1000</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C322" s="4">
-        <v>169521367</v>
+        <v>169351859</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="E322" s="4">
-        <v>7984315</v>
+        <v>6824154</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>49</v>
@@ -29636,41 +29653,45 @@
         <v>183</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1507</v>
+        <v>1491</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M322" s="4"/>
-      <c r="N322" s="4"/>
+        <v>354</v>
+      </c>
+      <c r="M322" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="N322" s="4">
+        <v>12</v>
+      </c>
       <c r="O322" s="4" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="P322" s="5"/>
       <c r="Q322" s="4" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="R322" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S322" s="4">
-        <v>807922.91</v>
+        <v>0</v>
       </c>
       <c r="T322" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U322" s="4"/>
       <c r="V322" s="4"/>
       <c r="W322" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X322" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y322" s="4"/>
       <c r="Z322" s="4" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="AA322" s="4" t="s">
         <v>46</v>
@@ -29684,16 +29705,16 @@
         <v>1000</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1293</v>
+        <v>33</v>
       </c>
       <c r="C323" s="4">
-        <v>169355862</v>
+        <v>169521367</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>57</v>
+        <v>471</v>
       </c>
       <c r="E323" s="4">
-        <v>1025722</v>
+        <v>7984315</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>49</v>
@@ -29708,49 +29729,45 @@
         <v>183</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M323" s="4" t="s">
-        <v>1511</v>
-      </c>
+      <c r="M323" s="4"/>
       <c r="N323" s="4"/>
       <c r="O323" s="4" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="4" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="R323" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S323" s="4">
-        <v>0</v>
+        <v>807922.91</v>
       </c>
       <c r="T323" s="4">
-        <v>0</v>
-      </c>
-      <c r="U323" s="4" t="s">
-        <v>1514</v>
-      </c>
-      <c r="V323" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U323" s="4"/>
+      <c r="V323" s="4"/>
       <c r="W323" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X323" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="AA323" s="4"/>
+        <v>1515</v>
+      </c>
+      <c r="AA323" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB323" s="4" t="s">
         <v>47</v>
       </c>
@@ -29760,16 +29777,16 @@
         <v>1000</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>33</v>
+        <v>1298</v>
       </c>
       <c r="C324" s="4">
-        <v>168895978</v>
+        <v>169355862</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E324" s="4">
-        <v>1052361</v>
+        <v>1025722</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>49</v>
@@ -29784,11 +29801,11 @@
         <v>183</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
-        <v>177</v>
+        <v>289</v>
       </c>
       <c r="M324" s="4" t="s">
         <v>1516</v>
@@ -29802,7 +29819,7 @@
         <v>1518</v>
       </c>
       <c r="R324" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S324" s="4">
         <v>0</v>
@@ -29814,17 +29831,17 @@
         <v>1519</v>
       </c>
       <c r="V324" s="4" t="s">
-        <v>1520</v>
+        <v>127</v>
       </c>
       <c r="W324" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X324" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1521</v>
+        <v>671</v>
       </c>
       <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
@@ -29836,16 +29853,16 @@
         <v>1000</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1522</v>
+        <v>33</v>
       </c>
       <c r="C325" s="4">
-        <v>168896121</v>
+        <v>168895978</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E325" s="4">
-        <v>1052274</v>
+        <v>1052361</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>49</v>
@@ -29860,22 +29877,22 @@
         <v>183</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
-        <v>1523</v>
+        <v>177</v>
       </c>
       <c r="M325" s="4" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="R325" s="4" t="s">
         <v>41</v>
@@ -29887,20 +29904,20 @@
         <v>0</v>
       </c>
       <c r="U325" s="4" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="V325" s="4" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="W325" s="4">
         <v>8</v>
       </c>
       <c r="X325" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="AA325" s="4"/>
       <c r="AB325" s="4" t="s">
@@ -29912,16 +29929,16 @@
         <v>1000</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="C326" s="4">
-        <v>169240252</v>
+        <v>168896121</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E326" s="4">
-        <v>1051677</v>
+        <v>1052274</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>49</v>
@@ -29936,14 +29953,14 @@
         <v>183</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>320</v>
+        <v>1528</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>299</v>
+        <v>1529</v>
       </c>
       <c r="N326" s="4"/>
       <c r="O326" s="4" t="s">
@@ -29954,7 +29971,7 @@
         <v>1531</v>
       </c>
       <c r="R326" s="4" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="S326" s="4">
         <v>0</v>
@@ -29966,21 +29983,19 @@
         <v>1532</v>
       </c>
       <c r="V326" s="4" t="s">
-        <v>1528</v>
+        <v>1533</v>
       </c>
       <c r="W326" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X326" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>1533</v>
-      </c>
-      <c r="AA326" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1534</v>
+      </c>
+      <c r="AA326" s="4"/>
       <c r="AB326" s="4" t="s">
         <v>47</v>
       </c>
@@ -29990,16 +30005,16 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="C327" s="4">
-        <v>168896063</v>
+        <v>169240252</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E327" s="4">
-        <v>1103901</v>
+        <v>1051677</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>49</v>
@@ -30014,25 +30029,25 @@
         <v>183</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
         <v>320</v>
       </c>
       <c r="M327" s="4" t="s">
-        <v>791</v>
+        <v>299</v>
       </c>
       <c r="N327" s="4"/>
       <c r="O327" s="4" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="P327" s="5"/>
       <c r="Q327" s="4" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="R327" s="4" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S327" s="4">
         <v>0</v>
@@ -30041,13 +30056,13 @@
         <v>0</v>
       </c>
       <c r="U327" s="4" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="V327" s="4" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="W327" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>202</v>
@@ -30068,16 +30083,16 @@
         <v>1000</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>455</v>
+        <v>1527</v>
       </c>
       <c r="C328" s="4">
-        <v>168896653</v>
+        <v>168896063</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E328" s="4">
-        <v>1052622</v>
+        <v>1103901</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>49</v>
@@ -30092,22 +30107,22 @@
         <v>183</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
-        <v>1539</v>
+        <v>320</v>
       </c>
       <c r="M328" s="4" t="s">
-        <v>1523</v>
+        <v>791</v>
       </c>
       <c r="N328" s="4"/>
       <c r="O328" s="4" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="R328" s="4" t="s">
         <v>41</v>
@@ -30118,8 +30133,12 @@
       <c r="T328" s="4">
         <v>0</v>
       </c>
-      <c r="U328" s="4"/>
-      <c r="V328" s="4"/>
+      <c r="U328" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="V328" s="4" t="s">
+        <v>1542</v>
+      </c>
       <c r="W328" s="4">
         <v>8</v>
       </c>
@@ -30128,10 +30147,10 @@
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="AA328" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB328" s="4" t="s">
         <v>47</v>
@@ -30142,16 +30161,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1522</v>
+        <v>455</v>
       </c>
       <c r="C329" s="4">
-        <v>168896015</v>
+        <v>168896653</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E329" s="4">
-        <v>7900282</v>
+        <v>1052622</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>49</v>
@@ -30166,38 +30185,34 @@
         <v>183</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="M329" s="4" t="s">
-        <v>177</v>
+        <v>1528</v>
       </c>
       <c r="N329" s="4"/>
       <c r="O329" s="4" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="R329" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S329" s="4">
-        <v>127746.05</v>
+        <v>0</v>
       </c>
       <c r="T329" s="4">
-        <v>1</v>
-      </c>
-      <c r="U329" s="4" t="s">
-        <v>1546</v>
-      </c>
-      <c r="V329" s="4" t="s">
-        <v>476</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U329" s="4"/>
+      <c r="V329" s="4"/>
       <c r="W329" s="4">
         <v>8</v>
       </c>
@@ -30209,7 +30224,7 @@
         <v>1547</v>
       </c>
       <c r="AA329" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB329" s="4" t="s">
         <v>47</v>
@@ -30220,16 +30235,16 @@
         <v>1000</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>455</v>
+        <v>1527</v>
       </c>
       <c r="C330" s="4">
-        <v>168896073</v>
+        <v>168896015</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E330" s="4">
-        <v>7769908</v>
+        <v>7900282</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>49</v>
@@ -30244,14 +30259,14 @@
         <v>183</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
         <v>1548</v>
       </c>
       <c r="M330" s="4" t="s">
-        <v>1523</v>
+        <v>177</v>
       </c>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
@@ -30265,13 +30280,17 @@
         <v>41</v>
       </c>
       <c r="S330" s="4">
-        <v>393191.56</v>
+        <v>127746.05</v>
       </c>
       <c r="T330" s="4">
         <v>1</v>
       </c>
-      <c r="U330" s="4"/>
-      <c r="V330" s="4"/>
+      <c r="U330" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="V330" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W330" s="4">
         <v>8</v>
       </c>
@@ -30280,7 +30299,7 @@
       </c>
       <c r="Y330" s="4"/>
       <c r="Z330" s="4" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="AA330" s="4" t="s">
         <v>215</v>
@@ -30297,13 +30316,13 @@
         <v>455</v>
       </c>
       <c r="C331" s="4">
-        <v>168896081</v>
+        <v>168896073</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E331" s="4">
-        <v>6943901</v>
+        <v>7769908</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>49</v>
@@ -30318,40 +30337,34 @@
         <v>183</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="M331" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="N331" s="4">
-        <v>12</v>
-      </c>
+        <v>1528</v>
+      </c>
+      <c r="N331" s="4"/>
       <c r="O331" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S331" s="4">
-        <v>0</v>
+        <v>393191.56</v>
       </c>
       <c r="T331" s="4">
-        <v>0</v>
-      </c>
-      <c r="U331" s="4" t="s">
-        <v>1554</v>
-      </c>
-      <c r="V331" s="4" t="s">
-        <v>966</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U331" s="4"/>
+      <c r="V331" s="4"/>
       <c r="W331" s="4">
         <v>8</v>
       </c>
@@ -30360,10 +30373,10 @@
       </c>
       <c r="Y331" s="4"/>
       <c r="Z331" s="4" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="AA331" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB331" s="4" t="s">
         <v>47</v>
@@ -30374,16 +30387,16 @@
         <v>1000</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1293</v>
+        <v>455</v>
       </c>
       <c r="C332" s="4">
-        <v>168896094</v>
+        <v>168896081</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E332" s="4">
-        <v>1052309</v>
+        <v>6943901</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>49</v>
@@ -30398,24 +30411,24 @@
         <v>183</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="M332" s="4" t="s">
         <v>568</v>
       </c>
       <c r="N332" s="4">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="O332" s="4" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>41</v>
@@ -30427,10 +30440,10 @@
         <v>0</v>
       </c>
       <c r="U332" s="4" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="V332" s="4" t="s">
-        <v>1033</v>
+        <v>966</v>
       </c>
       <c r="W332" s="4">
         <v>8</v>
@@ -30440,10 +30453,10 @@
       </c>
       <c r="Y332" s="4"/>
       <c r="Z332" s="4" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="AA332" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB332" s="4" t="s">
         <v>47</v>
@@ -30454,16 +30467,16 @@
         <v>1000</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>196</v>
+        <v>1298</v>
       </c>
       <c r="C333" s="4">
-        <v>169217388</v>
+        <v>168896094</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>1560</v>
+        <v>57</v>
       </c>
       <c r="E333" s="4">
-        <v>1052314</v>
+        <v>1052309</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>49</v>
@@ -30478,16 +30491,18 @@
         <v>183</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="M333" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="N333" s="4"/>
+        <v>568</v>
+      </c>
+      <c r="N333" s="4">
+        <v>59</v>
+      </c>
       <c r="O333" s="4" t="s">
         <v>1561</v>
       </c>
@@ -30496,7 +30511,7 @@
         <v>1562</v>
       </c>
       <c r="R333" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S333" s="4">
         <v>0</v>
@@ -30504,20 +30519,24 @@
       <c r="T333" s="4">
         <v>0</v>
       </c>
-      <c r="U333" s="4"/>
-      <c r="V333" s="4"/>
+      <c r="U333" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="V333" s="4" t="s">
+        <v>1033</v>
+      </c>
       <c r="W333" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X333" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y333" s="4"/>
       <c r="Z333" s="4" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="AA333" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB333" s="4" t="s">
         <v>47</v>
@@ -30528,16 +30547,16 @@
         <v>1000</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>455</v>
+        <v>196</v>
       </c>
       <c r="C334" s="4">
-        <v>168896120</v>
+        <v>169217388</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>57</v>
+        <v>1565</v>
       </c>
       <c r="E334" s="4">
-        <v>1052344</v>
+        <v>1052314</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>49</v>
@@ -30552,25 +30571,25 @@
         <v>183</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="M334" s="4" t="s">
-        <v>1564</v>
+        <v>907</v>
       </c>
       <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="R334" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S334" s="4">
         <v>0</v>
@@ -30578,14 +30597,10 @@
       <c r="T334" s="4">
         <v>0</v>
       </c>
-      <c r="U334" s="4" t="s">
-        <v>1567</v>
-      </c>
-      <c r="V334" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="U334" s="4"/>
+      <c r="V334" s="4"/>
       <c r="W334" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X334" s="4" t="s">
         <v>202</v>
@@ -30595,7 +30610,7 @@
         <v>1568</v>
       </c>
       <c r="AA334" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB334" s="4" t="s">
         <v>47</v>
@@ -30606,16 +30621,16 @@
         <v>1000</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>196</v>
+        <v>455</v>
       </c>
       <c r="C335" s="4">
-        <v>169097745</v>
+        <v>168896120</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E335" s="4">
-        <v>6930250</v>
+        <v>1052344</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>49</v>
@@ -30630,18 +30645,16 @@
         <v>183</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M335" s="4" t="s">
         <v>1569</v>
       </c>
-      <c r="M335" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="N335" s="4">
-        <v>22</v>
-      </c>
+      <c r="N335" s="4"/>
       <c r="O335" s="4" t="s">
         <v>1570</v>
       </c>
@@ -30662,10 +30675,10 @@
         <v>1572</v>
       </c>
       <c r="V335" s="4" t="s">
-        <v>303</v>
+        <v>153</v>
       </c>
       <c r="W335" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X335" s="4" t="s">
         <v>202</v>
@@ -30686,16 +30699,16 @@
         <v>1000</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C336" s="4">
-        <v>169361669</v>
+        <v>169097745</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E336" s="4">
-        <v>7730211</v>
+        <v>6930250</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>49</v>
@@ -30710,12 +30723,18 @@
         <v>183</v>
       </c>
       <c r="J336" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="K336" s="4"/>
+      <c r="L336" s="4" t="s">
         <v>1574</v>
       </c>
-      <c r="K336" s="4"/>
-      <c r="L336" s="4"/>
-      <c r="M336" s="4"/>
-      <c r="N336" s="4"/>
+      <c r="M336" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="N336" s="4">
+        <v>22</v>
+      </c>
       <c r="O336" s="4" t="s">
         <v>1575</v>
       </c>
@@ -30724,7 +30743,7 @@
         <v>1576</v>
       </c>
       <c r="R336" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S336" s="4">
         <v>0</v>
@@ -30736,10 +30755,10 @@
         <v>1577</v>
       </c>
       <c r="V336" s="4" t="s">
-        <v>74</v>
+        <v>303</v>
       </c>
       <c r="W336" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X336" s="4" t="s">
         <v>202</v>
@@ -30749,7 +30768,7 @@
         <v>1578</v>
       </c>
       <c r="AA336" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB336" s="4" t="s">
         <v>47</v>
@@ -30760,16 +30779,16 @@
         <v>1000</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="C337" s="4">
-        <v>169527541</v>
+        <v>169361669</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E337" s="4">
-        <v>7798459</v>
+        <v>7730211</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>49</v>
@@ -30784,25 +30803,21 @@
         <v>183</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="K337" s="4"/>
-      <c r="L337" s="4" t="s">
-        <v>613</v>
-      </c>
+      <c r="L337" s="4"/>
       <c r="M337" s="4"/>
-      <c r="N337" s="4">
-        <v>4</v>
-      </c>
+      <c r="N337" s="4"/>
       <c r="O337" s="4" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="R337" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S337" s="4">
         <v>0</v>
@@ -30811,23 +30826,23 @@
         <v>0</v>
       </c>
       <c r="U337" s="4" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="V337" s="4" t="s">
-        <v>445</v>
+        <v>74</v>
       </c>
       <c r="W337" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X337" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AA337" s="4" t="s">
-        <v>305</v>
+        <v>65</v>
       </c>
       <c r="AB337" s="4" t="s">
         <v>47</v>
@@ -30841,13 +30856,13 @@
         <v>33</v>
       </c>
       <c r="C338" s="4">
-        <v>169515495</v>
+        <v>169527541</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E338" s="4">
-        <v>5905827</v>
+        <v>7798459</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>49</v>
@@ -30862,14 +30877,16 @@
         <v>183</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="K338" s="4"/>
       <c r="L338" s="4" t="s">
-        <v>289</v>
+        <v>613</v>
       </c>
       <c r="M338" s="4"/>
-      <c r="N338" s="4"/>
+      <c r="N338" s="4">
+        <v>4</v>
+      </c>
       <c r="O338" s="4" t="s">
         <v>1584</v>
       </c>
@@ -30886,8 +30903,12 @@
       <c r="T338" s="4">
         <v>0</v>
       </c>
-      <c r="U338" s="4"/>
-      <c r="V338" s="4"/>
+      <c r="U338" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="V338" s="4" t="s">
+        <v>445</v>
+      </c>
       <c r="W338" s="4">
         <v>0</v>
       </c>
@@ -30896,9 +30917,11 @@
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
-        <v>1586</v>
-      </c>
-      <c r="AA338" s="4"/>
+        <v>1587</v>
+      </c>
+      <c r="AA338" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="AB338" s="4" t="s">
         <v>47</v>
       </c>
@@ -30908,16 +30931,16 @@
         <v>1000</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C339" s="4">
-        <v>169339010</v>
+        <v>169515495</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E339" s="4">
-        <v>8029935</v>
+        <v>5905827</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>49</v>
@@ -30932,43 +30955,43 @@
         <v>183</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="K339" s="4"/>
-      <c r="L339" s="4"/>
+      <c r="L339" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M339" s="4"/>
       <c r="N339" s="4"/>
       <c r="O339" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="R339" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S339" s="4">
-        <v>153870.42</v>
+        <v>0</v>
       </c>
       <c r="T339" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U339" s="4"/>
       <c r="V339" s="4"/>
       <c r="W339" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X339" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y339" s="4"/>
       <c r="Z339" s="4" t="s">
-        <v>1590</v>
-      </c>
-      <c r="AA339" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1591</v>
+      </c>
+      <c r="AA339" s="4"/>
       <c r="AB339" s="4" t="s">
         <v>47</v>
       </c>
@@ -30981,13 +31004,13 @@
         <v>337</v>
       </c>
       <c r="C340" s="4">
-        <v>169334978</v>
+        <v>169339010</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E340" s="4">
-        <v>2380524</v>
+        <v>8029935</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>49</v>
@@ -31002,36 +31025,30 @@
         <v>183</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="K340" s="4"/>
-      <c r="L340" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L340" s="4"/>
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="R340" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S340" s="4">
-        <v>0</v>
+        <v>153870.42</v>
       </c>
       <c r="T340" s="4">
-        <v>0</v>
-      </c>
-      <c r="U340" s="4" t="s">
-        <v>1593</v>
-      </c>
-      <c r="V340" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U340" s="4"/>
+      <c r="V340" s="4"/>
       <c r="W340" s="4">
         <v>2</v>
       </c>
@@ -31040,7 +31057,7 @@
       </c>
       <c r="Y340" s="4"/>
       <c r="Z340" s="4" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="AA340" s="4" t="s">
         <v>46</v>
@@ -31054,16 +31071,16 @@
         <v>1000</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C341" s="4">
-        <v>169512979</v>
+        <v>169334978</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E341" s="4">
-        <v>1107566</v>
+        <v>2380524</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>49</v>
@@ -31078,10 +31095,12 @@
         <v>183</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K341" s="4"/>
-      <c r="L341" s="4"/>
+      <c r="L341" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M341" s="4"/>
       <c r="N341" s="4"/>
       <c r="O341" s="4" t="s">
@@ -31095,10 +31114,10 @@
         <v>41</v>
       </c>
       <c r="S341" s="4">
-        <v>41450.93</v>
+        <v>0</v>
       </c>
       <c r="T341" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U341" s="4" t="s">
         <v>1598</v>
@@ -31107,10 +31126,10 @@
         <v>140</v>
       </c>
       <c r="W341" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X341" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y341" s="4"/>
       <c r="Z341" s="4" t="s">
@@ -31131,13 +31150,13 @@
         <v>33</v>
       </c>
       <c r="C342" s="4">
-        <v>169520460</v>
+        <v>169512979</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E342" s="4">
-        <v>7654420</v>
+        <v>1107566</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>49</v>
@@ -31152,36 +31171,34 @@
         <v>183</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="K342" s="4"/>
-      <c r="L342" s="4" t="s">
-        <v>1600</v>
-      </c>
-      <c r="M342" s="4" t="s">
+      <c r="L342" s="4"/>
+      <c r="M342" s="4"/>
+      <c r="N342" s="4"/>
+      <c r="O342" s="4" t="s">
         <v>1601</v>
-      </c>
-      <c r="N342" s="4">
-        <v>48</v>
-      </c>
-      <c r="O342" s="4" t="s">
-        <v>1602</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="R342" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S342" s="4">
-        <v>0</v>
+        <v>41450.93</v>
       </c>
       <c r="T342" s="4">
-        <v>0</v>
-      </c>
-      <c r="U342" s="4"/>
-      <c r="V342" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U342" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="V342" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="W342" s="4">
         <v>0</v>
       </c>
@@ -31193,7 +31210,7 @@
         <v>1604</v>
       </c>
       <c r="AA342" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB342" s="4" t="s">
         <v>47</v>
@@ -31204,16 +31221,16 @@
         <v>1000</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="C343" s="4">
-        <v>169087616</v>
+        <v>169520460</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E343" s="4">
-        <v>8397569</v>
+        <v>7654420</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>49</v>
@@ -31228,21 +31245,27 @@
         <v>183</v>
       </c>
       <c r="J343" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="K343" s="4"/>
+      <c r="L343" s="4" t="s">
         <v>1605</v>
       </c>
-      <c r="K343" s="4"/>
-      <c r="L343" s="4"/>
-      <c r="M343" s="4"/>
-      <c r="N343" s="4"/>
+      <c r="M343" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="N343" s="4">
+        <v>48</v>
+      </c>
       <c r="O343" s="4" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="R343" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S343" s="4">
         <v>0</v>
@@ -31253,18 +31276,20 @@
       <c r="U343" s="4"/>
       <c r="V343" s="4"/>
       <c r="W343" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X343" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y343" s="4"/>
       <c r="Z343" s="4" t="s">
-        <v>1608</v>
-      </c>
-      <c r="AA343" s="4"/>
+        <v>1609</v>
+      </c>
+      <c r="AA343" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB343" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="344" spans="1:28">
@@ -31275,13 +31300,13 @@
         <v>246</v>
       </c>
       <c r="C344" s="4">
-        <v>169088129</v>
+        <v>169087616</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E344" s="4">
-        <v>8397590</v>
+        <v>8397569</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>49</v>
@@ -31296,18 +31321,18 @@
         <v>183</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="K344" s="4"/>
       <c r="L344" s="4"/>
       <c r="M344" s="4"/>
       <c r="N344" s="4"/>
       <c r="O344" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="P344" s="5"/>
       <c r="Q344" s="4" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="R344" s="4" t="s">
         <v>61</v>
@@ -31328,7 +31353,7 @@
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="AA344" s="4"/>
       <c r="AB344" s="4" t="s">
@@ -31340,16 +31365,16 @@
         <v>1000</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C345" s="4">
-        <v>168912853</v>
+        <v>169088129</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E345" s="4">
-        <v>6956336</v>
+        <v>8397590</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>49</v>
@@ -31364,20 +31389,14 @@
         <v>183</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="K345" s="4"/>
-      <c r="L345" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="M345" s="4" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N345" s="4">
-        <v>2</v>
-      </c>
+      <c r="L345" s="4"/>
+      <c r="M345" s="4"/>
+      <c r="N345" s="4"/>
       <c r="O345" s="4" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="P345" s="5"/>
       <c r="Q345" s="4" t="s">
@@ -31387,32 +31406,26 @@
         <v>61</v>
       </c>
       <c r="S345" s="4">
-        <v>161390.36</v>
+        <v>0</v>
       </c>
       <c r="T345" s="4">
+        <v>0</v>
+      </c>
+      <c r="U345" s="4"/>
+      <c r="V345" s="4"/>
+      <c r="W345" s="4">
         <v>4</v>
-      </c>
-      <c r="U345" s="4" t="s">
-        <v>1613</v>
-      </c>
-      <c r="V345" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="W345" s="4">
-        <v>7</v>
       </c>
       <c r="X345" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1614</v>
-      </c>
-      <c r="AA345" s="4" t="s">
-        <v>336</v>
-      </c>
+        <v>1615</v>
+      </c>
+      <c r="AA345" s="4"/>
       <c r="AB345" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="346" spans="1:28">
@@ -31420,16 +31433,16 @@
         <v>1000</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>33</v>
+        <v>230</v>
       </c>
       <c r="C346" s="4">
-        <v>169528116</v>
+        <v>168912853</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E346" s="4">
-        <v>6528821</v>
+        <v>6956336</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>49</v>
@@ -31444,14 +31457,18 @@
         <v>183</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="K346" s="4"/>
       <c r="L346" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M346" s="4"/>
-      <c r="N346" s="4"/>
+        <v>812</v>
+      </c>
+      <c r="M346" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N346" s="4">
+        <v>2</v>
+      </c>
       <c r="O346" s="4" t="s">
         <v>1616</v>
       </c>
@@ -31460,32 +31477,32 @@
         <v>1617</v>
       </c>
       <c r="R346" s="4" t="s">
-        <v>257</v>
+        <v>61</v>
       </c>
       <c r="S346" s="4">
-        <v>0</v>
+        <v>161390.36</v>
       </c>
       <c r="T346" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U346" s="4" t="s">
         <v>1618</v>
       </c>
       <c r="V346" s="4" t="s">
-        <v>476</v>
+        <v>127</v>
       </c>
       <c r="W346" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X346" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y346" s="4"/>
       <c r="Z346" s="4" t="s">
         <v>1619</v>
       </c>
       <c r="AA346" s="4" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
       <c r="AB346" s="4" t="s">
         <v>47</v>
@@ -31499,13 +31516,13 @@
         <v>33</v>
       </c>
       <c r="C347" s="4">
-        <v>169465695</v>
+        <v>169528116</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>1105</v>
+        <v>34</v>
       </c>
       <c r="E347" s="4">
-        <v>1012616</v>
+        <v>6528821</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>49</v>
@@ -31524,11 +31541,9 @@
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="M347" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M347" s="4"/>
       <c r="N347" s="4"/>
       <c r="O347" s="4" t="s">
         <v>1621</v>
@@ -31550,20 +31565,20 @@
         <v>1623</v>
       </c>
       <c r="V347" s="4" t="s">
-        <v>1624</v>
+        <v>476</v>
       </c>
       <c r="W347" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X347" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y347" s="4"/>
       <c r="Z347" s="4" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AA347" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB347" s="4" t="s">
         <v>47</v>
@@ -31574,16 +31589,16 @@
         <v>1000</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="C348" s="4">
-        <v>168614318</v>
+        <v>169465695</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>48</v>
+        <v>1105</v>
       </c>
       <c r="E348" s="4">
-        <v>8296444</v>
+        <v>1012616</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>49</v>
@@ -31598,47 +31613,51 @@
         <v>183</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>1171</v>
+        <v>178</v>
       </c>
       <c r="M348" s="4" t="s">
-        <v>1627</v>
-      </c>
-      <c r="N348" s="4">
-        <v>74</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N348" s="4"/>
       <c r="O348" s="4" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
+        <v>1627</v>
+      </c>
+      <c r="R348" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="S348" s="4">
+        <v>0</v>
+      </c>
+      <c r="T348" s="4">
+        <v>0</v>
+      </c>
+      <c r="U348" s="4" t="s">
+        <v>1628</v>
+      </c>
+      <c r="V348" s="4" t="s">
         <v>1629</v>
       </c>
-      <c r="R348" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S348" s="4">
-        <v>0</v>
-      </c>
-      <c r="T348" s="4">
-        <v>0</v>
-      </c>
-      <c r="U348" s="4"/>
-      <c r="V348" s="4"/>
       <c r="W348" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X348" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y348" s="4"/>
       <c r="Z348" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA348" s="4"/>
+        <v>1630</v>
+      </c>
+      <c r="AA348" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB348" s="4" t="s">
         <v>47</v>
       </c>
@@ -31648,16 +31667,16 @@
         <v>1000</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="C349" s="4">
-        <v>169354713</v>
+        <v>168614318</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E349" s="4">
-        <v>7533945</v>
+        <v>8296444</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>49</v>
@@ -31672,24 +31691,24 @@
         <v>183</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
         <v>1171</v>
       </c>
       <c r="M349" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="N349" s="4">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O349" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="R349" s="4" t="s">
         <v>79</v>
@@ -31703,18 +31722,16 @@
       <c r="U349" s="4"/>
       <c r="V349" s="4"/>
       <c r="W349" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X349" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y349" s="4"/>
       <c r="Z349" s="4" t="s">
-        <v>1633</v>
-      </c>
-      <c r="AA349" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA349" s="4"/>
       <c r="AB349" s="4" t="s">
         <v>47</v>
       </c>
@@ -31724,16 +31741,16 @@
         <v>1000</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1634</v>
+        <v>420</v>
       </c>
       <c r="C350" s="4">
-        <v>169240215</v>
+        <v>169354713</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E350" s="4">
-        <v>1037589</v>
+        <v>7533945</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>49</v>
@@ -31748,25 +31765,27 @@
         <v>183</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
-        <v>289</v>
+        <v>1171</v>
       </c>
       <c r="M350" s="4" t="s">
+        <v>1635</v>
+      </c>
+      <c r="N350" s="4">
+        <v>76</v>
+      </c>
+      <c r="O350" s="4" t="s">
         <v>1636</v>
-      </c>
-      <c r="N350" s="4"/>
-      <c r="O350" s="4" t="s">
-        <v>1637</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="R350" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S350" s="4">
         <v>0</v>
@@ -31774,21 +31793,17 @@
       <c r="T350" s="4">
         <v>0</v>
       </c>
-      <c r="U350" s="4" t="s">
-        <v>1639</v>
-      </c>
-      <c r="V350" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U350" s="4"/>
+      <c r="V350" s="4"/>
       <c r="W350" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y350" s="4"/>
       <c r="Z350" s="4" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="AA350" s="4" t="s">
         <v>46</v>
@@ -31802,16 +31817,16 @@
         <v>1000</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>872</v>
+        <v>1639</v>
       </c>
       <c r="C351" s="4">
-        <v>169240216</v>
+        <v>169240215</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E351" s="4">
-        <v>1037569</v>
+        <v>1037589</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>49</v>
@@ -31826,7 +31841,7 @@
         <v>183</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
@@ -31856,7 +31871,7 @@
         <v>1644</v>
       </c>
       <c r="V351" s="4" t="s">
-        <v>426</v>
+        <v>127</v>
       </c>
       <c r="W351" s="4">
         <v>3</v>
@@ -31866,10 +31881,10 @@
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1380</v>
+        <v>1645</v>
       </c>
       <c r="AA351" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB351" s="4" t="s">
         <v>47</v>
@@ -31880,16 +31895,16 @@
         <v>1000</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>667</v>
+        <v>872</v>
       </c>
       <c r="C352" s="4">
-        <v>168725375</v>
+        <v>169240216</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E352" s="4">
-        <v>4321965</v>
+        <v>1037569</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>49</v>
@@ -31904,11 +31919,11 @@
         <v>183</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="M352" s="4" t="s">
         <v>1646</v>
@@ -31922,32 +31937,32 @@
         <v>1648</v>
       </c>
       <c r="R352" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S352" s="4">
-        <v>165052.22</v>
+        <v>0</v>
       </c>
       <c r="T352" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U352" s="4" t="s">
         <v>1649</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="W352" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X352" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y352" s="4"/>
       <c r="Z352" s="4" t="s">
-        <v>1650</v>
+        <v>1385</v>
       </c>
       <c r="AA352" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB352" s="4" t="s">
         <v>47</v>
@@ -31958,16 +31973,16 @@
         <v>1000</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1522</v>
+        <v>667</v>
       </c>
       <c r="C353" s="4">
-        <v>168896049</v>
+        <v>168725375</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E353" s="4">
-        <v>8020879</v>
+        <v>4321965</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>49</v>
@@ -31982,18 +31997,16 @@
         <v>183</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M353" s="4" t="s">
         <v>1651</v>
       </c>
-      <c r="M353" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="N353" s="4">
-        <v>30</v>
-      </c>
+      <c r="N353" s="4"/>
       <c r="O353" s="4" t="s">
         <v>1652</v>
       </c>
@@ -32002,27 +32015,33 @@
         <v>1653</v>
       </c>
       <c r="R353" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S353" s="4">
-        <v>0</v>
+        <v>165052.22</v>
       </c>
       <c r="T353" s="4">
-        <v>0</v>
-      </c>
-      <c r="U353" s="4"/>
-      <c r="V353" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U353" s="4" t="s">
+        <v>1654</v>
+      </c>
+      <c r="V353" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="W353" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X353" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1654</v>
-      </c>
-      <c r="AA353" s="4"/>
+        <v>1655</v>
+      </c>
+      <c r="AA353" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB353" s="4" t="s">
         <v>47</v>
       </c>
@@ -32032,16 +32051,16 @@
         <v>1000</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>230</v>
+        <v>1527</v>
       </c>
       <c r="C354" s="4">
-        <v>169511125</v>
+        <v>168896049</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E354" s="4">
-        <v>1030462</v>
+        <v>8020879</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>49</v>
@@ -32056,16 +32075,18 @@
         <v>183</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>289</v>
+        <v>1656</v>
       </c>
       <c r="M354" s="4" t="s">
-        <v>1656</v>
-      </c>
-      <c r="N354" s="4"/>
+        <v>523</v>
+      </c>
+      <c r="N354" s="4">
+        <v>30</v>
+      </c>
       <c r="O354" s="4" t="s">
         <v>1657</v>
       </c>
@@ -32074,7 +32095,7 @@
         <v>1658</v>
       </c>
       <c r="R354" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S354" s="4">
         <v>0</v>
@@ -32085,7 +32106,7 @@
       <c r="U354" s="4"/>
       <c r="V354" s="4"/>
       <c r="W354" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>202</v>
@@ -32104,16 +32125,16 @@
         <v>1000</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>872</v>
+        <v>230</v>
       </c>
       <c r="C355" s="4">
-        <v>169354695</v>
+        <v>169511125</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E355" s="4">
-        <v>1037638</v>
+        <v>1030462</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>49</v>
@@ -32134,14 +32155,16 @@
       <c r="L355" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M355" s="4"/>
+      <c r="M355" s="4" t="s">
+        <v>1661</v>
+      </c>
       <c r="N355" s="4"/>
       <c r="O355" s="4" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="R355" s="4" t="s">
         <v>61</v>
@@ -32155,18 +32178,16 @@
       <c r="U355" s="4"/>
       <c r="V355" s="4"/>
       <c r="W355" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X355" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AA355" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1664</v>
+      </c>
+      <c r="AA355" s="4"/>
       <c r="AB355" s="4" t="s">
         <v>47</v>
       </c>
@@ -32176,16 +32197,16 @@
         <v>1000</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1634</v>
+        <v>872</v>
       </c>
       <c r="C356" s="4">
-        <v>169354696</v>
+        <v>169354695</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E356" s="4">
-        <v>1037665</v>
+        <v>1037638</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>49</v>
@@ -32200,7 +32221,7 @@
         <v>183</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K356" s="4"/>
       <c r="L356" s="4" t="s">
@@ -32209,11 +32230,11 @@
       <c r="M356" s="4"/>
       <c r="N356" s="4"/>
       <c r="O356" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="P356" s="5"/>
       <c r="Q356" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="R356" s="4" t="s">
         <v>61</v>
@@ -32234,7 +32255,7 @@
       </c>
       <c r="Y356" s="4"/>
       <c r="Z356" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="AA356" s="4" t="s">
         <v>46</v>
@@ -32248,16 +32269,16 @@
         <v>1000</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="C357" s="4">
-        <v>169354700</v>
+        <v>169354696</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E357" s="4">
-        <v>1037643</v>
+        <v>1037665</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>49</v>
@@ -32272,7 +32293,7 @@
         <v>183</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K357" s="4"/>
       <c r="L357" s="4" t="s">
@@ -32281,20 +32302,20 @@
       <c r="M357" s="4"/>
       <c r="N357" s="4"/>
       <c r="O357" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="P357" s="5"/>
       <c r="Q357" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="R357" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S357" s="4">
-        <v>16183109.58</v>
+        <v>0</v>
       </c>
       <c r="T357" s="4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="U357" s="4"/>
       <c r="V357" s="4"/>
@@ -32306,13 +32327,13 @@
       </c>
       <c r="Y357" s="4"/>
       <c r="Z357" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="AA357" s="4" t="s">
-        <v>388</v>
+        <v>46</v>
       </c>
       <c r="AB357" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="358" spans="1:28">
@@ -32320,16 +32341,16 @@
         <v>1000</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="C358" s="4">
-        <v>169354701</v>
+        <v>169354700</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E358" s="4">
-        <v>1037642</v>
+        <v>1037643</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>49</v>
@@ -32344,7 +32365,7 @@
         <v>183</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
@@ -32353,27 +32374,23 @@
       <c r="M358" s="4"/>
       <c r="N358" s="4"/>
       <c r="O358" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="P358" s="5"/>
       <c r="Q358" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="R358" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S358" s="4">
-        <v>532142.46</v>
+        <v>16183109.58</v>
       </c>
       <c r="T358" s="4">
-        <v>2</v>
-      </c>
-      <c r="U358" s="4" t="s">
-        <v>1672</v>
-      </c>
-      <c r="V358" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="U358" s="4"/>
+      <c r="V358" s="4"/>
       <c r="W358" s="4">
         <v>2</v>
       </c>
@@ -32382,13 +32399,13 @@
       </c>
       <c r="Y358" s="4"/>
       <c r="Z358" s="4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="AA358" s="4" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="AB358" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="359" spans="1:28">
@@ -32396,16 +32413,16 @@
         <v>1000</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="C359" s="4">
-        <v>169354702</v>
+        <v>169354701</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E359" s="4">
-        <v>1037647</v>
+        <v>1037642</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>49</v>
@@ -32420,7 +32437,7 @@
         <v>183</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
@@ -32429,23 +32446,27 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="R359" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S359" s="4">
-        <v>0</v>
+        <v>532142.46</v>
       </c>
       <c r="T359" s="4">
-        <v>0</v>
-      </c>
-      <c r="U359" s="4"/>
-      <c r="V359" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U359" s="4" t="s">
+        <v>1677</v>
+      </c>
+      <c r="V359" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W359" s="4">
         <v>2</v>
       </c>
@@ -32454,10 +32475,10 @@
       </c>
       <c r="Y359" s="4"/>
       <c r="Z359" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="AA359" s="4" t="s">
-        <v>65</v>
+        <v>336</v>
       </c>
       <c r="AB359" s="4" t="s">
         <v>47</v>
@@ -32468,16 +32489,16 @@
         <v>1000</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1331</v>
+        <v>1639</v>
       </c>
       <c r="C360" s="4">
-        <v>169354703</v>
+        <v>169354702</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E360" s="4">
-        <v>1037655</v>
+        <v>1037647</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>49</v>
@@ -32492,7 +32513,7 @@
         <v>183</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
@@ -32501,11 +32522,11 @@
       <c r="M360" s="4"/>
       <c r="N360" s="4"/>
       <c r="O360" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="P360" s="5"/>
       <c r="Q360" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="R360" s="4" t="s">
         <v>61</v>
@@ -32516,12 +32537,8 @@
       <c r="T360" s="4">
         <v>0</v>
       </c>
-      <c r="U360" s="4" t="s">
-        <v>1679</v>
-      </c>
-      <c r="V360" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U360" s="4"/>
+      <c r="V360" s="4"/>
       <c r="W360" s="4">
         <v>2</v>
       </c>
@@ -32530,7 +32547,7 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="AA360" s="4" t="s">
         <v>65</v>
@@ -32544,16 +32561,16 @@
         <v>1000</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="C361" s="4">
-        <v>169354708</v>
+        <v>169354703</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E361" s="4">
-        <v>1037651</v>
+        <v>1037655</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>49</v>
@@ -32568,7 +32585,7 @@
         <v>183</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
@@ -32577,11 +32594,11 @@
       <c r="M361" s="4"/>
       <c r="N361" s="4"/>
       <c r="O361" s="4" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="R361" s="4" t="s">
         <v>61</v>
@@ -32593,7 +32610,7 @@
         <v>0</v>
       </c>
       <c r="U361" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="V361" s="4" t="s">
         <v>127</v>
@@ -32606,10 +32623,10 @@
       </c>
       <c r="Y361" s="4"/>
       <c r="Z361" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="AA361" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB361" s="4" t="s">
         <v>47</v>
@@ -32620,16 +32637,16 @@
         <v>1000</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>352</v>
+        <v>1336</v>
       </c>
       <c r="C362" s="4">
-        <v>169354710</v>
+        <v>169354708</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E362" s="4">
-        <v>7616012</v>
+        <v>1037651</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>49</v>
@@ -32644,7 +32661,7 @@
         <v>183</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4" t="s">
@@ -32653,11 +32670,11 @@
       <c r="M362" s="4"/>
       <c r="N362" s="4"/>
       <c r="O362" s="4" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="P362" s="5"/>
       <c r="Q362" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="R362" s="4" t="s">
         <v>61</v>
@@ -32668,8 +32685,12 @@
       <c r="T362" s="4">
         <v>0</v>
       </c>
-      <c r="U362" s="4"/>
-      <c r="V362" s="4"/>
+      <c r="U362" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="V362" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W362" s="4">
         <v>2</v>
       </c>
@@ -32678,10 +32699,10 @@
       </c>
       <c r="Y362" s="4"/>
       <c r="Z362" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="AA362" s="4" t="s">
-        <v>351</v>
+        <v>46</v>
       </c>
       <c r="AB362" s="4" t="s">
         <v>47</v>
@@ -32695,13 +32716,13 @@
         <v>352</v>
       </c>
       <c r="C363" s="4">
-        <v>169354711</v>
+        <v>169354710</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E363" s="4">
-        <v>5918582</v>
+        <v>7616012</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>49</v>
@@ -32716,7 +32737,7 @@
         <v>183</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4" t="s">
@@ -32725,27 +32746,23 @@
       <c r="M363" s="4"/>
       <c r="N363" s="4"/>
       <c r="O363" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="P363" s="5"/>
       <c r="Q363" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="R363" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S363" s="4">
-        <v>9429108.630000001</v>
+        <v>0</v>
       </c>
       <c r="T363" s="4">
-        <v>75</v>
-      </c>
-      <c r="U363" s="4" t="s">
-        <v>1690</v>
-      </c>
-      <c r="V363" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U363" s="4"/>
+      <c r="V363" s="4"/>
       <c r="W363" s="4">
         <v>2</v>
       </c>
@@ -32754,11 +32771,13 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>1691</v>
-      </c>
-      <c r="AA363" s="4"/>
+        <v>1692</v>
+      </c>
+      <c r="AA363" s="4" t="s">
+        <v>351</v>
+      </c>
       <c r="AB363" s="4" t="s">
-        <v>428</v>
+        <v>47</v>
       </c>
     </row>
     <row r="364" spans="1:28">
@@ -32769,13 +32788,13 @@
         <v>352</v>
       </c>
       <c r="C364" s="4">
-        <v>169354712</v>
+        <v>169354711</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E364" s="4">
-        <v>1037657</v>
+        <v>5918582</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>49</v>
@@ -32790,7 +32809,7 @@
         <v>183</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4" t="s">
@@ -32799,26 +32818,26 @@
       <c r="M364" s="4"/>
       <c r="N364" s="4"/>
       <c r="O364" s="4" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="R364" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S364" s="4">
-        <v>0</v>
+        <v>9429108.630000001</v>
       </c>
       <c r="T364" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U364" s="4" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="V364" s="4" t="s">
-        <v>476</v>
+        <v>127</v>
       </c>
       <c r="W364" s="4">
         <v>2</v>
@@ -32828,13 +32847,11 @@
       </c>
       <c r="Y364" s="4"/>
       <c r="Z364" s="4" t="s">
-        <v>1695</v>
-      </c>
-      <c r="AA364" s="4" t="s">
-        <v>215</v>
-      </c>
+        <v>1696</v>
+      </c>
+      <c r="AA364" s="4"/>
       <c r="AB364" s="4" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
     </row>
     <row r="365" spans="1:28">
@@ -32845,13 +32862,13 @@
         <v>352</v>
       </c>
       <c r="C365" s="4">
-        <v>169354709</v>
+        <v>169354712</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E365" s="4">
-        <v>1037653</v>
+        <v>1037657</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>49</v>
@@ -32866,15 +32883,13 @@
         <v>183</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M365" s="4" t="s">
-        <v>1696</v>
-      </c>
+      <c r="M365" s="4"/>
       <c r="N365" s="4"/>
       <c r="O365" s="4" t="s">
         <v>1697</v>
@@ -32892,8 +32907,12 @@
       <c r="T365" s="4">
         <v>0</v>
       </c>
-      <c r="U365" s="4"/>
-      <c r="V365" s="4"/>
+      <c r="U365" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="V365" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="W365" s="4">
         <v>2</v>
       </c>
@@ -32902,7 +32921,7 @@
       </c>
       <c r="Y365" s="4"/>
       <c r="Z365" s="4" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="AA365" s="4" t="s">
         <v>215</v>
@@ -32916,16 +32935,16 @@
         <v>1000</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C366" s="4">
-        <v>169360455</v>
+        <v>169354709</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E366" s="4">
-        <v>1037656</v>
+        <v>1037653</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>49</v>
@@ -32940,31 +32959,31 @@
         <v>183</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="K366" s="4"/>
       <c r="L366" s="4" t="s">
         <v>289</v>
       </c>
       <c r="M366" s="4" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="P366" s="5"/>
       <c r="Q366" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="R366" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S366" s="4">
-        <v>57340.82</v>
+        <v>0</v>
       </c>
       <c r="T366" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U366" s="4"/>
       <c r="V366" s="4"/>
@@ -32976,7 +32995,7 @@
       </c>
       <c r="Y366" s="4"/>
       <c r="Z366" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="AA366" s="4" t="s">
         <v>215</v>
@@ -32990,16 +33009,16 @@
         <v>1000</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C367" s="4">
-        <v>169527823</v>
+        <v>169360455</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E367" s="4">
-        <v>4268253</v>
+        <v>1037656</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>49</v>
@@ -33014,50 +33033,46 @@
         <v>183</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1703</v>
+        <v>1665</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="M367" s="4" t="s">
-        <v>517</v>
+        <v>1701</v>
       </c>
       <c r="N367" s="4"/>
       <c r="O367" s="4" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="R367" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S367" s="4">
-        <v>0</v>
+        <v>57340.82</v>
       </c>
       <c r="T367" s="4">
-        <v>0</v>
-      </c>
-      <c r="U367" s="4" t="s">
-        <v>1706</v>
-      </c>
-      <c r="V367" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U367" s="4"/>
+      <c r="V367" s="4"/>
       <c r="W367" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X367" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y367" s="4"/>
       <c r="Z367" s="4" t="s">
         <v>1707</v>
       </c>
       <c r="AA367" s="4" t="s">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="AB367" s="4" t="s">
         <v>47</v>
@@ -33068,16 +33083,16 @@
         <v>1000</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C368" s="4">
-        <v>169345689</v>
+        <v>169527823</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>722</v>
+        <v>34</v>
       </c>
       <c r="E368" s="4">
-        <v>1030127</v>
+        <v>4268253</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>49</v>
@@ -33096,9 +33111,11 @@
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M368" s="4"/>
+        <v>224</v>
+      </c>
+      <c r="M368" s="4" t="s">
+        <v>517</v>
+      </c>
       <c r="N368" s="4"/>
       <c r="O368" s="4" t="s">
         <v>1709</v>
@@ -33108,7 +33125,7 @@
         <v>1710</v>
       </c>
       <c r="R368" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S368" s="4">
         <v>0</v>
@@ -33120,20 +33137,20 @@
         <v>1711</v>
       </c>
       <c r="V368" s="4" t="s">
-        <v>1712</v>
+        <v>69</v>
       </c>
       <c r="W368" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X368" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y368" s="4"/>
       <c r="Z368" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="AA368" s="4" t="s">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="AB368" s="4" t="s">
         <v>47</v>
@@ -33144,16 +33161,16 @@
         <v>1000</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>645</v>
+        <v>337</v>
       </c>
       <c r="C369" s="4">
-        <v>169240241</v>
+        <v>169345689</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>57</v>
+        <v>722</v>
       </c>
       <c r="E369" s="4">
-        <v>6825959</v>
+        <v>1030127</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>49</v>
@@ -33168,7 +33185,7 @@
         <v>183</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
@@ -33177,32 +33194,36 @@
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="R369" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S369" s="4">
+        <v>0</v>
+      </c>
+      <c r="T369" s="4">
+        <v>0</v>
+      </c>
+      <c r="U369" s="4" t="s">
         <v>1716</v>
       </c>
-      <c r="R369" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S369" s="4">
-        <v>412514.71</v>
-      </c>
-      <c r="T369" s="4">
-        <v>1</v>
-      </c>
-      <c r="U369" s="4"/>
-      <c r="V369" s="4"/>
+      <c r="V369" s="4" t="s">
+        <v>1717</v>
+      </c>
       <c r="W369" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X369" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y369" s="4"/>
       <c r="Z369" s="4" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="AA369" s="4" t="s">
         <v>46</v>
@@ -33216,16 +33237,16 @@
         <v>1000</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>33</v>
+        <v>645</v>
       </c>
       <c r="C370" s="4">
-        <v>169521806</v>
+        <v>169240241</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E370" s="4">
-        <v>6699162</v>
+        <v>6825959</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>49</v>
@@ -33240,7 +33261,7 @@
         <v>183</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -33249,35 +33270,35 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="R370" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S370" s="4">
-        <v>0</v>
+        <v>412514.71</v>
       </c>
       <c r="T370" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U370" s="4"/>
       <c r="V370" s="4"/>
       <c r="W370" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X370" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y370" s="4"/>
       <c r="Z370" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="AA370" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB370" s="4" t="s">
         <v>47</v>
@@ -33291,13 +33312,13 @@
         <v>33</v>
       </c>
       <c r="C371" s="4">
-        <v>169511424</v>
+        <v>169521806</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E371" s="4">
-        <v>7187541</v>
+        <v>6699162</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>49</v>
@@ -33312,7 +33333,7 @@
         <v>183</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
@@ -33321,14 +33342,14 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="R371" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S371" s="4">
         <v>0</v>
@@ -33336,12 +33357,8 @@
       <c r="T371" s="4">
         <v>0</v>
       </c>
-      <c r="U371" s="4" t="s">
-        <v>1724</v>
-      </c>
-      <c r="V371" s="4" t="s">
-        <v>604</v>
-      </c>
+      <c r="U371" s="4"/>
+      <c r="V371" s="4"/>
       <c r="W371" s="4">
         <v>0</v>
       </c>
@@ -33352,7 +33369,9 @@
       <c r="Z371" s="4" t="s">
         <v>1725</v>
       </c>
-      <c r="AA371" s="4"/>
+      <c r="AA371" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB371" s="4" t="s">
         <v>47</v>
       </c>
@@ -33362,16 +33381,16 @@
         <v>1000</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C372" s="4">
-        <v>169347543</v>
+        <v>169511424</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>580</v>
+        <v>34</v>
       </c>
       <c r="E372" s="4">
-        <v>1072186</v>
+        <v>7187541</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>49</v>
@@ -33405,30 +33424,28 @@
         <v>79</v>
       </c>
       <c r="S372" s="4">
-        <v>20024.22</v>
+        <v>0</v>
       </c>
       <c r="T372" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U372" s="4" t="s">
         <v>1729</v>
       </c>
       <c r="V372" s="4" t="s">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="W372" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X372" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
         <v>1730</v>
       </c>
-      <c r="AA372" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA372" s="4"/>
       <c r="AB372" s="4" t="s">
         <v>47</v>
       </c>
@@ -33438,16 +33455,16 @@
         <v>1000</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="C373" s="4">
-        <v>169527018</v>
+        <v>169347543</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>34</v>
+        <v>580</v>
       </c>
       <c r="E373" s="4">
-        <v>6658632</v>
+        <v>1072186</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>49</v>
@@ -33456,54 +33473,130 @@
         <v>36</v>
       </c>
       <c r="H373" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I373" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J373" s="4" t="s">
         <v>1731</v>
       </c>
-      <c r="I373" s="4" t="s">
-        <v>1732</v>
-      </c>
-      <c r="J373" s="4" t="s">
-        <v>1733</v>
-      </c>
       <c r="K373" s="4"/>
-      <c r="L373" s="4"/>
+      <c r="L373" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="R373" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S373" s="4">
-        <v>0</v>
+        <v>20024.22</v>
       </c>
       <c r="T373" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U373" s="4" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="V373" s="4" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="W373" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X373" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
+        <v>1735</v>
+      </c>
+      <c r="AA373" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB373" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="374" spans="1:28">
+      <c r="A374" s="4">
+        <v>1000</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C374" s="4">
+        <v>169527018</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E374" s="4">
+        <v>6658632</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G374" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="I374" s="4" t="s">
         <v>1737</v>
       </c>
-      <c r="AA373" s="4" t="s">
+      <c r="J374" s="4" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K374" s="4"/>
+      <c r="L374" s="4"/>
+      <c r="M374" s="4"/>
+      <c r="N374" s="4"/>
+      <c r="O374" s="4" t="s">
+        <v>1739</v>
+      </c>
+      <c r="P374" s="5"/>
+      <c r="Q374" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="R374" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S374" s="4">
+        <v>0</v>
+      </c>
+      <c r="T374" s="4">
+        <v>0</v>
+      </c>
+      <c r="U374" s="4" t="s">
+        <v>1741</v>
+      </c>
+      <c r="V374" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W374" s="4">
+        <v>0</v>
+      </c>
+      <c r="X374" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y374" s="4"/>
+      <c r="Z374" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AA374" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AB373" s="4" t="s">
+      <c r="AB374" s="4" t="s">
         <v>47</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1744">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/10/2026 a las 09:00:57</t>
+    <t>18/10/2026 a las 10:00:50</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -3732,18 +3732,6 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD PQR usuario william jimenez puerta celular 3135760395 revision de medidor por consumo estimado y posible irregularidad revison total</t>
-  </si>
-  <si>
-    <t>SECTOR 1 # MZ G - 11 DPL AN5915</t>
-  </si>
-  <si>
-    <t>MERCADO MANOTAS  JESUS MARIA</t>
-  </si>
-  <si>
-    <t>12059885-MCA54</t>
-  </si>
-  <si>
-    <t>Investigar Dano medidor yo acometida Reportado por IVR - Tel 3013134292</t>
   </si>
   <si>
     <t>ALEXIS DAVID SAMPER RAMIREZ</t>
@@ -5652,7 +5640,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB375"/>
+  <dimension ref="A1:AB374"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -24790,16 +24778,16 @@
         <v>1000</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>196</v>
+        <v>1239</v>
       </c>
       <c r="C257" s="4">
-        <v>169101360</v>
+        <v>168898228</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E257" s="4">
-        <v>4321758</v>
+        <v>6938291</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>49</v>
@@ -24818,16 +24806,20 @@
       </c>
       <c r="K257" s="4"/>
       <c r="L257" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M257" s="4"/>
-      <c r="N257" s="4"/>
+        <v>673</v>
+      </c>
+      <c r="M257" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="N257" s="4">
+        <v>53</v>
+      </c>
       <c r="O257" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="P257" s="5"/>
       <c r="Q257" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="R257" s="4" t="s">
         <v>41</v>
@@ -24839,22 +24831,24 @@
         <v>0</v>
       </c>
       <c r="U257" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="V257" s="4" t="s">
         <v>127</v>
       </c>
       <c r="W257" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X257" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y257" s="4"/>
       <c r="Z257" s="4" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AA257" s="4"/>
+        <v>1243</v>
+      </c>
+      <c r="AA257" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB257" s="4" t="s">
         <v>47</v>
       </c>
@@ -24864,16 +24858,16 @@
         <v>1000</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>1243</v>
+        <v>33</v>
       </c>
       <c r="C258" s="4">
-        <v>168898228</v>
+        <v>169483274</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="E258" s="4">
-        <v>6938291</v>
+        <v>8384193</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>49</v>
@@ -24885,30 +24879,30 @@
         <v>183</v>
       </c>
       <c r="I258" s="4" t="s">
-        <v>183</v>
+        <v>1244</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="K258" s="4"/>
       <c r="L258" s="4" t="s">
-        <v>673</v>
+        <v>460</v>
       </c>
       <c r="M258" s="4" t="s">
-        <v>524</v>
+        <v>467</v>
       </c>
       <c r="N258" s="4">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="O258" s="4" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="P258" s="5"/>
       <c r="Q258" s="4" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="R258" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S258" s="4">
         <v>0</v>
@@ -24916,25 +24910,19 @@
       <c r="T258" s="4">
         <v>0</v>
       </c>
-      <c r="U258" s="4" t="s">
-        <v>1246</v>
-      </c>
-      <c r="V258" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U258" s="4"/>
+      <c r="V258" s="4"/>
       <c r="W258" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X258" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y258" s="4"/>
       <c r="Z258" s="4" t="s">
-        <v>1247</v>
-      </c>
-      <c r="AA258" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA258" s="4"/>
       <c r="AB258" s="4" t="s">
         <v>47</v>
       </c>
@@ -24944,16 +24932,16 @@
         <v>1000</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>33</v>
+        <v>319</v>
       </c>
       <c r="C259" s="4">
-        <v>169483274</v>
+        <v>168617735</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="E259" s="4">
-        <v>8384193</v>
+        <v>7007877</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>49</v>
@@ -24965,27 +24953,25 @@
         <v>183</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="K259" s="4"/>
       <c r="L259" s="4" t="s">
-        <v>460</v>
+        <v>1247</v>
       </c>
       <c r="M259" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="N259" s="4">
-        <v>30</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N259" s="4"/>
       <c r="O259" s="4" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="P259" s="5"/>
       <c r="Q259" s="4" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="R259" s="4" t="s">
         <v>79</v>
@@ -24996,19 +24982,25 @@
       <c r="T259" s="4">
         <v>0</v>
       </c>
-      <c r="U259" s="4"/>
-      <c r="V259" s="4"/>
+      <c r="U259" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="V259" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W259" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X259" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y259" s="4"/>
       <c r="Z259" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA259" s="4"/>
+        <v>1251</v>
+      </c>
+      <c r="AA259" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB259" s="4" t="s">
         <v>47</v>
       </c>
@@ -25018,16 +25010,16 @@
         <v>1000</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>319</v>
+        <v>33</v>
       </c>
       <c r="C260" s="4">
-        <v>168617735</v>
+        <v>169085226</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E260" s="4">
-        <v>7007877</v>
+        <v>5914143</v>
       </c>
       <c r="F260" s="4" t="s">
         <v>49</v>
@@ -25039,28 +25031,28 @@
         <v>183</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="K260" s="4"/>
       <c r="L260" s="4" t="s">
-        <v>1251</v>
+        <v>123</v>
       </c>
       <c r="M260" s="4" t="s">
-        <v>484</v>
+        <v>1252</v>
       </c>
       <c r="N260" s="4"/>
       <c r="O260" s="4" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="P260" s="5"/>
       <c r="Q260" s="4" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="R260" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S260" s="4">
         <v>0</v>
@@ -25069,23 +25061,23 @@
         <v>0</v>
       </c>
       <c r="U260" s="4" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="V260" s="4" t="s">
-        <v>69</v>
+        <v>464</v>
       </c>
       <c r="W260" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X260" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y260" s="4"/>
       <c r="Z260" s="4" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="AA260" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB260" s="4" t="s">
         <v>47</v>
@@ -25096,16 +25088,16 @@
         <v>1000</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>33</v>
+        <v>319</v>
       </c>
       <c r="C261" s="4">
-        <v>169085226</v>
+        <v>169236551</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E261" s="4">
-        <v>5914143</v>
+        <v>1056366</v>
       </c>
       <c r="F261" s="4" t="s">
         <v>49</v>
@@ -25117,53 +25109,49 @@
         <v>183</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="K261" s="4"/>
       <c r="L261" s="4" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="M261" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="N261" s="4"/>
       <c r="O261" s="4" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="P261" s="5"/>
       <c r="Q261" s="4" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="R261" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S261" s="4">
-        <v>0</v>
+        <v>923639.33</v>
       </c>
       <c r="T261" s="4">
-        <v>0</v>
-      </c>
-      <c r="U261" s="4" t="s">
-        <v>1259</v>
-      </c>
-      <c r="V261" s="4" t="s">
-        <v>464</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U261" s="4"/>
+      <c r="V261" s="4"/>
       <c r="W261" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X261" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y261" s="4"/>
       <c r="Z261" s="4" t="s">
         <v>1260</v>
       </c>
       <c r="AA261" s="4" t="s">
-        <v>215</v>
+        <v>352</v>
       </c>
       <c r="AB261" s="4" t="s">
         <v>47</v>
@@ -25174,16 +25162,16 @@
         <v>1000</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>319</v>
+        <v>33</v>
       </c>
       <c r="C262" s="4">
-        <v>169236551</v>
+        <v>169483359</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="E262" s="4">
-        <v>1056366</v>
+        <v>8394283</v>
       </c>
       <c r="F262" s="4" t="s">
         <v>49</v>
@@ -25195,50 +25183,50 @@
         <v>183</v>
       </c>
       <c r="I262" s="4" t="s">
-        <v>1248</v>
+        <v>183</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="K262" s="4"/>
       <c r="L262" s="4" t="s">
-        <v>52</v>
+        <v>1262</v>
       </c>
       <c r="M262" s="4" t="s">
-        <v>1261</v>
-      </c>
-      <c r="N262" s="4"/>
+        <v>1263</v>
+      </c>
+      <c r="N262" s="4">
+        <v>42</v>
+      </c>
       <c r="O262" s="4" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="P262" s="5"/>
       <c r="Q262" s="4" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="R262" s="4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="S262" s="4">
-        <v>923639.33</v>
+        <v>0</v>
       </c>
       <c r="T262" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U262" s="4"/>
       <c r="V262" s="4"/>
       <c r="W262" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X262" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y262" s="4"/>
       <c r="Z262" s="4" t="s">
-        <v>1264</v>
-      </c>
-      <c r="AA262" s="4" t="s">
-        <v>352</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA262" s="4"/>
       <c r="AB262" s="4" t="s">
         <v>47</v>
       </c>
@@ -25248,16 +25236,16 @@
         <v>1000</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>33</v>
+        <v>421</v>
       </c>
       <c r="C263" s="4">
-        <v>169483359</v>
+        <v>168725418</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E263" s="4">
-        <v>8394283</v>
+        <v>6957391</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>49</v>
@@ -25272,17 +25260,17 @@
         <v>183</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="K263" s="4"/>
       <c r="L263" s="4" t="s">
-        <v>1266</v>
+        <v>467</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="N263" s="4">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O263" s="4" t="s">
         <v>1268</v>
@@ -25292,7 +25280,7 @@
         <v>1269</v>
       </c>
       <c r="R263" s="4" t="s">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="S263" s="4">
         <v>0</v>
@@ -25300,19 +25288,25 @@
       <c r="T263" s="4">
         <v>0</v>
       </c>
-      <c r="U263" s="4"/>
-      <c r="V263" s="4"/>
+      <c r="U263" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="V263" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W263" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X263" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y263" s="4"/>
       <c r="Z263" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA263" s="4"/>
+        <v>1271</v>
+      </c>
+      <c r="AA263" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB263" s="4" t="s">
         <v>47</v>
       </c>
@@ -25322,16 +25316,16 @@
         <v>1000</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>421</v>
+        <v>33</v>
       </c>
       <c r="C264" s="4">
-        <v>168725418</v>
+        <v>169525716</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>57</v>
+        <v>472</v>
       </c>
       <c r="E264" s="4">
-        <v>6957391</v>
+        <v>7709720</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>49</v>
@@ -25346,55 +25340,55 @@
         <v>183</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="K264" s="4"/>
       <c r="L264" s="4" t="s">
-        <v>467</v>
+        <v>97</v>
       </c>
       <c r="M264" s="4" t="s">
-        <v>1271</v>
+        <v>524</v>
       </c>
       <c r="N264" s="4">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O264" s="4" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="P264" s="5"/>
       <c r="Q264" s="4" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="R264" s="4" t="s">
-        <v>257</v>
+        <v>61</v>
       </c>
       <c r="S264" s="4">
-        <v>0</v>
+        <v>1383640.89</v>
       </c>
       <c r="T264" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U264" s="4" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="V264" s="4" t="s">
-        <v>69</v>
+        <v>477</v>
       </c>
       <c r="W264" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X264" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y264" s="4"/>
       <c r="Z264" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="AA264" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB264" s="4" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="265" spans="1:28">
@@ -25405,13 +25399,13 @@
         <v>33</v>
       </c>
       <c r="C265" s="4">
-        <v>169525716</v>
+        <v>169470167</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>472</v>
+        <v>188</v>
       </c>
       <c r="E265" s="4">
-        <v>7709720</v>
+        <v>7725658</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>49</v>
@@ -25423,58 +25417,58 @@
         <v>183</v>
       </c>
       <c r="I265" s="4" t="s">
-        <v>183</v>
+        <v>1277</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="K265" s="4"/>
       <c r="L265" s="4" t="s">
-        <v>97</v>
+        <v>1279</v>
       </c>
       <c r="M265" s="4" t="s">
-        <v>524</v>
+        <v>1101</v>
       </c>
       <c r="N265" s="4">
-        <v>5</v>
+        <v>254</v>
       </c>
       <c r="O265" s="4" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="P265" s="5"/>
       <c r="Q265" s="4" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="R265" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S265" s="4">
-        <v>1383640.89</v>
+        <v>0</v>
       </c>
       <c r="T265" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U265" s="4" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="V265" s="4" t="s">
-        <v>477</v>
+        <v>74</v>
       </c>
       <c r="W265" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X265" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y265" s="4"/>
       <c r="Z265" s="4" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="AA265" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB265" s="4" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
     </row>
     <row r="266" spans="1:28">
@@ -25485,13 +25479,13 @@
         <v>33</v>
       </c>
       <c r="C266" s="4">
-        <v>169470167</v>
+        <v>168796051</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="E266" s="4">
-        <v>7725658</v>
+        <v>8384343</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>49</v>
@@ -25503,56 +25497,44 @@
         <v>183</v>
       </c>
       <c r="I266" s="4" t="s">
-        <v>1281</v>
+        <v>183</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="K266" s="4"/>
-      <c r="L266" s="4" t="s">
-        <v>1283</v>
-      </c>
-      <c r="M266" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="N266" s="4">
-        <v>254</v>
-      </c>
+      <c r="L266" s="4"/>
+      <c r="M266" s="4"/>
+      <c r="N266" s="4"/>
       <c r="O266" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="P266" s="5"/>
       <c r="Q266" s="4" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="R266" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S266" s="4">
-        <v>0</v>
+        <v>401418.42</v>
       </c>
       <c r="T266" s="4">
-        <v>0</v>
-      </c>
-      <c r="U266" s="4" t="s">
-        <v>1286</v>
-      </c>
-      <c r="V266" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U266" s="4"/>
+      <c r="V266" s="4"/>
       <c r="W266" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X266" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y266" s="4"/>
       <c r="Z266" s="4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="AA266" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA266" s="4"/>
       <c r="AB266" s="4" t="s">
         <v>47</v>
       </c>
@@ -25565,13 +25547,13 @@
         <v>33</v>
       </c>
       <c r="C267" s="4">
-        <v>168796051</v>
+        <v>168799239</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E267" s="4">
-        <v>8384343</v>
+        <v>8391518</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>49</v>
@@ -25586,27 +25568,27 @@
         <v>183</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4"/>
       <c r="M267" s="4"/>
       <c r="N267" s="4"/>
       <c r="O267" s="4" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="P267" s="5"/>
       <c r="Q267" s="4" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="R267" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S267" s="4">
-        <v>401418.42</v>
+        <v>0</v>
       </c>
       <c r="T267" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
@@ -25630,16 +25612,16 @@
         <v>1000</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>33</v>
+        <v>246</v>
       </c>
       <c r="C268" s="4">
-        <v>168799239</v>
+        <v>169339745</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E268" s="4">
-        <v>8391518</v>
+        <v>8001278</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>49</v>
@@ -25654,18 +25636,18 @@
         <v>183</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4"/>
       <c r="M268" s="4"/>
       <c r="N268" s="4"/>
       <c r="O268" s="4" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="P268" s="5"/>
       <c r="Q268" s="4" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="R268" s="4" t="s">
         <v>79</v>
@@ -25679,16 +25661,18 @@
       <c r="U268" s="4"/>
       <c r="V268" s="4"/>
       <c r="W268" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X268" s="4" t="s">
-        <v>44</v>
+        <v>342</v>
       </c>
       <c r="Y268" s="4"/>
       <c r="Z268" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA268" s="4"/>
+        <v>1291</v>
+      </c>
+      <c r="AA268" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB268" s="4" t="s">
         <v>47</v>
       </c>
@@ -25698,16 +25682,16 @@
         <v>1000</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>246</v>
+        <v>196</v>
       </c>
       <c r="C269" s="4">
-        <v>169339745</v>
+        <v>168886822</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E269" s="4">
-        <v>8001278</v>
+        <v>8392361</v>
       </c>
       <c r="F269" s="4" t="s">
         <v>49</v>
@@ -25722,7 +25706,7 @@
         <v>183</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4"/>
@@ -25747,18 +25731,16 @@
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
       <c r="W269" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="X269" s="4" t="s">
-        <v>342</v>
+        <v>202</v>
       </c>
       <c r="Y269" s="4"/>
       <c r="Z269" s="4" t="s">
-        <v>1295</v>
-      </c>
-      <c r="AA269" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA269" s="4"/>
       <c r="AB269" s="4" t="s">
         <v>47</v>
       </c>
@@ -25768,16 +25750,16 @@
         <v>1000</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>196</v>
+        <v>1295</v>
       </c>
       <c r="C270" s="4">
-        <v>168886822</v>
+        <v>166657163</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E270" s="4">
-        <v>8392361</v>
+        <v>1346167</v>
       </c>
       <c r="F270" s="4" t="s">
         <v>49</v>
@@ -25792,11 +25774,15 @@
         <v>183</v>
       </c>
       <c r="J270" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="K270" s="4"/>
+      <c r="L270" s="4" t="s">
         <v>1296</v>
       </c>
-      <c r="K270" s="4"/>
-      <c r="L270" s="4"/>
-      <c r="M270" s="4"/>
+      <c r="M270" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="N270" s="4"/>
       <c r="O270" s="4" t="s">
         <v>1297</v>
@@ -25814,19 +25800,25 @@
       <c r="T270" s="4">
         <v>0</v>
       </c>
-      <c r="U270" s="4"/>
-      <c r="V270" s="4"/>
+      <c r="U270" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="V270" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W270" s="4">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="X270" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y270" s="4"/>
       <c r="Z270" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA270" s="4"/>
+        <v>1300</v>
+      </c>
+      <c r="AA270" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB270" s="4" t="s">
         <v>47</v>
       </c>
@@ -25836,16 +25828,16 @@
         <v>1000</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>1299</v>
+        <v>33</v>
       </c>
       <c r="C271" s="4">
-        <v>166657163</v>
+        <v>168799295</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E271" s="4">
-        <v>1346167</v>
+        <v>8391485</v>
       </c>
       <c r="F271" s="4" t="s">
         <v>49</v>
@@ -25860,22 +25852,18 @@
         <v>183</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="K271" s="4"/>
-      <c r="L271" s="4" t="s">
-        <v>1300</v>
-      </c>
-      <c r="M271" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="L271" s="4"/>
+      <c r="M271" s="4"/>
       <c r="N271" s="4"/>
       <c r="O271" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P271" s="5"/>
       <c r="Q271" s="4" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="R271" s="4" t="s">
         <v>79</v>
@@ -25886,25 +25874,19 @@
       <c r="T271" s="4">
         <v>0</v>
       </c>
-      <c r="U271" s="4" t="s">
-        <v>1303</v>
-      </c>
-      <c r="V271" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U271" s="4"/>
+      <c r="V271" s="4"/>
       <c r="W271" s="4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="X271" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y271" s="4"/>
       <c r="Z271" s="4" t="s">
-        <v>1304</v>
-      </c>
-      <c r="AA271" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA271" s="4"/>
       <c r="AB271" s="4" t="s">
         <v>47</v>
       </c>
@@ -25914,16 +25896,16 @@
         <v>1000</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="C272" s="4">
-        <v>168799295</v>
+        <v>169343653</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="E272" s="4">
-        <v>8391485</v>
+        <v>7951786</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>49</v>
@@ -25938,39 +25920,45 @@
         <v>183</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="K272" s="4"/>
-      <c r="L272" s="4"/>
+      <c r="L272" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M272" s="4"/>
       <c r="N272" s="4"/>
       <c r="O272" s="4" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="R272" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S272" s="4">
+        <v>0</v>
+      </c>
+      <c r="T272" s="4">
+        <v>0</v>
+      </c>
+      <c r="U272" s="4" t="s">
         <v>1307</v>
       </c>
-      <c r="R272" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S272" s="4">
-        <v>0</v>
-      </c>
-      <c r="T272" s="4">
-        <v>0</v>
-      </c>
-      <c r="U272" s="4"/>
-      <c r="V272" s="4"/>
+      <c r="V272" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W272" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X272" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
-        <v>56</v>
+        <v>1308</v>
       </c>
       <c r="AA272" s="4"/>
       <c r="AB272" s="4" t="s">
@@ -25982,16 +25970,16 @@
         <v>1000</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>222</v>
+        <v>448</v>
       </c>
       <c r="C273" s="4">
-        <v>169343653</v>
+        <v>169009528</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E273" s="4">
-        <v>7951786</v>
+        <v>6903524</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>49</v>
@@ -26006,7 +25994,7 @@
         <v>183</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="K273" s="4"/>
       <c r="L273" s="4" t="s">
@@ -26015,11 +26003,11 @@
       <c r="M273" s="4"/>
       <c r="N273" s="4"/>
       <c r="O273" s="4" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="P273" s="5"/>
       <c r="Q273" s="4" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="R273" s="4" t="s">
         <v>61</v>
@@ -26030,14 +26018,10 @@
       <c r="T273" s="4">
         <v>0</v>
       </c>
-      <c r="U273" s="4" t="s">
-        <v>1311</v>
-      </c>
-      <c r="V273" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U273" s="4"/>
+      <c r="V273" s="4"/>
       <c r="W273" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X273" s="4" t="s">
         <v>202</v>
@@ -26046,7 +26030,9 @@
       <c r="Z273" s="4" t="s">
         <v>1312</v>
       </c>
-      <c r="AA273" s="4"/>
+      <c r="AA273" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB273" s="4" t="s">
         <v>47</v>
       </c>
@@ -26056,16 +26042,16 @@
         <v>1000</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="C274" s="4">
-        <v>169009528</v>
+        <v>169519267</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E274" s="4">
-        <v>6903524</v>
+        <v>6862401</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>49</v>
@@ -26080,7 +26066,7 @@
         <v>183</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4" t="s">
@@ -26089,14 +26075,14 @@
       <c r="M274" s="4"/>
       <c r="N274" s="4"/>
       <c r="O274" s="4" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="P274" s="5"/>
       <c r="Q274" s="4" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="R274" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S274" s="4">
         <v>0</v>
@@ -26107,14 +26093,14 @@
       <c r="U274" s="4"/>
       <c r="V274" s="4"/>
       <c r="W274" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X274" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="AA274" s="4" t="s">
         <v>46</v>
@@ -26128,16 +26114,16 @@
         <v>1000</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>33</v>
+        <v>618</v>
       </c>
       <c r="C275" s="4">
-        <v>169519267</v>
+        <v>169089966</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E275" s="4">
-        <v>6862401</v>
+        <v>8397606</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>49</v>
@@ -26152,12 +26138,10 @@
         <v>183</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="K275" s="4"/>
-      <c r="L275" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L275" s="4"/>
       <c r="M275" s="4"/>
       <c r="N275" s="4"/>
       <c r="O275" s="4" t="s">
@@ -26179,20 +26163,18 @@
       <c r="U275" s="4"/>
       <c r="V275" s="4"/>
       <c r="W275" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X275" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y275" s="4"/>
       <c r="Z275" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="AA275" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA275" s="4"/>
       <c r="AB275" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="276" spans="1:28">
@@ -26200,16 +26182,16 @@
         <v>1000</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>618</v>
+        <v>893</v>
       </c>
       <c r="C276" s="4">
-        <v>169089966</v>
+        <v>169227224</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E276" s="4">
-        <v>8397606</v>
+        <v>8391001</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>49</v>
@@ -26224,18 +26206,18 @@
         <v>183</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="K276" s="4"/>
       <c r="L276" s="4"/>
       <c r="M276" s="4"/>
       <c r="N276" s="4"/>
       <c r="O276" s="4" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="P276" s="5"/>
       <c r="Q276" s="4" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="R276" s="4" t="s">
         <v>41</v>
@@ -26249,14 +26231,14 @@
       <c r="U276" s="4"/>
       <c r="V276" s="4"/>
       <c r="W276" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X276" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y276" s="4"/>
       <c r="Z276" s="4" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="AA276" s="4"/>
       <c r="AB276" s="4" t="s">
@@ -26268,16 +26250,16 @@
         <v>1000</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>893</v>
+        <v>448</v>
       </c>
       <c r="C277" s="4">
-        <v>169227224</v>
+        <v>169487174</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E277" s="4">
-        <v>8391001</v>
+        <v>6959985</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>49</v>
@@ -26292,10 +26274,12 @@
         <v>183</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="K277" s="4"/>
-      <c r="L277" s="4"/>
+      <c r="L277" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M277" s="4"/>
       <c r="N277" s="4"/>
       <c r="O277" s="4" t="s">
@@ -26314,21 +26298,27 @@
       <c r="T277" s="4">
         <v>0</v>
       </c>
-      <c r="U277" s="4"/>
-      <c r="V277" s="4"/>
+      <c r="U277" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="V277" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W277" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X277" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y277" s="4"/>
       <c r="Z277" s="4" t="s">
-        <v>1326</v>
-      </c>
-      <c r="AA277" s="4"/>
+        <v>1327</v>
+      </c>
+      <c r="AA277" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB277" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -26336,16 +26326,16 @@
         <v>1000</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>448</v>
+        <v>267</v>
       </c>
       <c r="C278" s="4">
-        <v>169487174</v>
+        <v>168896173</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="E278" s="4">
-        <v>6959985</v>
+        <v>6619680</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>49</v>
@@ -26360,7 +26350,7 @@
         <v>183</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="K278" s="4"/>
       <c r="L278" s="4" t="s">
@@ -26369,39 +26359,39 @@
       <c r="M278" s="4"/>
       <c r="N278" s="4"/>
       <c r="O278" s="4" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="P278" s="5"/>
       <c r="Q278" s="4" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="R278" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S278" s="4">
-        <v>0</v>
+        <v>338342.08</v>
       </c>
       <c r="T278" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U278" s="4" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="V278" s="4" t="s">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="W278" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X278" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y278" s="4"/>
       <c r="Z278" s="4" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="AA278" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB278" s="4" t="s">
         <v>47</v>
@@ -26412,16 +26402,16 @@
         <v>1000</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>267</v>
+        <v>1333</v>
       </c>
       <c r="C279" s="4">
-        <v>168896173</v>
+        <v>169240223</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E279" s="4">
-        <v>6619680</v>
+        <v>5873839</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>49</v>
@@ -26436,7 +26426,7 @@
         <v>183</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="K279" s="4"/>
       <c r="L279" s="4" t="s">
@@ -26445,29 +26435,25 @@
       <c r="M279" s="4"/>
       <c r="N279" s="4"/>
       <c r="O279" s="4" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="P279" s="5"/>
       <c r="Q279" s="4" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="R279" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S279" s="4">
-        <v>338342.08</v>
+        <v>0</v>
       </c>
       <c r="T279" s="4">
-        <v>1</v>
-      </c>
-      <c r="U279" s="4" t="s">
-        <v>1335</v>
-      </c>
-      <c r="V279" s="4" t="s">
-        <v>350</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U279" s="4"/>
+      <c r="V279" s="4"/>
       <c r="W279" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X279" s="4" t="s">
         <v>202</v>
@@ -26477,7 +26463,7 @@
         <v>1336</v>
       </c>
       <c r="AA279" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB279" s="4" t="s">
         <v>47</v>
@@ -26488,16 +26474,16 @@
         <v>1000</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C280" s="4">
-        <v>169240223</v>
+        <v>169240234</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E280" s="4">
-        <v>5873839</v>
+        <v>8020360</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>49</v>
@@ -26512,14 +26498,18 @@
         <v>183</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="K280" s="4"/>
       <c r="L280" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M280" s="4"/>
-      <c r="N280" s="4"/>
+      <c r="M280" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="N280" s="4">
+        <v>8</v>
+      </c>
       <c r="O280" s="4" t="s">
         <v>1338</v>
       </c>
@@ -26549,7 +26539,7 @@
         <v>1340</v>
       </c>
       <c r="AA280" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB280" s="4" t="s">
         <v>47</v>
@@ -26560,16 +26550,16 @@
         <v>1000</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>1337</v>
+        <v>33</v>
       </c>
       <c r="C281" s="4">
-        <v>169240234</v>
+        <v>168725355</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E281" s="4">
-        <v>8020360</v>
+        <v>6893139</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>49</v>
@@ -26584,18 +26574,14 @@
         <v>183</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
       <c r="K281" s="4"/>
       <c r="L281" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M281" s="4" t="s">
-        <v>1341</v>
-      </c>
-      <c r="N281" s="4">
-        <v>8</v>
-      </c>
+      <c r="M281" s="4"/>
+      <c r="N281" s="4"/>
       <c r="O281" s="4" t="s">
         <v>1342</v>
       </c>
@@ -26604,7 +26590,7 @@
         <v>1343</v>
       </c>
       <c r="R281" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S281" s="4">
         <v>0</v>
@@ -26615,14 +26601,14 @@
       <c r="U281" s="4"/>
       <c r="V281" s="4"/>
       <c r="W281" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X281" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y281" s="4"/>
       <c r="Z281" s="4" t="s">
-        <v>1344</v>
+        <v>1271</v>
       </c>
       <c r="AA281" s="4" t="s">
         <v>65</v>
@@ -26636,16 +26622,16 @@
         <v>1000</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>33</v>
+        <v>646</v>
       </c>
       <c r="C282" s="4">
-        <v>168725355</v>
+        <v>169240243</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E282" s="4">
-        <v>6893139</v>
+        <v>7703360</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>49</v>
@@ -26660,11 +26646,11 @@
         <v>183</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="K282" s="4"/>
       <c r="L282" s="4" t="s">
-        <v>289</v>
+        <v>1345</v>
       </c>
       <c r="M282" s="4"/>
       <c r="N282" s="4"/>
@@ -26679,22 +26665,22 @@
         <v>61</v>
       </c>
       <c r="S282" s="4">
-        <v>0</v>
+        <v>173348.56</v>
       </c>
       <c r="T282" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U282" s="4"/>
       <c r="V282" s="4"/>
       <c r="W282" s="4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="X282" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y282" s="4"/>
       <c r="Z282" s="4" t="s">
-        <v>1275</v>
+        <v>1348</v>
       </c>
       <c r="AA282" s="4" t="s">
         <v>65</v>
@@ -26708,16 +26694,16 @@
         <v>1000</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>646</v>
+        <v>33</v>
       </c>
       <c r="C283" s="4">
-        <v>169240243</v>
+        <v>169522397</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E283" s="4">
-        <v>7703360</v>
+        <v>7703225</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>49</v>
@@ -26732,41 +26718,41 @@
         <v>183</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="K283" s="4"/>
       <c r="L283" s="4" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="M283" s="4"/>
       <c r="N283" s="4"/>
       <c r="O283" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="P283" s="5"/>
       <c r="Q283" s="4" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="R283" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S283" s="4">
-        <v>173348.56</v>
+        <v>0</v>
       </c>
       <c r="T283" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U283" s="4"/>
       <c r="V283" s="4"/>
       <c r="W283" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X283" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y283" s="4"/>
       <c r="Z283" s="4" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="AA283" s="4" t="s">
         <v>65</v>
@@ -26780,16 +26766,16 @@
         <v>1000</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>33</v>
+        <v>618</v>
       </c>
       <c r="C284" s="4">
-        <v>169522397</v>
+        <v>168805201</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="E284" s="4">
-        <v>7703225</v>
+        <v>8397173</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>49</v>
@@ -26804,12 +26790,10 @@
         <v>183</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="K284" s="4"/>
-      <c r="L284" s="4" t="s">
-        <v>1349</v>
-      </c>
+      <c r="L284" s="4"/>
       <c r="M284" s="4"/>
       <c r="N284" s="4"/>
       <c r="O284" s="4" t="s">
@@ -26831,20 +26815,18 @@
       <c r="U284" s="4"/>
       <c r="V284" s="4"/>
       <c r="W284" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X284" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y284" s="4"/>
       <c r="Z284" s="4" t="s">
         <v>1355</v>
       </c>
-      <c r="AA284" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA284" s="4"/>
       <c r="AB284" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="285" spans="1:28">
@@ -26852,16 +26834,16 @@
         <v>1000</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>618</v>
+        <v>421</v>
       </c>
       <c r="C285" s="4">
-        <v>168805201</v>
+        <v>169354697</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>247</v>
+        <v>57</v>
       </c>
       <c r="E285" s="4">
-        <v>8397173</v>
+        <v>1125234</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>49</v>
@@ -26879,7 +26861,9 @@
         <v>1356</v>
       </c>
       <c r="K285" s="4"/>
-      <c r="L285" s="4"/>
+      <c r="L285" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M285" s="4"/>
       <c r="N285" s="4"/>
       <c r="O285" s="4" t="s">
@@ -26898,21 +26882,27 @@
       <c r="T285" s="4">
         <v>0</v>
       </c>
-      <c r="U285" s="4"/>
-      <c r="V285" s="4"/>
+      <c r="U285" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="V285" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W285" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X285" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y285" s="4"/>
       <c r="Z285" s="4" t="s">
-        <v>1359</v>
-      </c>
-      <c r="AA285" s="4"/>
+        <v>1360</v>
+      </c>
+      <c r="AA285" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB285" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="286" spans="1:28">
@@ -26923,13 +26913,13 @@
         <v>421</v>
       </c>
       <c r="C286" s="4">
-        <v>169354697</v>
+        <v>169354698</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E286" s="4">
-        <v>1125234</v>
+        <v>6560463</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>49</v>
@@ -26944,7 +26934,7 @@
         <v>183</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K286" s="4"/>
       <c r="L286" s="4" t="s">
@@ -26957,7 +26947,7 @@
       </c>
       <c r="P286" s="5"/>
       <c r="Q286" s="4" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="R286" s="4" t="s">
         <v>61</v>
@@ -26969,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="U286" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="V286" s="4" t="s">
         <v>1363</v>
-      </c>
-      <c r="V286" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="W286" s="4">
         <v>3</v>
@@ -26985,7 +26975,7 @@
         <v>1364</v>
       </c>
       <c r="AA286" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB286" s="4" t="s">
         <v>47</v>
@@ -26996,16 +26986,16 @@
         <v>1000</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="C287" s="4">
-        <v>169354698</v>
+        <v>169468953</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E287" s="4">
-        <v>6560463</v>
+        <v>1034443</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>49</v>
@@ -27020,20 +27010,24 @@
         <v>183</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K287" s="4"/>
       <c r="L287" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M287" s="4"/>
-      <c r="N287" s="4"/>
+        <v>1365</v>
+      </c>
+      <c r="M287" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="N287" s="4">
+        <v>34</v>
+      </c>
       <c r="O287" s="4" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="4" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="R287" s="4" t="s">
         <v>61</v>
@@ -27044,24 +27038,20 @@
       <c r="T287" s="4">
         <v>0</v>
       </c>
-      <c r="U287" s="4" t="s">
-        <v>1366</v>
-      </c>
-      <c r="V287" s="4" t="s">
-        <v>1367</v>
-      </c>
+      <c r="U287" s="4"/>
+      <c r="V287" s="4"/>
       <c r="W287" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X287" s="4" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="Y287" s="4"/>
       <c r="Z287" s="4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="AA287" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB287" s="4" t="s">
         <v>47</v>
@@ -27072,16 +27062,16 @@
         <v>1000</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>337</v>
+        <v>968</v>
       </c>
       <c r="C288" s="4">
-        <v>169468953</v>
+        <v>169240185</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E288" s="4">
-        <v>1034443</v>
+        <v>6517492</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>49</v>
@@ -27096,17 +27086,17 @@
         <v>183</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K288" s="4"/>
       <c r="L288" s="4" t="s">
-        <v>1369</v>
+        <v>876</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>1370</v>
       </c>
       <c r="N288" s="4">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="O288" s="4" t="s">
         <v>1371</v>
@@ -27124,21 +27114,23 @@
       <c r="T288" s="4">
         <v>0</v>
       </c>
-      <c r="U288" s="4"/>
-      <c r="V288" s="4"/>
+      <c r="U288" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="V288" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="W288" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X288" s="4" t="s">
-        <v>342</v>
+        <v>202</v>
       </c>
       <c r="Y288" s="4"/>
       <c r="Z288" s="4" t="s">
-        <v>1373</v>
-      </c>
-      <c r="AA288" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1374</v>
+      </c>
+      <c r="AA288" s="4"/>
       <c r="AB288" s="4" t="s">
         <v>47</v>
       </c>
@@ -27148,16 +27140,16 @@
         <v>1000</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>968</v>
+        <v>918</v>
       </c>
       <c r="C289" s="4">
-        <v>169240185</v>
+        <v>169240208</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E289" s="4">
-        <v>6517492</v>
+        <v>6508453</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>49</v>
@@ -27172,24 +27164,24 @@
         <v>183</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K289" s="4"/>
       <c r="L289" s="4" t="s">
         <v>876</v>
       </c>
       <c r="M289" s="4" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="N289" s="4">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="O289" s="4" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="P289" s="5"/>
       <c r="Q289" s="4" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="R289" s="4" t="s">
         <v>61</v>
@@ -27200,12 +27192,8 @@
       <c r="T289" s="4">
         <v>0</v>
       </c>
-      <c r="U289" s="4" t="s">
-        <v>1377</v>
-      </c>
-      <c r="V289" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="U289" s="4"/>
+      <c r="V289" s="4"/>
       <c r="W289" s="4">
         <v>4</v>
       </c>
@@ -27214,9 +27202,11 @@
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1378</v>
-      </c>
-      <c r="AA289" s="4"/>
+        <v>1336</v>
+      </c>
+      <c r="AA289" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB289" s="4" t="s">
         <v>47</v>
       </c>
@@ -27226,16 +27216,16 @@
         <v>1000</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>918</v>
+        <v>33</v>
       </c>
       <c r="C290" s="4">
-        <v>169240208</v>
+        <v>169240192</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E290" s="4">
-        <v>6508453</v>
+        <v>6568702</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>49</v>
@@ -27250,48 +27240,52 @@
         <v>183</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="M290" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="M290" s="4" t="s">
+      <c r="N290" s="4">
+        <v>12</v>
+      </c>
+      <c r="O290" s="4" t="s">
         <v>1379</v>
-      </c>
-      <c r="N290" s="4">
-        <v>31</v>
-      </c>
-      <c r="O290" s="4" t="s">
-        <v>1380</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="R290" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S290" s="4">
+        <v>0</v>
+      </c>
+      <c r="T290" s="4">
+        <v>0</v>
+      </c>
+      <c r="U290" s="4" t="s">
         <v>1381</v>
       </c>
-      <c r="R290" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S290" s="4">
-        <v>0</v>
-      </c>
-      <c r="T290" s="4">
-        <v>0</v>
-      </c>
-      <c r="U290" s="4"/>
-      <c r="V290" s="4"/>
+      <c r="V290" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="W290" s="4">
         <v>4</v>
       </c>
       <c r="X290" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y290" s="4"/>
       <c r="Z290" s="4" t="s">
-        <v>1340</v>
+        <v>1382</v>
       </c>
       <c r="AA290" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB290" s="4" t="s">
         <v>47</v>
@@ -27305,13 +27299,13 @@
         <v>33</v>
       </c>
       <c r="C291" s="4">
-        <v>169240192</v>
+        <v>169240194</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E291" s="4">
-        <v>6568702</v>
+        <v>6837112</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>49</v>
@@ -27326,17 +27320,17 @@
         <v>183</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="K291" s="4"/>
       <c r="L291" s="4" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>876</v>
       </c>
       <c r="N291" s="4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O291" s="4" t="s">
         <v>1383</v>
@@ -27346,7 +27340,7 @@
         <v>1384</v>
       </c>
       <c r="R291" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S291" s="4">
         <v>0</v>
@@ -27354,12 +27348,8 @@
       <c r="T291" s="4">
         <v>0</v>
       </c>
-      <c r="U291" s="4" t="s">
-        <v>1385</v>
-      </c>
-      <c r="V291" s="4" t="s">
-        <v>477</v>
-      </c>
+      <c r="U291" s="4"/>
+      <c r="V291" s="4"/>
       <c r="W291" s="4">
         <v>4</v>
       </c>
@@ -27368,7 +27358,7 @@
       </c>
       <c r="Y291" s="4"/>
       <c r="Z291" s="4" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="AA291" s="4" t="s">
         <v>65</v>
@@ -27382,16 +27372,16 @@
         <v>1000</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C292" s="4">
-        <v>169240194</v>
+        <v>169338674</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E292" s="4">
-        <v>6837112</v>
+        <v>8330993</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>49</v>
@@ -27406,49 +27396,41 @@
         <v>183</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="K292" s="4"/>
-      <c r="L292" s="4" t="s">
-        <v>1382</v>
-      </c>
-      <c r="M292" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="N292" s="4">
-        <v>4</v>
-      </c>
+      <c r="L292" s="4"/>
+      <c r="M292" s="4"/>
+      <c r="N292" s="4"/>
       <c r="O292" s="4" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="R292" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S292" s="4">
-        <v>0</v>
+        <v>93737.62</v>
       </c>
       <c r="T292" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U292" s="4"/>
       <c r="V292" s="4"/>
       <c r="W292" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X292" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y292" s="4"/>
       <c r="Z292" s="4" t="s">
-        <v>1386</v>
-      </c>
-      <c r="AA292" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1388</v>
+      </c>
+      <c r="AA292" s="4"/>
       <c r="AB292" s="4" t="s">
         <v>47</v>
       </c>
@@ -27458,16 +27440,16 @@
         <v>1000</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C293" s="4">
-        <v>169338674</v>
+        <v>169528013</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E293" s="4">
-        <v>8330993</v>
+        <v>7815930</v>
       </c>
       <c r="F293" s="4" t="s">
         <v>49</v>
@@ -27485,9 +27467,13 @@
         <v>1389</v>
       </c>
       <c r="K293" s="4"/>
-      <c r="L293" s="4"/>
+      <c r="L293" s="4" t="s">
+        <v>517</v>
+      </c>
       <c r="M293" s="4"/>
-      <c r="N293" s="4"/>
+      <c r="N293" s="4">
+        <v>25</v>
+      </c>
       <c r="O293" s="4" t="s">
         <v>1390</v>
       </c>
@@ -27499,24 +27485,26 @@
         <v>61</v>
       </c>
       <c r="S293" s="4">
-        <v>93737.62</v>
+        <v>0</v>
       </c>
       <c r="T293" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U293" s="4"/>
       <c r="V293" s="4"/>
       <c r="W293" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X293" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y293" s="4"/>
       <c r="Z293" s="4" t="s">
         <v>1392</v>
       </c>
-      <c r="AA293" s="4"/>
+      <c r="AA293" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB293" s="4" t="s">
         <v>47</v>
       </c>
@@ -27526,16 +27514,16 @@
         <v>1000</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
       <c r="C294" s="4">
-        <v>169528013</v>
+        <v>169355860</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E294" s="4">
-        <v>7815930</v>
+        <v>7063828</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>49</v>
@@ -27553,13 +27541,9 @@
         <v>1393</v>
       </c>
       <c r="K294" s="4"/>
-      <c r="L294" s="4" t="s">
-        <v>517</v>
-      </c>
+      <c r="L294" s="4"/>
       <c r="M294" s="4"/>
-      <c r="N294" s="4">
-        <v>25</v>
-      </c>
+      <c r="N294" s="4"/>
       <c r="O294" s="4" t="s">
         <v>1394</v>
       </c>
@@ -27568,28 +27552,28 @@
         <v>1395</v>
       </c>
       <c r="R294" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S294" s="4">
-        <v>0</v>
+        <v>99693.64999999999</v>
       </c>
       <c r="T294" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U294" s="4"/>
       <c r="V294" s="4"/>
       <c r="W294" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X294" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y294" s="4"/>
       <c r="Z294" s="4" t="s">
-        <v>1396</v>
+        <v>287</v>
       </c>
       <c r="AA294" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB294" s="4" t="s">
         <v>47</v>
@@ -27603,13 +27587,13 @@
         <v>196</v>
       </c>
       <c r="C295" s="4">
-        <v>169355860</v>
+        <v>169355855</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E295" s="4">
-        <v>7063828</v>
+        <v>5883241</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>49</v>
@@ -27624,27 +27608,29 @@
         <v>183</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="K295" s="4"/>
-      <c r="L295" s="4"/>
+      <c r="L295" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
       <c r="O295" s="4" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S295" s="4">
-        <v>99693.64999999999</v>
+        <v>179936.31</v>
       </c>
       <c r="T295" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U295" s="4"/>
       <c r="V295" s="4"/>
@@ -27656,10 +27642,10 @@
       </c>
       <c r="Y295" s="4"/>
       <c r="Z295" s="4" t="s">
-        <v>287</v>
+        <v>404</v>
       </c>
       <c r="AA295" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB295" s="4" t="s">
         <v>47</v>
@@ -27670,16 +27656,16 @@
         <v>1000</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C296" s="4">
-        <v>169355855</v>
+        <v>169359076</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E296" s="4">
-        <v>5883241</v>
+        <v>6989239</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>49</v>
@@ -27694,29 +27680,29 @@
         <v>183</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
-        <v>289</v>
+        <v>1345</v>
       </c>
       <c r="M296" s="4"/>
       <c r="N296" s="4"/>
       <c r="O296" s="4" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S296" s="4">
-        <v>179936.31</v>
+        <v>0</v>
       </c>
       <c r="T296" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
@@ -27728,10 +27714,10 @@
       </c>
       <c r="Y296" s="4"/>
       <c r="Z296" s="4" t="s">
-        <v>404</v>
+        <v>1400</v>
       </c>
       <c r="AA296" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB296" s="4" t="s">
         <v>47</v>
@@ -27742,16 +27728,16 @@
         <v>1000</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C297" s="4">
-        <v>169359076</v>
+        <v>169475694</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E297" s="4">
-        <v>6989239</v>
+        <v>7353382</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>49</v>
@@ -27766,20 +27752,20 @@
         <v>183</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="M297" s="4"/>
       <c r="N297" s="4"/>
       <c r="O297" s="4" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>79</v>
@@ -27793,17 +27779,17 @@
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
       <c r="W297" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X297" s="4" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="AA297" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB297" s="4" t="s">
         <v>47</v>
@@ -27814,16 +27800,16 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>246</v>
+        <v>1404</v>
       </c>
       <c r="C298" s="4">
-        <v>169475694</v>
+        <v>168725316</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E298" s="4">
-        <v>7353382</v>
+        <v>1099225</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>49</v>
@@ -27838,44 +27824,50 @@
         <v>183</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>1349</v>
-      </c>
-      <c r="M298" s="4"/>
+        <v>1406</v>
+      </c>
+      <c r="M298" s="4" t="s">
+        <v>1407</v>
+      </c>
       <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="R298" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S298" s="4">
-        <v>0</v>
+        <v>724798.47</v>
       </c>
       <c r="T298" s="4">
-        <v>0</v>
-      </c>
-      <c r="U298" s="4"/>
-      <c r="V298" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U298" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="V298" s="4" t="s">
+        <v>1411</v>
+      </c>
       <c r="W298" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X298" s="4" t="s">
-        <v>342</v>
+        <v>202</v>
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>1407</v>
+        <v>1271</v>
       </c>
       <c r="AA298" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB298" s="4" t="s">
         <v>47</v>
@@ -27886,13 +27878,13 @@
         <v>1000</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>1408</v>
+        <v>33</v>
       </c>
       <c r="C299" s="4">
-        <v>168725316</v>
+        <v>169523105</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E299" s="4">
         <v>1099225</v>
@@ -27910,47 +27902,47 @@
         <v>183</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="M299" s="4" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="N299" s="4"/>
       <c r="O299" s="4" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S299" s="4">
-        <v>724798.47</v>
+        <v>364931.37</v>
       </c>
       <c r="T299" s="4">
         <v>3</v>
       </c>
       <c r="U299" s="4" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="V299" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="W299" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X299" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y299" s="4"/>
       <c r="Z299" s="4" t="s">
-        <v>1275</v>
+        <v>1412</v>
       </c>
       <c r="AA299" s="4" t="s">
         <v>65</v>
@@ -27964,16 +27956,16 @@
         <v>1000</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>33</v>
+        <v>448</v>
       </c>
       <c r="C300" s="4">
-        <v>169523105</v>
+        <v>169228645</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E300" s="4">
-        <v>1099225</v>
+        <v>8388337</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>49</v>
@@ -27988,53 +27980,43 @@
         <v>183</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="K300" s="4"/>
-      <c r="L300" s="4" t="s">
-        <v>1410</v>
-      </c>
-      <c r="M300" s="4" t="s">
-        <v>1411</v>
-      </c>
+      <c r="L300" s="4"/>
+      <c r="M300" s="4"/>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="R300" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S300" s="4">
-        <v>364931.37</v>
+        <v>0</v>
       </c>
       <c r="T300" s="4">
-        <v>3</v>
-      </c>
-      <c r="U300" s="4" t="s">
-        <v>1414</v>
-      </c>
-      <c r="V300" s="4" t="s">
-        <v>1415</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U300" s="4"/>
+      <c r="V300" s="4"/>
       <c r="W300" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X300" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
         <v>1416</v>
       </c>
-      <c r="AA300" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA300" s="4"/>
       <c r="AB300" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="301" spans="1:28">
@@ -28042,16 +28024,16 @@
         <v>1000</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="C301" s="4">
-        <v>169228645</v>
+        <v>169348751</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E301" s="4">
-        <v>8388337</v>
+        <v>7936320</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>49</v>
@@ -28066,32 +28048,38 @@
         <v>183</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="K301" s="4"/>
-      <c r="L301" s="4"/>
+      <c r="L301" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
       <c r="O301" s="4" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="R301" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S301" s="4">
+        <v>0</v>
+      </c>
+      <c r="T301" s="4">
+        <v>0</v>
+      </c>
+      <c r="U301" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="R301" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S301" s="4">
-        <v>0</v>
-      </c>
-      <c r="T301" s="4">
-        <v>0</v>
-      </c>
-      <c r="U301" s="4"/>
-      <c r="V301" s="4"/>
+      <c r="V301" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="W301" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X301" s="4" t="s">
         <v>202</v>
@@ -28102,7 +28090,7 @@
       </c>
       <c r="AA301" s="4"/>
       <c r="AB301" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="302" spans="1:28">
@@ -28110,16 +28098,16 @@
         <v>1000</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C302" s="4">
-        <v>169348751</v>
+        <v>169528466</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E302" s="4">
-        <v>7936320</v>
+        <v>1116215</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>49</v>
@@ -28134,13 +28122,15 @@
         <v>183</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M302" s="4"/>
+        <v>284</v>
+      </c>
+      <c r="M302" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="N302" s="4"/>
       <c r="O302" s="4" t="s">
         <v>1421</v>
@@ -28150,7 +28140,7 @@
         <v>1422</v>
       </c>
       <c r="R302" s="4" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S302" s="4">
         <v>0</v>
@@ -28162,17 +28152,17 @@
         <v>1423</v>
       </c>
       <c r="V302" s="4" t="s">
-        <v>69</v>
+        <v>1424</v>
       </c>
       <c r="W302" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X302" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="AA302" s="4"/>
       <c r="AB302" s="4" t="s">
@@ -28184,16 +28174,16 @@
         <v>1000</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>33</v>
+        <v>448</v>
       </c>
       <c r="C303" s="4">
-        <v>169528466</v>
+        <v>168897696</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E303" s="4">
-        <v>1116215</v>
+        <v>8305739</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>49</v>
@@ -28208,49 +28198,49 @@
         <v>183</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4" t="s">
-        <v>284</v>
+        <v>881</v>
       </c>
       <c r="M303" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="N303" s="4"/>
+        <v>983</v>
+      </c>
+      <c r="N303" s="4">
+        <v>101</v>
+      </c>
       <c r="O303" s="4" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="R303" s="4" t="s">
-        <v>257</v>
+        <v>61</v>
       </c>
       <c r="S303" s="4">
-        <v>0</v>
+        <v>184614.72</v>
       </c>
       <c r="T303" s="4">
-        <v>0</v>
-      </c>
-      <c r="U303" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="V303" s="4" t="s">
-        <v>1428</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U303" s="4"/>
+      <c r="V303" s="4"/>
       <c r="W303" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X303" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="AA303" s="4"/>
+        <v>1428</v>
+      </c>
+      <c r="AA303" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="AB303" s="4" t="s">
         <v>47</v>
       </c>
@@ -28260,16 +28250,16 @@
         <v>1000</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="C304" s="4">
-        <v>168897696</v>
+        <v>169525511</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E304" s="4">
-        <v>8305739</v>
+        <v>8305779</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>49</v>
@@ -28284,7 +28274,7 @@
         <v>183</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
@@ -28297,32 +28287,32 @@
         <v>101</v>
       </c>
       <c r="O304" s="4" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S304" s="4">
-        <v>184614.72</v>
+        <v>54320.17</v>
       </c>
       <c r="T304" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U304" s="4"/>
       <c r="V304" s="4"/>
       <c r="W304" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X304" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y304" s="4"/>
       <c r="Z304" s="4" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="AA304" s="4" t="s">
         <v>305</v>
@@ -28339,13 +28329,13 @@
         <v>33</v>
       </c>
       <c r="C305" s="4">
-        <v>169525511</v>
+        <v>169525177</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>188</v>
+        <v>472</v>
       </c>
       <c r="E305" s="4">
-        <v>8305779</v>
+        <v>8289365</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>49</v>
@@ -28360,33 +28350,33 @@
         <v>183</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1417</v>
+        <v>1432</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
-        <v>881</v>
+        <v>1433</v>
       </c>
       <c r="M305" s="4" t="s">
-        <v>983</v>
+        <v>1434</v>
       </c>
       <c r="N305" s="4">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="O305" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="R305" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S305" s="4">
-        <v>54320.17</v>
+        <v>469783.86</v>
       </c>
       <c r="T305" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U305" s="4"/>
       <c r="V305" s="4"/>
@@ -28398,13 +28388,13 @@
       </c>
       <c r="Y305" s="4"/>
       <c r="Z305" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="AA305" s="4" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="AB305" s="4" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="306" spans="1:28">
@@ -28412,16 +28402,16 @@
         <v>1000</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>33</v>
+        <v>421</v>
       </c>
       <c r="C306" s="4">
-        <v>169525177</v>
+        <v>168896160</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>472</v>
+        <v>57</v>
       </c>
       <c r="E306" s="4">
-        <v>8289365</v>
+        <v>5920990</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>49</v>
@@ -28436,51 +28426,55 @@
         <v>183</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="M306" s="4" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="N306" s="4">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="R306" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S306" s="4">
-        <v>469783.86</v>
+        <v>181369.34</v>
       </c>
       <c r="T306" s="4">
-        <v>4</v>
-      </c>
-      <c r="U306" s="4"/>
-      <c r="V306" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U306" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="V306" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="W306" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X306" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y306" s="4"/>
       <c r="Z306" s="4" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="AA306" s="4" t="s">
-        <v>46</v>
+        <v>1445</v>
       </c>
       <c r="AB306" s="4" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
     </row>
     <row r="307" spans="1:28">
@@ -28488,16 +28482,16 @@
         <v>1000</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="C307" s="4">
-        <v>168896160</v>
+        <v>169365038</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E307" s="4">
-        <v>5920990</v>
+        <v>6591932</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>49</v>
@@ -28512,52 +28506,52 @@
         <v>183</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="M307" s="4" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="N307" s="4">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S307" s="4">
-        <v>181369.34</v>
+        <v>0</v>
       </c>
       <c r="T307" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U307" s="4" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="V307" s="4" t="s">
-        <v>477</v>
+        <v>43</v>
       </c>
       <c r="W307" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X307" s="4" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="AA307" s="4" t="s">
-        <v>1449</v>
+        <v>46</v>
       </c>
       <c r="AB307" s="4" t="s">
         <v>47</v>
@@ -28568,16 +28562,16 @@
         <v>1000</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="C308" s="4">
-        <v>169365038</v>
+        <v>169240239</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E308" s="4">
-        <v>6591932</v>
+        <v>7735512</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>49</v>
@@ -28592,17 +28586,17 @@
         <v>183</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
-        <v>1450</v>
+        <v>107</v>
       </c>
       <c r="M308" s="4" t="s">
-        <v>1451</v>
+        <v>876</v>
       </c>
       <c r="N308" s="4">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="O308" s="4" t="s">
         <v>1452</v>
@@ -28620,21 +28614,17 @@
       <c r="T308" s="4">
         <v>0</v>
       </c>
-      <c r="U308" s="4" t="s">
-        <v>1454</v>
-      </c>
-      <c r="V308" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="U308" s="4"/>
+      <c r="V308" s="4"/>
       <c r="W308" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X308" s="4" t="s">
-        <v>342</v>
+        <v>202</v>
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="AA308" s="4" t="s">
         <v>46</v>
@@ -28651,13 +28641,13 @@
         <v>353</v>
       </c>
       <c r="C309" s="4">
-        <v>169240239</v>
+        <v>169240240</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E309" s="4">
-        <v>7735512</v>
+        <v>6588082</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>49</v>
@@ -28672,7 +28662,7 @@
         <v>183</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
@@ -28685,11 +28675,11 @@
         <v>58</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="R309" s="4" t="s">
         <v>61</v>
@@ -28710,10 +28700,10 @@
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="AA309" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB309" s="4" t="s">
         <v>47</v>
@@ -28727,13 +28717,13 @@
         <v>353</v>
       </c>
       <c r="C310" s="4">
-        <v>169240240</v>
+        <v>169240182</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E310" s="4">
-        <v>6588082</v>
+        <v>5878950</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>49</v>
@@ -28748,7 +28738,7 @@
         <v>183</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -28758,17 +28748,17 @@
         <v>876</v>
       </c>
       <c r="N310" s="4">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="S310" s="4">
         <v>0</v>
@@ -28786,10 +28776,10 @@
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="AA310" s="4" t="s">
-        <v>65</v>
+        <v>352</v>
       </c>
       <c r="AB310" s="4" t="s">
         <v>47</v>
@@ -28800,16 +28790,16 @@
         <v>1000</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>353</v>
+        <v>1333</v>
       </c>
       <c r="C311" s="4">
-        <v>169240182</v>
+        <v>169240231</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E311" s="4">
-        <v>5878950</v>
+        <v>8026082</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>49</v>
@@ -28824,17 +28814,17 @@
         <v>183</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
-        <v>107</v>
+        <v>1175</v>
       </c>
       <c r="M311" s="4" t="s">
-        <v>876</v>
+        <v>1460</v>
       </c>
       <c r="N311" s="4">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="O311" s="4" t="s">
         <v>1461</v>
@@ -28844,7 +28834,7 @@
         <v>1462</v>
       </c>
       <c r="R311" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S311" s="4">
         <v>0</v>
@@ -28865,7 +28855,7 @@
         <v>1463</v>
       </c>
       <c r="AA311" s="4" t="s">
-        <v>352</v>
+        <v>46</v>
       </c>
       <c r="AB311" s="4" t="s">
         <v>47</v>
@@ -28876,16 +28866,16 @@
         <v>1000</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1337</v>
+        <v>33</v>
       </c>
       <c r="C312" s="4">
-        <v>169240231</v>
+        <v>168896205</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E312" s="4">
-        <v>8026082</v>
+        <v>6530459</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>49</v>
@@ -28900,24 +28890,24 @@
         <v>183</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>1175</v>
+        <v>875</v>
       </c>
       <c r="M312" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="N312" s="4">
+        <v>105</v>
+      </c>
+      <c r="O312" s="4" t="s">
         <v>1464</v>
-      </c>
-      <c r="N312" s="4">
-        <v>6</v>
-      </c>
-      <c r="O312" s="4" t="s">
-        <v>1465</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>61</v>
@@ -28928,13 +28918,17 @@
       <c r="T312" s="4">
         <v>0</v>
       </c>
-      <c r="U312" s="4"/>
-      <c r="V312" s="4"/>
+      <c r="U312" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="V312" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="W312" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X312" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
@@ -28952,16 +28946,16 @@
         <v>1000</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>33</v>
+        <v>1333</v>
       </c>
       <c r="C313" s="4">
-        <v>168896205</v>
+        <v>169240188</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E313" s="4">
-        <v>6530459</v>
+        <v>6567408</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>49</v>
@@ -28976,24 +28970,24 @@
         <v>183</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>875</v>
+        <v>1440</v>
       </c>
       <c r="M313" s="4" t="s">
-        <v>876</v>
+        <v>1468</v>
       </c>
       <c r="N313" s="4">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="O313" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="R313" s="4" t="s">
         <v>61</v>
@@ -29005,24 +28999,22 @@
         <v>0</v>
       </c>
       <c r="U313" s="4" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="V313" s="4" t="s">
-        <v>477</v>
+        <v>1472</v>
       </c>
       <c r="W313" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X313" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
-        <v>1471</v>
-      </c>
-      <c r="AA313" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1473</v>
+      </c>
+      <c r="AA313" s="4"/>
       <c r="AB313" s="4" t="s">
         <v>47</v>
       </c>
@@ -29032,16 +29024,16 @@
         <v>1000</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1337</v>
+        <v>33</v>
       </c>
       <c r="C314" s="4">
-        <v>169240188</v>
+        <v>169528015</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E314" s="4">
-        <v>6567408</v>
+        <v>7609168</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>49</v>
@@ -29056,24 +29048,24 @@
         <v>183</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1442</v>
+        <v>1474</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>1444</v>
+        <v>950</v>
       </c>
       <c r="M314" s="4" t="s">
-        <v>1472</v>
+        <v>750</v>
       </c>
       <c r="N314" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O314" s="4" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>61</v>
@@ -29084,23 +29076,21 @@
       <c r="T314" s="4">
         <v>0</v>
       </c>
-      <c r="U314" s="4" t="s">
-        <v>1475</v>
-      </c>
-      <c r="V314" s="4" t="s">
-        <v>1476</v>
-      </c>
+      <c r="U314" s="4"/>
+      <c r="V314" s="4"/>
       <c r="W314" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X314" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="AA314" s="4"/>
+      <c r="AA314" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB314" s="4" t="s">
         <v>47</v>
       </c>
@@ -29110,16 +29100,16 @@
         <v>1000</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>33</v>
+        <v>1404</v>
       </c>
       <c r="C315" s="4">
-        <v>169528015</v>
+        <v>168725318</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E315" s="4">
-        <v>7609168</v>
+        <v>7378230</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>49</v>
@@ -29138,44 +29128,48 @@
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
-        <v>950</v>
+        <v>1479</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>750</v>
+        <v>1480</v>
       </c>
       <c r="N315" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O315" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="R315" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S315" s="4">
-        <v>0</v>
+        <v>736214.27</v>
       </c>
       <c r="T315" s="4">
-        <v>0</v>
-      </c>
-      <c r="U315" s="4"/>
-      <c r="V315" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="U315" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="V315" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W315" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="X315" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y315" s="4"/>
       <c r="Z315" s="4" t="s">
-        <v>1481</v>
+        <v>593</v>
       </c>
       <c r="AA315" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB315" s="4" t="s">
         <v>47</v>
@@ -29186,16 +29180,16 @@
         <v>1000</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1408</v>
+        <v>246</v>
       </c>
       <c r="C316" s="4">
-        <v>168725318</v>
+        <v>169350529</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E316" s="4">
-        <v>7378230</v>
+        <v>6817697</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>49</v>
@@ -29210,18 +29204,14 @@
         <v>183</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>1483</v>
-      </c>
-      <c r="M316" s="4" t="s">
-        <v>1484</v>
-      </c>
-      <c r="N316" s="4">
-        <v>17</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M316" s="4"/>
+      <c r="N316" s="4"/>
       <c r="O316" s="4" t="s">
         <v>1485</v>
       </c>
@@ -29230,29 +29220,25 @@
         <v>1486</v>
       </c>
       <c r="R316" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S316" s="4">
-        <v>736214.27</v>
+        <v>0</v>
       </c>
       <c r="T316" s="4">
-        <v>6</v>
-      </c>
-      <c r="U316" s="4" t="s">
-        <v>1487</v>
-      </c>
-      <c r="V316" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U316" s="4"/>
+      <c r="V316" s="4"/>
       <c r="W316" s="4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="X316" s="4" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>593</v>
+        <v>1487</v>
       </c>
       <c r="AA316" s="4" t="s">
         <v>46</v>
@@ -29266,16 +29252,16 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="C317" s="4">
-        <v>169350529</v>
+        <v>169536657</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E317" s="4">
-        <v>6817697</v>
+        <v>6840794</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>49</v>
@@ -29290,7 +29276,7 @@
         <v>183</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="K317" s="4"/>
       <c r="L317" s="4" t="s">
@@ -29299,36 +29285,38 @@
       <c r="M317" s="4"/>
       <c r="N317" s="4"/>
       <c r="O317" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="R317" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S317" s="4">
+        <v>0</v>
+      </c>
+      <c r="T317" s="4">
+        <v>0</v>
+      </c>
+      <c r="U317" s="4" t="s">
         <v>1490</v>
       </c>
-      <c r="R317" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S317" s="4">
-        <v>0</v>
-      </c>
-      <c r="T317" s="4">
-        <v>0</v>
-      </c>
-      <c r="U317" s="4"/>
-      <c r="V317" s="4"/>
+      <c r="V317" s="4" t="s">
+        <v>992</v>
+      </c>
       <c r="W317" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X317" s="4" t="s">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="Y317" s="4"/>
       <c r="Z317" s="4" t="s">
         <v>1491</v>
       </c>
-      <c r="AA317" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA317" s="4"/>
       <c r="AB317" s="4" t="s">
         <v>47</v>
       </c>
@@ -29338,16 +29326,16 @@
         <v>1000</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>33</v>
+        <v>448</v>
       </c>
       <c r="C318" s="4">
-        <v>169536657</v>
+        <v>168910101</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E318" s="4">
-        <v>6840794</v>
+        <v>8307826</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>49</v>
@@ -29362,20 +29350,18 @@
         <v>183</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="K318" s="4"/>
-      <c r="L318" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L318" s="4"/>
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
       <c r="O318" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="R318" s="4" t="s">
         <v>61</v>
@@ -29386,23 +29372,21 @@
       <c r="T318" s="4">
         <v>0</v>
       </c>
-      <c r="U318" s="4" t="s">
-        <v>1494</v>
-      </c>
-      <c r="V318" s="4" t="s">
-        <v>992</v>
-      </c>
+      <c r="U318" s="4"/>
+      <c r="V318" s="4"/>
       <c r="W318" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X318" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
         <v>1495</v>
       </c>
-      <c r="AA318" s="4"/>
+      <c r="AA318" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="AB318" s="4" t="s">
         <v>47</v>
       </c>
@@ -29415,13 +29399,13 @@
         <v>448</v>
       </c>
       <c r="C319" s="4">
-        <v>168910101</v>
+        <v>168908257</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>188</v>
+        <v>581</v>
       </c>
       <c r="E319" s="4">
-        <v>8307826</v>
+        <v>6945604</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>49</v>
@@ -29436,30 +29420,36 @@
         <v>183</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="K319" s="4"/>
-      <c r="L319" s="4"/>
+      <c r="L319" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M319" s="4"/>
       <c r="N319" s="4"/>
       <c r="O319" s="4" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="R319" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S319" s="4">
+        <v>0</v>
+      </c>
+      <c r="T319" s="4">
+        <v>0</v>
+      </c>
+      <c r="U319" s="4" t="s">
         <v>1498</v>
       </c>
-      <c r="R319" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S319" s="4">
-        <v>0</v>
-      </c>
-      <c r="T319" s="4">
-        <v>0</v>
-      </c>
-      <c r="U319" s="4"/>
-      <c r="V319" s="4"/>
+      <c r="V319" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="W319" s="4">
         <v>8</v>
       </c>
@@ -29471,7 +29461,7 @@
         <v>1499</v>
       </c>
       <c r="AA319" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB319" s="4" t="s">
         <v>47</v>
@@ -29482,16 +29472,16 @@
         <v>1000</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="C320" s="4">
-        <v>168908257</v>
+        <v>169517835</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>581</v>
+        <v>472</v>
       </c>
       <c r="E320" s="4">
-        <v>6945604</v>
+        <v>7666029</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>49</v>
@@ -29506,45 +29496,49 @@
         <v>183</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M320" s="4"/>
-      <c r="N320" s="4"/>
+        <v>1500</v>
+      </c>
+      <c r="M320" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="N320" s="4">
+        <v>19</v>
+      </c>
       <c r="O320" s="4" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="R320" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S320" s="4">
-        <v>0</v>
+        <v>65879.17999999999</v>
       </c>
       <c r="T320" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U320" s="4" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="V320" s="4" t="s">
         <v>477</v>
       </c>
       <c r="W320" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X320" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y320" s="4"/>
       <c r="Z320" s="4" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="AA320" s="4" t="s">
         <v>46</v>
@@ -29561,13 +29555,13 @@
         <v>33</v>
       </c>
       <c r="C321" s="4">
-        <v>169517835</v>
+        <v>169531384</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>472</v>
+        <v>188</v>
       </c>
       <c r="E321" s="4">
-        <v>7666029</v>
+        <v>7770159</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>49</v>
@@ -29582,36 +29576,36 @@
         <v>183</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>1504</v>
+        <v>713</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>713</v>
+        <v>1505</v>
       </c>
       <c r="N321" s="4">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O321" s="4" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="R321" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S321" s="4">
-        <v>65879.17999999999</v>
+        <v>398662.86</v>
       </c>
       <c r="T321" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U321" s="4" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="V321" s="4" t="s">
         <v>477</v>
@@ -29624,13 +29618,13 @@
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="AA321" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB321" s="4" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="322" spans="1:28">
@@ -29638,16 +29632,16 @@
         <v>1000</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C322" s="4">
-        <v>169531384</v>
+        <v>169351859</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E322" s="4">
-        <v>7770159</v>
+        <v>6824154</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>49</v>
@@ -29662,17 +29656,17 @@
         <v>183</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>713</v>
+        <v>355</v>
       </c>
       <c r="M322" s="4" t="s">
-        <v>1509</v>
+        <v>517</v>
       </c>
       <c r="N322" s="4">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="O322" s="4" t="s">
         <v>1510</v>
@@ -29682,35 +29676,31 @@
         <v>1511</v>
       </c>
       <c r="R322" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S322" s="4">
-        <v>398662.86</v>
+        <v>0</v>
       </c>
       <c r="T322" s="4">
-        <v>5</v>
-      </c>
-      <c r="U322" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="V322" s="4" t="s">
-        <v>477</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U322" s="4"/>
+      <c r="V322" s="4"/>
       <c r="W322" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X322" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y322" s="4"/>
       <c r="Z322" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="AA322" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB322" s="4" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
     </row>
     <row r="323" spans="1:28">
@@ -29718,16 +29708,16 @@
         <v>1000</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C323" s="4">
-        <v>169351859</v>
+        <v>169521367</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>188</v>
+        <v>472</v>
       </c>
       <c r="E323" s="4">
-        <v>6824154</v>
+        <v>7984315</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>49</v>
@@ -29742,18 +29732,14 @@
         <v>183</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1496</v>
+        <v>1513</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="M323" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="N323" s="4">
-        <v>12</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M323" s="4"/>
+      <c r="N323" s="4"/>
       <c r="O323" s="4" t="s">
         <v>1514</v>
       </c>
@@ -29765,18 +29751,18 @@
         <v>61</v>
       </c>
       <c r="S323" s="4">
-        <v>0</v>
+        <v>807922.91</v>
       </c>
       <c r="T323" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U323" s="4"/>
       <c r="V323" s="4"/>
       <c r="W323" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X323" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
@@ -29794,16 +29780,16 @@
         <v>1000</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>33</v>
+        <v>1295</v>
       </c>
       <c r="C324" s="4">
-        <v>169521367</v>
+        <v>169355862</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>472</v>
+        <v>57</v>
       </c>
       <c r="E324" s="4">
-        <v>7984315</v>
+        <v>1025722</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>49</v>
@@ -29818,13 +29804,15 @@
         <v>183</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M324" s="4"/>
+      <c r="M324" s="4" t="s">
+        <v>1517</v>
+      </c>
       <c r="N324" s="4"/>
       <c r="O324" s="4" t="s">
         <v>1518</v>
@@ -29837,26 +29825,28 @@
         <v>61</v>
       </c>
       <c r="S324" s="4">
-        <v>807922.91</v>
+        <v>0</v>
       </c>
       <c r="T324" s="4">
-        <v>4</v>
-      </c>
-      <c r="U324" s="4"/>
-      <c r="V324" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U324" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="V324" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W324" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X324" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1520</v>
-      </c>
-      <c r="AA324" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
         <v>47</v>
       </c>
@@ -29866,16 +29856,16 @@
         <v>1000</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1299</v>
+        <v>33</v>
       </c>
       <c r="C325" s="4">
-        <v>169355862</v>
+        <v>168895978</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E325" s="4">
-        <v>1025722</v>
+        <v>1052361</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>49</v>
@@ -29890,25 +29880,25 @@
         <v>183</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
-        <v>289</v>
+        <v>177</v>
       </c>
       <c r="M325" s="4" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="R325" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S325" s="4">
         <v>0</v>
@@ -29917,20 +29907,20 @@
         <v>0</v>
       </c>
       <c r="U325" s="4" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="V325" s="4" t="s">
-        <v>127</v>
+        <v>1526</v>
       </c>
       <c r="W325" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="X325" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>672</v>
+        <v>1527</v>
       </c>
       <c r="AA325" s="4"/>
       <c r="AB325" s="4" t="s">
@@ -29942,16 +29932,16 @@
         <v>1000</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>33</v>
+        <v>1528</v>
       </c>
       <c r="C326" s="4">
-        <v>168895978</v>
+        <v>168896121</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E326" s="4">
-        <v>1052361</v>
+        <v>1052274</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>49</v>
@@ -29966,22 +29956,22 @@
         <v>183</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>177</v>
+        <v>1529</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="N326" s="4"/>
       <c r="O326" s="4" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="R326" s="4" t="s">
         <v>41</v>
@@ -29993,20 +29983,20 @@
         <v>0</v>
       </c>
       <c r="U326" s="4" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="V326" s="4" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="W326" s="4">
         <v>9</v>
       </c>
       <c r="X326" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="AA326" s="4"/>
       <c r="AB326" s="4" t="s">
@@ -30018,16 +30008,16 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C327" s="4">
-        <v>168896121</v>
+        <v>169240252</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E327" s="4">
-        <v>1052274</v>
+        <v>1051677</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>49</v>
@@ -30042,25 +30032,25 @@
         <v>183</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
-        <v>1533</v>
+        <v>320</v>
       </c>
       <c r="M327" s="4" t="s">
-        <v>1534</v>
+        <v>299</v>
       </c>
       <c r="N327" s="4"/>
       <c r="O327" s="4" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="P327" s="5"/>
       <c r="Q327" s="4" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="R327" s="4" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S327" s="4">
         <v>0</v>
@@ -30069,13 +30059,13 @@
         <v>0</v>
       </c>
       <c r="U327" s="4" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="V327" s="4" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="W327" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>202</v>
@@ -30084,7 +30074,9 @@
       <c r="Z327" s="4" t="s">
         <v>1539</v>
       </c>
-      <c r="AA327" s="4"/>
+      <c r="AA327" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB327" s="4" t="s">
         <v>47</v>
       </c>
@@ -30094,16 +30086,16 @@
         <v>1000</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C328" s="4">
-        <v>169240252</v>
+        <v>168896063</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E328" s="4">
-        <v>1051677</v>
+        <v>1103901</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>49</v>
@@ -30118,14 +30110,14 @@
         <v>183</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
         <v>320</v>
       </c>
       <c r="M328" s="4" t="s">
-        <v>299</v>
+        <v>792</v>
       </c>
       <c r="N328" s="4"/>
       <c r="O328" s="4" t="s">
@@ -30136,7 +30128,7 @@
         <v>1541</v>
       </c>
       <c r="R328" s="4" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="S328" s="4">
         <v>0</v>
@@ -30148,17 +30140,17 @@
         <v>1542</v>
       </c>
       <c r="V328" s="4" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="W328" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X328" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="AA328" s="4" t="s">
         <v>46</v>
@@ -30172,16 +30164,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1532</v>
+        <v>456</v>
       </c>
       <c r="C329" s="4">
-        <v>168896063</v>
+        <v>168896653</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E329" s="4">
-        <v>1103901</v>
+        <v>1052622</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>49</v>
@@ -30196,22 +30188,22 @@
         <v>183</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
-        <v>320</v>
+        <v>1545</v>
       </c>
       <c r="M329" s="4" t="s">
-        <v>792</v>
+        <v>1529</v>
       </c>
       <c r="N329" s="4"/>
       <c r="O329" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="R329" s="4" t="s">
         <v>41</v>
@@ -30222,12 +30214,8 @@
       <c r="T329" s="4">
         <v>0</v>
       </c>
-      <c r="U329" s="4" t="s">
-        <v>1546</v>
-      </c>
-      <c r="V329" s="4" t="s">
-        <v>1547</v>
-      </c>
+      <c r="U329" s="4"/>
+      <c r="V329" s="4"/>
       <c r="W329" s="4">
         <v>9</v>
       </c>
@@ -30239,7 +30227,7 @@
         <v>1548</v>
       </c>
       <c r="AA329" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB329" s="4" t="s">
         <v>47</v>
@@ -30250,16 +30238,16 @@
         <v>1000</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>456</v>
+        <v>1528</v>
       </c>
       <c r="C330" s="4">
-        <v>168896653</v>
+        <v>168896015</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E330" s="4">
-        <v>1052622</v>
+        <v>7900282</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>49</v>
@@ -30274,14 +30262,14 @@
         <v>183</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
         <v>1549</v>
       </c>
       <c r="M330" s="4" t="s">
-        <v>1533</v>
+        <v>177</v>
       </c>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
@@ -30295,13 +30283,17 @@
         <v>41</v>
       </c>
       <c r="S330" s="4">
-        <v>0</v>
+        <v>127746.05</v>
       </c>
       <c r="T330" s="4">
-        <v>0</v>
-      </c>
-      <c r="U330" s="4"/>
-      <c r="V330" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U330" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="V330" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="W330" s="4">
         <v>9</v>
       </c>
@@ -30310,10 +30302,10 @@
       </c>
       <c r="Y330" s="4"/>
       <c r="Z330" s="4" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="AA330" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB330" s="4" t="s">
         <v>47</v>
@@ -30324,16 +30316,16 @@
         <v>1000</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1532</v>
+        <v>456</v>
       </c>
       <c r="C331" s="4">
-        <v>168896015</v>
+        <v>168896073</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E331" s="4">
-        <v>7900282</v>
+        <v>7769908</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>49</v>
@@ -30348,38 +30340,34 @@
         <v>183</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="M331" s="4" t="s">
-        <v>177</v>
+        <v>1529</v>
       </c>
       <c r="N331" s="4"/>
       <c r="O331" s="4" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S331" s="4">
-        <v>127746.05</v>
+        <v>393191.56</v>
       </c>
       <c r="T331" s="4">
         <v>1</v>
       </c>
-      <c r="U331" s="4" t="s">
-        <v>1556</v>
-      </c>
-      <c r="V331" s="4" t="s">
-        <v>477</v>
-      </c>
+      <c r="U331" s="4"/>
+      <c r="V331" s="4"/>
       <c r="W331" s="4">
         <v>9</v>
       </c>
@@ -30405,13 +30393,13 @@
         <v>456</v>
       </c>
       <c r="C332" s="4">
-        <v>168896073</v>
+        <v>168896081</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E332" s="4">
-        <v>7769908</v>
+        <v>6943901</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>49</v>
@@ -30426,34 +30414,40 @@
         <v>183</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="M332" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="N332" s="4">
+        <v>12</v>
+      </c>
+      <c r="O332" s="4" t="s">
         <v>1558</v>
-      </c>
-      <c r="M332" s="4" t="s">
-        <v>1533</v>
-      </c>
-      <c r="N332" s="4"/>
-      <c r="O332" s="4" t="s">
-        <v>1559</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S332" s="4">
-        <v>393191.56</v>
+        <v>0</v>
       </c>
       <c r="T332" s="4">
-        <v>1</v>
-      </c>
-      <c r="U332" s="4"/>
-      <c r="V332" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U332" s="4" t="s">
+        <v>1560</v>
+      </c>
+      <c r="V332" s="4" t="s">
+        <v>967</v>
+      </c>
       <c r="W332" s="4">
         <v>9</v>
       </c>
@@ -30465,7 +30459,7 @@
         <v>1561</v>
       </c>
       <c r="AA332" s="4" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="AB332" s="4" t="s">
         <v>47</v>
@@ -30476,16 +30470,16 @@
         <v>1000</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>456</v>
+        <v>1295</v>
       </c>
       <c r="C333" s="4">
-        <v>168896081</v>
+        <v>168896094</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E333" s="4">
-        <v>6943901</v>
+        <v>1052309</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>49</v>
@@ -30500,17 +30494,17 @@
         <v>183</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="M333" s="4" t="s">
         <v>569</v>
       </c>
       <c r="N333" s="4">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="O333" s="4" t="s">
         <v>1562</v>
@@ -30532,7 +30526,7 @@
         <v>1564</v>
       </c>
       <c r="V333" s="4" t="s">
-        <v>967</v>
+        <v>1034</v>
       </c>
       <c r="W333" s="4">
         <v>9</v>
@@ -30545,7 +30539,7 @@
         <v>1565</v>
       </c>
       <c r="AA333" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB333" s="4" t="s">
         <v>47</v>
@@ -30556,16 +30550,16 @@
         <v>1000</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1299</v>
+        <v>1239</v>
       </c>
       <c r="C334" s="4">
-        <v>168896094</v>
+        <v>169217388</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>57</v>
+        <v>1566</v>
       </c>
       <c r="E334" s="4">
-        <v>1052309</v>
+        <v>1052314</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>49</v>
@@ -30580,27 +30574,25 @@
         <v>183</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="M334" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="N334" s="4">
-        <v>59</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="R334" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S334" s="4">
         <v>0</v>
@@ -30608,14 +30600,10 @@
       <c r="T334" s="4">
         <v>0</v>
       </c>
-      <c r="U334" s="4" t="s">
-        <v>1568</v>
-      </c>
-      <c r="V334" s="4" t="s">
-        <v>1034</v>
-      </c>
+      <c r="U334" s="4"/>
+      <c r="V334" s="4"/>
       <c r="W334" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X334" s="4" t="s">
         <v>202</v>
@@ -30625,7 +30613,7 @@
         <v>1569</v>
       </c>
       <c r="AA334" s="4" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="AB334" s="4" t="s">
         <v>47</v>
@@ -30636,16 +30624,16 @@
         <v>1000</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1243</v>
+        <v>456</v>
       </c>
       <c r="C335" s="4">
-        <v>169217388</v>
+        <v>168896120</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>1570</v>
+        <v>57</v>
       </c>
       <c r="E335" s="4">
-        <v>1052314</v>
+        <v>1052344</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>49</v>
@@ -30660,14 +30648,14 @@
         <v>183</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="M335" s="4" t="s">
-        <v>908</v>
+        <v>1570</v>
       </c>
       <c r="N335" s="4"/>
       <c r="O335" s="4" t="s">
@@ -30678,7 +30666,7 @@
         <v>1572</v>
       </c>
       <c r="R335" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S335" s="4">
         <v>0</v>
@@ -30686,20 +30674,24 @@
       <c r="T335" s="4">
         <v>0</v>
       </c>
-      <c r="U335" s="4"/>
-      <c r="V335" s="4"/>
+      <c r="U335" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="V335" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="W335" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X335" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="AA335" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB335" s="4" t="s">
         <v>47</v>
@@ -30710,16 +30702,16 @@
         <v>1000</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>456</v>
+        <v>33</v>
       </c>
       <c r="C336" s="4">
-        <v>168896120</v>
+        <v>169097745</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E336" s="4">
-        <v>1052344</v>
+        <v>6930250</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>49</v>
@@ -30734,22 +30726,24 @@
         <v>183</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="K336" s="4"/>
       <c r="L336" s="4" t="s">
-        <v>1558</v>
+        <v>1575</v>
       </c>
       <c r="M336" s="4" t="s">
-        <v>1574</v>
-      </c>
-      <c r="N336" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="N336" s="4">
+        <v>22</v>
+      </c>
       <c r="O336" s="4" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="R336" s="4" t="s">
         <v>41</v>
@@ -30761,20 +30755,20 @@
         <v>0</v>
       </c>
       <c r="U336" s="4" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="V336" s="4" t="s">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="W336" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X336" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="AA336" s="4" t="s">
         <v>46</v>
@@ -30788,16 +30782,16 @@
         <v>1000</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="C337" s="4">
-        <v>169097745</v>
+        <v>169361669</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E337" s="4">
-        <v>6930250</v>
+        <v>7730211</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>49</v>
@@ -30812,27 +30806,21 @@
         <v>183</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1525</v>
+        <v>1580</v>
       </c>
       <c r="K337" s="4"/>
-      <c r="L337" s="4" t="s">
-        <v>1579</v>
-      </c>
-      <c r="M337" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="N337" s="4">
-        <v>22</v>
-      </c>
+      <c r="L337" s="4"/>
+      <c r="M337" s="4"/>
+      <c r="N337" s="4"/>
       <c r="O337" s="4" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="R337" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S337" s="4">
         <v>0</v>
@@ -30841,23 +30829,23 @@
         <v>0</v>
       </c>
       <c r="U337" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="V337" s="4" t="s">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="W337" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X337" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="AA337" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB337" s="4" t="s">
         <v>47</v>
@@ -30868,16 +30856,16 @@
         <v>1000</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="C338" s="4">
-        <v>169361669</v>
+        <v>169527541</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E338" s="4">
-        <v>7730211</v>
+        <v>7798459</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>49</v>
@@ -30892,12 +30880,16 @@
         <v>183</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="K338" s="4"/>
-      <c r="L338" s="4"/>
+      <c r="L338" s="4" t="s">
+        <v>614</v>
+      </c>
       <c r="M338" s="4"/>
-      <c r="N338" s="4"/>
+      <c r="N338" s="4">
+        <v>4</v>
+      </c>
       <c r="O338" s="4" t="s">
         <v>1585</v>
       </c>
@@ -30906,7 +30898,7 @@
         <v>1586</v>
       </c>
       <c r="R338" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S338" s="4">
         <v>0</v>
@@ -30918,20 +30910,20 @@
         <v>1587</v>
       </c>
       <c r="V338" s="4" t="s">
-        <v>74</v>
+        <v>446</v>
       </c>
       <c r="W338" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X338" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="AA338" s="4" t="s">
-        <v>65</v>
+        <v>305</v>
       </c>
       <c r="AB338" s="4" t="s">
         <v>47</v>
@@ -30945,13 +30937,13 @@
         <v>33</v>
       </c>
       <c r="C339" s="4">
-        <v>169527541</v>
+        <v>169515495</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="E339" s="4">
-        <v>7798459</v>
+        <v>5905827</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>49</v>
@@ -30966,22 +30958,20 @@
         <v>183</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
       <c r="K339" s="4"/>
       <c r="L339" s="4" t="s">
-        <v>614</v>
+        <v>289</v>
       </c>
       <c r="M339" s="4"/>
-      <c r="N339" s="4">
-        <v>4</v>
-      </c>
+      <c r="N339" s="4"/>
       <c r="O339" s="4" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="R339" s="4" t="s">
         <v>41</v>
@@ -30992,12 +30982,8 @@
       <c r="T339" s="4">
         <v>0</v>
       </c>
-      <c r="U339" s="4" t="s">
-        <v>1591</v>
-      </c>
-      <c r="V339" s="4" t="s">
-        <v>446</v>
-      </c>
+      <c r="U339" s="4"/>
+      <c r="V339" s="4"/>
       <c r="W339" s="4">
         <v>1</v>
       </c>
@@ -31008,9 +30994,7 @@
       <c r="Z339" s="4" t="s">
         <v>1592</v>
       </c>
-      <c r="AA339" s="4" t="s">
-        <v>305</v>
-      </c>
+      <c r="AA339" s="4"/>
       <c r="AB339" s="4" t="s">
         <v>47</v>
       </c>
@@ -31020,16 +31004,16 @@
         <v>1000</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C340" s="4">
-        <v>169515495</v>
+        <v>169339010</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E340" s="4">
-        <v>5905827</v>
+        <v>8029935</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>49</v>
@@ -31047,9 +31031,7 @@
         <v>1593</v>
       </c>
       <c r="K340" s="4"/>
-      <c r="L340" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L340" s="4"/>
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
@@ -31060,27 +31042,29 @@
         <v>1595</v>
       </c>
       <c r="R340" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S340" s="4">
-        <v>0</v>
+        <v>153870.42</v>
       </c>
       <c r="T340" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U340" s="4"/>
       <c r="V340" s="4"/>
       <c r="W340" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X340" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y340" s="4"/>
       <c r="Z340" s="4" t="s">
         <v>1596</v>
       </c>
-      <c r="AA340" s="4"/>
+      <c r="AA340" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB340" s="4" t="s">
         <v>47</v>
       </c>
@@ -31093,13 +31077,13 @@
         <v>337</v>
       </c>
       <c r="C341" s="4">
-        <v>169339010</v>
+        <v>169334978</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E341" s="4">
-        <v>8029935</v>
+        <v>2380524</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>49</v>
@@ -31114,30 +31098,36 @@
         <v>183</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="K341" s="4"/>
-      <c r="L341" s="4"/>
+      <c r="L341" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="M341" s="4"/>
       <c r="N341" s="4"/>
       <c r="O341" s="4" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="R341" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S341" s="4">
+        <v>0</v>
+      </c>
+      <c r="T341" s="4">
+        <v>0</v>
+      </c>
+      <c r="U341" s="4" t="s">
         <v>1599</v>
       </c>
-      <c r="R341" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="S341" s="4">
-        <v>153870.42</v>
-      </c>
-      <c r="T341" s="4">
-        <v>1</v>
-      </c>
-      <c r="U341" s="4"/>
-      <c r="V341" s="4"/>
+      <c r="V341" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="W341" s="4">
         <v>3</v>
       </c>
@@ -31160,16 +31150,16 @@
         <v>1000</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C342" s="4">
-        <v>169334978</v>
+        <v>169512979</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E342" s="4">
-        <v>2380524</v>
+        <v>1107566</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>49</v>
@@ -31184,45 +31174,43 @@
         <v>183</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="K342" s="4"/>
-      <c r="L342" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L342" s="4"/>
       <c r="M342" s="4"/>
       <c r="N342" s="4"/>
       <c r="O342" s="4" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="R342" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S342" s="4">
-        <v>0</v>
+        <v>41450.93</v>
       </c>
       <c r="T342" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U342" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="V342" s="4" t="s">
         <v>140</v>
       </c>
       <c r="W342" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X342" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y342" s="4"/>
       <c r="Z342" s="4" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="AA342" s="4" t="s">
         <v>46</v>
@@ -31239,13 +31227,13 @@
         <v>33</v>
       </c>
       <c r="C343" s="4">
-        <v>169512979</v>
+        <v>169520460</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E343" s="4">
-        <v>1107566</v>
+        <v>7654420</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>49</v>
@@ -31260,34 +31248,36 @@
         <v>183</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K343" s="4"/>
-      <c r="L343" s="4"/>
-      <c r="M343" s="4"/>
-      <c r="N343" s="4"/>
+      <c r="L343" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M343" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="N343" s="4">
+        <v>48</v>
+      </c>
       <c r="O343" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="R343" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S343" s="4">
-        <v>41450.93</v>
+        <v>0</v>
       </c>
       <c r="T343" s="4">
-        <v>1</v>
-      </c>
-      <c r="U343" s="4" t="s">
-        <v>1608</v>
-      </c>
-      <c r="V343" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U343" s="4"/>
+      <c r="V343" s="4"/>
       <c r="W343" s="4">
         <v>1</v>
       </c>
@@ -31296,10 +31286,10 @@
       </c>
       <c r="Y343" s="4"/>
       <c r="Z343" s="4" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="AA343" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB343" s="4" t="s">
         <v>47</v>
@@ -31310,16 +31300,16 @@
         <v>1000</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>33</v>
+        <v>246</v>
       </c>
       <c r="C344" s="4">
-        <v>169520460</v>
+        <v>169087616</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E344" s="4">
-        <v>7654420</v>
+        <v>8397569</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>49</v>
@@ -31334,18 +31324,12 @@
         <v>183</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="K344" s="4"/>
-      <c r="L344" s="4" t="s">
-        <v>1610</v>
-      </c>
-      <c r="M344" s="4" t="s">
-        <v>1611</v>
-      </c>
-      <c r="N344" s="4">
-        <v>48</v>
-      </c>
+      <c r="L344" s="4"/>
+      <c r="M344" s="4"/>
+      <c r="N344" s="4"/>
       <c r="O344" s="4" t="s">
         <v>1612</v>
       </c>
@@ -31354,7 +31338,7 @@
         <v>1613</v>
       </c>
       <c r="R344" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S344" s="4">
         <v>0</v>
@@ -31365,20 +31349,18 @@
       <c r="U344" s="4"/>
       <c r="V344" s="4"/>
       <c r="W344" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X344" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
         <v>1614</v>
       </c>
-      <c r="AA344" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA344" s="4"/>
       <c r="AB344" s="4" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
     </row>
     <row r="345" spans="1:28">
@@ -31389,13 +31371,13 @@
         <v>246</v>
       </c>
       <c r="C345" s="4">
-        <v>169087616</v>
+        <v>169088129</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E345" s="4">
-        <v>8397569</v>
+        <v>8397590</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>49</v>
@@ -31410,18 +31392,18 @@
         <v>183</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="K345" s="4"/>
       <c r="L345" s="4"/>
       <c r="M345" s="4"/>
       <c r="N345" s="4"/>
       <c r="O345" s="4" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="P345" s="5"/>
       <c r="Q345" s="4" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="R345" s="4" t="s">
         <v>61</v>
@@ -31442,7 +31424,7 @@
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="AA345" s="4"/>
       <c r="AB345" s="4" t="s">
@@ -31454,16 +31436,16 @@
         <v>1000</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C346" s="4">
-        <v>169088129</v>
+        <v>168912853</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="E346" s="4">
-        <v>8397590</v>
+        <v>6956336</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>49</v>
@@ -31478,32 +31460,42 @@
         <v>183</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="K346" s="4"/>
-      <c r="L346" s="4"/>
-      <c r="M346" s="4"/>
-      <c r="N346" s="4"/>
+      <c r="L346" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="M346" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N346" s="4">
+        <v>2</v>
+      </c>
       <c r="O346" s="4" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="P346" s="5"/>
       <c r="Q346" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="R346" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S346" s="4">
-        <v>0</v>
+        <v>161390.36</v>
       </c>
       <c r="T346" s="4">
-        <v>0</v>
-      </c>
-      <c r="U346" s="4"/>
-      <c r="V346" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="U346" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="V346" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W346" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X346" s="4" t="s">
         <v>202</v>
@@ -31512,9 +31504,11 @@
       <c r="Z346" s="4" t="s">
         <v>1620</v>
       </c>
-      <c r="AA346" s="4"/>
+      <c r="AA346" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="AB346" s="4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
     </row>
     <row r="347" spans="1:28">
@@ -31522,16 +31516,16 @@
         <v>1000</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="C347" s="4">
-        <v>168912853</v>
+        <v>169528116</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="E347" s="4">
-        <v>6956336</v>
+        <v>6528821</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>49</v>
@@ -31546,52 +31540,48 @@
         <v>183</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1615</v>
+        <v>1621</v>
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="M347" s="4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="N347" s="4">
-        <v>2</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M347" s="4"/>
+      <c r="N347" s="4"/>
       <c r="O347" s="4" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="4" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="R347" s="4" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="S347" s="4">
-        <v>161390.36</v>
+        <v>0</v>
       </c>
       <c r="T347" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U347" s="4" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="V347" s="4" t="s">
-        <v>127</v>
+        <v>477</v>
       </c>
       <c r="W347" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X347" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y347" s="4"/>
       <c r="Z347" s="4" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="AA347" s="4" t="s">
-        <v>336</v>
+        <v>46</v>
       </c>
       <c r="AB347" s="4" t="s">
         <v>47</v>
@@ -31605,13 +31595,13 @@
         <v>33</v>
       </c>
       <c r="C348" s="4">
-        <v>169528116</v>
+        <v>169465695</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>34</v>
+        <v>1105</v>
       </c>
       <c r="E348" s="4">
-        <v>6528821</v>
+        <v>1012616</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>49</v>
@@ -31626,20 +31616,22 @@
         <v>183</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M348" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="M348" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="N348" s="4"/>
       <c r="O348" s="4" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="R348" s="4" t="s">
         <v>257</v>
@@ -31651,23 +31643,23 @@
         <v>0</v>
       </c>
       <c r="U348" s="4" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="V348" s="4" t="s">
-        <v>477</v>
+        <v>1630</v>
       </c>
       <c r="W348" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X348" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y348" s="4"/>
       <c r="Z348" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="AA348" s="4" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="AB348" s="4" t="s">
         <v>47</v>
@@ -31678,16 +31670,16 @@
         <v>1000</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>33</v>
+        <v>230</v>
       </c>
       <c r="C349" s="4">
-        <v>169465695</v>
+        <v>168614318</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>1105</v>
+        <v>48</v>
       </c>
       <c r="E349" s="4">
-        <v>1012616</v>
+        <v>8296444</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>49</v>
@@ -31702,25 +31694,27 @@
         <v>183</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
-        <v>178</v>
+        <v>1171</v>
       </c>
       <c r="M349" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="N349" s="4"/>
+        <v>1633</v>
+      </c>
+      <c r="N349" s="4">
+        <v>74</v>
+      </c>
       <c r="O349" s="4" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="R349" s="4" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="S349" s="4">
         <v>0</v>
@@ -31728,25 +31722,19 @@
       <c r="T349" s="4">
         <v>0</v>
       </c>
-      <c r="U349" s="4" t="s">
-        <v>1633</v>
-      </c>
-      <c r="V349" s="4" t="s">
-        <v>1634</v>
-      </c>
+      <c r="U349" s="4"/>
+      <c r="V349" s="4"/>
       <c r="W349" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X349" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y349" s="4"/>
       <c r="Z349" s="4" t="s">
-        <v>1635</v>
-      </c>
-      <c r="AA349" s="4" t="s">
-        <v>215</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA349" s="4"/>
       <c r="AB349" s="4" t="s">
         <v>47</v>
       </c>
@@ -31756,16 +31744,16 @@
         <v>1000</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="C350" s="4">
-        <v>168614318</v>
+        <v>169354713</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E350" s="4">
-        <v>8296444</v>
+        <v>7533945</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>49</v>
@@ -31780,24 +31768,24 @@
         <v>183</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
         <v>1171</v>
       </c>
       <c r="M350" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="N350" s="4">
+        <v>76</v>
+      </c>
+      <c r="O350" s="4" t="s">
         <v>1637</v>
-      </c>
-      <c r="N350" s="4">
-        <v>74</v>
-      </c>
-      <c r="O350" s="4" t="s">
-        <v>1638</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="R350" s="4" t="s">
         <v>79</v>
@@ -31811,16 +31799,18 @@
       <c r="U350" s="4"/>
       <c r="V350" s="4"/>
       <c r="W350" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y350" s="4"/>
       <c r="Z350" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA350" s="4"/>
+        <v>1639</v>
+      </c>
+      <c r="AA350" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB350" s="4" t="s">
         <v>47</v>
       </c>
@@ -31830,16 +31820,16 @@
         <v>1000</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>421</v>
+        <v>1640</v>
       </c>
       <c r="C351" s="4">
-        <v>169354713</v>
+        <v>169240215</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E351" s="4">
-        <v>7533945</v>
+        <v>1037589</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>49</v>
@@ -31854,27 +31844,25 @@
         <v>183</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
-        <v>1171</v>
+        <v>289</v>
       </c>
       <c r="M351" s="4" t="s">
-        <v>1640</v>
-      </c>
-      <c r="N351" s="4">
-        <v>76</v>
-      </c>
+        <v>1642</v>
+      </c>
+      <c r="N351" s="4"/>
       <c r="O351" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="P351" s="5"/>
       <c r="Q351" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="R351" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S351" s="4">
         <v>0</v>
@@ -31882,17 +31870,21 @@
       <c r="T351" s="4">
         <v>0</v>
       </c>
-      <c r="U351" s="4"/>
-      <c r="V351" s="4"/>
+      <c r="U351" s="4" t="s">
+        <v>1645</v>
+      </c>
+      <c r="V351" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W351" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X351" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="AA351" s="4" t="s">
         <v>46</v>
@@ -31906,16 +31898,16 @@
         <v>1000</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1644</v>
+        <v>873</v>
       </c>
       <c r="C352" s="4">
-        <v>169240215</v>
+        <v>169240216</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E352" s="4">
-        <v>1037589</v>
+        <v>1037569</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>49</v>
@@ -31930,22 +31922,22 @@
         <v>183</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
         <v>289</v>
       </c>
       <c r="M352" s="4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="N352" s="4"/>
       <c r="O352" s="4" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="P352" s="5"/>
       <c r="Q352" s="4" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="R352" s="4" t="s">
         <v>61</v>
@@ -31957,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="U352" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>127</v>
+        <v>427</v>
       </c>
       <c r="W352" s="4">
         <v>4</v>
@@ -31970,10 +31962,10 @@
       </c>
       <c r="Y352" s="4"/>
       <c r="Z352" s="4" t="s">
-        <v>1650</v>
+        <v>1382</v>
       </c>
       <c r="AA352" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB352" s="4" t="s">
         <v>47</v>
@@ -31984,16 +31976,16 @@
         <v>1000</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>873</v>
+        <v>668</v>
       </c>
       <c r="C353" s="4">
-        <v>169240216</v>
+        <v>168725375</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E353" s="4">
-        <v>1037569</v>
+        <v>4321965</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>49</v>
@@ -32008,50 +32000,50 @@
         <v>183</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1645</v>
+        <v>1651</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M353" s="4" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="N353" s="4"/>
       <c r="O353" s="4" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="P353" s="5"/>
       <c r="Q353" s="4" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="R353" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S353" s="4">
-        <v>0</v>
+        <v>165052.22</v>
       </c>
       <c r="T353" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U353" s="4" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="V353" s="4" t="s">
-        <v>427</v>
+        <v>74</v>
       </c>
       <c r="W353" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X353" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1386</v>
+        <v>1656</v>
       </c>
       <c r="AA353" s="4" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="AB353" s="4" t="s">
         <v>47</v>
@@ -32062,16 +32054,16 @@
         <v>1000</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>668</v>
+        <v>1528</v>
       </c>
       <c r="C354" s="4">
-        <v>168725375</v>
+        <v>168896049</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E354" s="4">
-        <v>4321965</v>
+        <v>8020879</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>49</v>
@@ -32086,40 +32078,38 @@
         <v>183</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>307</v>
+        <v>1657</v>
       </c>
       <c r="M354" s="4" t="s">
-        <v>1656</v>
-      </c>
-      <c r="N354" s="4"/>
+        <v>524</v>
+      </c>
+      <c r="N354" s="4">
+        <v>30</v>
+      </c>
       <c r="O354" s="4" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="P354" s="5"/>
       <c r="Q354" s="4" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="R354" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="S354" s="4">
-        <v>165052.22</v>
+        <v>0</v>
       </c>
       <c r="T354" s="4">
-        <v>1</v>
-      </c>
-      <c r="U354" s="4" t="s">
-        <v>1659</v>
-      </c>
-      <c r="V354" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U354" s="4"/>
+      <c r="V354" s="4"/>
       <c r="W354" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>202</v>
@@ -32128,9 +32118,7 @@
       <c r="Z354" s="4" t="s">
         <v>1660</v>
       </c>
-      <c r="AA354" s="4" t="s">
-        <v>215</v>
-      </c>
+      <c r="AA354" s="4"/>
       <c r="AB354" s="4" t="s">
         <v>47</v>
       </c>
@@ -32140,16 +32128,16 @@
         <v>1000</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1532</v>
+        <v>196</v>
       </c>
       <c r="C355" s="4">
-        <v>168896049</v>
+        <v>169511125</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E355" s="4">
-        <v>8020879</v>
+        <v>1030462</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>49</v>
@@ -32164,27 +32152,25 @@
         <v>183</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1655</v>
+        <v>1661</v>
       </c>
       <c r="K355" s="4"/>
       <c r="L355" s="4" t="s">
-        <v>1661</v>
+        <v>289</v>
       </c>
       <c r="M355" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="N355" s="4">
-        <v>30</v>
-      </c>
+        <v>1662</v>
+      </c>
+      <c r="N355" s="4"/>
       <c r="O355" s="4" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="R355" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S355" s="4">
         <v>0</v>
@@ -32195,14 +32181,14 @@
       <c r="U355" s="4"/>
       <c r="V355" s="4"/>
       <c r="W355" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X355" s="4" t="s">
         <v>202</v>
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="AA355" s="4"/>
       <c r="AB355" s="4" t="s">
@@ -32214,16 +32200,16 @@
         <v>1000</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>196</v>
+        <v>873</v>
       </c>
       <c r="C356" s="4">
-        <v>169511125</v>
+        <v>169354695</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E356" s="4">
-        <v>1030462</v>
+        <v>1037638</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>49</v>
@@ -32238,15 +32224,13 @@
         <v>183</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="K356" s="4"/>
       <c r="L356" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M356" s="4" t="s">
-        <v>1666</v>
-      </c>
+      <c r="M356" s="4"/>
       <c r="N356" s="4"/>
       <c r="O356" s="4" t="s">
         <v>1667</v>
@@ -32267,7 +32251,7 @@
       <c r="U356" s="4"/>
       <c r="V356" s="4"/>
       <c r="W356" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X356" s="4" t="s">
         <v>202</v>
@@ -32276,7 +32260,9 @@
       <c r="Z356" s="4" t="s">
         <v>1669</v>
       </c>
-      <c r="AA356" s="4"/>
+      <c r="AA356" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB356" s="4" t="s">
         <v>47</v>
       </c>
@@ -32286,16 +32272,16 @@
         <v>1000</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>873</v>
+        <v>1640</v>
       </c>
       <c r="C357" s="4">
-        <v>169354695</v>
+        <v>169354696</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E357" s="4">
-        <v>1037638</v>
+        <v>1037665</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>49</v>
@@ -32310,7 +32296,7 @@
         <v>183</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K357" s="4"/>
       <c r="L357" s="4" t="s">
@@ -32319,11 +32305,11 @@
       <c r="M357" s="4"/>
       <c r="N357" s="4"/>
       <c r="O357" s="4" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="P357" s="5"/>
       <c r="Q357" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="R357" s="4" t="s">
         <v>61</v>
@@ -32344,7 +32330,7 @@
       </c>
       <c r="Y357" s="4"/>
       <c r="Z357" s="4" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="AA357" s="4" t="s">
         <v>46</v>
@@ -32358,16 +32344,16 @@
         <v>1000</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="C358" s="4">
-        <v>169354696</v>
+        <v>169354700</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E358" s="4">
-        <v>1037665</v>
+        <v>1037643</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>49</v>
@@ -32382,7 +32368,7 @@
         <v>183</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
@@ -32391,20 +32377,20 @@
       <c r="M358" s="4"/>
       <c r="N358" s="4"/>
       <c r="O358" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="P358" s="5"/>
       <c r="Q358" s="4" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="R358" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S358" s="4">
-        <v>0</v>
+        <v>16183109.58</v>
       </c>
       <c r="T358" s="4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="U358" s="4"/>
       <c r="V358" s="4"/>
@@ -32416,13 +32402,13 @@
       </c>
       <c r="Y358" s="4"/>
       <c r="Z358" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="AA358" s="4" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
       <c r="AB358" s="4" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="359" spans="1:28">
@@ -32430,16 +32416,16 @@
         <v>1000</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="C359" s="4">
-        <v>169354700</v>
+        <v>169354701</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E359" s="4">
-        <v>1037643</v>
+        <v>1037642</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>49</v>
@@ -32454,7 +32440,7 @@
         <v>183</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
@@ -32463,23 +32449,27 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="R359" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S359" s="4">
-        <v>16183109.58</v>
+        <v>532142.46</v>
       </c>
       <c r="T359" s="4">
-        <v>39</v>
-      </c>
-      <c r="U359" s="4"/>
-      <c r="V359" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U359" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="V359" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W359" s="4">
         <v>3</v>
       </c>
@@ -32491,10 +32481,10 @@
         <v>1679</v>
       </c>
       <c r="AA359" s="4" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="AB359" s="4" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
     </row>
     <row r="360" spans="1:28">
@@ -32502,16 +32492,16 @@
         <v>1000</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="C360" s="4">
-        <v>169354701</v>
+        <v>169354702</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E360" s="4">
-        <v>1037642</v>
+        <v>1037647</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>49</v>
@@ -32526,7 +32516,7 @@
         <v>183</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
@@ -32545,17 +32535,13 @@
         <v>61</v>
       </c>
       <c r="S360" s="4">
-        <v>532142.46</v>
+        <v>0</v>
       </c>
       <c r="T360" s="4">
-        <v>2</v>
-      </c>
-      <c r="U360" s="4" t="s">
-        <v>1682</v>
-      </c>
-      <c r="V360" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U360" s="4"/>
+      <c r="V360" s="4"/>
       <c r="W360" s="4">
         <v>3</v>
       </c>
@@ -32564,10 +32550,10 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AA360" s="4" t="s">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="AB360" s="4" t="s">
         <v>47</v>
@@ -32578,16 +32564,16 @@
         <v>1000</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1644</v>
+        <v>1333</v>
       </c>
       <c r="C361" s="4">
-        <v>169354702</v>
+        <v>169354703</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E361" s="4">
-        <v>1037647</v>
+        <v>1037655</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>49</v>
@@ -32602,7 +32588,7 @@
         <v>183</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
@@ -32611,11 +32597,11 @@
       <c r="M361" s="4"/>
       <c r="N361" s="4"/>
       <c r="O361" s="4" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="R361" s="4" t="s">
         <v>61</v>
@@ -32626,8 +32612,12 @@
       <c r="T361" s="4">
         <v>0</v>
       </c>
-      <c r="U361" s="4"/>
-      <c r="V361" s="4"/>
+      <c r="U361" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="V361" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W361" s="4">
         <v>3</v>
       </c>
@@ -32650,16 +32640,16 @@
         <v>1000</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C362" s="4">
-        <v>169354703</v>
+        <v>169354708</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E362" s="4">
-        <v>1037655</v>
+        <v>1037651</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>49</v>
@@ -32674,7 +32664,7 @@
         <v>183</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4" t="s">
@@ -32715,7 +32705,7 @@
         <v>1690</v>
       </c>
       <c r="AA362" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB362" s="4" t="s">
         <v>47</v>
@@ -32726,16 +32716,16 @@
         <v>1000</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1337</v>
+        <v>353</v>
       </c>
       <c r="C363" s="4">
-        <v>169354708</v>
+        <v>169354710</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E363" s="4">
-        <v>1037651</v>
+        <v>7616012</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>49</v>
@@ -32750,7 +32740,7 @@
         <v>183</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4" t="s">
@@ -32774,12 +32764,8 @@
       <c r="T363" s="4">
         <v>0</v>
       </c>
-      <c r="U363" s="4" t="s">
-        <v>1693</v>
-      </c>
-      <c r="V363" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="U363" s="4"/>
+      <c r="V363" s="4"/>
       <c r="W363" s="4">
         <v>3</v>
       </c>
@@ -32788,10 +32774,10 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AA363" s="4" t="s">
-        <v>46</v>
+        <v>352</v>
       </c>
       <c r="AB363" s="4" t="s">
         <v>47</v>
@@ -32805,13 +32791,13 @@
         <v>353</v>
       </c>
       <c r="C364" s="4">
-        <v>169354710</v>
+        <v>169354711</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E364" s="4">
-        <v>7616012</v>
+        <v>5918582</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>49</v>
@@ -32826,7 +32812,7 @@
         <v>183</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4" t="s">
@@ -32835,23 +32821,27 @@
       <c r="M364" s="4"/>
       <c r="N364" s="4"/>
       <c r="O364" s="4" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="R364" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S364" s="4">
-        <v>0</v>
+        <v>9429108.630000001</v>
       </c>
       <c r="T364" s="4">
-        <v>0</v>
-      </c>
-      <c r="U364" s="4"/>
-      <c r="V364" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="U364" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="V364" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="W364" s="4">
         <v>3</v>
       </c>
@@ -32862,11 +32852,9 @@
       <c r="Z364" s="4" t="s">
         <v>1697</v>
       </c>
-      <c r="AA364" s="4" t="s">
-        <v>352</v>
-      </c>
+      <c r="AA364" s="4"/>
       <c r="AB364" s="4" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="365" spans="1:28">
@@ -32877,13 +32865,13 @@
         <v>353</v>
       </c>
       <c r="C365" s="4">
-        <v>169354711</v>
+        <v>169354712</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E365" s="4">
-        <v>5918582</v>
+        <v>1037657</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>49</v>
@@ -32898,7 +32886,7 @@
         <v>183</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4" t="s">
@@ -32917,16 +32905,16 @@
         <v>61</v>
       </c>
       <c r="S365" s="4">
-        <v>9429108.630000001</v>
+        <v>0</v>
       </c>
       <c r="T365" s="4">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U365" s="4" t="s">
         <v>1700</v>
       </c>
       <c r="V365" s="4" t="s">
-        <v>127</v>
+        <v>477</v>
       </c>
       <c r="W365" s="4">
         <v>3</v>
@@ -32938,9 +32926,11 @@
       <c r="Z365" s="4" t="s">
         <v>1701</v>
       </c>
-      <c r="AA365" s="4"/>
+      <c r="AA365" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB365" s="4" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
     </row>
     <row r="366" spans="1:28">
@@ -32951,13 +32941,13 @@
         <v>353</v>
       </c>
       <c r="C366" s="4">
-        <v>169354712</v>
+        <v>169354709</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E366" s="4">
-        <v>1037657</v>
+        <v>1037653</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>49</v>
@@ -32972,20 +32962,22 @@
         <v>183</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K366" s="4"/>
       <c r="L366" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="M366" s="4"/>
+      <c r="M366" s="4" t="s">
+        <v>1702</v>
+      </c>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="P366" s="5"/>
       <c r="Q366" s="4" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="R366" s="4" t="s">
         <v>61</v>
@@ -32996,12 +32988,8 @@
       <c r="T366" s="4">
         <v>0</v>
       </c>
-      <c r="U366" s="4" t="s">
-        <v>1704</v>
-      </c>
-      <c r="V366" s="4" t="s">
-        <v>477</v>
-      </c>
+      <c r="U366" s="4"/>
+      <c r="V366" s="4"/>
       <c r="W366" s="4">
         <v>3</v>
       </c>
@@ -33024,16 +33012,16 @@
         <v>1000</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C367" s="4">
-        <v>169354709</v>
+        <v>169360455</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E367" s="4">
-        <v>1037653</v>
+        <v>1037656</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>49</v>
@@ -33048,31 +33036,31 @@
         <v>183</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
         <v>289</v>
       </c>
       <c r="M367" s="4" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="N367" s="4"/>
       <c r="O367" s="4" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="R367" s="4" t="s">
         <v>61</v>
       </c>
       <c r="S367" s="4">
-        <v>0</v>
+        <v>57340.82</v>
       </c>
       <c r="T367" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U367" s="4"/>
       <c r="V367" s="4"/>
@@ -33080,11 +33068,11 @@
         <v>3</v>
       </c>
       <c r="X367" s="4" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="Y367" s="4"/>
       <c r="Z367" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="AA367" s="4" t="s">
         <v>215</v>
@@ -33098,16 +33086,16 @@
         <v>1000</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="C368" s="4">
-        <v>169360455</v>
+        <v>169527823</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E368" s="4">
-        <v>1037656</v>
+        <v>4268253</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>49</v>
@@ -33122,14 +33110,14 @@
         <v>183</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1670</v>
+        <v>1709</v>
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
-        <v>289</v>
+        <v>224</v>
       </c>
       <c r="M368" s="4" t="s">
-        <v>1706</v>
+        <v>518</v>
       </c>
       <c r="N368" s="4"/>
       <c r="O368" s="4" t="s">
@@ -33140,28 +33128,32 @@
         <v>1711</v>
       </c>
       <c r="R368" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S368" s="4">
-        <v>57340.82</v>
+        <v>0</v>
       </c>
       <c r="T368" s="4">
+        <v>0</v>
+      </c>
+      <c r="U368" s="4" t="s">
+        <v>1712</v>
+      </c>
+      <c r="V368" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W368" s="4">
         <v>1</v>
       </c>
-      <c r="U368" s="4"/>
-      <c r="V368" s="4"/>
-      <c r="W368" s="4">
-        <v>3</v>
-      </c>
       <c r="X368" s="4" t="s">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="Y368" s="4"/>
       <c r="Z368" s="4" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="AA368" s="4" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="AB368" s="4" t="s">
         <v>47</v>
@@ -33172,16 +33164,16 @@
         <v>1000</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="C369" s="4">
-        <v>169527823</v>
+        <v>169345689</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>34</v>
+        <v>723</v>
       </c>
       <c r="E369" s="4">
-        <v>4268253</v>
+        <v>1030127</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>49</v>
@@ -33196,25 +33188,23 @@
         <v>183</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="M369" s="4" t="s">
-        <v>518</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="R369" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="S369" s="4">
         <v>0</v>
@@ -33223,23 +33213,23 @@
         <v>0</v>
       </c>
       <c r="U369" s="4" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="V369" s="4" t="s">
-        <v>69</v>
+        <v>1718</v>
       </c>
       <c r="W369" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X369" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y369" s="4"/>
       <c r="Z369" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="AA369" s="4" t="s">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="AB369" s="4" t="s">
         <v>47</v>
@@ -33250,16 +33240,16 @@
         <v>1000</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>337</v>
+        <v>646</v>
       </c>
       <c r="C370" s="4">
-        <v>169345689</v>
+        <v>169240241</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>723</v>
+        <v>57</v>
       </c>
       <c r="E370" s="4">
-        <v>1030127</v>
+        <v>6825959</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>49</v>
@@ -33274,7 +33264,7 @@
         <v>183</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -33283,29 +33273,25 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="R370" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="S370" s="4">
-        <v>0</v>
+        <v>412514.71</v>
       </c>
       <c r="T370" s="4">
-        <v>0</v>
-      </c>
-      <c r="U370" s="4" t="s">
-        <v>1721</v>
-      </c>
-      <c r="V370" s="4" t="s">
-        <v>1722</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U370" s="4"/>
+      <c r="V370" s="4"/>
       <c r="W370" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X370" s="4" t="s">
         <v>202</v>
@@ -33326,16 +33312,16 @@
         <v>1000</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>646</v>
+        <v>33</v>
       </c>
       <c r="C371" s="4">
-        <v>169240241</v>
+        <v>169521806</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E371" s="4">
-        <v>6825959</v>
+        <v>6699162</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>49</v>
@@ -33350,7 +33336,7 @@
         <v>183</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
@@ -33359,35 +33345,35 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="R371" s="4" t="s">
         <v>41</v>
       </c>
       <c r="S371" s="4">
-        <v>412514.71</v>
+        <v>0</v>
       </c>
       <c r="T371" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U371" s="4"/>
       <c r="V371" s="4"/>
       <c r="W371" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X371" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y371" s="4"/>
       <c r="Z371" s="4" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="AA371" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB371" s="4" t="s">
         <v>47</v>
@@ -33401,13 +33387,13 @@
         <v>33</v>
       </c>
       <c r="C372" s="4">
-        <v>169521806</v>
+        <v>169511424</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E372" s="4">
-        <v>6699162</v>
+        <v>7187541</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>49</v>
@@ -33422,7 +33408,7 @@
         <v>183</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="K372" s="4"/>
       <c r="L372" s="4" t="s">
@@ -33438,7 +33424,7 @@
         <v>1729</v>
       </c>
       <c r="R372" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="S372" s="4">
         <v>0</v>
@@ -33446,8 +33432,12 @@
       <c r="T372" s="4">
         <v>0</v>
       </c>
-      <c r="U372" s="4"/>
-      <c r="V372" s="4"/>
+      <c r="U372" s="4" t="s">
+        <v>1730</v>
+      </c>
+      <c r="V372" s="4" t="s">
+        <v>605</v>
+      </c>
       <c r="W372" s="4">
         <v>1</v>
       </c>
@@ -33456,11 +33446,9 @@
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
-        <v>1730</v>
-      </c>
-      <c r="AA372" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>1731</v>
+      </c>
+      <c r="AA372" s="4"/>
       <c r="AB372" s="4" t="s">
         <v>47</v>
       </c>
@@ -33470,16 +33458,16 @@
         <v>1000</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="C373" s="4">
-        <v>169511424</v>
+        <v>169347543</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>34</v>
+        <v>581</v>
       </c>
       <c r="E373" s="4">
-        <v>7187541</v>
+        <v>1072186</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>49</v>
@@ -33494,7 +33482,7 @@
         <v>183</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="K373" s="4"/>
       <c r="L373" s="4" t="s">
@@ -33503,38 +33491,40 @@
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="R373" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S373" s="4">
-        <v>0</v>
+        <v>20024.22</v>
       </c>
       <c r="T373" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U373" s="4" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="V373" s="4" t="s">
-        <v>605</v>
+        <v>140</v>
       </c>
       <c r="W373" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X373" s="4" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
-        <v>1735</v>
-      </c>
-      <c r="AA373" s="4"/>
+        <v>1736</v>
+      </c>
+      <c r="AA373" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB373" s="4" t="s">
         <v>47</v>
       </c>
@@ -33544,16 +33534,16 @@
         <v>1000</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C374" s="4">
-        <v>169347543</v>
+        <v>169527018</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>581</v>
+        <v>34</v>
       </c>
       <c r="E374" s="4">
-        <v>1072186</v>
+        <v>6658632</v>
       </c>
       <c r="F374" s="4" t="s">
         <v>49</v>
@@ -33562,130 +33552,54 @@
         <v>36</v>
       </c>
       <c r="H374" s="4" t="s">
-        <v>183</v>
+        <v>1737</v>
       </c>
       <c r="I374" s="4" t="s">
-        <v>183</v>
+        <v>1738</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="K374" s="4"/>
-      <c r="L374" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="L374" s="4"/>
       <c r="M374" s="4"/>
       <c r="N374" s="4"/>
       <c r="O374" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="P374" s="5"/>
       <c r="Q374" s="4" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="R374" s="4" t="s">
         <v>79</v>
       </c>
       <c r="S374" s="4">
-        <v>20024.22</v>
+        <v>0</v>
       </c>
       <c r="T374" s="4">
+        <v>0</v>
+      </c>
+      <c r="U374" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="V374" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W374" s="4">
         <v>1</v>
       </c>
-      <c r="U374" s="4" t="s">
-        <v>1739</v>
-      </c>
-      <c r="V374" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="W374" s="4">
-        <v>3</v>
-      </c>
       <c r="X374" s="4" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="Y374" s="4"/>
       <c r="Z374" s="4" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="AA374" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AB374" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="375" spans="1:28">
-      <c r="A375" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B375" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C375" s="4">
-        <v>169527018</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E375" s="4">
-        <v>6658632</v>
-      </c>
-      <c r="F375" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G375" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H375" s="4" t="s">
-        <v>1741</v>
-      </c>
-      <c r="I375" s="4" t="s">
-        <v>1742</v>
-      </c>
-      <c r="J375" s="4" t="s">
-        <v>1743</v>
-      </c>
-      <c r="K375" s="4"/>
-      <c r="L375" s="4"/>
-      <c r="M375" s="4"/>
-      <c r="N375" s="4"/>
-      <c r="O375" s="4" t="s">
-        <v>1744</v>
-      </c>
-      <c r="P375" s="5"/>
-      <c r="Q375" s="4" t="s">
-        <v>1745</v>
-      </c>
-      <c r="R375" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S375" s="4">
-        <v>0</v>
-      </c>
-      <c r="T375" s="4">
-        <v>0</v>
-      </c>
-      <c r="U375" s="4" t="s">
-        <v>1746</v>
-      </c>
-      <c r="V375" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="W375" s="4">
-        <v>1</v>
-      </c>
-      <c r="X375" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y375" s="4"/>
-      <c r="Z375" s="4" t="s">
-        <v>1747</v>
-      </c>
-      <c r="AA375" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB375" s="4" t="s">
         <v>47</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>22/10/2026 a las 21:11:51</t>
+    <t>22/10/2026 a las 22:00:55</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>23/10/2026 a las 07:57:27</t>
+    <t>23/10/2026 a las 08:01:08</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -26141,7 +26141,7 @@
         <v>1000</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>454</v>
+        <v>201</v>
       </c>
       <c r="C240" s="4">
         <v>169948127</v>
@@ -26199,7 +26199,7 @@
         <v>2</v>
       </c>
       <c r="X240" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="Y240" s="4"/>
       <c r="Z240" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>24/10/2026 a las 07:42:42</t>
+    <t>24/10/2026 a las 07:45:53</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>26/10/2026 a las 07:56:47</t>
+    <t>26/10/2026 a las 08:00:58</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -12553,7 +12553,7 @@
         <v>5</v>
       </c>
       <c r="X69" s="4" t="s">
-        <v>399</v>
+        <v>71</v>
       </c>
       <c r="Y69" s="4"/>
       <c r="Z69" s="4" t="s">
@@ -12571,7 +12571,7 @@
         <v>1000</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>33</v>
+        <v>375</v>
       </c>
       <c r="C70" s="4">
         <v>170177841</v>
@@ -12631,7 +12631,7 @@
         <v>3</v>
       </c>
       <c r="X70" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4" t="s">
@@ -12647,7 +12647,7 @@
         <v>1000</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>33</v>
+        <v>375</v>
       </c>
       <c r="C71" s="4">
         <v>169960797</v>
@@ -12703,7 +12703,7 @@
         <v>5</v>
       </c>
       <c r="X71" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Y71" s="4"/>
       <c r="Z71" s="4" t="s">
@@ -12719,7 +12719,7 @@
         <v>1000</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>33</v>
+        <v>375</v>
       </c>
       <c r="C72" s="4">
         <v>170177842</v>
@@ -12781,7 +12781,7 @@
         <v>3</v>
       </c>
       <c r="X72" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Y72" s="4"/>
       <c r="Z72" s="4" t="s">
@@ -12873,7 +12873,7 @@
         <v>1000</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>33</v>
+        <v>375</v>
       </c>
       <c r="C74" s="4">
         <v>170177843</v>
@@ -12929,7 +12929,7 @@
         <v>3</v>
       </c>
       <c r="X74" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4" t="s">
@@ -12947,7 +12947,7 @@
         <v>1000</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>33</v>
+        <v>375</v>
       </c>
       <c r="C75" s="4">
         <v>169960799</v>
@@ -13009,7 +13009,7 @@
         <v>5</v>
       </c>
       <c r="X75" s="4" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Y75" s="4"/>
       <c r="Z75" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/10/2026 a las 07:59:21</t>
+    <t>28/10/2026 a las 08:00:56</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -35337,7 +35337,7 @@
         <v>1000</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>33</v>
+        <v>1172</v>
       </c>
       <c r="C363" s="4">
         <v>170340331</v>
@@ -35393,7 +35393,7 @@
         <v>2</v>
       </c>
       <c r="X363" s="4" t="s">
-        <v>46</v>
+        <v>1179</v>
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2261">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/10/2026 a las 07:36:34</t>
+    <t>29/10/2026 a las 07:37:37</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -3735,6 +3735,9 @@
   </si>
   <si>
     <t>FULA MONTENEGRO BMT  KARINA</t>
+  </si>
+  <si>
+    <t>GELVER DE JESUS MORENO FORNARIS</t>
   </si>
   <si>
     <t>CL 29K3</t>
@@ -27116,7 +27119,7 @@
         <v>1000</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C265" s="4">
         <v>170412211</v>
@@ -27147,17 +27150,17 @@
         <v>499</v>
       </c>
       <c r="M265" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N265" s="4">
         <v>27</v>
       </c>
       <c r="O265" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="P265" s="5"/>
       <c r="Q265" s="4" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="R265" s="4" t="s">
         <v>69</v>
@@ -27174,7 +27177,7 @@
         <v>2</v>
       </c>
       <c r="X265" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y265" s="4"/>
       <c r="Z265" s="4" t="s">
@@ -27214,7 +27217,7 @@
         <v>107</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="K266" s="4"/>
       <c r="L266" s="4" t="s">
@@ -27227,11 +27230,11 @@
         <v>91</v>
       </c>
       <c r="O266" s="4" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="P266" s="5"/>
       <c r="Q266" s="4" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="R266" s="4" t="s">
         <v>41</v>
@@ -27290,7 +27293,7 @@
         <v>418</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4" t="s">
@@ -27301,11 +27304,11 @@
       </c>
       <c r="N267" s="4"/>
       <c r="O267" s="4" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="P267" s="5"/>
       <c r="Q267" s="4" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="R267" s="4" t="s">
         <v>41</v>
@@ -27317,7 +27320,7 @@
         <v>0</v>
       </c>
       <c r="U267" s="4" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="V267" s="4" t="s">
         <v>197</v>
@@ -27368,7 +27371,7 @@
         <v>418</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4" t="s">
@@ -27379,11 +27382,11 @@
       </c>
       <c r="N268" s="4"/>
       <c r="O268" s="4" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="P268" s="5"/>
       <c r="Q268" s="4" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="R268" s="4" t="s">
         <v>41</v>
@@ -27395,7 +27398,7 @@
         <v>2</v>
       </c>
       <c r="U268" s="4" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="V268" s="4" t="s">
         <v>222</v>
@@ -27446,7 +27449,7 @@
         <v>107</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4" t="s">
@@ -27459,11 +27462,11 @@
         <v>5</v>
       </c>
       <c r="O269" s="4" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="P269" s="5"/>
       <c r="Q269" s="4" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="R269" s="4" t="s">
         <v>195</v>
@@ -27484,7 +27487,7 @@
       </c>
       <c r="Y269" s="4"/>
       <c r="Z269" s="4" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="AA269" s="4" t="s">
         <v>395</v>
@@ -27522,24 +27525,24 @@
         <v>107</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="K270" s="4"/>
       <c r="L270" s="4" t="s">
         <v>321</v>
       </c>
       <c r="M270" s="4" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="N270" s="4">
         <v>29</v>
       </c>
       <c r="O270" s="4" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="P270" s="5"/>
       <c r="Q270" s="4" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R270" s="4" t="s">
         <v>41</v>
@@ -27551,10 +27554,10 @@
         <v>1</v>
       </c>
       <c r="U270" s="4" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="V270" s="4" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="W270" s="4">
         <v>4</v>
@@ -27564,7 +27567,7 @@
       </c>
       <c r="Y270" s="4"/>
       <c r="Z270" s="4" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="AA270" s="4"/>
       <c r="AB270" s="4" t="s">
@@ -27600,11 +27603,11 @@
         <v>107</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="K271" s="4"/>
       <c r="L271" s="4" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="M271" s="4" t="s">
         <v>321</v>
@@ -27613,11 +27616,11 @@
         <v>37</v>
       </c>
       <c r="O271" s="4" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="P271" s="5"/>
       <c r="Q271" s="4" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="R271" s="4" t="s">
         <v>41</v>
@@ -27676,24 +27679,24 @@
         <v>107</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="K272" s="4"/>
       <c r="L272" s="4" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M272" s="4" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N272" s="4">
         <v>51</v>
       </c>
       <c r="O272" s="4" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="4" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="R272" s="4" t="s">
         <v>41</v>
@@ -27714,7 +27717,7 @@
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="AA272" s="4"/>
       <c r="AB272" s="4" t="s">
@@ -27750,24 +27753,24 @@
         <v>107</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="K273" s="4"/>
       <c r="L273" s="4" t="s">
         <v>327</v>
       </c>
       <c r="M273" s="4" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N273" s="4">
         <v>30</v>
       </c>
       <c r="O273" s="4" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="P273" s="5"/>
       <c r="Q273" s="4" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="R273" s="4" t="s">
         <v>41</v>
@@ -27779,7 +27782,7 @@
         <v>3</v>
       </c>
       <c r="U273" s="4" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="V273" s="4" t="s">
         <v>162</v>
@@ -27830,18 +27833,18 @@
         <v>107</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4"/>
       <c r="M274" s="4"/>
       <c r="N274" s="4"/>
       <c r="O274" s="4" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="P274" s="5"/>
       <c r="Q274" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="R274" s="4" t="s">
         <v>60</v>
@@ -27862,7 +27865,7 @@
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="AA274" s="4"/>
       <c r="AB274" s="4" t="s">
@@ -27874,7 +27877,7 @@
         <v>1000</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C275" s="4">
         <v>170412269</v>
@@ -27898,18 +27901,18 @@
         <v>107</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K275" s="4"/>
       <c r="L275" s="4"/>
       <c r="M275" s="4"/>
       <c r="N275" s="4"/>
       <c r="O275" s="4" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="P275" s="5"/>
       <c r="Q275" s="4" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="R275" s="4" t="s">
         <v>41</v>
@@ -27926,7 +27929,7 @@
         <v>2</v>
       </c>
       <c r="X275" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y275" s="4"/>
       <c r="Z275" s="4" t="s">
@@ -27942,7 +27945,7 @@
         <v>1000</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C276" s="4">
         <v>170412316</v>
@@ -27966,18 +27969,18 @@
         <v>107</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K276" s="4"/>
       <c r="L276" s="4"/>
       <c r="M276" s="4"/>
       <c r="N276" s="4"/>
       <c r="O276" s="4" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="P276" s="5"/>
       <c r="Q276" s="4" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="R276" s="4" t="s">
         <v>69</v>
@@ -27994,7 +27997,7 @@
         <v>2</v>
       </c>
       <c r="X276" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y276" s="4"/>
       <c r="Z276" s="4" t="s">
@@ -28034,11 +28037,11 @@
         <v>107</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K277" s="4"/>
       <c r="L277" s="4" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="M277" s="4" t="s">
         <v>478</v>
@@ -28047,11 +28050,11 @@
         <v>0</v>
       </c>
       <c r="O277" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="P277" s="5"/>
       <c r="Q277" s="4" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="R277" s="4" t="s">
         <v>74</v>
@@ -28110,24 +28113,24 @@
         <v>107</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K278" s="4"/>
       <c r="L278" s="4" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="M278" s="4" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N278" s="4">
         <v>19</v>
       </c>
       <c r="O278" s="4" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="P278" s="5"/>
       <c r="Q278" s="4" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="R278" s="4" t="s">
         <v>60</v>
@@ -28148,7 +28151,7 @@
       </c>
       <c r="Y278" s="4"/>
       <c r="Z278" s="4" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="AA278" s="4" t="s">
         <v>46</v>
@@ -28186,11 +28189,11 @@
         <v>107</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K279" s="4"/>
       <c r="L279" s="4" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="M279" s="4" t="s">
         <v>752</v>
@@ -28199,11 +28202,11 @@
         <v>6</v>
       </c>
       <c r="O279" s="4" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="P279" s="5"/>
       <c r="Q279" s="4" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="R279" s="4" t="s">
         <v>60</v>
@@ -28224,7 +28227,7 @@
       </c>
       <c r="Y279" s="4"/>
       <c r="Z279" s="4" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="AA279" s="4" t="s">
         <v>46</v>
@@ -28262,22 +28265,22 @@
         <v>107</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K280" s="4"/>
       <c r="L280" s="4" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="M280" s="4" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="N280" s="4"/>
       <c r="O280" s="4" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="P280" s="5"/>
       <c r="Q280" s="4" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="R280" s="4" t="s">
         <v>74</v>
@@ -28289,7 +28292,7 @@
         <v>1</v>
       </c>
       <c r="U280" s="4" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="V280" s="4" t="s">
         <v>843</v>
@@ -28302,7 +28305,7 @@
       </c>
       <c r="Y280" s="4"/>
       <c r="Z280" s="4" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="AA280" s="4" t="s">
         <v>665</v>
@@ -28340,7 +28343,7 @@
         <v>107</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K281" s="4"/>
       <c r="L281" s="4" t="s">
@@ -28353,11 +28356,11 @@
         <v>2</v>
       </c>
       <c r="O281" s="4" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="P281" s="5"/>
       <c r="Q281" s="4" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="R281" s="4" t="s">
         <v>195</v>
@@ -28369,7 +28372,7 @@
         <v>1</v>
       </c>
       <c r="U281" s="4" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="V281" s="4" t="s">
         <v>162</v>
@@ -28420,7 +28423,7 @@
         <v>107</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K282" s="4"/>
       <c r="L282" s="4" t="s">
@@ -28431,11 +28434,11 @@
       </c>
       <c r="N282" s="4"/>
       <c r="O282" s="4" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="P282" s="5"/>
       <c r="Q282" s="4" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="R282" s="4" t="s">
         <v>195</v>
@@ -28447,7 +28450,7 @@
         <v>0</v>
       </c>
       <c r="U282" s="4" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="V282" s="4" t="s">
         <v>162</v>
@@ -28498,7 +28501,7 @@
         <v>107</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K283" s="4"/>
       <c r="L283" s="4" t="s">
@@ -28511,11 +28514,11 @@
         <v>79</v>
       </c>
       <c r="O283" s="4" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="P283" s="5"/>
       <c r="Q283" s="4" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="R283" s="4" t="s">
         <v>195</v>
@@ -28527,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="U283" s="4" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="V283" s="4" t="s">
         <v>180</v>
@@ -28578,24 +28581,24 @@
         <v>107</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K284" s="4"/>
       <c r="L284" s="4" t="s">
         <v>623</v>
       </c>
       <c r="M284" s="4" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="N284" s="4">
         <v>67</v>
       </c>
       <c r="O284" s="4" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="P284" s="5"/>
       <c r="Q284" s="4" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="R284" s="4" t="s">
         <v>60</v>
@@ -28616,7 +28619,7 @@
       </c>
       <c r="Y284" s="4"/>
       <c r="Z284" s="4" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="AA284" s="4" t="s">
         <v>46</v>
@@ -28654,22 +28657,22 @@
         <v>107</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K285" s="4"/>
       <c r="L285" s="4" t="s">
         <v>623</v>
       </c>
       <c r="M285" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N285" s="4"/>
       <c r="O285" s="4" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="P285" s="5"/>
       <c r="Q285" s="4" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="R285" s="4" t="s">
         <v>60</v>
@@ -28690,7 +28693,7 @@
       </c>
       <c r="Y285" s="4"/>
       <c r="Z285" s="4" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="AA285" s="4" t="s">
         <v>714</v>
@@ -28728,7 +28731,7 @@
         <v>107</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K286" s="4"/>
       <c r="L286" s="4" t="s">
@@ -28739,11 +28742,11 @@
       </c>
       <c r="N286" s="4"/>
       <c r="O286" s="4" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="P286" s="5"/>
       <c r="Q286" s="4" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="R286" s="4" t="s">
         <v>60</v>
@@ -28755,7 +28758,7 @@
         <v>1</v>
       </c>
       <c r="U286" s="4" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="V286" s="4" t="s">
         <v>43</v>
@@ -28768,7 +28771,7 @@
       </c>
       <c r="Y286" s="4"/>
       <c r="Z286" s="4" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="AA286" s="4" t="s">
         <v>190</v>
@@ -28806,24 +28809,24 @@
         <v>107</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K287" s="4"/>
       <c r="L287" s="4" t="s">
         <v>125</v>
       </c>
       <c r="M287" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N287" s="4">
         <v>50</v>
       </c>
       <c r="O287" s="4" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="4" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="R287" s="4" t="s">
         <v>60</v>
@@ -28835,7 +28838,7 @@
         <v>1</v>
       </c>
       <c r="U287" s="4" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="V287" s="4" t="s">
         <v>1131</v>
@@ -28848,7 +28851,7 @@
       </c>
       <c r="Y287" s="4"/>
       <c r="Z287" s="4" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="AA287" s="4" t="s">
         <v>395</v>
@@ -28886,24 +28889,24 @@
         <v>107</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K288" s="4"/>
       <c r="L288" s="4" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="M288" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N288" s="4">
         <v>35</v>
       </c>
       <c r="O288" s="4" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="P288" s="5"/>
       <c r="Q288" s="4" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="R288" s="4" t="s">
         <v>69</v>
@@ -28915,7 +28918,7 @@
         <v>0</v>
       </c>
       <c r="U288" s="4" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="V288" s="4" t="s">
         <v>289</v>
@@ -28928,7 +28931,7 @@
       </c>
       <c r="Y288" s="4"/>
       <c r="Z288" s="4" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="AA288" s="4" t="s">
         <v>56</v>
@@ -28966,7 +28969,7 @@
         <v>107</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K289" s="4"/>
       <c r="L289" s="4" t="s">
@@ -28979,11 +28982,11 @@
         <v>171</v>
       </c>
       <c r="O289" s="4" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="P289" s="5"/>
       <c r="Q289" s="4" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="R289" s="4" t="s">
         <v>69</v>
@@ -28995,7 +28998,7 @@
         <v>44</v>
       </c>
       <c r="U289" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="V289" s="4" t="s">
         <v>289</v>
@@ -29008,7 +29011,7 @@
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="AA289" s="4" t="s">
         <v>966</v>
@@ -29046,7 +29049,7 @@
         <v>107</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
@@ -29055,11 +29058,11 @@
       <c r="M290" s="4"/>
       <c r="N290" s="4"/>
       <c r="O290" s="4" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="R290" s="4" t="s">
         <v>41</v>
@@ -29071,7 +29074,7 @@
         <v>0</v>
       </c>
       <c r="U290" s="4" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="V290" s="4" t="s">
         <v>540</v>
@@ -29120,7 +29123,7 @@
         <v>107</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K291" s="4"/>
       <c r="L291" s="4" t="s">
@@ -29129,11 +29132,11 @@
       <c r="M291" s="4"/>
       <c r="N291" s="4"/>
       <c r="O291" s="4" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="P291" s="5"/>
       <c r="Q291" s="4" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="R291" s="4" t="s">
         <v>41</v>
@@ -29145,7 +29148,7 @@
         <v>0</v>
       </c>
       <c r="U291" s="4" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="V291" s="4" t="s">
         <v>540</v>
@@ -29158,7 +29161,7 @@
       </c>
       <c r="Y291" s="4"/>
       <c r="Z291" s="4" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="AA291" s="4"/>
       <c r="AB291" s="4" t="s">
@@ -29194,11 +29197,11 @@
         <v>107</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="K292" s="4"/>
       <c r="L292" s="4" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="M292" s="4" t="s">
         <v>218</v>
@@ -29207,11 +29210,11 @@
         <v>44</v>
       </c>
       <c r="O292" s="4" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="R292" s="4" t="s">
         <v>69</v>
@@ -29223,10 +29226,10 @@
         <v>0</v>
       </c>
       <c r="U292" s="4" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="V292" s="4" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="W292" s="4">
         <v>2</v>
@@ -29274,7 +29277,7 @@
         <v>107</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="K293" s="4"/>
       <c r="L293" s="4" t="s">
@@ -29287,11 +29290,11 @@
         <v>28</v>
       </c>
       <c r="O293" s="4" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="P293" s="5"/>
       <c r="Q293" s="4" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="R293" s="4" t="s">
         <v>69</v>
@@ -29303,7 +29306,7 @@
         <v>2</v>
       </c>
       <c r="U293" s="4" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="V293" s="4" t="s">
         <v>283</v>
@@ -29354,7 +29357,7 @@
         <v>107</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="K294" s="4"/>
       <c r="L294" s="4" t="s">
@@ -29367,11 +29370,11 @@
         <v>4</v>
       </c>
       <c r="O294" s="4" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="P294" s="5"/>
       <c r="Q294" s="4" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="R294" s="4" t="s">
         <v>69</v>
@@ -29383,7 +29386,7 @@
         <v>0</v>
       </c>
       <c r="U294" s="4" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="V294" s="4" t="s">
         <v>137</v>
@@ -29432,7 +29435,7 @@
         <v>107</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K295" s="4"/>
       <c r="L295" s="4" t="s">
@@ -29445,11 +29448,11 @@
         <v>113</v>
       </c>
       <c r="O295" s="4" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>60</v>
@@ -29506,7 +29509,7 @@
         <v>107</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
@@ -29519,11 +29522,11 @@
         <v>113</v>
       </c>
       <c r="O296" s="4" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>60</v>
@@ -29580,24 +29583,24 @@
         <v>107</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
         <v>65</v>
       </c>
       <c r="M297" s="4" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="N297" s="4">
         <v>33</v>
       </c>
       <c r="O297" s="4" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>69</v>
@@ -29654,7 +29657,7 @@
         <v>107</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
@@ -29665,11 +29668,11 @@
       </c>
       <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="R298" s="4" t="s">
         <v>69</v>
@@ -29690,7 +29693,7 @@
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="AA298" s="4" t="s">
         <v>56</v>
@@ -29728,7 +29731,7 @@
         <v>107</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
@@ -29741,11 +29744,11 @@
         <v>134</v>
       </c>
       <c r="O299" s="4" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>60</v>
@@ -29802,22 +29805,22 @@
         <v>107</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K300" s="4"/>
       <c r="L300" s="4" t="s">
         <v>268</v>
       </c>
       <c r="M300" s="4" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="R300" s="4" t="s">
         <v>60</v>
@@ -29838,7 +29841,7 @@
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="AA300" s="4" t="s">
         <v>966</v>
@@ -29876,7 +29879,7 @@
         <v>107</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K301" s="4"/>
       <c r="L301" s="4" t="s">
@@ -29889,11 +29892,11 @@
         <v>56</v>
       </c>
       <c r="O301" s="4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="R301" s="4" t="s">
         <v>60</v>
@@ -29905,7 +29908,7 @@
         <v>0</v>
       </c>
       <c r="U301" s="4" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="V301" s="4" t="s">
         <v>289</v>
@@ -29918,7 +29921,7 @@
       </c>
       <c r="Y301" s="4"/>
       <c r="Z301" s="4" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="AA301" s="4" t="s">
         <v>46</v>
@@ -29956,24 +29959,24 @@
         <v>107</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4" t="s">
         <v>192</v>
       </c>
       <c r="M302" s="4" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="N302" s="4">
         <v>35</v>
       </c>
       <c r="O302" s="4" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="P302" s="5"/>
       <c r="Q302" s="4" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="R302" s="4" t="s">
         <v>60</v>
@@ -29985,7 +29988,7 @@
         <v>0</v>
       </c>
       <c r="U302" s="4" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="V302" s="4" t="s">
         <v>152</v>
@@ -29998,7 +30001,7 @@
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="AA302" s="4" t="s">
         <v>46</v>
@@ -30036,7 +30039,7 @@
         <v>107</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4" t="s">
@@ -30049,11 +30052,11 @@
         <v>24</v>
       </c>
       <c r="O303" s="4" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="R303" s="4" t="s">
         <v>69</v>
@@ -30110,24 +30113,24 @@
         <v>107</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
         <v>192</v>
       </c>
       <c r="M304" s="4" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="N304" s="4">
         <v>30</v>
       </c>
       <c r="O304" s="4" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>69</v>
@@ -30184,7 +30187,7 @@
         <v>418</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
@@ -30197,11 +30200,11 @@
         <v>250</v>
       </c>
       <c r="O305" s="4" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="R305" s="4" t="s">
         <v>41</v>
@@ -30213,7 +30216,7 @@
         <v>3</v>
       </c>
       <c r="U305" s="4" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="V305" s="4" t="s">
         <v>490</v>
@@ -30264,7 +30267,7 @@
         <v>418</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
@@ -30277,11 +30280,11 @@
         <v>282</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="R306" s="4" t="s">
         <v>41</v>
@@ -30293,7 +30296,7 @@
         <v>0</v>
       </c>
       <c r="U306" s="4" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="V306" s="4" t="s">
         <v>531</v>
@@ -30344,7 +30347,7 @@
         <v>418</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
@@ -30357,11 +30360,11 @@
         <v>305</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>41</v>
@@ -30373,7 +30376,7 @@
         <v>0</v>
       </c>
       <c r="U307" s="4" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="V307" s="4" t="s">
         <v>180</v>
@@ -30424,7 +30427,7 @@
         <v>418</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
@@ -30437,11 +30440,11 @@
         <v>339</v>
       </c>
       <c r="O308" s="4" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="4" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="R308" s="4" t="s">
         <v>41</v>
@@ -30453,7 +30456,7 @@
         <v>2</v>
       </c>
       <c r="U308" s="4" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="V308" s="4" t="s">
         <v>289</v>
@@ -30504,7 +30507,7 @@
         <v>418</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
@@ -30517,11 +30520,11 @@
         <v>362</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="R309" s="4" t="s">
         <v>41</v>
@@ -30533,7 +30536,7 @@
         <v>0</v>
       </c>
       <c r="U309" s="4" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="V309" s="4" t="s">
         <v>168</v>
@@ -30546,7 +30549,7 @@
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="AA309" s="4" t="s">
         <v>46</v>
@@ -30584,7 +30587,7 @@
         <v>418</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -30597,11 +30600,11 @@
         <v>386</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="R310" s="4" t="s">
         <v>41</v>
@@ -30613,7 +30616,7 @@
         <v>0</v>
       </c>
       <c r="U310" s="4" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="V310" s="4" t="s">
         <v>162</v>
@@ -30661,21 +30664,21 @@
         <v>107</v>
       </c>
       <c r="I311" s="4" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4"/>
       <c r="M311" s="4"/>
       <c r="N311" s="4"/>
       <c r="O311" s="4" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="P311" s="5"/>
       <c r="Q311" s="4" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="R311" s="4" t="s">
         <v>41</v>
@@ -30696,7 +30699,7 @@
       </c>
       <c r="Y311" s="4"/>
       <c r="Z311" s="4" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="AA311" s="4"/>
       <c r="AB311" s="4" t="s">
@@ -30732,11 +30735,11 @@
         <v>107</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M312" s="4" t="s">
         <v>473</v>
@@ -30745,11 +30748,11 @@
         <v>331</v>
       </c>
       <c r="O312" s="4" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>69</v>
@@ -30761,7 +30764,7 @@
         <v>0</v>
       </c>
       <c r="U312" s="4" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="V312" s="4" t="s">
         <v>283</v>
@@ -30812,11 +30815,11 @@
         <v>107</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M313" s="4" t="s">
         <v>473</v>
@@ -30825,11 +30828,11 @@
         <v>377</v>
       </c>
       <c r="O313" s="4" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="R313" s="4" t="s">
         <v>69</v>
@@ -30841,10 +30844,10 @@
         <v>0</v>
       </c>
       <c r="U313" s="4" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="V313" s="4" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="W313" s="4">
         <v>2</v>
@@ -30892,22 +30895,22 @@
         <v>107</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="M314" s="4" t="s">
         <v>192</v>
       </c>
       <c r="N314" s="4"/>
       <c r="O314" s="4" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>41</v>
@@ -30928,7 +30931,7 @@
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="AA314" s="4" t="s">
         <v>56</v>
@@ -30966,24 +30969,24 @@
         <v>107</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
         <v>192</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="N315" s="4">
         <v>48</v>
       </c>
       <c r="O315" s="4" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="R315" s="4" t="s">
         <v>41</v>
@@ -31039,21 +31042,21 @@
         <v>107</v>
       </c>
       <c r="I316" s="4" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4"/>
       <c r="M316" s="4"/>
       <c r="N316" s="4"/>
       <c r="O316" s="4" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="4" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="R316" s="4" t="s">
         <v>41</v>
@@ -31074,7 +31077,7 @@
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="AA316" s="4" t="s">
         <v>56</v>
@@ -31109,21 +31112,21 @@
         <v>107</v>
       </c>
       <c r="I317" s="4" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="K317" s="4"/>
       <c r="L317" s="4"/>
       <c r="M317" s="4"/>
       <c r="N317" s="4"/>
       <c r="O317" s="4" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="R317" s="4" t="s">
         <v>41</v>
@@ -31144,7 +31147,7 @@
       </c>
       <c r="Y317" s="4"/>
       <c r="Z317" s="4" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="AA317" s="4" t="s">
         <v>46</v>
@@ -31182,7 +31185,7 @@
         <v>848</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="K318" s="4"/>
       <c r="L318" s="4" t="s">
@@ -31195,11 +31198,11 @@
         <v>51</v>
       </c>
       <c r="O318" s="4" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="R318" s="4" t="s">
         <v>41</v>
@@ -31220,7 +31223,7 @@
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="AA318" s="4" t="s">
         <v>56</v>
@@ -31258,22 +31261,22 @@
         <v>848</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="M319" s="4" t="s">
         <v>259</v>
       </c>
       <c r="N319" s="4"/>
       <c r="O319" s="4" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="R319" s="4" t="s">
         <v>41</v>
@@ -31285,7 +31288,7 @@
         <v>0</v>
       </c>
       <c r="U319" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="V319" s="4" t="s">
         <v>627</v>
@@ -31336,7 +31339,7 @@
         <v>107</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
@@ -31349,11 +31352,11 @@
         <v>4</v>
       </c>
       <c r="O320" s="4" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="R320" s="4" t="s">
         <v>41</v>
@@ -31365,10 +31368,10 @@
         <v>0</v>
       </c>
       <c r="U320" s="4" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="V320" s="4" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="W320" s="4">
         <v>1</v>
@@ -31378,7 +31381,7 @@
       </c>
       <c r="Y320" s="4"/>
       <c r="Z320" s="4" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="AA320" s="4" t="s">
         <v>395</v>
@@ -31416,7 +31419,7 @@
         <v>107</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
@@ -31429,11 +31432,11 @@
         <v>14</v>
       </c>
       <c r="O321" s="4" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="R321" s="4" t="s">
         <v>41</v>
@@ -31445,7 +31448,7 @@
         <v>0</v>
       </c>
       <c r="U321" s="4" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="V321" s="4" t="s">
         <v>43</v>
@@ -31496,7 +31499,7 @@
         <v>107</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
@@ -31509,11 +31512,11 @@
         <v>35</v>
       </c>
       <c r="O322" s="4" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="P322" s="5"/>
       <c r="Q322" s="4" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="R322" s="4" t="s">
         <v>41</v>
@@ -31525,7 +31528,7 @@
         <v>1</v>
       </c>
       <c r="U322" s="4" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="V322" s="4" t="s">
         <v>43</v>
@@ -31576,7 +31579,7 @@
         <v>107</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
@@ -31589,11 +31592,11 @@
         <v>23</v>
       </c>
       <c r="O323" s="4" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="4" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="R323" s="4" t="s">
         <v>41</v>
@@ -31614,7 +31617,7 @@
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="AA323" s="4" t="s">
         <v>56</v>
@@ -31652,22 +31655,22 @@
         <v>107</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
         <v>387</v>
       </c>
       <c r="M324" s="4" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="N324" s="4"/>
       <c r="O324" s="4" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="4" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="R324" s="4" t="s">
         <v>69</v>
@@ -31679,7 +31682,7 @@
         <v>0</v>
       </c>
       <c r="U324" s="4" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="V324" s="4" t="s">
         <v>289</v>
@@ -31692,7 +31695,7 @@
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
@@ -31728,7 +31731,7 @@
         <v>107</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
@@ -31739,11 +31742,11 @@
       </c>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="R325" s="4" t="s">
         <v>69</v>
@@ -31755,10 +31758,10 @@
         <v>43</v>
       </c>
       <c r="U325" s="4" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="V325" s="4" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="W325" s="4">
         <v>8</v>
@@ -31768,7 +31771,7 @@
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="AA325" s="4" t="s">
         <v>714</v>
@@ -31806,24 +31809,24 @@
         <v>107</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="N326" s="4">
         <v>17</v>
       </c>
       <c r="O326" s="4" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="R326" s="4" t="s">
         <v>60</v>
@@ -31844,7 +31847,7 @@
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="AA326" s="4" t="s">
         <v>395</v>
@@ -31882,7 +31885,7 @@
         <v>107</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
@@ -31895,11 +31898,11 @@
         <v>16</v>
       </c>
       <c r="O327" s="4" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="P327" s="5"/>
       <c r="Q327" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="R327" s="4" t="s">
         <v>60</v>
@@ -31911,7 +31914,7 @@
         <v>0</v>
       </c>
       <c r="U327" s="4" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="V327" s="4" t="s">
         <v>283</v>
@@ -31924,7 +31927,7 @@
       </c>
       <c r="Y327" s="4"/>
       <c r="Z327" s="4" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="AA327" s="4" t="s">
         <v>714</v>
@@ -31962,7 +31965,7 @@
         <v>107</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
@@ -31975,11 +31978,11 @@
         <v>16</v>
       </c>
       <c r="O328" s="4" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="R328" s="4" t="s">
         <v>60</v>
@@ -31991,7 +31994,7 @@
         <v>0</v>
       </c>
       <c r="U328" s="4" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="V328" s="4" t="s">
         <v>283</v>
@@ -32004,7 +32007,7 @@
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="AA328" s="4" t="s">
         <v>714</v>
@@ -32042,7 +32045,7 @@
         <v>418</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
@@ -32055,11 +32058,11 @@
         <v>246</v>
       </c>
       <c r="O329" s="4" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="R329" s="4" t="s">
         <v>69</v>
@@ -32071,7 +32074,7 @@
         <v>3</v>
       </c>
       <c r="U329" s="4" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="V329" s="4" t="s">
         <v>162</v>
@@ -32084,7 +32087,7 @@
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="AA329" s="4" t="s">
         <v>56</v>
@@ -32122,24 +32125,24 @@
         <v>418</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
         <v>285</v>
       </c>
       <c r="M330" s="4" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="N330" s="4">
         <v>119</v>
       </c>
       <c r="O330" s="4" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="P330" s="5"/>
       <c r="Q330" s="4" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="R330" s="4" t="s">
         <v>41</v>
@@ -32151,7 +32154,7 @@
         <v>1</v>
       </c>
       <c r="U330" s="4" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="V330" s="4" t="s">
         <v>43</v>
@@ -32202,24 +32205,24 @@
         <v>418</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
         <v>285</v>
       </c>
       <c r="M331" s="4" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="N331" s="4">
         <v>132</v>
       </c>
       <c r="O331" s="4" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>41</v>
@@ -32276,11 +32279,11 @@
         <v>107</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="M332" s="4" t="s">
         <v>1201</v>
@@ -32289,11 +32292,11 @@
         <v>13</v>
       </c>
       <c r="O332" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>60</v>
@@ -32305,10 +32308,10 @@
         <v>0</v>
       </c>
       <c r="U332" s="4" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="V332" s="4" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="W332" s="4">
         <v>1</v>
@@ -32318,7 +32321,7 @@
       </c>
       <c r="Y332" s="4"/>
       <c r="Z332" s="4" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="AA332" s="4" t="s">
         <v>395</v>
@@ -32356,11 +32359,11 @@
         <v>107</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M333" s="4" t="s">
         <v>660</v>
@@ -32369,11 +32372,11 @@
         <v>89</v>
       </c>
       <c r="O333" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="4" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R333" s="4" t="s">
         <v>60</v>
@@ -32385,7 +32388,7 @@
         <v>0</v>
       </c>
       <c r="U333" s="4" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="V333" s="4" t="s">
         <v>162</v>
@@ -32398,7 +32401,7 @@
       </c>
       <c r="Y333" s="4"/>
       <c r="Z333" s="4" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="AA333" s="4" t="s">
         <v>56</v>
@@ -32412,7 +32415,7 @@
         <v>1000</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C334" s="4">
         <v>170412874</v>
@@ -32436,7 +32439,7 @@
         <v>107</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
@@ -32449,11 +32452,11 @@
         <v>21</v>
       </c>
       <c r="O334" s="4" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="R334" s="4" t="s">
         <v>69</v>
@@ -32470,7 +32473,7 @@
         <v>2</v>
       </c>
       <c r="X334" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y334" s="4"/>
       <c r="Z334" s="4" t="s">
@@ -32510,22 +32513,22 @@
         <v>107</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
         <v>660</v>
       </c>
       <c r="M335" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="N335" s="4"/>
       <c r="O335" s="4" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="P335" s="5"/>
       <c r="Q335" s="4" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="R335" s="4" t="s">
         <v>69</v>
@@ -32537,7 +32540,7 @@
         <v>0</v>
       </c>
       <c r="U335" s="4" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="V335" s="4" t="s">
         <v>152</v>
@@ -32550,7 +32553,7 @@
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="AA335" s="4" t="s">
         <v>46</v>
@@ -32564,7 +32567,7 @@
         <v>1000</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C336" s="4">
         <v>170412737</v>
@@ -32588,7 +32591,7 @@
         <v>107</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K336" s="4"/>
       <c r="L336" s="4" t="s">
@@ -32601,11 +32604,11 @@
         <v>107</v>
       </c>
       <c r="O336" s="4" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="R336" s="4" t="s">
         <v>41</v>
@@ -32622,7 +32625,7 @@
         <v>2</v>
       </c>
       <c r="X336" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
@@ -32638,7 +32641,7 @@
         <v>1000</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>33</v>
+        <v>1240</v>
       </c>
       <c r="C337" s="4">
         <v>170412819</v>
@@ -32662,24 +32665,24 @@
         <v>107</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K337" s="4"/>
       <c r="L337" s="4" t="s">
         <v>268</v>
       </c>
       <c r="M337" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="N337" s="4">
         <v>34</v>
       </c>
       <c r="O337" s="4" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="R337" s="4" t="s">
         <v>41</v>
@@ -32696,7 +32699,7 @@
         <v>2</v>
       </c>
       <c r="X337" s="4" t="s">
-        <v>44</v>
+        <v>1038</v>
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
@@ -32736,7 +32739,7 @@
         <v>107</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="K338" s="4"/>
       <c r="L338" s="4" t="s">
@@ -32747,11 +32750,11 @@
       </c>
       <c r="N338" s="4"/>
       <c r="O338" s="4" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="4" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="R338" s="4" t="s">
         <v>74</v>
@@ -32772,7 +32775,7 @@
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="AA338" s="4" t="s">
         <v>395</v>
@@ -32810,7 +32813,7 @@
         <v>107</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K339" s="4"/>
       <c r="L339" s="4" t="s">
@@ -32823,11 +32826,11 @@
         <v>55</v>
       </c>
       <c r="O339" s="4" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="R339" s="4" t="s">
         <v>74</v>
@@ -32886,7 +32889,7 @@
         <v>107</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K340" s="4"/>
       <c r="L340" s="4" t="s">
@@ -32897,11 +32900,11 @@
       </c>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="4" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="R340" s="4" t="s">
         <v>74</v>
@@ -32913,7 +32916,7 @@
         <v>0</v>
       </c>
       <c r="U340" s="4" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="V340" s="4" t="s">
         <v>588</v>
@@ -32962,7 +32965,7 @@
         <v>107</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K341" s="4"/>
       <c r="L341" s="4" t="s">
@@ -32973,11 +32976,11 @@
       </c>
       <c r="N341" s="4"/>
       <c r="O341" s="4" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="4" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="R341" s="4" t="s">
         <v>74</v>
@@ -32989,7 +32992,7 @@
         <v>11</v>
       </c>
       <c r="U341" s="4" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="V341" s="4" t="s">
         <v>588</v>
@@ -33040,7 +33043,7 @@
         <v>107</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K342" s="4"/>
       <c r="L342" s="4" t="s">
@@ -33051,11 +33054,11 @@
       </c>
       <c r="N342" s="4"/>
       <c r="O342" s="4" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="R342" s="4" t="s">
         <v>60</v>
@@ -33067,7 +33070,7 @@
         <v>4</v>
       </c>
       <c r="U342" s="4" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="V342" s="4" t="s">
         <v>363</v>
@@ -33080,7 +33083,7 @@
       </c>
       <c r="Y342" s="4"/>
       <c r="Z342" s="4" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="AA342" s="4" t="s">
         <v>46</v>
@@ -33118,7 +33121,7 @@
         <v>107</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K343" s="4"/>
       <c r="L343" s="4" t="s">
@@ -33129,11 +33132,11 @@
       </c>
       <c r="N343" s="4"/>
       <c r="O343" s="4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="R343" s="4" t="s">
         <v>60</v>
@@ -33192,7 +33195,7 @@
         <v>107</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K344" s="4"/>
       <c r="L344" s="4" t="s">
@@ -33203,11 +33206,11 @@
       </c>
       <c r="N344" s="4"/>
       <c r="O344" s="4" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="P344" s="5"/>
       <c r="Q344" s="4" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="R344" s="4" t="s">
         <v>60</v>
@@ -33219,7 +33222,7 @@
         <v>0</v>
       </c>
       <c r="U344" s="4" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="V344" s="4" t="s">
         <v>363</v>
@@ -33232,7 +33235,7 @@
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="AA344" s="4"/>
       <c r="AB344" s="4" t="s">
@@ -33268,7 +33271,7 @@
         <v>107</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K345" s="4"/>
       <c r="L345" s="4" t="s">
@@ -33279,11 +33282,11 @@
       </c>
       <c r="N345" s="4"/>
       <c r="O345" s="4" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="P345" s="5"/>
       <c r="Q345" s="4" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="R345" s="4" t="s">
         <v>60</v>
@@ -33295,7 +33298,7 @@
         <v>0</v>
       </c>
       <c r="U345" s="4" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="V345" s="4" t="s">
         <v>162</v>
@@ -33308,7 +33311,7 @@
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="AA345" s="4"/>
       <c r="AB345" s="4" t="s">
@@ -33344,22 +33347,22 @@
         <v>107</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K346" s="4"/>
       <c r="L346" s="4" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="M346" s="4" t="s">
         <v>65</v>
       </c>
       <c r="N346" s="4"/>
       <c r="O346" s="4" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="P346" s="5"/>
       <c r="Q346" s="4" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="R346" s="4" t="s">
         <v>60</v>
@@ -33380,7 +33383,7 @@
       </c>
       <c r="Y346" s="4"/>
       <c r="Z346" s="4" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="AA346" s="4" t="s">
         <v>46</v>
@@ -33418,7 +33421,7 @@
         <v>107</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
@@ -33429,11 +33432,11 @@
       </c>
       <c r="N347" s="4"/>
       <c r="O347" s="4" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="4" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="R347" s="4" t="s">
         <v>74</v>
@@ -33492,7 +33495,7 @@
         <v>107</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
@@ -33503,11 +33506,11 @@
       </c>
       <c r="N348" s="4"/>
       <c r="O348" s="4" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="R348" s="4" t="s">
         <v>74</v>
@@ -33519,10 +33522,10 @@
         <v>4</v>
       </c>
       <c r="U348" s="4" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="V348" s="4" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="W348" s="4">
         <v>6</v>
@@ -33570,7 +33573,7 @@
         <v>107</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
@@ -33581,11 +33584,11 @@
       </c>
       <c r="N349" s="4"/>
       <c r="O349" s="4" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="R349" s="4" t="s">
         <v>74</v>
@@ -33597,7 +33600,7 @@
         <v>5</v>
       </c>
       <c r="U349" s="4" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="V349" s="4" t="s">
         <v>162</v>
@@ -33648,7 +33651,7 @@
         <v>107</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
@@ -33659,11 +33662,11 @@
       </c>
       <c r="N350" s="4"/>
       <c r="O350" s="4" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="R350" s="4" t="s">
         <v>74</v>
@@ -33684,7 +33687,7 @@
       </c>
       <c r="Y350" s="4"/>
       <c r="Z350" s="4" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="AA350" s="4"/>
       <c r="AB350" s="4" t="s">
@@ -33720,7 +33723,7 @@
         <v>107</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
@@ -33731,11 +33734,11 @@
       </c>
       <c r="N351" s="4"/>
       <c r="O351" s="4" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="P351" s="5"/>
       <c r="Q351" s="4" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="R351" s="4" t="s">
         <v>60</v>
@@ -33747,7 +33750,7 @@
         <v>0</v>
       </c>
       <c r="U351" s="4" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="V351" s="4" t="s">
         <v>289</v>
@@ -33760,7 +33763,7 @@
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="AA351" s="4" t="s">
         <v>46</v>
@@ -33798,7 +33801,7 @@
         <v>107</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
@@ -33811,11 +33814,11 @@
         <v>86</v>
       </c>
       <c r="O352" s="4" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="P352" s="5"/>
       <c r="Q352" s="4" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="R352" s="4" t="s">
         <v>74</v>
@@ -33827,10 +33830,10 @@
         <v>2</v>
       </c>
       <c r="U352" s="4" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="W352" s="4">
         <v>6</v>
@@ -33878,7 +33881,7 @@
         <v>107</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
@@ -33889,11 +33892,11 @@
       </c>
       <c r="N353" s="4"/>
       <c r="O353" s="4" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="P353" s="5"/>
       <c r="Q353" s="4" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="R353" s="4" t="s">
         <v>60</v>
@@ -33914,7 +33917,7 @@
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="AA353" s="4"/>
       <c r="AB353" s="4" t="s">
@@ -33950,22 +33953,22 @@
         <v>107</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M354" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="N354" s="4"/>
       <c r="O354" s="4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="P354" s="5"/>
       <c r="Q354" s="4" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="R354" s="4" t="s">
         <v>60</v>
@@ -33977,7 +33980,7 @@
         <v>0</v>
       </c>
       <c r="U354" s="4" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="V354" s="4" t="s">
         <v>222</v>
@@ -33990,7 +33993,7 @@
       </c>
       <c r="Y354" s="4"/>
       <c r="Z354" s="4" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="AA354" s="4" t="s">
         <v>46</v>
@@ -34028,22 +34031,22 @@
         <v>107</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K355" s="4"/>
       <c r="L355" s="4" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="M355" s="4" t="s">
         <v>94</v>
       </c>
       <c r="N355" s="4"/>
       <c r="O355" s="4" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="R355" s="4" t="s">
         <v>41</v>
@@ -34055,7 +34058,7 @@
         <v>0</v>
       </c>
       <c r="U355" s="4" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="V355" s="4" t="s">
         <v>162</v>
@@ -34068,7 +34071,7 @@
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="AA355" s="4" t="s">
         <v>46</v>
@@ -34106,24 +34109,24 @@
         <v>107</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K356" s="4"/>
       <c r="L356" s="4" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="M356" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N356" s="4">
         <v>20</v>
       </c>
       <c r="O356" s="4" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="P356" s="5"/>
       <c r="Q356" s="4" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="R356" s="4" t="s">
         <v>69</v>
@@ -34135,7 +34138,7 @@
         <v>0</v>
       </c>
       <c r="U356" s="4" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="V356" s="4" t="s">
         <v>168</v>
@@ -34148,7 +34151,7 @@
       </c>
       <c r="Y356" s="4"/>
       <c r="Z356" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AA356" s="4" t="s">
         <v>56</v>
@@ -34186,7 +34189,7 @@
         <v>107</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K357" s="4"/>
       <c r="L357" s="4" t="s">
@@ -34199,11 +34202,11 @@
         <v>42</v>
       </c>
       <c r="O357" s="4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="P357" s="5"/>
       <c r="Q357" s="4" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="R357" s="4" t="s">
         <v>69</v>
@@ -34215,7 +34218,7 @@
         <v>0</v>
       </c>
       <c r="U357" s="4" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="V357" s="4" t="s">
         <v>1057</v>
@@ -34266,11 +34269,11 @@
         <v>107</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="M358" s="4" t="s">
         <v>699</v>
@@ -34279,11 +34282,11 @@
         <v>35</v>
       </c>
       <c r="O358" s="4" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="P358" s="5"/>
       <c r="Q358" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="R358" s="4" t="s">
         <v>69</v>
@@ -34295,7 +34298,7 @@
         <v>0</v>
       </c>
       <c r="U358" s="4" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="V358" s="4" t="s">
         <v>137</v>
@@ -34346,11 +34349,11 @@
         <v>107</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="M359" s="4" t="s">
         <v>789</v>
@@ -34359,11 +34362,11 @@
         <v>4</v>
       </c>
       <c r="O359" s="4" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="R359" s="4" t="s">
         <v>41</v>
@@ -34375,7 +34378,7 @@
         <v>1</v>
       </c>
       <c r="U359" s="4" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="V359" s="4" t="s">
         <v>197</v>
@@ -34426,24 +34429,24 @@
         <v>107</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="M360" s="4" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="N360" s="4">
         <v>41</v>
       </c>
       <c r="O360" s="4" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="P360" s="5"/>
       <c r="Q360" s="4" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="R360" s="4" t="s">
         <v>69</v>
@@ -34464,7 +34467,7 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="AA360" s="4" t="s">
         <v>46</v>
@@ -34502,7 +34505,7 @@
         <v>107</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
@@ -34515,11 +34518,11 @@
         <v>65</v>
       </c>
       <c r="O361" s="4" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="R361" s="4" t="s">
         <v>361</v>
@@ -34531,7 +34534,7 @@
         <v>0</v>
       </c>
       <c r="U361" s="4" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="V361" s="4" t="s">
         <v>1131</v>
@@ -34544,7 +34547,7 @@
       </c>
       <c r="Y361" s="4"/>
       <c r="Z361" s="4" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="AA361" s="4" t="s">
         <v>395</v>
@@ -34582,18 +34585,18 @@
         <v>107</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4"/>
       <c r="M362" s="4"/>
       <c r="N362" s="4"/>
       <c r="O362" s="4" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="P362" s="5"/>
       <c r="Q362" s="4" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="R362" s="4" t="s">
         <v>69</v>
@@ -34614,7 +34617,7 @@
       </c>
       <c r="Y362" s="4"/>
       <c r="Z362" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AA362" s="4" t="s">
         <v>56</v>
@@ -34652,18 +34655,18 @@
         <v>107</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4"/>
       <c r="M363" s="4"/>
       <c r="N363" s="4"/>
       <c r="O363" s="4" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="P363" s="5"/>
       <c r="Q363" s="4" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="R363" s="4" t="s">
         <v>69</v>
@@ -34684,7 +34687,7 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="AA363" s="4" t="s">
         <v>190</v>
@@ -34722,18 +34725,18 @@
         <v>107</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4"/>
       <c r="M364" s="4"/>
       <c r="N364" s="4"/>
       <c r="O364" s="4" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="R364" s="4" t="s">
         <v>69</v>
@@ -34754,7 +34757,7 @@
       </c>
       <c r="Y364" s="4"/>
       <c r="Z364" s="4" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="AA364" s="4" t="s">
         <v>550</v>
@@ -34792,18 +34795,18 @@
         <v>107</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
       <c r="N365" s="4"/>
       <c r="O365" s="4" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="P365" s="5"/>
       <c r="Q365" s="4" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="R365" s="4" t="s">
         <v>69</v>
@@ -34824,7 +34827,7 @@
       </c>
       <c r="Y365" s="4"/>
       <c r="Z365" s="4" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="AA365" s="4" t="s">
         <v>46</v>
@@ -34862,18 +34865,18 @@
         <v>107</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K366" s="4"/>
       <c r="L366" s="4"/>
       <c r="M366" s="4"/>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="P366" s="5"/>
       <c r="Q366" s="4" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="R366" s="4" t="s">
         <v>69</v>
@@ -34894,7 +34897,7 @@
       </c>
       <c r="Y366" s="4"/>
       <c r="Z366" s="4" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="AA366" s="4" t="s">
         <v>46</v>
@@ -34932,11 +34935,11 @@
         <v>107</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="M367" s="4" t="s">
         <v>1201</v>
@@ -34945,11 +34948,11 @@
         <v>1</v>
       </c>
       <c r="O367" s="4" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="R367" s="4" t="s">
         <v>69</v>
@@ -34961,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="U367" s="4" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="V367" s="4" t="s">
         <v>283</v>
@@ -35012,11 +35015,11 @@
         <v>107</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M368" s="4" t="s">
         <v>467</v>
@@ -35025,11 +35028,11 @@
         <v>40</v>
       </c>
       <c r="O368" s="4" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="P368" s="5"/>
       <c r="Q368" s="4" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="R368" s="4" t="s">
         <v>271</v>
@@ -35041,7 +35044,7 @@
         <v>0</v>
       </c>
       <c r="U368" s="4" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="V368" s="4" t="s">
         <v>197</v>
@@ -35054,7 +35057,7 @@
       </c>
       <c r="Y368" s="4"/>
       <c r="Z368" s="4" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="AA368" s="4" t="s">
         <v>46</v>
@@ -35092,7 +35095,7 @@
         <v>107</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
@@ -35105,11 +35108,11 @@
         <v>115</v>
       </c>
       <c r="O369" s="4" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="R369" s="4" t="s">
         <v>69</v>
@@ -35130,7 +35133,7 @@
       </c>
       <c r="Y369" s="4"/>
       <c r="Z369" s="4" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AA369" s="4" t="s">
         <v>714</v>
@@ -35150,7 +35153,7 @@
         <v>169614036</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="E370" s="4">
         <v>1351810</v>
@@ -35168,7 +35171,7 @@
         <v>107</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -35181,11 +35184,11 @@
         <v>29</v>
       </c>
       <c r="O370" s="4" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="R370" s="4" t="s">
         <v>60</v>
@@ -35197,7 +35200,7 @@
         <v>0</v>
       </c>
       <c r="U370" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="V370" s="4" t="s">
         <v>162</v>
@@ -35210,7 +35213,7 @@
       </c>
       <c r="Y370" s="4"/>
       <c r="Z370" s="4" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="AA370" s="4" t="s">
         <v>46</v>
@@ -35248,11 +35251,11 @@
         <v>107</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="M371" s="4" t="s">
         <v>478</v>
@@ -35261,11 +35264,11 @@
         <v>251</v>
       </c>
       <c r="O371" s="4" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="R371" s="4" t="s">
         <v>69</v>
@@ -35277,7 +35280,7 @@
         <v>0</v>
       </c>
       <c r="U371" s="4" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="V371" s="4" t="s">
         <v>137</v>
@@ -35326,7 +35329,7 @@
         <v>534</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="K372" s="4"/>
       <c r="L372" s="4" t="s">
@@ -35339,11 +35342,11 @@
         <v>275</v>
       </c>
       <c r="O372" s="4" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="P372" s="5"/>
       <c r="Q372" s="4" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="R372" s="4" t="s">
         <v>74</v>
@@ -35355,7 +35358,7 @@
         <v>4</v>
       </c>
       <c r="U372" s="4" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="V372" s="4" t="s">
         <v>283</v>
@@ -35368,7 +35371,7 @@
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="AA372" s="4" t="s">
         <v>56</v>
@@ -35406,11 +35409,11 @@
         <v>107</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="K373" s="4"/>
       <c r="L373" s="4" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="M373" s="4" t="s">
         <v>192</v>
@@ -35419,11 +35422,11 @@
         <v>24</v>
       </c>
       <c r="O373" s="4" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="R373" s="4" t="s">
         <v>195</v>
@@ -35444,7 +35447,7 @@
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="AA373" s="4"/>
       <c r="AB373" s="4" t="s">
@@ -35480,24 +35483,24 @@
         <v>107</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="K374" s="4"/>
       <c r="L374" s="4" t="s">
         <v>578</v>
       </c>
       <c r="M374" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="N374" s="4">
         <v>47</v>
       </c>
       <c r="O374" s="4" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="P374" s="5"/>
       <c r="Q374" s="4" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="R374" s="4" t="s">
         <v>74</v>
@@ -35518,7 +35521,7 @@
       </c>
       <c r="Y374" s="4"/>
       <c r="Z374" s="4" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="AA374" s="4" t="s">
         <v>56</v>
@@ -35556,7 +35559,7 @@
         <v>107</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="K375" s="4"/>
       <c r="L375" s="4" t="s">
@@ -35567,11 +35570,11 @@
       </c>
       <c r="N375" s="4"/>
       <c r="O375" s="4" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="P375" s="5"/>
       <c r="Q375" s="4" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="R375" s="4" t="s">
         <v>195</v>
@@ -35583,10 +35586,10 @@
         <v>0</v>
       </c>
       <c r="U375" s="4" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="V375" s="4" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="W375" s="4">
         <v>1</v>
@@ -35596,7 +35599,7 @@
       </c>
       <c r="Y375" s="4"/>
       <c r="Z375" s="4" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="AA375" s="4" t="s">
         <v>395</v>
@@ -35634,18 +35637,18 @@
         <v>107</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="K376" s="4"/>
       <c r="L376" s="4"/>
       <c r="M376" s="4"/>
       <c r="N376" s="4"/>
       <c r="O376" s="4" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="P376" s="5"/>
       <c r="Q376" s="4" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="R376" s="4" t="s">
         <v>271</v>
@@ -35666,7 +35669,7 @@
       </c>
       <c r="Y376" s="4"/>
       <c r="Z376" s="4" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="AA376" s="4" t="s">
         <v>395</v>
@@ -35704,24 +35707,24 @@
         <v>107</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="K377" s="4"/>
       <c r="L377" s="4" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="M377" s="4" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="N377" s="4">
         <v>8</v>
       </c>
       <c r="O377" s="4" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="P377" s="5"/>
       <c r="Q377" s="4" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="R377" s="4" t="s">
         <v>69</v>
@@ -35733,7 +35736,7 @@
         <v>4</v>
       </c>
       <c r="U377" s="4" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="V377" s="4" t="s">
         <v>162</v>
@@ -35784,7 +35787,7 @@
         <v>107</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K378" s="4"/>
       <c r="L378" s="4" t="s">
@@ -35797,11 +35800,11 @@
         <v>23</v>
       </c>
       <c r="O378" s="4" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="P378" s="5"/>
       <c r="Q378" s="4" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="R378" s="4" t="s">
         <v>41</v>
@@ -35858,7 +35861,7 @@
         <v>107</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K379" s="4"/>
       <c r="L379" s="4" t="s">
@@ -35871,11 +35874,11 @@
         <v>9</v>
       </c>
       <c r="O379" s="4" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="R379" s="4" t="s">
         <v>69</v>
@@ -35887,7 +35890,7 @@
         <v>0</v>
       </c>
       <c r="U379" s="4" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="V379" s="4" t="s">
         <v>43</v>
@@ -35900,7 +35903,7 @@
       </c>
       <c r="Y379" s="4"/>
       <c r="Z379" s="4" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="AA379" s="4" t="s">
         <v>372</v>
@@ -35938,24 +35941,24 @@
         <v>107</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K380" s="4"/>
       <c r="L380" s="4" t="s">
         <v>990</v>
       </c>
       <c r="M380" s="4" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="N380" s="4">
         <v>59</v>
       </c>
       <c r="O380" s="4" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="R380" s="4" t="s">
         <v>41</v>
@@ -36012,24 +36015,24 @@
         <v>107</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K381" s="4"/>
       <c r="L381" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M381" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="N381" s="4">
         <v>4</v>
       </c>
       <c r="O381" s="4" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="P381" s="5"/>
       <c r="Q381" s="4" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="R381" s="4" t="s">
         <v>41</v>
@@ -36041,7 +36044,7 @@
         <v>0</v>
       </c>
       <c r="U381" s="4" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="V381" s="4" t="s">
         <v>43</v>
@@ -36092,24 +36095,24 @@
         <v>107</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K382" s="4"/>
       <c r="L382" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="M382" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="N382" s="4">
         <v>5</v>
       </c>
       <c r="O382" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="P382" s="5"/>
       <c r="Q382" s="4" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="R382" s="4" t="s">
         <v>41</v>
@@ -36168,24 +36171,24 @@
         <v>107</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K383" s="4"/>
       <c r="L383" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="M383" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="N383" s="4">
         <v>3</v>
       </c>
       <c r="O383" s="4" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="P383" s="5"/>
       <c r="Q383" s="4" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="R383" s="4" t="s">
         <v>69</v>
@@ -36197,7 +36200,7 @@
         <v>0</v>
       </c>
       <c r="U383" s="4" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="V383" s="4" t="s">
         <v>162</v>
@@ -36248,24 +36251,24 @@
         <v>107</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K384" s="4"/>
       <c r="L384" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="M384" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="N384" s="4">
         <v>36</v>
       </c>
       <c r="O384" s="4" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="P384" s="5"/>
       <c r="Q384" s="4" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="R384" s="4" t="s">
         <v>41</v>
@@ -36277,7 +36280,7 @@
         <v>0</v>
       </c>
       <c r="U384" s="4" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="V384" s="4" t="s">
         <v>246</v>
@@ -36326,24 +36329,24 @@
         <v>107</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K385" s="4"/>
       <c r="L385" s="4" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="M385" s="4" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="N385" s="4">
         <v>30</v>
       </c>
       <c r="O385" s="4" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="P385" s="5"/>
       <c r="Q385" s="4" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="R385" s="4" t="s">
         <v>41</v>
@@ -36355,7 +36358,7 @@
         <v>2</v>
       </c>
       <c r="U385" s="4" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="V385" s="4" t="s">
         <v>152</v>
@@ -36368,7 +36371,7 @@
       </c>
       <c r="Y385" s="4"/>
       <c r="Z385" s="4" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="AA385" s="4" t="s">
         <v>56</v>
@@ -36406,24 +36409,24 @@
         <v>107</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K386" s="4"/>
       <c r="L386" s="4" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="M386" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="N386" s="4">
         <v>39</v>
       </c>
       <c r="O386" s="4" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="P386" s="5"/>
       <c r="Q386" s="4" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="R386" s="4" t="s">
         <v>41</v>
@@ -36480,22 +36483,22 @@
         <v>107</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="K387" s="4"/>
       <c r="L387" s="4" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="M387" s="4" t="s">
         <v>666</v>
       </c>
       <c r="N387" s="4"/>
       <c r="O387" s="4" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="P387" s="5"/>
       <c r="Q387" s="4" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="R387" s="4" t="s">
         <v>60</v>
@@ -36516,7 +36519,7 @@
       </c>
       <c r="Y387" s="4"/>
       <c r="Z387" s="4" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="AA387" s="4" t="s">
         <v>190</v>
@@ -36554,22 +36557,22 @@
         <v>107</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="K388" s="4"/>
       <c r="L388" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="M388" s="4" t="s">
         <v>659</v>
       </c>
       <c r="N388" s="4"/>
       <c r="O388" s="4" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="P388" s="5"/>
       <c r="Q388" s="4" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="R388" s="4" t="s">
         <v>60</v>
@@ -36581,7 +36584,7 @@
         <v>0</v>
       </c>
       <c r="U388" s="4" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="V388" s="4" t="s">
         <v>289</v>
@@ -36594,7 +36597,7 @@
       </c>
       <c r="Y388" s="4"/>
       <c r="Z388" s="4" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="AA388" s="4"/>
       <c r="AB388" s="4" t="s">
@@ -36630,24 +36633,24 @@
         <v>107</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="K389" s="4"/>
       <c r="L389" s="4" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="M389" s="4" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="N389" s="4">
         <v>66</v>
       </c>
       <c r="O389" s="4" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="R389" s="4" t="s">
         <v>69</v>
@@ -36659,7 +36662,7 @@
         <v>0</v>
       </c>
       <c r="U389" s="4" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="V389" s="4" t="s">
         <v>197</v>
@@ -36710,24 +36713,24 @@
         <v>107</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="K390" s="4"/>
       <c r="L390" s="4" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="M390" s="4" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="N390" s="4">
         <v>45</v>
       </c>
       <c r="O390" s="4" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="R390" s="4" t="s">
         <v>195</v>
@@ -36748,7 +36751,7 @@
       </c>
       <c r="Y390" s="4"/>
       <c r="Z390" s="4" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AA390" s="4"/>
       <c r="AB390" s="4" t="s">
@@ -36784,24 +36787,24 @@
         <v>107</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="K391" s="4"/>
       <c r="L391" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="M391" s="4" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="N391" s="4">
         <v>7</v>
       </c>
       <c r="O391" s="4" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="P391" s="5"/>
       <c r="Q391" s="4" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="R391" s="4" t="s">
         <v>69</v>
@@ -36860,22 +36863,22 @@
         <v>107</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K392" s="4"/>
       <c r="L392" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M392" s="4" t="s">
         <v>514</v>
       </c>
       <c r="N392" s="4"/>
       <c r="O392" s="4" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="P392" s="5"/>
       <c r="Q392" s="4" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="R392" s="4" t="s">
         <v>60</v>
@@ -36887,7 +36890,7 @@
         <v>0</v>
       </c>
       <c r="U392" s="4" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="V392" s="4" t="s">
         <v>363</v>
@@ -36900,7 +36903,7 @@
       </c>
       <c r="Y392" s="4"/>
       <c r="Z392" s="4" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="AA392" s="4" t="s">
         <v>372</v>
@@ -36938,22 +36941,22 @@
         <v>107</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K393" s="4"/>
       <c r="L393" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M393" s="4" t="s">
         <v>514</v>
       </c>
       <c r="N393" s="4"/>
       <c r="O393" s="4" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="P393" s="5"/>
       <c r="Q393" s="4" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="R393" s="4" t="s">
         <v>60</v>
@@ -36965,7 +36968,7 @@
         <v>0</v>
       </c>
       <c r="U393" s="4" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="V393" s="4" t="s">
         <v>363</v>
@@ -36978,7 +36981,7 @@
       </c>
       <c r="Y393" s="4"/>
       <c r="Z393" s="4" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="AA393" s="4" t="s">
         <v>372</v>
@@ -37016,22 +37019,22 @@
         <v>107</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K394" s="4"/>
       <c r="L394" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M394" s="4" t="s">
         <v>514</v>
       </c>
       <c r="N394" s="4"/>
       <c r="O394" s="4" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="P394" s="5"/>
       <c r="Q394" s="4" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="R394" s="4" t="s">
         <v>60</v>
@@ -37043,7 +37046,7 @@
         <v>0</v>
       </c>
       <c r="U394" s="4" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="V394" s="4" t="s">
         <v>363</v>
@@ -37056,7 +37059,7 @@
       </c>
       <c r="Y394" s="4"/>
       <c r="Z394" s="4" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="AA394" s="4" t="s">
         <v>372</v>
@@ -37094,22 +37097,22 @@
         <v>107</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K395" s="4"/>
       <c r="L395" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M395" s="4" t="s">
         <v>514</v>
       </c>
       <c r="N395" s="4"/>
       <c r="O395" s="4" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="P395" s="5"/>
       <c r="Q395" s="4" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="R395" s="4" t="s">
         <v>60</v>
@@ -37121,7 +37124,7 @@
         <v>0</v>
       </c>
       <c r="U395" s="4" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="V395" s="4" t="s">
         <v>363</v>
@@ -37134,7 +37137,7 @@
       </c>
       <c r="Y395" s="4"/>
       <c r="Z395" s="4" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA395" s="4" t="s">
         <v>372</v>
@@ -37172,11 +37175,11 @@
         <v>107</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K396" s="4"/>
       <c r="L396" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M396" s="4" t="s">
         <v>514</v>
@@ -37185,11 +37188,11 @@
         <v>9</v>
       </c>
       <c r="O396" s="4" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="P396" s="5"/>
       <c r="Q396" s="4" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="R396" s="4" t="s">
         <v>41</v>
@@ -37210,7 +37213,7 @@
       </c>
       <c r="Y396" s="4"/>
       <c r="Z396" s="4" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="AA396" s="4" t="s">
         <v>372</v>
@@ -37248,11 +37251,11 @@
         <v>107</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K397" s="4"/>
       <c r="L397" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M397" s="4" t="s">
         <v>514</v>
@@ -37261,11 +37264,11 @@
         <v>9</v>
       </c>
       <c r="O397" s="4" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="P397" s="5"/>
       <c r="Q397" s="4" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="R397" s="4" t="s">
         <v>60</v>
@@ -37286,7 +37289,7 @@
       </c>
       <c r="Y397" s="4"/>
       <c r="Z397" s="4" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="AA397" s="4" t="s">
         <v>372</v>
@@ -37324,11 +37327,11 @@
         <v>107</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K398" s="4"/>
       <c r="L398" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M398" s="4" t="s">
         <v>514</v>
@@ -37337,11 +37340,11 @@
         <v>9</v>
       </c>
       <c r="O398" s="4" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="P398" s="5"/>
       <c r="Q398" s="4" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="R398" s="4" t="s">
         <v>41</v>
@@ -37362,7 +37365,7 @@
       </c>
       <c r="Y398" s="4"/>
       <c r="Z398" s="4" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="AA398" s="4" t="s">
         <v>372</v>
@@ -37400,11 +37403,11 @@
         <v>107</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K399" s="4"/>
       <c r="L399" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M399" s="4" t="s">
         <v>514</v>
@@ -37413,11 +37416,11 @@
         <v>9</v>
       </c>
       <c r="O399" s="4" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="R399" s="4" t="s">
         <v>60</v>
@@ -37438,7 +37441,7 @@
       </c>
       <c r="Y399" s="4"/>
       <c r="Z399" s="4" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="AA399" s="4" t="s">
         <v>372</v>
@@ -37476,11 +37479,11 @@
         <v>107</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K400" s="4"/>
       <c r="L400" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M400" s="4" t="s">
         <v>514</v>
@@ -37489,11 +37492,11 @@
         <v>9</v>
       </c>
       <c r="O400" s="4" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="R400" s="4" t="s">
         <v>60</v>
@@ -37514,7 +37517,7 @@
       </c>
       <c r="Y400" s="4"/>
       <c r="Z400" s="4" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="AA400" s="4" t="s">
         <v>372</v>
@@ -37552,11 +37555,11 @@
         <v>107</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K401" s="4"/>
       <c r="L401" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M401" s="4" t="s">
         <v>514</v>
@@ -37565,11 +37568,11 @@
         <v>9</v>
       </c>
       <c r="O401" s="4" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="P401" s="5"/>
       <c r="Q401" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="R401" s="4" t="s">
         <v>60</v>
@@ -37590,7 +37593,7 @@
       </c>
       <c r="Y401" s="4"/>
       <c r="Z401" s="4" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="AA401" s="4" t="s">
         <v>372</v>
@@ -37628,11 +37631,11 @@
         <v>107</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K402" s="4"/>
       <c r="L402" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M402" s="4" t="s">
         <v>514</v>
@@ -37641,11 +37644,11 @@
         <v>9</v>
       </c>
       <c r="O402" s="4" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="P402" s="5"/>
       <c r="Q402" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="R402" s="4" t="s">
         <v>60</v>
@@ -37666,7 +37669,7 @@
       </c>
       <c r="Y402" s="4"/>
       <c r="Z402" s="4" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AA402" s="4" t="s">
         <v>372</v>
@@ -37704,11 +37707,11 @@
         <v>107</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K403" s="4"/>
       <c r="L403" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="M403" s="4" t="s">
         <v>514</v>
@@ -37717,11 +37720,11 @@
         <v>9</v>
       </c>
       <c r="O403" s="4" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="P403" s="5"/>
       <c r="Q403" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="R403" s="4" t="s">
         <v>60</v>
@@ -37742,7 +37745,7 @@
       </c>
       <c r="Y403" s="4"/>
       <c r="Z403" s="4" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="AA403" s="4"/>
       <c r="AB403" s="4" t="s">
@@ -37778,24 +37781,24 @@
         <v>107</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="K404" s="4"/>
       <c r="L404" s="4" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="M404" s="4" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="N404" s="4">
         <v>23</v>
       </c>
       <c r="O404" s="4" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="P404" s="5"/>
       <c r="Q404" s="4" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="R404" s="4" t="s">
         <v>60</v>
@@ -37816,7 +37819,7 @@
       </c>
       <c r="Y404" s="4"/>
       <c r="Z404" s="4" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AA404" s="4" t="s">
         <v>714</v>
@@ -37854,24 +37857,24 @@
         <v>107</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="K405" s="4"/>
       <c r="L405" s="4" t="s">
         <v>758</v>
       </c>
       <c r="M405" s="4" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="N405" s="4">
         <v>16</v>
       </c>
       <c r="O405" s="4" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="P405" s="5"/>
       <c r="Q405" s="4" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="R405" s="4" t="s">
         <v>69</v>
@@ -37883,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="U405" s="4" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="V405" s="4" t="s">
         <v>152</v>
@@ -37896,7 +37899,7 @@
       </c>
       <c r="Y405" s="4"/>
       <c r="Z405" s="4" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="AA405" s="4" t="s">
         <v>46</v>
@@ -37934,22 +37937,22 @@
         <v>107</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K406" s="4"/>
       <c r="L406" s="4" t="s">
         <v>408</v>
       </c>
       <c r="M406" s="4" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="N406" s="4"/>
       <c r="O406" s="4" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="P406" s="5"/>
       <c r="Q406" s="4" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="R406" s="4" t="s">
         <v>69</v>
@@ -37961,7 +37964,7 @@
         <v>0</v>
       </c>
       <c r="U406" s="4" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="V406" s="4" t="s">
         <v>222</v>
@@ -37974,7 +37977,7 @@
       </c>
       <c r="Y406" s="4"/>
       <c r="Z406" s="4" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AA406" s="4" t="s">
         <v>56</v>
@@ -38012,22 +38015,22 @@
         <v>107</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K407" s="4"/>
       <c r="L407" s="4" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="M407" s="4" t="s">
         <v>52</v>
       </c>
       <c r="N407" s="4"/>
       <c r="O407" s="4" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="P407" s="5"/>
       <c r="Q407" s="4" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="R407" s="4" t="s">
         <v>69</v>
@@ -38048,7 +38051,7 @@
       </c>
       <c r="Y407" s="4"/>
       <c r="Z407" s="4" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="AA407" s="4"/>
       <c r="AB407" s="4" t="s">
@@ -38084,11 +38087,11 @@
         <v>107</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K408" s="4"/>
       <c r="L408" s="4" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="M408" s="4" t="s">
         <v>52</v>
@@ -38097,11 +38100,11 @@
         <v>18</v>
       </c>
       <c r="O408" s="4" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="P408" s="5"/>
       <c r="Q408" s="4" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="R408" s="4" t="s">
         <v>60</v>
@@ -38160,11 +38163,11 @@
         <v>107</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K409" s="4"/>
       <c r="L409" s="4" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="M409" s="4" t="s">
         <v>52</v>
@@ -38173,11 +38176,11 @@
         <v>48</v>
       </c>
       <c r="O409" s="4" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="R409" s="4" t="s">
         <v>60</v>
@@ -38198,7 +38201,7 @@
       </c>
       <c r="Y409" s="4"/>
       <c r="Z409" s="4" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="AA409" s="4" t="s">
         <v>56</v>
@@ -38236,22 +38239,22 @@
         <v>107</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K410" s="4"/>
       <c r="L410" s="4" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="M410" s="4" t="s">
         <v>52</v>
       </c>
       <c r="N410" s="4"/>
       <c r="O410" s="4" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="R410" s="4" t="s">
         <v>69</v>
@@ -38272,7 +38275,7 @@
       </c>
       <c r="Y410" s="4"/>
       <c r="Z410" s="4" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="AA410" s="4" t="s">
         <v>714</v>
@@ -38310,24 +38313,24 @@
         <v>107</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="K411" s="4"/>
       <c r="L411" s="4" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="M411" s="4" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="N411" s="4">
         <v>31</v>
       </c>
       <c r="O411" s="4" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="P411" s="5"/>
       <c r="Q411" s="4" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="R411" s="4" t="s">
         <v>69</v>
@@ -38339,7 +38342,7 @@
         <v>0</v>
       </c>
       <c r="U411" s="4" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="V411" s="4" t="s">
         <v>43</v>
@@ -38390,7 +38393,7 @@
         <v>107</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="K412" s="4"/>
       <c r="L412" s="4" t="s">
@@ -38403,11 +38406,11 @@
         <v>70</v>
       </c>
       <c r="O412" s="4" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="P412" s="5"/>
       <c r="Q412" s="4" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="R412" s="4" t="s">
         <v>41</v>
@@ -38419,7 +38422,7 @@
         <v>2</v>
       </c>
       <c r="U412" s="4" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="V412" s="4" t="s">
         <v>152</v>
@@ -38468,7 +38471,7 @@
         <v>107</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="K413" s="4"/>
       <c r="L413" s="4" t="s">
@@ -38481,11 +38484,11 @@
         <v>70</v>
       </c>
       <c r="O413" s="4" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="P413" s="5"/>
       <c r="Q413" s="4" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="R413" s="4" t="s">
         <v>41</v>
@@ -38497,7 +38500,7 @@
         <v>0</v>
       </c>
       <c r="U413" s="4" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="V413" s="4" t="s">
         <v>137</v>
@@ -38546,7 +38549,7 @@
         <v>107</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="K414" s="4"/>
       <c r="L414" s="4" t="s">
@@ -38559,11 +38562,11 @@
         <v>82</v>
       </c>
       <c r="O414" s="4" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="P414" s="5"/>
       <c r="Q414" s="4" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="R414" s="4" t="s">
         <v>41</v>
@@ -38575,7 +38578,7 @@
         <v>0</v>
       </c>
       <c r="U414" s="4" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="V414" s="4" t="s">
         <v>80</v>
@@ -38623,10 +38626,10 @@
         <v>107</v>
       </c>
       <c r="I415" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K415" s="4"/>
       <c r="L415" s="4" t="s">
@@ -38637,11 +38640,11 @@
       </c>
       <c r="N415" s="4"/>
       <c r="O415" s="4" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="P415" s="5"/>
       <c r="Q415" s="4" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="R415" s="4" t="s">
         <v>41</v>
@@ -38653,7 +38656,7 @@
         <v>0</v>
       </c>
       <c r="U415" s="4" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="V415" s="4" t="s">
         <v>1131</v>
@@ -38666,7 +38669,7 @@
       </c>
       <c r="Y415" s="4"/>
       <c r="Z415" s="4" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="AA415" s="4" t="s">
         <v>56</v>
@@ -38701,10 +38704,10 @@
         <v>107</v>
       </c>
       <c r="I416" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K416" s="4"/>
       <c r="L416" s="4" t="s">
@@ -38715,11 +38718,11 @@
       </c>
       <c r="N416" s="4"/>
       <c r="O416" s="4" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="P416" s="5"/>
       <c r="Q416" s="4" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="R416" s="4" t="s">
         <v>69</v>
@@ -38731,7 +38734,7 @@
         <v>0</v>
       </c>
       <c r="U416" s="4" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="V416" s="4" t="s">
         <v>1131</v>
@@ -38744,7 +38747,7 @@
       </c>
       <c r="Y416" s="4"/>
       <c r="Z416" s="4" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="AA416" s="4" t="s">
         <v>56</v>
@@ -38779,25 +38782,25 @@
         <v>107</v>
       </c>
       <c r="I417" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K417" s="4"/>
       <c r="L417" s="4" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="M417" s="4" t="s">
         <v>747</v>
       </c>
       <c r="N417" s="4"/>
       <c r="O417" s="4" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="P417" s="5"/>
       <c r="Q417" s="4" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="R417" s="4" t="s">
         <v>69</v>
@@ -38809,7 +38812,7 @@
         <v>0</v>
       </c>
       <c r="U417" s="4" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="V417" s="4" t="s">
         <v>180</v>
@@ -38857,10 +38860,10 @@
         <v>107</v>
       </c>
       <c r="I418" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K418" s="4"/>
       <c r="L418" s="4" t="s">
@@ -38871,11 +38874,11 @@
       </c>
       <c r="N418" s="4"/>
       <c r="O418" s="4" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="P418" s="5"/>
       <c r="Q418" s="4" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="R418" s="4" t="s">
         <v>41</v>
@@ -38887,7 +38890,7 @@
         <v>59</v>
       </c>
       <c r="U418" s="4" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="V418" s="4" t="s">
         <v>137</v>
@@ -38933,25 +38936,25 @@
         <v>107</v>
       </c>
       <c r="I419" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K419" s="4"/>
       <c r="L419" s="4" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="M419" s="4" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="N419" s="4"/>
       <c r="O419" s="4" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="R419" s="4" t="s">
         <v>69</v>
@@ -38963,7 +38966,7 @@
         <v>0</v>
       </c>
       <c r="U419" s="4" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="V419" s="4" t="s">
         <v>197</v>
@@ -38976,7 +38979,7 @@
       </c>
       <c r="Y419" s="4"/>
       <c r="Z419" s="4" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="AA419" s="4" t="s">
         <v>966</v>
@@ -39011,25 +39014,25 @@
         <v>107</v>
       </c>
       <c r="I420" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K420" s="4"/>
       <c r="L420" s="4" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="M420" s="4" t="s">
         <v>527</v>
       </c>
       <c r="N420" s="4"/>
       <c r="O420" s="4" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="R420" s="4" t="s">
         <v>41</v>
@@ -39050,7 +39053,7 @@
       </c>
       <c r="Y420" s="4"/>
       <c r="Z420" s="4" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="AA420" s="4" t="s">
         <v>46</v>
@@ -39085,14 +39088,14 @@
         <v>107</v>
       </c>
       <c r="I421" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K421" s="4"/>
       <c r="L421" s="4" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="M421" s="4" t="s">
         <v>527</v>
@@ -39101,11 +39104,11 @@
         <v>165</v>
       </c>
       <c r="O421" s="4" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="P421" s="5"/>
       <c r="Q421" s="4" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="R421" s="4" t="s">
         <v>41</v>
@@ -39161,10 +39164,10 @@
         <v>107</v>
       </c>
       <c r="I422" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K422" s="4"/>
       <c r="L422" s="4" t="s">
@@ -39177,11 +39180,11 @@
         <v>10</v>
       </c>
       <c r="O422" s="4" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="P422" s="5"/>
       <c r="Q422" s="4" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="R422" s="4" t="s">
         <v>41</v>
@@ -39193,10 +39196,10 @@
         <v>0</v>
       </c>
       <c r="U422" s="4" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="V422" s="4" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="W422" s="4">
         <v>8</v>
@@ -39241,10 +39244,10 @@
         <v>107</v>
       </c>
       <c r="I423" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K423" s="4"/>
       <c r="L423" s="4" t="s">
@@ -39255,11 +39258,11 @@
       </c>
       <c r="N423" s="4"/>
       <c r="O423" s="4" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="P423" s="5"/>
       <c r="Q423" s="4" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="R423" s="4" t="s">
         <v>41</v>
@@ -39271,7 +39274,7 @@
         <v>0</v>
       </c>
       <c r="U423" s="4" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="V423" s="4" t="s">
         <v>289</v>
@@ -39284,7 +39287,7 @@
       </c>
       <c r="Y423" s="4"/>
       <c r="Z423" s="4" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="AA423" s="4" t="s">
         <v>56</v>
@@ -39319,10 +39322,10 @@
         <v>107</v>
       </c>
       <c r="I424" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K424" s="4"/>
       <c r="L424" s="4" t="s">
@@ -39335,11 +39338,11 @@
         <v>114</v>
       </c>
       <c r="O424" s="4" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="P424" s="5"/>
       <c r="Q424" s="4" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="R424" s="4" t="s">
         <v>41</v>
@@ -39360,7 +39363,7 @@
       </c>
       <c r="Y424" s="4"/>
       <c r="Z424" s="4" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="AA424" s="4" t="s">
         <v>56</v>
@@ -39398,24 +39401,24 @@
         <v>107</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="K425" s="4"/>
       <c r="L425" s="4" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="M425" s="4" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="N425" s="4">
         <v>74</v>
       </c>
       <c r="O425" s="4" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="P425" s="5"/>
       <c r="Q425" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="R425" s="4" t="s">
         <v>195</v>
@@ -39427,10 +39430,10 @@
         <v>0</v>
       </c>
       <c r="U425" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="V425" s="4" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="W425" s="4">
         <v>4</v>
@@ -39440,7 +39443,7 @@
       </c>
       <c r="Y425" s="4"/>
       <c r="Z425" s="4" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="AA425" s="4" t="s">
         <v>46</v>
@@ -39478,18 +39481,18 @@
         <v>418</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="K426" s="4"/>
       <c r="L426" s="4"/>
       <c r="M426" s="4"/>
       <c r="N426" s="4"/>
       <c r="O426" s="4" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="P426" s="5"/>
       <c r="Q426" s="4" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="R426" s="4" t="s">
         <v>41</v>
@@ -39501,7 +39504,7 @@
         <v>0</v>
       </c>
       <c r="U426" s="4" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="V426" s="4" t="s">
         <v>180</v>
@@ -39514,7 +39517,7 @@
       </c>
       <c r="Y426" s="4"/>
       <c r="Z426" s="4" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="AA426" s="4" t="s">
         <v>714</v>
@@ -39552,18 +39555,18 @@
         <v>107</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K427" s="4"/>
       <c r="L427" s="4"/>
       <c r="M427" s="4"/>
       <c r="N427" s="4"/>
       <c r="O427" s="4" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="P427" s="5"/>
       <c r="Q427" s="4" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="R427" s="4" t="s">
         <v>41</v>
@@ -39584,7 +39587,7 @@
       </c>
       <c r="Y427" s="4"/>
       <c r="Z427" s="4" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="AA427" s="4"/>
       <c r="AB427" s="4" t="s">
@@ -39620,18 +39623,18 @@
         <v>107</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K428" s="4"/>
       <c r="L428" s="4"/>
       <c r="M428" s="4"/>
       <c r="N428" s="4"/>
       <c r="O428" s="4" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="P428" s="5"/>
       <c r="Q428" s="4" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="R428" s="4" t="s">
         <v>41</v>
@@ -39652,7 +39655,7 @@
       </c>
       <c r="Y428" s="4"/>
       <c r="Z428" s="4" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="AA428" s="4"/>
       <c r="AB428" s="4" t="s">
@@ -39688,7 +39691,7 @@
         <v>107</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K429" s="4"/>
       <c r="L429" s="4" t="s">
@@ -39697,11 +39700,11 @@
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
       <c r="O429" s="4" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="P429" s="5"/>
       <c r="Q429" s="4" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="R429" s="4" t="s">
         <v>41</v>
@@ -39713,10 +39716,10 @@
         <v>1</v>
       </c>
       <c r="U429" s="4" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="V429" s="4" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="W429" s="4">
         <v>2</v>
@@ -39764,7 +39767,7 @@
         <v>107</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K430" s="4"/>
       <c r="L430" s="4" t="s">
@@ -39773,11 +39776,11 @@
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
       <c r="O430" s="4" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="P430" s="5"/>
       <c r="Q430" s="4" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="R430" s="4" t="s">
         <v>41</v>
@@ -39789,7 +39792,7 @@
         <v>0</v>
       </c>
       <c r="U430" s="4" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="V430" s="4" t="s">
         <v>162</v>
@@ -39838,7 +39841,7 @@
         <v>107</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K431" s="4"/>
       <c r="L431" s="4" t="s">
@@ -39847,11 +39850,11 @@
       <c r="M431" s="4"/>
       <c r="N431" s="4"/>
       <c r="O431" s="4" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="P431" s="5"/>
       <c r="Q431" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="R431" s="4" t="s">
         <v>41</v>
@@ -39863,7 +39866,7 @@
         <v>1</v>
       </c>
       <c r="U431" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="V431" s="4" t="s">
         <v>162</v>
@@ -39914,7 +39917,7 @@
         <v>107</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K432" s="4"/>
       <c r="L432" s="4" t="s">
@@ -39923,11 +39926,11 @@
       <c r="M432" s="4"/>
       <c r="N432" s="4"/>
       <c r="O432" s="4" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="P432" s="5"/>
       <c r="Q432" s="4" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="R432" s="4" t="s">
         <v>41</v>
@@ -39939,7 +39942,7 @@
         <v>0</v>
       </c>
       <c r="U432" s="4" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="V432" s="4" t="s">
         <v>627</v>
@@ -39952,7 +39955,7 @@
       </c>
       <c r="Y432" s="4"/>
       <c r="Z432" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AA432" s="4" t="s">
         <v>56</v>
@@ -39990,7 +39993,7 @@
         <v>107</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="K433" s="4"/>
       <c r="L433" s="4" t="s">
@@ -39999,11 +40002,11 @@
       <c r="M433" s="4"/>
       <c r="N433" s="4"/>
       <c r="O433" s="4" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="P433" s="5"/>
       <c r="Q433" s="4" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="R433" s="4" t="s">
         <v>41</v>
@@ -40024,7 +40027,7 @@
       </c>
       <c r="Y433" s="4"/>
       <c r="Z433" s="4" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="AA433" s="4" t="s">
         <v>46</v>
@@ -40062,7 +40065,7 @@
         <v>107</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="K434" s="4"/>
       <c r="L434" s="4" t="s">
@@ -40071,11 +40074,11 @@
       <c r="M434" s="4"/>
       <c r="N434" s="4"/>
       <c r="O434" s="4" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="P434" s="5"/>
       <c r="Q434" s="4" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="R434" s="4" t="s">
         <v>41</v>
@@ -40087,7 +40090,7 @@
         <v>0</v>
       </c>
       <c r="U434" s="4" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="V434" s="4" t="s">
         <v>162</v>
@@ -40138,7 +40141,7 @@
         <v>107</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="K435" s="4"/>
       <c r="L435" s="4" t="s">
@@ -40147,11 +40150,11 @@
       <c r="M435" s="4"/>
       <c r="N435" s="4"/>
       <c r="O435" s="4" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="P435" s="5"/>
       <c r="Q435" s="4" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="R435" s="4" t="s">
         <v>41</v>
@@ -40163,7 +40166,7 @@
         <v>1</v>
       </c>
       <c r="U435" s="4" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="V435" s="4" t="s">
         <v>137</v>
@@ -40214,7 +40217,7 @@
         <v>107</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="K436" s="4"/>
       <c r="L436" s="4" t="s">
@@ -40223,11 +40226,11 @@
       <c r="M436" s="4"/>
       <c r="N436" s="4"/>
       <c r="O436" s="4" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="P436" s="5"/>
       <c r="Q436" s="4" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="R436" s="4" t="s">
         <v>41</v>
@@ -40239,7 +40242,7 @@
         <v>4</v>
       </c>
       <c r="U436" s="4" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="V436" s="4" t="s">
         <v>540</v>
@@ -40290,18 +40293,18 @@
         <v>107</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="K437" s="4"/>
       <c r="L437" s="4"/>
       <c r="M437" s="4"/>
       <c r="N437" s="4"/>
       <c r="O437" s="4" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="P437" s="5"/>
       <c r="Q437" s="4" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="R437" s="4" t="s">
         <v>41</v>
@@ -40358,22 +40361,22 @@
         <v>107</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="K438" s="4"/>
       <c r="L438" s="4" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="M438" s="4" t="s">
         <v>789</v>
       </c>
       <c r="N438" s="4"/>
       <c r="O438" s="4" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="P438" s="5"/>
       <c r="Q438" s="4" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="R438" s="4" t="s">
         <v>41</v>
@@ -40385,10 +40388,10 @@
         <v>0</v>
       </c>
       <c r="U438" s="4" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="V438" s="4" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="W438" s="4">
         <v>2</v>
@@ -40398,7 +40401,7 @@
       </c>
       <c r="Y438" s="4"/>
       <c r="Z438" s="4" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="AA438" s="4"/>
       <c r="AB438" s="4" t="s">
@@ -40434,7 +40437,7 @@
         <v>107</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="K439" s="4"/>
       <c r="L439" s="4" t="s">
@@ -40443,11 +40446,11 @@
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
       <c r="O439" s="4" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="P439" s="5"/>
       <c r="Q439" s="4" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="R439" s="4" t="s">
         <v>41</v>
@@ -40459,7 +40462,7 @@
         <v>0</v>
       </c>
       <c r="U439" s="4" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="V439" s="4" t="s">
         <v>180</v>
@@ -40472,7 +40475,7 @@
       </c>
       <c r="Y439" s="4"/>
       <c r="Z439" s="4" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="AA439" s="4" t="s">
         <v>56</v>
@@ -40510,7 +40513,7 @@
         <v>107</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="K440" s="4"/>
       <c r="L440" s="4" t="s">
@@ -40519,11 +40522,11 @@
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
       <c r="O440" s="4" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="P440" s="5"/>
       <c r="Q440" s="4" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="R440" s="4" t="s">
         <v>41</v>
@@ -40580,7 +40583,7 @@
         <v>107</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="K441" s="4"/>
       <c r="L441" s="4" t="s">
@@ -40593,11 +40596,11 @@
         <v>20</v>
       </c>
       <c r="O441" s="4" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="P441" s="5"/>
       <c r="Q441" s="4" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="R441" s="4" t="s">
         <v>41</v>
@@ -40656,7 +40659,7 @@
         <v>107</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="K442" s="4"/>
       <c r="L442" s="4" t="s">
@@ -40669,11 +40672,11 @@
         <v>6</v>
       </c>
       <c r="O442" s="4" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="P442" s="5"/>
       <c r="Q442" s="4" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="R442" s="4" t="s">
         <v>69</v>
@@ -40732,7 +40735,7 @@
         <v>107</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="K443" s="4"/>
       <c r="L443" s="4" t="s">
@@ -40741,11 +40744,11 @@
       <c r="M443" s="4"/>
       <c r="N443" s="4"/>
       <c r="O443" s="4" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="P443" s="5"/>
       <c r="Q443" s="4" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="R443" s="4" t="s">
         <v>69</v>
@@ -40757,7 +40760,7 @@
         <v>0</v>
       </c>
       <c r="U443" s="4" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="V443" s="4" t="s">
         <v>289</v>
@@ -40806,7 +40809,7 @@
         <v>107</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="K444" s="4"/>
       <c r="L444" s="4" t="s">
@@ -40815,11 +40818,11 @@
       <c r="M444" s="4"/>
       <c r="N444" s="4"/>
       <c r="O444" s="4" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="P444" s="5"/>
       <c r="Q444" s="4" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="R444" s="4" t="s">
         <v>60</v>
@@ -40831,7 +40834,7 @@
         <v>0</v>
       </c>
       <c r="U444" s="4" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="V444" s="4" t="s">
         <v>180</v>
@@ -40844,7 +40847,7 @@
       </c>
       <c r="Y444" s="4"/>
       <c r="Z444" s="4" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="AA444" s="4" t="s">
         <v>46</v>
@@ -40882,18 +40885,18 @@
         <v>107</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="K445" s="4"/>
       <c r="L445" s="4"/>
       <c r="M445" s="4"/>
       <c r="N445" s="4"/>
       <c r="O445" s="4" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="P445" s="5"/>
       <c r="Q445" s="4" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="R445" s="4" t="s">
         <v>69</v>
@@ -40914,7 +40917,7 @@
       </c>
       <c r="Y445" s="4"/>
       <c r="Z445" s="4" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="AA445" s="4"/>
       <c r="AB445" s="4" t="s">
@@ -40950,18 +40953,18 @@
         <v>107</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="K446" s="4"/>
       <c r="L446" s="4"/>
       <c r="M446" s="4"/>
       <c r="N446" s="4"/>
       <c r="O446" s="4" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="P446" s="5"/>
       <c r="Q446" s="4" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="R446" s="4" t="s">
         <v>69</v>
@@ -40982,7 +40985,7 @@
       </c>
       <c r="Y446" s="4"/>
       <c r="Z446" s="4" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA446" s="4"/>
       <c r="AB446" s="4" t="s">
@@ -41018,7 +41021,7 @@
         <v>107</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="K447" s="4"/>
       <c r="L447" s="4" t="s">
@@ -41027,11 +41030,11 @@
       <c r="M447" s="4"/>
       <c r="N447" s="4"/>
       <c r="O447" s="4" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="P447" s="5"/>
       <c r="Q447" s="4" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="R447" s="4" t="s">
         <v>41</v>
@@ -41043,7 +41046,7 @@
         <v>1</v>
       </c>
       <c r="U447" s="4" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="V447" s="4" t="s">
         <v>197</v>
@@ -41094,7 +41097,7 @@
         <v>107</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="K448" s="4"/>
       <c r="L448" s="4" t="s">
@@ -41103,11 +41106,11 @@
       <c r="M448" s="4"/>
       <c r="N448" s="4"/>
       <c r="O448" s="4" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="P448" s="5"/>
       <c r="Q448" s="4" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="R448" s="4" t="s">
         <v>60</v>
@@ -41128,7 +41131,7 @@
       </c>
       <c r="Y448" s="4"/>
       <c r="Z448" s="4" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="AA448" s="4" t="s">
         <v>46</v>
@@ -41166,7 +41169,7 @@
         <v>107</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="K449" s="4"/>
       <c r="L449" s="4" t="s">
@@ -41175,11 +41178,11 @@
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
       <c r="O449" s="4" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="P449" s="5"/>
       <c r="Q449" s="4" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="R449" s="4" t="s">
         <v>60</v>
@@ -41200,7 +41203,7 @@
       </c>
       <c r="Y449" s="4"/>
       <c r="Z449" s="4" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="AA449" s="4" t="s">
         <v>56</v>
@@ -41238,7 +41241,7 @@
         <v>107</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="K450" s="4"/>
       <c r="L450" s="4" t="s">
@@ -41247,11 +41250,11 @@
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
       <c r="O450" s="4" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="P450" s="5"/>
       <c r="Q450" s="4" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="R450" s="4" t="s">
         <v>60</v>
@@ -41263,7 +41266,7 @@
         <v>0</v>
       </c>
       <c r="U450" s="4" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="V450" s="4" t="s">
         <v>197</v>
@@ -41276,7 +41279,7 @@
       </c>
       <c r="Y450" s="4"/>
       <c r="Z450" s="4" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="AA450" s="4" t="s">
         <v>46</v>
@@ -41314,24 +41317,24 @@
         <v>107</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="K451" s="4"/>
       <c r="L451" s="4" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="M451" s="4" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="N451" s="4">
         <v>12</v>
       </c>
       <c r="O451" s="4" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="P451" s="5"/>
       <c r="Q451" s="4" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="R451" s="4" t="s">
         <v>41</v>
@@ -41343,10 +41346,10 @@
         <v>0</v>
       </c>
       <c r="U451" s="4" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="V451" s="4" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="W451" s="4">
         <v>7</v>
@@ -41356,7 +41359,7 @@
       </c>
       <c r="Y451" s="4"/>
       <c r="Z451" s="4" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="AA451" s="4" t="s">
         <v>56</v>
@@ -41394,18 +41397,18 @@
         <v>107</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K452" s="4"/>
       <c r="L452" s="4"/>
       <c r="M452" s="4"/>
       <c r="N452" s="4"/>
       <c r="O452" s="4" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="P452" s="5"/>
       <c r="Q452" s="4" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="R452" s="4" t="s">
         <v>41</v>
@@ -41417,7 +41420,7 @@
         <v>0</v>
       </c>
       <c r="U452" s="4" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="V452" s="4" t="s">
         <v>43</v>
@@ -41468,18 +41471,18 @@
         <v>107</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K453" s="4"/>
       <c r="L453" s="4"/>
       <c r="M453" s="4"/>
       <c r="N453" s="4"/>
       <c r="O453" s="4" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="P453" s="5"/>
       <c r="Q453" s="4" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="R453" s="4" t="s">
         <v>41</v>
@@ -41491,7 +41494,7 @@
         <v>0</v>
       </c>
       <c r="U453" s="4" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="V453" s="4" t="s">
         <v>197</v>
@@ -41542,18 +41545,18 @@
         <v>107</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K454" s="4"/>
       <c r="L454" s="4"/>
       <c r="M454" s="4"/>
       <c r="N454" s="4"/>
       <c r="O454" s="4" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="P454" s="5"/>
       <c r="Q454" s="4" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="R454" s="4" t="s">
         <v>69</v>
@@ -41565,7 +41568,7 @@
         <v>0</v>
       </c>
       <c r="U454" s="4" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="V454" s="4" t="s">
         <v>627</v>
@@ -41578,7 +41581,7 @@
       </c>
       <c r="Y454" s="4"/>
       <c r="Z454" s="4" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="AA454" s="4" t="s">
         <v>56</v>
@@ -41616,7 +41619,7 @@
         <v>107</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K455" s="4"/>
       <c r="L455" s="4" t="s">
@@ -41625,11 +41628,11 @@
       <c r="M455" s="4"/>
       <c r="N455" s="4"/>
       <c r="O455" s="4" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="P455" s="5"/>
       <c r="Q455" s="4" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="R455" s="4" t="s">
         <v>41</v>
@@ -41641,7 +41644,7 @@
         <v>0</v>
       </c>
       <c r="U455" s="4" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="V455" s="4" t="s">
         <v>137</v>
@@ -41692,7 +41695,7 @@
         <v>107</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K456" s="4"/>
       <c r="L456" s="4" t="s">
@@ -41701,11 +41704,11 @@
       <c r="M456" s="4"/>
       <c r="N456" s="4"/>
       <c r="O456" s="4" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="P456" s="5"/>
       <c r="Q456" s="4" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="R456" s="4" t="s">
         <v>41</v>
@@ -41717,7 +41720,7 @@
         <v>0</v>
       </c>
       <c r="U456" s="4" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="V456" s="4" t="s">
         <v>180</v>
@@ -41768,24 +41771,24 @@
         <v>107</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="K457" s="4"/>
       <c r="L457" s="4" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="M457" s="4" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="N457" s="4">
         <v>6</v>
       </c>
       <c r="O457" s="4" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="P457" s="5"/>
       <c r="Q457" s="4" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="R457" s="4" t="s">
         <v>41</v>
@@ -41797,7 +41800,7 @@
         <v>1</v>
       </c>
       <c r="U457" s="4" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="V457" s="4" t="s">
         <v>137</v>
@@ -41848,24 +41851,24 @@
         <v>107</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="K458" s="4"/>
       <c r="L458" s="4" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M458" s="4" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="N458" s="4">
         <v>65</v>
       </c>
       <c r="O458" s="4" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="P458" s="5"/>
       <c r="Q458" s="4" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="R458" s="4" t="s">
         <v>69</v>
@@ -41924,24 +41927,24 @@
         <v>107</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="K459" s="4"/>
       <c r="L459" s="4" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="M459" s="4" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="N459" s="4">
         <v>7</v>
       </c>
       <c r="O459" s="4" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="P459" s="5"/>
       <c r="Q459" s="4" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="R459" s="4" t="s">
         <v>69</v>
@@ -42000,18 +42003,18 @@
         <v>107</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="K460" s="4"/>
       <c r="L460" s="4"/>
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
       <c r="O460" s="4" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="P460" s="5"/>
       <c r="Q460" s="4" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="R460" s="4" t="s">
         <v>60</v>
@@ -42032,7 +42035,7 @@
       </c>
       <c r="Y460" s="4"/>
       <c r="Z460" s="4" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="AA460" s="4"/>
       <c r="AB460" s="4" t="s">
@@ -42068,18 +42071,18 @@
         <v>107</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="K461" s="4"/>
       <c r="L461" s="4"/>
       <c r="M461" s="4"/>
       <c r="N461" s="4"/>
       <c r="O461" s="4" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="P461" s="5"/>
       <c r="Q461" s="4" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="R461" s="4" t="s">
         <v>60</v>
@@ -42100,7 +42103,7 @@
       </c>
       <c r="Y461" s="4"/>
       <c r="Z461" s="4" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA461" s="4"/>
       <c r="AB461" s="4" t="s">
@@ -42136,18 +42139,18 @@
         <v>107</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="K462" s="4"/>
       <c r="L462" s="4"/>
       <c r="M462" s="4"/>
       <c r="N462" s="4"/>
       <c r="O462" s="4" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="P462" s="5"/>
       <c r="Q462" s="4" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="R462" s="4" t="s">
         <v>60</v>
@@ -42168,7 +42171,7 @@
       </c>
       <c r="Y462" s="4"/>
       <c r="Z462" s="4" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="AA462" s="4"/>
       <c r="AB462" s="4" t="s">
@@ -42204,7 +42207,7 @@
         <v>107</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="K463" s="4"/>
       <c r="L463" s="4" t="s">
@@ -42213,11 +42216,11 @@
       <c r="M463" s="4"/>
       <c r="N463" s="4"/>
       <c r="O463" s="4" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="P463" s="5"/>
       <c r="Q463" s="4" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="R463" s="4" t="s">
         <v>69</v>
@@ -42229,7 +42232,7 @@
         <v>2</v>
       </c>
       <c r="U463" s="4" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="V463" s="4" t="s">
         <v>43</v>
@@ -42278,7 +42281,7 @@
         <v>107</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="K464" s="4"/>
       <c r="L464" s="4" t="s">
@@ -42287,11 +42290,11 @@
       <c r="M464" s="4"/>
       <c r="N464" s="4"/>
       <c r="O464" s="4" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="P464" s="5"/>
       <c r="Q464" s="4" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="R464" s="4" t="s">
         <v>69</v>
@@ -42312,7 +42315,7 @@
       </c>
       <c r="Y464" s="4"/>
       <c r="Z464" s="4" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AA464" s="4" t="s">
         <v>46</v>
@@ -42350,24 +42353,24 @@
         <v>107</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="K465" s="4"/>
       <c r="L465" s="4" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="M465" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="N465" s="4">
         <v>36</v>
       </c>
       <c r="O465" s="4" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="P465" s="5"/>
       <c r="Q465" s="4" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="R465" s="4" t="s">
         <v>41</v>
@@ -42388,7 +42391,7 @@
       </c>
       <c r="Y465" s="4"/>
       <c r="Z465" s="4" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="AA465" s="4" t="s">
         <v>46</v>
@@ -42426,24 +42429,24 @@
         <v>107</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="K466" s="4"/>
       <c r="L466" s="4" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="M466" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="N466" s="4">
         <v>48</v>
       </c>
       <c r="O466" s="4" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="P466" s="5"/>
       <c r="Q466" s="4" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="R466" s="4" t="s">
         <v>41</v>
@@ -42464,7 +42467,7 @@
       </c>
       <c r="Y466" s="4"/>
       <c r="Z466" s="4" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="AA466" s="4"/>
       <c r="AB466" s="4" t="s">
@@ -42500,11 +42503,11 @@
         <v>107</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="K467" s="4"/>
       <c r="L467" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="M467" s="4" t="s">
         <v>241</v>
@@ -42513,11 +42516,11 @@
         <v>52</v>
       </c>
       <c r="O467" s="4" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="P467" s="5"/>
       <c r="Q467" s="4" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="R467" s="4" t="s">
         <v>41</v>
@@ -42529,7 +42532,7 @@
         <v>2</v>
       </c>
       <c r="U467" s="4" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="V467" s="4" t="s">
         <v>162</v>
@@ -42578,24 +42581,24 @@
         <v>107</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="K468" s="4"/>
       <c r="L468" s="4" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="M468" s="4" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="N468" s="4">
         <v>45</v>
       </c>
       <c r="O468" s="4" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="P468" s="5"/>
       <c r="Q468" s="4" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="R468" s="4" t="s">
         <v>69</v>
@@ -42616,7 +42619,7 @@
       </c>
       <c r="Y468" s="4"/>
       <c r="Z468" s="4" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="AA468" s="4" t="s">
         <v>46</v>
@@ -42654,7 +42657,7 @@
         <v>107</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="K469" s="4"/>
       <c r="L469" s="4" t="s">
@@ -42663,11 +42666,11 @@
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
       <c r="O469" s="4" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="P469" s="5"/>
       <c r="Q469" s="4" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="R469" s="4" t="s">
         <v>60</v>
@@ -42679,7 +42682,7 @@
         <v>0</v>
       </c>
       <c r="U469" s="4" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="V469" s="4" t="s">
         <v>289</v>
@@ -42692,7 +42695,7 @@
       </c>
       <c r="Y469" s="4"/>
       <c r="Z469" s="4" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="AA469" s="4" t="s">
         <v>46</v>
@@ -42730,7 +42733,7 @@
         <v>107</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="K470" s="4"/>
       <c r="L470" s="4" t="s">
@@ -42739,11 +42742,11 @@
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
       <c r="O470" s="4" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="P470" s="5"/>
       <c r="Q470" s="4" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="R470" s="4" t="s">
         <v>60</v>
@@ -42755,7 +42758,7 @@
         <v>0</v>
       </c>
       <c r="U470" s="4" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="V470" s="4" t="s">
         <v>289</v>
@@ -42768,7 +42771,7 @@
       </c>
       <c r="Y470" s="4"/>
       <c r="Z470" s="4" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="AA470" s="4" t="s">
         <v>46</v>
@@ -42806,7 +42809,7 @@
         <v>107</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="K471" s="4"/>
       <c r="L471" s="4" t="s">
@@ -42815,11 +42818,11 @@
       <c r="M471" s="4"/>
       <c r="N471" s="4"/>
       <c r="O471" s="4" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="P471" s="5"/>
       <c r="Q471" s="4" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="R471" s="4" t="s">
         <v>60</v>
@@ -42840,7 +42843,7 @@
       </c>
       <c r="Y471" s="4"/>
       <c r="Z471" s="4" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="AA471" s="4" t="s">
         <v>46</v>
@@ -42878,18 +42881,18 @@
         <v>107</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K472" s="4"/>
       <c r="L472" s="4"/>
       <c r="M472" s="4"/>
       <c r="N472" s="4"/>
       <c r="O472" s="4" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="P472" s="5"/>
       <c r="Q472" s="4" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="R472" s="4" t="s">
         <v>69</v>
@@ -42910,7 +42913,7 @@
       </c>
       <c r="Y472" s="4"/>
       <c r="Z472" s="4" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="AA472" s="4"/>
       <c r="AB472" s="4" t="s">
@@ -42946,24 +42949,24 @@
         <v>107</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K473" s="4"/>
       <c r="L473" s="4" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="M473" s="4" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="N473" s="4">
         <v>46</v>
       </c>
       <c r="O473" s="4" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="P473" s="5"/>
       <c r="Q473" s="4" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="R473" s="4" t="s">
         <v>41</v>
@@ -43022,24 +43025,24 @@
         <v>107</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K474" s="4"/>
       <c r="L474" s="4" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="M474" s="4" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="N474" s="4">
         <v>54</v>
       </c>
       <c r="O474" s="4" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="P474" s="5"/>
       <c r="Q474" s="4" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="R474" s="4" t="s">
         <v>41</v>
@@ -43098,24 +43101,24 @@
         <v>107</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K475" s="4"/>
       <c r="L475" s="4" t="s">
         <v>358</v>
       </c>
       <c r="M475" s="4" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="N475" s="4">
         <v>4</v>
       </c>
       <c r="O475" s="4" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="P475" s="5"/>
       <c r="Q475" s="4" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="R475" s="4" t="s">
         <v>41</v>
@@ -43127,7 +43130,7 @@
         <v>0</v>
       </c>
       <c r="U475" s="4" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="V475" s="4" t="s">
         <v>222</v>
@@ -43140,7 +43143,7 @@
       </c>
       <c r="Y475" s="4"/>
       <c r="Z475" s="4" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="AA475" s="4" t="s">
         <v>56</v>
@@ -43178,24 +43181,24 @@
         <v>107</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K476" s="4"/>
       <c r="L476" s="4" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="M476" s="4" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="N476" s="4">
         <v>15</v>
       </c>
       <c r="O476" s="4" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="P476" s="5"/>
       <c r="Q476" s="4" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="R476" s="4" t="s">
         <v>41</v>
@@ -43216,7 +43219,7 @@
       </c>
       <c r="Y476" s="4"/>
       <c r="Z476" s="4" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="AA476" s="4"/>
       <c r="AB476" s="4" t="s">
@@ -43252,24 +43255,24 @@
         <v>107</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K477" s="4"/>
       <c r="L477" s="4" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="M477" s="4" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="N477" s="4">
         <v>30</v>
       </c>
       <c r="O477" s="4" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="P477" s="5"/>
       <c r="Q477" s="4" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="R477" s="4" t="s">
         <v>41</v>
@@ -43328,7 +43331,7 @@
         <v>107</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="K478" s="4"/>
       <c r="L478" s="4" t="s">
@@ -43337,11 +43340,11 @@
       <c r="M478" s="4"/>
       <c r="N478" s="4"/>
       <c r="O478" s="4" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="P478" s="5"/>
       <c r="Q478" s="4" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="R478" s="4" t="s">
         <v>60</v>
@@ -43353,7 +43356,7 @@
         <v>0</v>
       </c>
       <c r="U478" s="4" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="V478" s="4" t="s">
         <v>180</v>
@@ -43366,7 +43369,7 @@
       </c>
       <c r="Y478" s="4"/>
       <c r="Z478" s="4" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AA478" s="4"/>
       <c r="AB478" s="4" t="s">
@@ -43402,24 +43405,24 @@
         <v>107</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="K479" s="4"/>
       <c r="L479" s="4" t="s">
         <v>883</v>
       </c>
       <c r="M479" s="4" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="N479" s="4">
         <v>43</v>
       </c>
       <c r="O479" s="4" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="P479" s="5"/>
       <c r="Q479" s="4" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="R479" s="4" t="s">
         <v>69</v>
@@ -43431,7 +43434,7 @@
         <v>2</v>
       </c>
       <c r="U479" s="4" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="V479" s="4" t="s">
         <v>1057</v>
@@ -43482,22 +43485,22 @@
         <v>107</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="K480" s="4"/>
       <c r="L480" s="4" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="M480" s="4" t="s">
         <v>192</v>
       </c>
       <c r="N480" s="4"/>
       <c r="O480" s="4" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="P480" s="5"/>
       <c r="Q480" s="4" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="R480" s="4" t="s">
         <v>69</v>
@@ -43556,11 +43559,11 @@
         <v>107</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="K481" s="4"/>
       <c r="L481" s="4" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="M481" s="4" t="s">
         <v>365</v>
@@ -43569,11 +43572,11 @@
         <v>22</v>
       </c>
       <c r="O481" s="4" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="P481" s="5"/>
       <c r="Q481" s="4" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="R481" s="4" t="s">
         <v>69</v>
@@ -43594,7 +43597,7 @@
       </c>
       <c r="Y481" s="4"/>
       <c r="Z481" s="4" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AA481" s="4" t="s">
         <v>46</v>
@@ -43632,18 +43635,18 @@
         <v>107</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K482" s="4"/>
       <c r="L482" s="4"/>
       <c r="M482" s="4"/>
       <c r="N482" s="4"/>
       <c r="O482" s="4" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="P482" s="5"/>
       <c r="Q482" s="4" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="R482" s="4" t="s">
         <v>41</v>
@@ -43664,7 +43667,7 @@
       </c>
       <c r="Y482" s="4"/>
       <c r="Z482" s="4" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="AA482" s="4" t="s">
         <v>56</v>
@@ -43702,18 +43705,18 @@
         <v>107</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K483" s="4"/>
       <c r="L483" s="4"/>
       <c r="M483" s="4"/>
       <c r="N483" s="4"/>
       <c r="O483" s="4" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="P483" s="5"/>
       <c r="Q483" s="4" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="R483" s="4" t="s">
         <v>41</v>
@@ -43725,7 +43728,7 @@
         <v>0</v>
       </c>
       <c r="U483" s="4" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="V483" s="4" t="s">
         <v>152</v>
@@ -43738,7 +43741,7 @@
       </c>
       <c r="Y483" s="4"/>
       <c r="Z483" s="4" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="AA483" s="4" t="s">
         <v>56</v>
@@ -43776,18 +43779,18 @@
         <v>107</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K484" s="4"/>
       <c r="L484" s="4"/>
       <c r="M484" s="4"/>
       <c r="N484" s="4"/>
       <c r="O484" s="4" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="P484" s="5"/>
       <c r="Q484" s="4" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="R484" s="4" t="s">
         <v>41</v>
@@ -43846,18 +43849,18 @@
         <v>107</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K485" s="4"/>
       <c r="L485" s="4"/>
       <c r="M485" s="4"/>
       <c r="N485" s="4"/>
       <c r="O485" s="4" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="P485" s="5"/>
       <c r="Q485" s="4" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="R485" s="4" t="s">
         <v>41</v>
@@ -43916,18 +43919,18 @@
         <v>107</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K486" s="4"/>
       <c r="L486" s="4"/>
       <c r="M486" s="4"/>
       <c r="N486" s="4"/>
       <c r="O486" s="4" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="P486" s="5"/>
       <c r="Q486" s="4" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="R486" s="4" t="s">
         <v>41</v>
@@ -43939,7 +43942,7 @@
         <v>0</v>
       </c>
       <c r="U486" s="4" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="V486" s="4" t="s">
         <v>152</v>
@@ -43990,18 +43993,18 @@
         <v>107</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K487" s="4"/>
       <c r="L487" s="4"/>
       <c r="M487" s="4"/>
       <c r="N487" s="4"/>
       <c r="O487" s="4" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="P487" s="5"/>
       <c r="Q487" s="4" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="R487" s="4" t="s">
         <v>41</v>
@@ -44060,18 +44063,18 @@
         <v>107</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K488" s="4"/>
       <c r="L488" s="4"/>
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
       <c r="O488" s="4" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="P488" s="5"/>
       <c r="Q488" s="4" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="R488" s="4" t="s">
         <v>41</v>
@@ -44083,7 +44086,7 @@
         <v>0</v>
       </c>
       <c r="U488" s="4" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="V488" s="4" t="s">
         <v>283</v>
@@ -44134,18 +44137,18 @@
         <v>107</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K489" s="4"/>
       <c r="L489" s="4"/>
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
       <c r="O489" s="4" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="P489" s="5"/>
       <c r="Q489" s="4" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="R489" s="4" t="s">
         <v>41</v>
@@ -44157,7 +44160,7 @@
         <v>2</v>
       </c>
       <c r="U489" s="4" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="V489" s="4" t="s">
         <v>152</v>
@@ -44208,18 +44211,18 @@
         <v>107</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K490" s="4"/>
       <c r="L490" s="4"/>
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
       <c r="O490" s="4" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="P490" s="5"/>
       <c r="Q490" s="4" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="R490" s="4" t="s">
         <v>41</v>
@@ -44231,7 +44234,7 @@
         <v>1</v>
       </c>
       <c r="U490" s="4" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="V490" s="4" t="s">
         <v>152</v>
@@ -44282,18 +44285,18 @@
         <v>107</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K491" s="4"/>
       <c r="L491" s="4"/>
       <c r="M491" s="4"/>
       <c r="N491" s="4"/>
       <c r="O491" s="4" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="P491" s="5"/>
       <c r="Q491" s="4" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="R491" s="4" t="s">
         <v>41</v>
@@ -44314,7 +44317,7 @@
       </c>
       <c r="Y491" s="4"/>
       <c r="Z491" s="4" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="AA491" s="4" t="s">
         <v>56</v>
@@ -44352,18 +44355,18 @@
         <v>107</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K492" s="4"/>
       <c r="L492" s="4"/>
       <c r="M492" s="4"/>
       <c r="N492" s="4"/>
       <c r="O492" s="4" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="P492" s="5"/>
       <c r="Q492" s="4" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="R492" s="4" t="s">
         <v>41</v>
@@ -44375,7 +44378,7 @@
         <v>2</v>
       </c>
       <c r="U492" s="4" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="V492" s="4" t="s">
         <v>152</v>
@@ -44388,7 +44391,7 @@
       </c>
       <c r="Y492" s="4"/>
       <c r="Z492" s="4" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="AA492" s="4" t="s">
         <v>56</v>
@@ -44426,18 +44429,18 @@
         <v>107</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K493" s="4"/>
       <c r="L493" s="4"/>
       <c r="M493" s="4"/>
       <c r="N493" s="4"/>
       <c r="O493" s="4" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="P493" s="5"/>
       <c r="Q493" s="4" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="R493" s="4" t="s">
         <v>60</v>
@@ -44458,7 +44461,7 @@
       </c>
       <c r="Y493" s="4"/>
       <c r="Z493" s="4" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="AA493" s="4" t="s">
         <v>372</v>
@@ -44496,18 +44499,18 @@
         <v>107</v>
       </c>
       <c r="J494" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K494" s="4"/>
       <c r="L494" s="4"/>
       <c r="M494" s="4"/>
       <c r="N494" s="4"/>
       <c r="O494" s="4" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="P494" s="5"/>
       <c r="Q494" s="4" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="R494" s="4" t="s">
         <v>41</v>
@@ -44519,7 +44522,7 @@
         <v>0</v>
       </c>
       <c r="U494" s="4" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="V494" s="4" t="s">
         <v>152</v>
@@ -44532,7 +44535,7 @@
       </c>
       <c r="Y494" s="4"/>
       <c r="Z494" s="4" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="AA494" s="4"/>
       <c r="AB494" s="4" t="s">
@@ -44568,22 +44571,22 @@
         <v>107</v>
       </c>
       <c r="J495" s="4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="K495" s="4"/>
       <c r="L495" s="4" t="s">
         <v>817</v>
       </c>
       <c r="M495" s="4" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="N495" s="4"/>
       <c r="O495" s="4" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="P495" s="5"/>
       <c r="Q495" s="4" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="R495" s="4" t="s">
         <v>60</v>
@@ -44595,7 +44598,7 @@
         <v>0</v>
       </c>
       <c r="U495" s="4" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="V495" s="4" t="s">
         <v>363</v>
@@ -44608,7 +44611,7 @@
       </c>
       <c r="Y495" s="4"/>
       <c r="Z495" s="4" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="AA495" s="4" t="s">
         <v>372</v>
@@ -44646,18 +44649,18 @@
         <v>107</v>
       </c>
       <c r="J496" s="4" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="K496" s="4"/>
       <c r="L496" s="4"/>
       <c r="M496" s="4"/>
       <c r="N496" s="4"/>
       <c r="O496" s="4" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="P496" s="5"/>
       <c r="Q496" s="4" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="R496" s="4" t="s">
         <v>60</v>
@@ -44678,7 +44681,7 @@
       </c>
       <c r="Y496" s="4"/>
       <c r="Z496" s="4" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="AA496" s="4"/>
       <c r="AB496" s="4" t="s">
@@ -44714,7 +44717,7 @@
         <v>107</v>
       </c>
       <c r="J497" s="4" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="K497" s="4"/>
       <c r="L497" s="4" t="s">
@@ -44723,11 +44726,11 @@
       <c r="M497" s="4"/>
       <c r="N497" s="4"/>
       <c r="O497" s="4" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="P497" s="5"/>
       <c r="Q497" s="4" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="R497" s="4" t="s">
         <v>69</v>
@@ -44739,7 +44742,7 @@
         <v>0</v>
       </c>
       <c r="U497" s="4" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="V497" s="4" t="s">
         <v>162</v>
@@ -44752,7 +44755,7 @@
       </c>
       <c r="Y497" s="4"/>
       <c r="Z497" s="4" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="AA497" s="4" t="s">
         <v>46</v>
@@ -44790,7 +44793,7 @@
         <v>107</v>
       </c>
       <c r="J498" s="4" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="K498" s="4"/>
       <c r="L498" s="4" t="s">
@@ -44799,11 +44802,11 @@
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
       <c r="O498" s="4" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="P498" s="5"/>
       <c r="Q498" s="4" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="R498" s="4" t="s">
         <v>69</v>
@@ -44815,7 +44818,7 @@
         <v>0</v>
       </c>
       <c r="U498" s="4" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="V498" s="4" t="s">
         <v>289</v>
@@ -44828,7 +44831,7 @@
       </c>
       <c r="Y498" s="4"/>
       <c r="Z498" s="4" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AA498" s="4" t="s">
         <v>46</v>
@@ -44866,18 +44869,18 @@
         <v>107</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K499" s="4"/>
       <c r="L499" s="4"/>
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
       <c r="O499" s="4" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="P499" s="5"/>
       <c r="Q499" s="4" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="R499" s="4" t="s">
         <v>69</v>
@@ -44889,7 +44892,7 @@
         <v>0</v>
       </c>
       <c r="U499" s="4" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="V499" s="4" t="s">
         <v>843</v>
@@ -44940,18 +44943,18 @@
         <v>107</v>
       </c>
       <c r="J500" s="4" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K500" s="4"/>
       <c r="L500" s="4"/>
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
       <c r="O500" s="4" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="P500" s="5"/>
       <c r="Q500" s="4" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="R500" s="4" t="s">
         <v>69</v>
@@ -44972,7 +44975,7 @@
       </c>
       <c r="Y500" s="4"/>
       <c r="Z500" s="4" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="AA500" s="4"/>
       <c r="AB500" s="4" t="s">
@@ -45008,18 +45011,18 @@
         <v>107</v>
       </c>
       <c r="J501" s="4" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K501" s="4"/>
       <c r="L501" s="4"/>
       <c r="M501" s="4"/>
       <c r="N501" s="4"/>
       <c r="O501" s="4" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="P501" s="5"/>
       <c r="Q501" s="4" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="R501" s="4" t="s">
         <v>69</v>
@@ -45031,7 +45034,7 @@
         <v>0</v>
       </c>
       <c r="U501" s="4" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="V501" s="4" t="s">
         <v>222</v>
@@ -45044,7 +45047,7 @@
       </c>
       <c r="Y501" s="4"/>
       <c r="Z501" s="4" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="AA501" s="4" t="s">
         <v>46</v>
@@ -45082,24 +45085,24 @@
         <v>107</v>
       </c>
       <c r="J502" s="4" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K502" s="4"/>
       <c r="L502" s="4" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="M502" s="4" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="N502" s="4">
         <v>48</v>
       </c>
       <c r="O502" s="4" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="P502" s="5"/>
       <c r="Q502" s="4" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="R502" s="4" t="s">
         <v>69</v>
@@ -45120,7 +45123,7 @@
       </c>
       <c r="Y502" s="4"/>
       <c r="Z502" s="4" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="AA502" s="4" t="s">
         <v>56</v>
@@ -45134,7 +45137,7 @@
         <v>1000</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C503" s="4">
         <v>170414897</v>
@@ -45158,18 +45161,18 @@
         <v>418</v>
       </c>
       <c r="J503" s="4" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="K503" s="4"/>
       <c r="L503" s="4"/>
       <c r="M503" s="4"/>
       <c r="N503" s="4"/>
       <c r="O503" s="4" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="P503" s="5"/>
       <c r="Q503" s="4" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="R503" s="4" t="s">
         <v>41</v>
@@ -45204,7 +45207,7 @@
         <v>1000</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C504" s="4">
         <v>170414898</v>
@@ -45228,18 +45231,18 @@
         <v>418</v>
       </c>
       <c r="J504" s="4" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="K504" s="4"/>
       <c r="L504" s="4"/>
       <c r="M504" s="4"/>
       <c r="N504" s="4"/>
       <c r="O504" s="4" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="P504" s="5"/>
       <c r="Q504" s="4" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="R504" s="4" t="s">
         <v>41</v>
@@ -45274,7 +45277,7 @@
         <v>1000</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C505" s="4">
         <v>170414901</v>
@@ -45298,7 +45301,7 @@
         <v>418</v>
       </c>
       <c r="J505" s="4" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="K505" s="4"/>
       <c r="L505" s="4" t="s">
@@ -45307,11 +45310,11 @@
       <c r="M505" s="4"/>
       <c r="N505" s="4"/>
       <c r="O505" s="4" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="P505" s="5"/>
       <c r="Q505" s="4" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="R505" s="4" t="s">
         <v>69</v>
@@ -45323,7 +45326,7 @@
         <v>0</v>
       </c>
       <c r="U505" s="4" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="V505" s="4" t="s">
         <v>162</v>
@@ -45350,7 +45353,7 @@
         <v>1000</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C506" s="4">
         <v>170415685</v>
@@ -45374,7 +45377,7 @@
         <v>418</v>
       </c>
       <c r="J506" s="4" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="K506" s="4"/>
       <c r="L506" s="4" t="s">
@@ -45383,11 +45386,11 @@
       <c r="M506" s="4"/>
       <c r="N506" s="4"/>
       <c r="O506" s="4" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="P506" s="5"/>
       <c r="Q506" s="4" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="R506" s="4" t="s">
         <v>41</v>
@@ -45399,7 +45402,7 @@
         <v>0</v>
       </c>
       <c r="U506" s="4" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="V506" s="4" t="s">
         <v>180</v>
@@ -45450,24 +45453,24 @@
         <v>107</v>
       </c>
       <c r="J507" s="4" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K507" s="4"/>
       <c r="L507" s="4" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="M507" s="4" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="N507" s="4">
         <v>15</v>
       </c>
       <c r="O507" s="4" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="P507" s="5"/>
       <c r="Q507" s="4" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="R507" s="4" t="s">
         <v>60</v>
@@ -45479,7 +45482,7 @@
         <v>0</v>
       </c>
       <c r="U507" s="4" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="V507" s="4" t="s">
         <v>197</v>
@@ -45492,7 +45495,7 @@
       </c>
       <c r="Y507" s="4"/>
       <c r="Z507" s="4" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AA507" s="4" t="s">
         <v>56</v>
@@ -45530,24 +45533,24 @@
         <v>107</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K508" s="4"/>
       <c r="L508" s="4" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="M508" s="4" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="N508" s="4">
         <v>40</v>
       </c>
       <c r="O508" s="4" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="P508" s="5"/>
       <c r="Q508" s="4" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="R508" s="4" t="s">
         <v>60</v>
@@ -45559,7 +45562,7 @@
         <v>0</v>
       </c>
       <c r="U508" s="4" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="V508" s="4" t="s">
         <v>168</v>
@@ -45572,7 +45575,7 @@
       </c>
       <c r="Y508" s="4"/>
       <c r="Z508" s="4" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="AA508" s="4" t="s">
         <v>46</v>
@@ -45610,24 +45613,24 @@
         <v>107</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K509" s="4"/>
       <c r="L509" s="4" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="M509" s="4" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="N509" s="4">
         <v>10</v>
       </c>
       <c r="O509" s="4" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="P509" s="5"/>
       <c r="Q509" s="4" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="R509" s="4" t="s">
         <v>60</v>
@@ -45648,7 +45651,7 @@
       </c>
       <c r="Y509" s="4"/>
       <c r="Z509" s="4" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="AA509" s="4" t="s">
         <v>46</v>
@@ -45686,24 +45689,24 @@
         <v>107</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K510" s="4"/>
       <c r="L510" s="4" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="M510" s="4" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="N510" s="4">
         <v>4</v>
       </c>
       <c r="O510" s="4" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="P510" s="5"/>
       <c r="Q510" s="4" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="R510" s="4" t="s">
         <v>60</v>
@@ -45724,7 +45727,7 @@
       </c>
       <c r="Y510" s="4"/>
       <c r="Z510" s="4" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA510" s="4" t="s">
         <v>46</v>
@@ -45762,7 +45765,7 @@
         <v>107</v>
       </c>
       <c r="J511" s="4" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="K511" s="4"/>
       <c r="L511" s="4" t="s">
@@ -45773,11 +45776,11 @@
       </c>
       <c r="N511" s="4"/>
       <c r="O511" s="4" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="P511" s="5"/>
       <c r="Q511" s="4" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="R511" s="4" t="s">
         <v>195</v>
@@ -45789,7 +45792,7 @@
         <v>0</v>
       </c>
       <c r="U511" s="4" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="V511" s="4" t="s">
         <v>719</v>
@@ -45802,7 +45805,7 @@
       </c>
       <c r="Y511" s="4"/>
       <c r="Z511" s="4" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="AA511" s="4" t="s">
         <v>190</v>
@@ -45840,7 +45843,7 @@
         <v>107</v>
       </c>
       <c r="J512" s="4" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="K512" s="4"/>
       <c r="L512" s="4" t="s">
@@ -45853,11 +45856,11 @@
         <v>50</v>
       </c>
       <c r="O512" s="4" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="P512" s="5"/>
       <c r="Q512" s="4" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="R512" s="4" t="s">
         <v>41</v>
@@ -45869,10 +45872,10 @@
         <v>0</v>
       </c>
       <c r="U512" s="4" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="V512" s="4" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="W512" s="4">
         <v>1</v>
@@ -45918,7 +45921,7 @@
         <v>107</v>
       </c>
       <c r="J513" s="4" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="K513" s="4"/>
       <c r="L513" s="4" t="s">
@@ -45931,11 +45934,11 @@
         <v>50</v>
       </c>
       <c r="O513" s="4" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="P513" s="5"/>
       <c r="Q513" s="4" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="R513" s="4" t="s">
         <v>41</v>
@@ -45947,7 +45950,7 @@
         <v>1</v>
       </c>
       <c r="U513" s="4" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="V513" s="4" t="s">
         <v>180</v>
@@ -45996,7 +45999,7 @@
         <v>107</v>
       </c>
       <c r="J514" s="4" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="K514" s="4"/>
       <c r="L514" s="4" t="s">
@@ -46009,11 +46012,11 @@
         <v>50</v>
       </c>
       <c r="O514" s="4" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="P514" s="5"/>
       <c r="Q514" s="4" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="R514" s="4" t="s">
         <v>41</v>
@@ -46025,10 +46028,10 @@
         <v>1</v>
       </c>
       <c r="U514" s="4" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="V514" s="4" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="W514" s="4">
         <v>1</v>
@@ -46050,7 +46053,7 @@
         <v>1000</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C515" s="4">
         <v>170414903</v>
@@ -46074,18 +46077,18 @@
         <v>418</v>
       </c>
       <c r="J515" s="4" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="K515" s="4"/>
       <c r="L515" s="4"/>
       <c r="M515" s="4"/>
       <c r="N515" s="4"/>
       <c r="O515" s="4" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="P515" s="5"/>
       <c r="Q515" s="4" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="R515" s="4" t="s">
         <v>69</v>
@@ -46142,18 +46145,18 @@
         <v>418</v>
       </c>
       <c r="J516" s="4" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="K516" s="4"/>
       <c r="L516" s="4"/>
       <c r="M516" s="4"/>
       <c r="N516" s="4"/>
       <c r="O516" s="4" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="P516" s="5"/>
       <c r="Q516" s="4" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="R516" s="4" t="s">
         <v>69</v>
@@ -46174,7 +46177,7 @@
       </c>
       <c r="Y516" s="4"/>
       <c r="Z516" s="4" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AA516" s="4" t="s">
         <v>46</v>
@@ -46212,7 +46215,7 @@
         <v>418</v>
       </c>
       <c r="J517" s="4" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="K517" s="4"/>
       <c r="L517" s="4" t="s">
@@ -46221,11 +46224,11 @@
       <c r="M517" s="4"/>
       <c r="N517" s="4"/>
       <c r="O517" s="4" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="P517" s="5"/>
       <c r="Q517" s="4" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="R517" s="4" t="s">
         <v>69</v>
@@ -46237,7 +46240,7 @@
         <v>0</v>
       </c>
       <c r="U517" s="4" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="V517" s="4" t="s">
         <v>180</v>
@@ -46250,7 +46253,7 @@
       </c>
       <c r="Y517" s="4"/>
       <c r="Z517" s="4" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="AA517" s="4"/>
       <c r="AB517" s="4" t="s">
@@ -46262,7 +46265,7 @@
         <v>1000</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C518" s="4">
         <v>170414904</v>
@@ -46286,7 +46289,7 @@
         <v>418</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="K518" s="4"/>
       <c r="L518" s="4" t="s">
@@ -46295,11 +46298,11 @@
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
       <c r="O518" s="4" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="P518" s="5"/>
       <c r="Q518" s="4" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="R518" s="4" t="s">
         <v>69</v>
@@ -46311,7 +46314,7 @@
         <v>0</v>
       </c>
       <c r="U518" s="4" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="V518" s="4" t="s">
         <v>283</v>
@@ -46324,7 +46327,7 @@
       </c>
       <c r="Y518" s="4"/>
       <c r="Z518" s="4" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AA518" s="4" t="s">
         <v>46</v>
@@ -46362,7 +46365,7 @@
         <v>107</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="K519" s="4"/>
       <c r="L519" s="4" t="s">
@@ -46373,11 +46376,11 @@
       </c>
       <c r="N519" s="4"/>
       <c r="O519" s="4" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="P519" s="5"/>
       <c r="Q519" s="4" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="R519" s="4" t="s">
         <v>361</v>
@@ -46398,7 +46401,7 @@
       </c>
       <c r="Y519" s="4"/>
       <c r="Z519" s="4" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="AA519" s="4" t="s">
         <v>714</v>
@@ -46436,18 +46439,18 @@
         <v>107</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="K520" s="4"/>
       <c r="L520" s="4"/>
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
       <c r="O520" s="4" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="P520" s="5"/>
       <c r="Q520" s="4" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="R520" s="4" t="s">
         <v>41</v>
@@ -46468,10 +46471,10 @@
       </c>
       <c r="Y520" s="4"/>
       <c r="Z520" s="4" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AA520" s="4" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AB520" s="4" t="s">
         <v>47</v>
@@ -46506,22 +46509,22 @@
         <v>107</v>
       </c>
       <c r="J521" s="4" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="K521" s="4"/>
       <c r="L521" s="4" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="M521" s="4"/>
       <c r="N521" s="4">
         <v>29</v>
       </c>
       <c r="O521" s="4" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="P521" s="5"/>
       <c r="Q521" s="4" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="R521" s="4" t="s">
         <v>41</v>
@@ -46578,7 +46581,7 @@
         <v>107</v>
       </c>
       <c r="J522" s="4" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="K522" s="4"/>
       <c r="L522" s="4" t="s">
@@ -46591,11 +46594,11 @@
         <v>81</v>
       </c>
       <c r="O522" s="4" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="P522" s="5"/>
       <c r="Q522" s="4" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="R522" s="4" t="s">
         <v>41</v>
@@ -46652,7 +46655,7 @@
         <v>107</v>
       </c>
       <c r="J523" s="4" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="K523" s="4"/>
       <c r="L523" s="4" t="s">
@@ -46665,11 +46668,11 @@
         <v>81</v>
       </c>
       <c r="O523" s="4" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="P523" s="5"/>
       <c r="Q523" s="4" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="R523" s="4" t="s">
         <v>41</v>
@@ -46726,11 +46729,11 @@
         <v>107</v>
       </c>
       <c r="J524" s="4" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="K524" s="4"/>
       <c r="L524" s="4" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="M524" s="4" t="s">
         <v>358</v>
@@ -46739,11 +46742,11 @@
         <v>31</v>
       </c>
       <c r="O524" s="4" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="P524" s="5"/>
       <c r="Q524" s="4" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="R524" s="4" t="s">
         <v>69</v>
@@ -46802,11 +46805,11 @@
         <v>107</v>
       </c>
       <c r="J525" s="4" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="K525" s="4"/>
       <c r="L525" s="4" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="M525" s="4" t="s">
         <v>358</v>
@@ -46815,11 +46818,11 @@
         <v>40</v>
       </c>
       <c r="O525" s="4" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="P525" s="5"/>
       <c r="Q525" s="4" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="R525" s="4" t="s">
         <v>69</v>
@@ -46854,7 +46857,7 @@
         <v>1000</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C526" s="4">
         <v>170414905</v>
@@ -46878,11 +46881,11 @@
         <v>107</v>
       </c>
       <c r="J526" s="4" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="K526" s="4"/>
       <c r="L526" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="M526" s="4" t="s">
         <v>817</v>
@@ -46891,11 +46894,11 @@
         <v>105</v>
       </c>
       <c r="O526" s="4" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="P526" s="5"/>
       <c r="Q526" s="4" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="R526" s="4" t="s">
         <v>69</v>
@@ -46916,7 +46919,7 @@
       </c>
       <c r="Y526" s="4"/>
       <c r="Z526" s="4" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA526" s="4" t="s">
         <v>46</v>
@@ -46954,7 +46957,7 @@
         <v>107</v>
       </c>
       <c r="J527" s="4" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="K527" s="4"/>
       <c r="L527" s="4" t="s">
@@ -46963,11 +46966,11 @@
       <c r="M527" s="4"/>
       <c r="N527" s="4"/>
       <c r="O527" s="4" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="P527" s="5"/>
       <c r="Q527" s="4" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="R527" s="4" t="s">
         <v>60</v>
@@ -46979,7 +46982,7 @@
         <v>0</v>
       </c>
       <c r="U527" s="4" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="V527" s="4" t="s">
         <v>289</v>
@@ -46992,7 +46995,7 @@
       </c>
       <c r="Y527" s="4"/>
       <c r="Z527" s="4" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AA527" s="4" t="s">
         <v>56</v>
@@ -47030,7 +47033,7 @@
         <v>107</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="K528" s="4"/>
       <c r="L528" s="4" t="s">
@@ -47039,11 +47042,11 @@
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
       <c r="O528" s="4" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="P528" s="5"/>
       <c r="Q528" s="4" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="R528" s="4" t="s">
         <v>60</v>
@@ -47055,7 +47058,7 @@
         <v>0</v>
       </c>
       <c r="U528" s="4" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="V528" s="4" t="s">
         <v>289</v>
@@ -47068,7 +47071,7 @@
       </c>
       <c r="Y528" s="4"/>
       <c r="Z528" s="4" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="AA528" s="4" t="s">
         <v>56</v>
@@ -47106,7 +47109,7 @@
         <v>418</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="K529" s="4"/>
       <c r="L529" s="4" t="s">
@@ -47119,11 +47122,11 @@
         <v>2</v>
       </c>
       <c r="O529" s="4" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="P529" s="5"/>
       <c r="Q529" s="4" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="R529" s="4" t="s">
         <v>41</v>
@@ -47135,7 +47138,7 @@
         <v>0</v>
       </c>
       <c r="U529" s="4" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="V529" s="4" t="s">
         <v>762</v>
@@ -47186,7 +47189,7 @@
         <v>107</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="K530" s="4"/>
       <c r="L530" s="4" t="s">
@@ -47195,11 +47198,11 @@
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
       <c r="O530" s="4" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="P530" s="5"/>
       <c r="Q530" s="4" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="R530" s="4" t="s">
         <v>60</v>
@@ -47211,10 +47214,10 @@
         <v>0</v>
       </c>
       <c r="U530" s="4" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="V530" s="4" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="W530" s="4">
         <v>14</v>
@@ -47224,7 +47227,7 @@
       </c>
       <c r="Y530" s="4"/>
       <c r="Z530" s="4" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA530" s="4" t="s">
         <v>46</v>
@@ -47262,7 +47265,7 @@
         <v>107</v>
       </c>
       <c r="J531" s="4" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="K531" s="4"/>
       <c r="L531" s="4" t="s">
@@ -47271,11 +47274,11 @@
       <c r="M531" s="4"/>
       <c r="N531" s="4"/>
       <c r="O531" s="4" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="P531" s="5"/>
       <c r="Q531" s="4" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="R531" s="4" t="s">
         <v>41</v>
@@ -47287,7 +47290,7 @@
         <v>0</v>
       </c>
       <c r="U531" s="4" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="V531" s="4" t="s">
         <v>180</v>
@@ -47300,7 +47303,7 @@
       </c>
       <c r="Y531" s="4"/>
       <c r="Z531" s="4" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AA531" s="4" t="s">
         <v>46</v>
@@ -47338,7 +47341,7 @@
         <v>107</v>
       </c>
       <c r="J532" s="4" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="K532" s="4"/>
       <c r="L532" s="4" t="s">
@@ -47347,11 +47350,11 @@
       <c r="M532" s="4"/>
       <c r="N532" s="4"/>
       <c r="O532" s="4" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="P532" s="5"/>
       <c r="Q532" s="4" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="R532" s="4" t="s">
         <v>41</v>
@@ -47363,7 +47366,7 @@
         <v>0</v>
       </c>
       <c r="U532" s="4" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="V532" s="4" t="s">
         <v>43</v>
@@ -47376,7 +47379,7 @@
       </c>
       <c r="Y532" s="4"/>
       <c r="Z532" s="4" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA532" s="4" t="s">
         <v>46</v>
@@ -47414,7 +47417,7 @@
         <v>107</v>
       </c>
       <c r="J533" s="4" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="K533" s="4"/>
       <c r="L533" s="4" t="s">
@@ -47423,11 +47426,11 @@
       <c r="M533" s="4"/>
       <c r="N533" s="4"/>
       <c r="O533" s="4" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="P533" s="5"/>
       <c r="Q533" s="4" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="R533" s="4" t="s">
         <v>69</v>
@@ -47439,7 +47442,7 @@
         <v>0</v>
       </c>
       <c r="U533" s="4" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="V533" s="4" t="s">
         <v>188</v>
@@ -47452,7 +47455,7 @@
       </c>
       <c r="Y533" s="4"/>
       <c r="Z533" s="4" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="AA533" s="4" t="s">
         <v>46</v>
@@ -47490,11 +47493,11 @@
         <v>418</v>
       </c>
       <c r="J534" s="4" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="K534" s="4"/>
       <c r="L534" s="4" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="M534" s="4" t="s">
         <v>478</v>
@@ -47503,11 +47506,11 @@
         <v>20</v>
       </c>
       <c r="O534" s="4" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="P534" s="5"/>
       <c r="Q534" s="4" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="R534" s="4" t="s">
         <v>41</v>
@@ -47519,7 +47522,7 @@
         <v>0</v>
       </c>
       <c r="U534" s="4" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="V534" s="4" t="s">
         <v>197</v>
@@ -47532,7 +47535,7 @@
       </c>
       <c r="Y534" s="4"/>
       <c r="Z534" s="4" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AA534" s="4" t="s">
         <v>46</v>
@@ -47552,7 +47555,7 @@
         <v>170357344</v>
       </c>
       <c r="D535" s="4" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="E535" s="4">
         <v>1072186</v>
@@ -47570,7 +47573,7 @@
         <v>107</v>
       </c>
       <c r="J535" s="4" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="K535" s="4"/>
       <c r="L535" s="4" t="s">
@@ -47579,11 +47582,11 @@
       <c r="M535" s="4"/>
       <c r="N535" s="4"/>
       <c r="O535" s="4" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="P535" s="5"/>
       <c r="Q535" s="4" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="R535" s="4" t="s">
         <v>41</v>
@@ -47595,7 +47598,7 @@
         <v>2</v>
       </c>
       <c r="U535" s="4" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="V535" s="4" t="s">
         <v>289</v>
@@ -47608,7 +47611,7 @@
       </c>
       <c r="Y535" s="4"/>
       <c r="Z535" s="4" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="AA535" s="4" t="s">
         <v>46</v>
@@ -47640,17 +47643,17 @@
         <v>36</v>
       </c>
       <c r="H536" s="4" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="I536" s="4" t="s">
         <v>903</v>
       </c>
       <c r="J536" s="4" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="K536" s="4"/>
       <c r="L536" s="4" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="M536" s="4" t="s">
         <v>478</v>
@@ -47659,11 +47662,11 @@
         <v>8</v>
       </c>
       <c r="O536" s="4" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="P536" s="5"/>
       <c r="Q536" s="4" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="R536" s="4" t="s">
         <v>384</v>
@@ -47675,7 +47678,7 @@
         <v>0</v>
       </c>
       <c r="U536" s="4" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="V536" s="4" t="s">
         <v>482</v>
@@ -47688,7 +47691,7 @@
       </c>
       <c r="Y536" s="4"/>
       <c r="Z536" s="4" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="AA536" s="4" t="s">
         <v>56</v>
